--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Snapshots" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="HoldingsSnapshots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshots" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HoldingsSnapshots" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,16 +22,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="#,##0.####"/>
   </numFmts>
-  <fonts count="3">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -51,7 +48,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -59,19 +56,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -490,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44051.3</v>
+        <v>44183.28</v>
       </c>
     </row>
     <row r="5">
@@ -500,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43994.36</v>
+        <v>44126.32</v>
       </c>
     </row>
     <row r="6">
@@ -520,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6116.37</v>
+        <v>6248.33</v>
       </c>
     </row>
     <row r="8">
@@ -530,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1614755693213922</v>
+        <v>0.1649593867045215</v>
       </c>
     </row>
     <row r="9">
@@ -550,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>56.94</v>
+        <v>56.96</v>
       </c>
     </row>
     <row r="11">
@@ -581,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-08 22:15:28</t>
+          <t>2026-08-10 10:16:50</t>
         </is>
       </c>
     </row>
@@ -610,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -721,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>111.06</v>
+        <v>111.121</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7107.84</v>
+        <v>7111.74</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1616376987258351</v>
+        <v>0.161237511401192</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1062.07</v>
+        <v>1065.97</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1756715852571302</v>
+        <v>0.1763166643785655</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -778,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.772</v>
+        <v>14.973</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4283.88</v>
+        <v>4342.17</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09741869609018076</v>
+        <v>0.09844576501403511</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>853.17</v>
+        <v>911.46</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2486861320251493</v>
+        <v>0.2656767841059139</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -835,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1529.2</v>
+        <v>1527.6</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2697.4</v>
+        <v>2694.58</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06134093177998767</v>
+        <v>0.06109157160855487</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1501.44</v>
+        <v>1498.62</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.255426602896418</v>
+        <v>1.253068664503829</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -898,19 +889,19 @@
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2089.78</v>
+        <v>2090.46</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04752318989218605</v>
+        <v>0.04739495089580552</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>163.97</v>
+        <v>164.65</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.08514339420815138</v>
+        <v>0.08549649238502241</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-9.68</v>
+        <v>-9.06</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -949,25 +940,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>223.76</v>
+        <v>225.05</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1809.66</v>
+        <v>1820.69</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04115304760323737</v>
+        <v>0.04127872006471501</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>556.98</v>
+        <v>568.01</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4446307117539994</v>
+        <v>0.4534358335728199</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-38.79</v>
+        <v>-38.39</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -1006,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>483.17</v>
+        <v>488</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1788.22</v>
+        <v>1806.68</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04066548566308651</v>
+        <v>0.04096108506473882</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-110.33</v>
+        <v>-91.87</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.05811277027204972</v>
+        <v>-0.04838956045403071</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-11.14</v>
+        <v>-10.53</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1063,25 +1054,25 @@
         <v>79.71079663</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>121.69</v>
+        <v>122.08</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1693.97</v>
+        <v>1699.95</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.03852216883196623</v>
+        <v>0.0385413003718438</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>573.97</v>
+        <v>579.95</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.5124732142857144</v>
+        <v>0.5178125</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-10.4</v>
+        <v>-10.04</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>1.15856288</v>
@@ -1120,22 +1111,22 @@
         <v>3299</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3277.5</v>
+        <v>3261.9</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1649.5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1638.75</v>
+        <v>1630.95</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03726642394693216</v>
+        <v>0.03697693099294605</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-10.75</v>
+        <v>-18.55</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.006517126401939982</v>
+        <v>-0.01124583207032434</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
@@ -1177,25 +1168,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>218.71</v>
+        <v>224.15</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1554.14</v>
+        <v>1593.32</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03534232806278269</v>
+        <v>0.03612378288094718</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-441.92</v>
+        <v>-402.74</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2213961504163202</v>
+        <v>-0.2017674819394207</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-16.68</v>
+        <v>-16.04</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1234,25 +1225,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>161.68</v>
+        <v>161.63</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1505.79</v>
+        <v>1505.82</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03424281221360852</v>
+        <v>0.03413998113234497</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-366.05</v>
+        <v>-366.02</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.1955562441234294</v>
+        <v>-0.1955402171125737</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-88.09</v>
+        <v>-87.5</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1291,25 +1282,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>118.94</v>
+        <v>118.99</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1400.01</v>
+        <v>1401.06</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03183729439508436</v>
+        <v>0.03176486031881848</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>56.22</v>
+        <v>57.27</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.04183689415756926</v>
+        <v>0.04261826624695823</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-13.23</v>
+        <v>-12.79</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1348,25 +1339,25 @@
         <v>37.05</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>43.46</v>
+        <v>43.35</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1392.17</v>
+        <v>1390.47</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.03165900681995457</v>
+        <v>0.03152476362718765</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>163.83</v>
+        <v>162.13</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.1333751241512936</v>
+        <v>0.131991142517544</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-41.5</v>
+        <v>-39.94</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1405,25 +1396,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>433.5</v>
+        <v>437.5</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1195.53</v>
+        <v>1206.85</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02718726335394404</v>
+        <v>0.02736172731772092</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>281.04</v>
+        <v>292.36</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.3073188334481515</v>
+        <v>0.3196973176305919</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>-2.45</v>
+        <v>-2.23</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0</v>
@@ -1462,22 +1453,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>115.15</v>
+        <v>114.82</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1168.04</v>
+        <v>1164.69</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02656211980288307</v>
+        <v>0.02640587495519442</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>560.85</v>
+        <v>557.5</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.9236812200464434</v>
+        <v>0.9181640013834219</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1519,22 +1510,22 @@
         <v>470.9125</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>712.4</v>
+        <v>709.9</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1139.84</v>
+        <v>1135.84</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02592083031070703</v>
+        <v>0.02575178717865529</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>386.38</v>
+        <v>382.38</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.5128075810261991</v>
+        <v>0.5074987391500544</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>0</v>
@@ -1576,25 +1567,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>330.2</v>
+        <v>330</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1070.89</v>
+        <v>1070.59</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02435285476157448</v>
+        <v>0.02427243787469764</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>428.9</v>
+        <v>428.6</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.6680789420395956</v>
+        <v>0.6676116450412001</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-32.7</v>
+        <v>-32.5</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1633,25 +1624,25 @@
         <v>207.72976897</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>313.25</v>
+        <v>313.58</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>490.05</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>708.48</v>
+        <v>709.45</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.016111375156627</v>
+        <v>0.01608466457766675</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>218.43</v>
+        <v>219.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.4457300275482094</v>
+        <v>0.4477094174063871</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-20.22</v>
+        <v>-20.08</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.46065664</v>
@@ -1690,25 +1681,25 @@
         <v>57.84</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>47.24</v>
+        <v>46.67</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>699.34</v>
+        <v>691.13</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01590352459072313</v>
+        <v>0.0156693131715594</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-168.24</v>
+        <v>-176.45</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>-0.1939187164296088</v>
+        <v>-0.2033818206966504</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-11.32</v>
+        <v>-11.03</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0</v>
@@ -1747,25 +1738,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>499.45</v>
+        <v>498.68</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>689.49</v>
+        <v>688.65</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.0156795280837042</v>
+        <v>0.01561308656199902</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>155.11</v>
+        <v>154.27</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.29026161158726</v>
+        <v>0.2886896964706763</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-24.34</v>
+        <v>-24.17</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0.3650317</v>
@@ -1804,25 +1795,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>94.5</v>
+        <v>95.27</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>643.25</v>
+        <v>648.7</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01462799524263256</v>
+        <v>0.01470733936363721</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>94.06999999999999</v>
+        <v>99.52</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.1712917440547726</v>
+        <v>0.1812156305764959</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-23.67</v>
+        <v>-23.51</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1861,22 +1852,22 @@
         <v>1019.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>983.5</v>
+        <v>986.003</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>639.28</v>
+        <v>640.9</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01453771441696097</v>
+        <v>0.01453049760776181</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-23.4</v>
+        <v>-21.78</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.03531116074123257</v>
+        <v>-0.03286654192068571</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>0</v>
@@ -1918,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>341.63</v>
+        <v>340</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>589.21</v>
+        <v>586.59</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01339908445691649</v>
+        <v>0.0132991802024294</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>99.94</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.204263494593987</v>
+        <v>0.1989085780857195</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-31.15</v>
+        <v>-31</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1975,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.8325</v>
+        <v>3.8393</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>536.55</v>
+        <v>537.5</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.0122015559229452</v>
+        <v>0.01218621074141359</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-1.82</v>
+        <v>-0.87</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.003380574697698609</v>
+        <v>-0.001615989003844939</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2032,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>354.75</v>
+        <v>356.69</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>525.17</v>
+        <v>528.22</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01194276604986139</v>
+        <v>0.01197581439596184</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>117.25</v>
+        <v>120.3</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2874338105510885</v>
+        <v>0.2949107668170229</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-9.06</v>
+        <v>-8.92</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2089,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>237.1</v>
+        <v>236</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>194.85</v>
+        <v>194.01</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004431037501790835</v>
+        <v>0.004398598597100747</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-1.67</v>
+        <v>-2.51</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.008497862812945246</v>
+        <v>-0.01277223692245064</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.86</v>
+        <v>-1.79</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2121,17 +2112,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2140,55 +2131,55 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.7</v>
+        <v>0.63422137</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>225.62857143</v>
+        <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>245.78</v>
+        <v>270.96</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>118.76</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>127.35</v>
+        <v>127.24</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002896036057752439</v>
+        <v>0.002884787822767378</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>8.59</v>
+        <v>27.39</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.07233075109464465</v>
+        <v>0.2743114672008012</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-1.85</v>
+        <v>0.06</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0</v>
+        <v>0.63422137</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2197,55 +2188,55 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.7</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>212.76482689</v>
+        <v>225.62857143</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>270</v>
+        <v>242.26</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>118.76</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>126.75</v>
+        <v>125.57</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002882391600472098</v>
+        <v>0.002846925549394056</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>26.9</v>
+        <v>6.81</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2694041061592389</v>
+        <v>0.05734253957561468</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.03</v>
+        <v>-1.81</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2254,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>350.55601106</v>
+        <v>91.20399179</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>403</v>
+        <v>107.76</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>109.16</v>
+        <v>105.28</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>125.32</v>
+        <v>124.32</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002849872310620618</v>
+        <v>0.002818585524414024</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>16.16</v>
+        <v>19.04</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1480395749358739</v>
+        <v>0.1808510638297872</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.06</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2292,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2311,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.42010405</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>91.20399179</v>
+        <v>350.55601106</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>107.66</v>
+        <v>397.01</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>105.28</v>
+        <v>109.16</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>124.16</v>
+        <v>123.5</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002823493026545291</v>
+        <v>0.002799994468027124</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>18.88</v>
+        <v>14.34</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1793313069908815</v>
+        <v>0.1313668010260169</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.42010405</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2374,25 +2365,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>64.59</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>119.73</v>
+        <v>119.52</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002722751450292105</v>
+        <v>0.002709759828490703</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>12.92</v>
+        <v>12.71</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.120962456698811</v>
+        <v>0.1189963486564928</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>2.50421091</v>
@@ -2431,25 +2422,25 @@
         <v>322.35040597</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>366.69</v>
+        <v>367.55</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>118.3</v>
+        <v>118.61</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002690232160440625</v>
+        <v>0.00268912829030524</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>14.26</v>
+        <v>14.57</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1370626682045367</v>
+        <v>0.1400422914263745</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>0.43583007</v>
@@ -2488,25 +2479,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>58.94</v>
+        <v>58.78</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>118.11</v>
+        <v>117.83</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002685911415635183</v>
+        <v>0.0026714441147177</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>10.47</v>
+        <v>10.19</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.09726867335562989</v>
+        <v>0.09466740988480118</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.08</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>2.70722512</v>
@@ -2545,25 +2536,25 @@
         <v>509.16500577</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>563.05</v>
+        <v>562.08</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>116.85</v>
+        <v>116.69</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002657258055346467</v>
+        <v>0.002645598011935911</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>11.1</v>
+        <v>10.94</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1049645390070922</v>
+        <v>0.103451536643026</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>0.28038062</v>
@@ -2577,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2596,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.51881442</v>
+        <v>3.81488812</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>249.91595261</v>
+        <v>38.28159448</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>298.9</v>
+        <v>40.61</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>95.94</v>
+        <v>108.23</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>114.79</v>
+        <v>114.71</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002610412085350628</v>
+        <v>0.002600707412367541</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>18.85</v>
+        <v>6.48</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1964769647696477</v>
+        <v>0.0598724937632819</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.51881442</v>
+        <v>3.81488812</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2659,25 +2650,25 @@
         <v>228.00445932</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>260</v>
+        <v>259.71</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>113.9</v>
+        <v>113.81</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002590172807051456</v>
+        <v>0.002580302594381919</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>14.05</v>
+        <v>13.96</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1407110665998999</v>
+        <v>0.1398097145718578</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>0.59183053</v>
@@ -2691,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2710,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.51881442</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>38.28159448</v>
+        <v>249.91595261</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>39.85</v>
+        <v>295.48</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>108.23</v>
+        <v>95.94</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>112.53</v>
+        <v>113.51</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.00255901796292801</v>
+        <v>0.002573500988386711</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>4.3</v>
+        <v>17.57</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.03973020419477039</v>
+        <v>0.1831352928913905</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.51881442</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2773,25 +2764,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>114.43</v>
+        <v>115.34</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>112.28</v>
+        <v>113.21</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002553332772394534</v>
+        <v>0.002566699382391503</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-7.45</v>
+        <v>-6.52</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.06222333583897102</v>
+        <v>-0.05445585901611959</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.31</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>1.32559468</v>
@@ -2805,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2824,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>221.99877812</v>
+        <v>12.56856884</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>273</v>
+        <v>13.33</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.16</v>
+        <v>112.53</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002550603880938466</v>
+        <v>0.002551282408802366</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>20.98</v>
+        <v>6.38</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.2300943189295898</v>
+        <v>0.06010362694300517</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2862,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2881,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>3.30858696</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>79.10567143</v>
+        <v>45.93199509</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>87.16</v>
+        <v>45.9</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>101.53</v>
+        <v>112.71</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>111.87</v>
+        <v>112.45</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002544009059919634</v>
+        <v>0.002549468647203644</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>10.34</v>
+        <v>-0.26</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1018418201516793</v>
+        <v>-0.002306805074971165</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0</v>
+        <v>-0.18</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>3.30858696</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2919,17 +2910,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2938,34 +2929,34 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.5550481</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>45.93199509</v>
+        <v>221.99877812</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>45.6</v>
+        <v>272.85</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>112.71</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.68</v>
+        <v>112.14</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002539688315114193</v>
+        <v>0.002542440321008596</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-1.03</v>
+        <v>20.96</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.009138497027770386</v>
+        <v>0.2298749725817065</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.22</v>
+        <v>0.06</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.5550481</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2976,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2995,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.73400968</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>341.38450299</v>
+        <v>79.10567143</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>394.99</v>
+        <v>87</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>101.53</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>110.55</v>
+        <v>111.7</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002513991253902883</v>
+        <v>0.002532464632215625</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>15.04</v>
+        <v>10.17</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.157470421945346</v>
+        <v>0.1001674381956072</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.73400968</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3033,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3052,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.35094641</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>324.07677699</v>
+        <v>96.717382</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>352</v>
+        <v>110.34</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>101.39</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.1</v>
+        <v>110.37</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002503757910942627</v>
+        <v>0.002502310845636872</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>13.69</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.0859059078804616</v>
+        <v>0.1416011584609019</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.35094641</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3090,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3109,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>96.717382</v>
+        <v>341.38450299</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>109.64</v>
+        <v>392.55</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>109.64</v>
+        <v>109.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002493297160361032</v>
+        <v>0.00249165499624438</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>12.96</v>
+        <v>14.39</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1340504757964419</v>
+        <v>0.150664851847974</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3147,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3166,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.7905852</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>12.56856884</v>
+        <v>188.32884805</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>12.95</v>
+        <v>187.68</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>106.15</v>
+        <v>110.41</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>109.28</v>
+        <v>109.86</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002485110485992828</v>
+        <v>0.002490748115445019</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>3.13</v>
+        <v>-0.55</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.02948657560056523</v>
+        <v>-0.004981432841228151</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.17</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.7905852</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3204,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3223,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.42255419</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>188.32884805</v>
+        <v>324.07677699</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>186.65</v>
+        <v>350.1</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>110.41</v>
+        <v>101.39</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>109.23</v>
+        <v>109.54</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002483973447886132</v>
+        <v>0.002483493069050131</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>-1.18</v>
+        <v>8.15</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.01068743773208948</v>
+        <v>0.08038268073774535</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.01</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.42255419</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3261,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3280,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.74206342</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>113.12478542</v>
+        <v>74.99726962</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>124.61</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>98.72</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>108.79</v>
+        <v>108.73</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002473967512547216</v>
+        <v>0.00246512873286307</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>10.07</v>
+        <v>12.05</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1020056726094003</v>
+        <v>0.1246379809681423</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.74206342</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3318,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3337,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.61215748</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>74.99726962</v>
+        <v>194.45976548</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>84.29000000000001</v>
+        <v>239.2</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>108.69</v>
+        <v>108.42</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002471693436333825</v>
+        <v>0.002458100406668022</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>12.01</v>
+        <v>20.33</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1242242449317335</v>
+        <v>0.2307866954251334</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.61215748</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3375,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3394,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.80409618</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>306.99401668</v>
+        <v>148.63893521</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>358.2</v>
+        <v>181.55</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>92.83</v>
+        <v>88.44</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>108.36</v>
+        <v>108.09</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002464188984829638</v>
+        <v>0.002450618640073294</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>15.53</v>
+        <v>19.65</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.167295055477755</v>
+        <v>0.2221845318860244</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.80409618</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3432,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3451,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.40867246</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>148.63893521</v>
+        <v>306.99401668</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>181.55</v>
+        <v>357.17</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>88.44</v>
+        <v>92.83</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>108.06</v>
+        <v>108.08</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002457366756189467</v>
+        <v>0.002450391919873454</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>19.62</v>
+        <v>15.25</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.2218453188602443</v>
+        <v>0.1642787891845309</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.03</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.40867246</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3489,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3508,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.17949395</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>113.12478542</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1133.43</v>
+        <v>123.71</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>98.89</v>
+        <v>98.72</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>107.86</v>
+        <v>108.04</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002452818603762686</v>
+        <v>0.002449485039074093</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>8.970000000000001</v>
+        <v>9.32</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.0907068459904945</v>
+        <v>0.09440842787682334</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.17949395</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3546,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3565,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.62445608</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>176.50746647</v>
+        <v>235.02053179</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>212.09</v>
+        <v>232.99</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>108.77</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>107.53</v>
+        <v>107.73</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002445314152258499</v>
+        <v>0.002442456712879045</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>18.07</v>
+        <v>-1.04</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.2019897160742231</v>
+        <v>-0.009561459961386413</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.1</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.62445608</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3603,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3622,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.68495686</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>194.45976548</v>
+        <v>176.50746647</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>236.4</v>
+        <v>212</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>88.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>107.12</v>
+        <v>107.52</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002435990439783599</v>
+        <v>0.002437695588682399</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>19.03</v>
+        <v>18.06</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.216029061187422</v>
+        <v>0.2018779342723005</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.68495686</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3660,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3679,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>13.30225117</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>257.81779936</v>
+        <v>10.85229847</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>285.32</v>
+        <v>10.87</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.96</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>107.02</v>
+        <v>107.06</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002433716363570208</v>
+        <v>0.002427266459489748</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>10.34</v>
+        <v>0.1</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.1069507654116673</v>
+        <v>0.0009349289454001497</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>13.30225117</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3717,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3736,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.50675322</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>10.85229847</v>
+        <v>257.81779936</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>10.86</v>
+        <v>285.31</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>106.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>106.93</v>
+        <v>107.05</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002431669694978158</v>
+        <v>0.002427039739289908</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>-0.03</v>
+        <v>10.37</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>-0.0002804786836200449</v>
+        <v>0.1072610674389739</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.50675322</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3774,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3793,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.1285649</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>235.02053179</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>230.1</v>
+        <v>1111.21</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>108.77</v>
+        <v>98.89</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>106.36</v>
+        <v>105.78</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002418707460561833</v>
+        <v>0.002398246273910195</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>-2.41</v>
+        <v>6.89</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.02215684471821274</v>
+        <v>0.06967337445646678</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.14</v>
+        <v>0.06</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.1285649</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3831,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3850,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.90543241</v>
+        <v>2.27580753</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>137.713206</v>
+        <v>62.95787236</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>158.26</v>
+        <v>62.64</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>92.27</v>
+        <v>106.15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>106.07</v>
+        <v>105.56</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002412112639543002</v>
+        <v>0.00239325842951371</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>13.8</v>
+        <v>-0.59</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.1495610707705647</v>
+        <v>-0.005558172397550635</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.90543241</v>
+        <v>2.27580753</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3888,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3907,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.90543241</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>62.95787236</v>
+        <v>137.713206</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>62.67</v>
+        <v>157.09</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>106.15</v>
+        <v>92.27</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>105.57</v>
+        <v>105.32</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.00240074225847605</v>
+        <v>0.002387817144717544</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-0.58</v>
+        <v>13.05</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.005463966085727743</v>
+        <v>0.141432751706947</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.06</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.90543241</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3976,19 +3967,19 @@
         <v>89.66</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>104.58</v>
+        <v>104.61</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002378228903963487</v>
+        <v>0.002371720010528886</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>14.92</v>
+        <v>14.95</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.1664064242694624</v>
+        <v>0.1667410216372965</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>1.59010207</v>
@@ -4033,19 +4024,19 @@
         <v>104.98</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>104.07</v>
+        <v>104.11</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002366631115275197</v>
+        <v>0.002360384000536873</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>-0.91</v>
+        <v>-0.87</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>-0.008668317774814251</v>
+        <v>-0.008287292817679558</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.03</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>1.85908491</v>
@@ -4059,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4078,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.76637723</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>104.90344487</v>
+        <v>54.82621761</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>121.31</v>
+        <v>50.77</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>89.53</v>
+        <v>112.48</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>103.56</v>
+        <v>103.99</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002355033326586907</v>
+        <v>0.00235766335813879</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>14.03</v>
+        <v>-8.49</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.1567072489668268</v>
+        <v>-0.07548008534850641</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.02</v>
+        <v>-0.18</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.76637723</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4116,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4135,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.1533463</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>54.82621761</v>
+        <v>104.90344487</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>50.54</v>
+        <v>121.51</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>112.48</v>
+        <v>89.53</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>103.49</v>
+        <v>103.77</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002353441473237534</v>
+        <v>0.002352675513742305</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-8.99</v>
+        <v>14.24</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.07992532005689901</v>
+        <v>0.1590528314531442</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.21</v>
+        <v>0.06</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.1533463</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4198,25 +4189,25 @@
         <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>125</v>
+        <v>125.21</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>103.44</v>
+        <v>103.65</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002352304435130839</v>
+        <v>0.002349954871344222</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-1.92</v>
+        <v>-1.71</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.01822323462414579</v>
+        <v>-0.01623006833712984</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>1.11796351</v>
@@ -4255,25 +4246,25 @@
         <v>627.34014747</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>591.8</v>
+        <v>594.27</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>119.82</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>103.07</v>
+        <v>103.54</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002343890353141295</v>
+        <v>0.002347460949145979</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-16.75</v>
+        <v>-16.28</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.1397930228676348</v>
+        <v>-0.1358704723752295</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-10.56</v>
+        <v>-10.52</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>0</v>
@@ -4287,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4306,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.16558147</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>234.11448729</v>
+        <v>107.56862839</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>222.82</v>
+        <v>119.15</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>107.82</v>
+        <v>92.77</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>102.5</v>
+        <v>102.83</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002330928118724971</v>
+        <v>0.002331363814957321</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-5.32</v>
+        <v>10.06</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.04934149508439993</v>
+        <v>0.1084402285221516</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.12</v>
+        <v>0.06</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.16558147</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4344,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4363,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.6214908</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>107.56862839</v>
+        <v>234.11448729</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>117.66</v>
+        <v>222.23</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>92.77</v>
+        <v>107.82</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>101.51</v>
+        <v>102.27</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002308414764212408</v>
+        <v>0.002318667483766267</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>8.74</v>
+        <v>-5.55</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.09421149078365852</v>
+        <v>-0.05147468002225932</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.6214908</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4426,25 +4417,25 @@
         <v>154.44822659</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>139.1</v>
+        <v>138.8</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>100.19</v>
+        <v>100.01</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002278396958195657</v>
+        <v>0.00226742871860237</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-11.25</v>
+        <v>-11.43</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.1009511844938981</v>
+        <v>-0.1025664034458004</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.16</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>0.97307689</v>
@@ -4458,17 +4449,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4477,34 +4468,34 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.10445851</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>147.21071381</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>145.87</v>
+        <v>1277.55</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>98.94</v>
+        <v>98.81</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002249971005528279</v>
+        <v>0.002240222294621539</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-0.91</v>
+        <v>9.92</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.009113670505758639</v>
+        <v>0.1115986050174373</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.10445851</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4515,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4534,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>147.21071381</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1277.55</v>
+        <v>145.19</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>88.89</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>98.78</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002246332483586855</v>
+        <v>0.002233420688626332</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>-1.34</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.1112611092361346</v>
+        <v>-0.01342013019529294</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>0.03</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4597,25 +4588,25 @@
         <v>105.04894536</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>23.25</v>
+        <v>23.29</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>97.95</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002227457651015716</v>
+        <v>0.002225258761432083</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-355.01</v>
+        <v>-354.81</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.783755740021194</v>
+        <v>-0.7833141999293536</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-10.41</v>
+        <v>-10.27</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>0</v>
@@ -4654,25 +4645,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>111.78</v>
+        <v>111.73</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>97.06</v>
+        <v>97.05</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002207218372716543</v>
+        <v>0.002200319539449655</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-13.39</v>
+        <v>-13.4</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1212313263920326</v>
+        <v>-0.1213218650973291</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.14</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.17308322</v>
@@ -4717,19 +4708,19 @@
         <v>110.53</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>94.18000000000001</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.002141724977770905</v>
+        <v>0.002135931002695023</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-16.35</v>
+        <v>-16.32</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.1479236406405501</v>
+        <v>-0.147652221116439</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>1.84694851</v>
@@ -4768,25 +4759,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>135.16</v>
+        <v>134.81</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>93.5</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.002126261259519851</v>
+        <v>0.00211507274430972</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>5.12</v>
+        <v>4.91</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.0579316587463227</v>
+        <v>0.05555555555555556</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.93456659</v>
@@ -4825,25 +4816,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>114.02</v>
+        <v>114.96</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>53.36</v>
+        <v>53.82</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001213447067465019</v>
+        <v>0.001220208115540241</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>5.49</v>
+        <v>5.95</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.1146856068518906</v>
+        <v>0.1242949655316482</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.63221571</v>
@@ -4882,25 +4873,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>274.53</v>
+        <v>274.19</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>49.25</v>
+        <v>49.21</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.001119982535094681</v>
+        <v>0.001115690103413885</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>-2.86</v>
+        <v>-2.9</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>-0.05488389944348494</v>
+        <v>-0.0556515064287085</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>0.24236298</v>
@@ -4931,7 +4922,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -4992,34 +4983,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-08 22:15:28</t>
+          <t>2026-08-10 10:16:50</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44051.3</v>
+        <v>44183.28</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43994.36</v>
+        <v>44126.32</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37877.99</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6116.37</v>
+        <v>6248.33</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1614755693213922</v>
+        <v>0.1649593867045215</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1251.59</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>77.40000000000001</v>
+        <v>77.42</v>
       </c>
       <c r="J2" t="n">
         <v>74</v>
@@ -5088,7 +5079,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5100,22 +5091,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>111.06</v>
+        <v>111.121</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7107.84</v>
+        <v>7111.74</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1062.07</v>
+        <v>1065.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5127,22 +5118,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.772</v>
+        <v>14.973</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4283.88</v>
+        <v>4342.17</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>853.17</v>
+        <v>911.46</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5154,22 +5145,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1529.2</v>
+        <v>1527.6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2697.4</v>
+        <v>2694.58</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1501.44</v>
+        <v>1498.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5184,19 +5175,19 @@
         <v>24.55</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2089.78</v>
+        <v>2090.46</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>163.97</v>
+        <v>164.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5208,22 +5199,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D6" t="n">
-        <v>223.76</v>
+        <v>225.05</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1809.66</v>
+        <v>1820.69</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>556.98</v>
+        <v>568.01</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5235,22 +5226,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>483.17</v>
+        <v>488</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1788.22</v>
+        <v>1806.68</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-110.33</v>
+        <v>-91.87</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5262,22 +5253,22 @@
         <v>18.80610988</v>
       </c>
       <c r="D8" t="n">
-        <v>121.69</v>
+        <v>122.08</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1693.97</v>
+        <v>1699.95</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>573.97</v>
+        <v>579.95</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5289,22 +5280,22 @@
         <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>3277.5</v>
+        <v>3261.9</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1638.75</v>
+        <v>1630.95</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1649.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-10.75</v>
+        <v>-18.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5316,22 +5307,22 @@
         <v>9.6</v>
       </c>
       <c r="D10" t="n">
-        <v>218.71</v>
+        <v>224.15</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1554.14</v>
+        <v>1593.32</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-441.92</v>
+        <v>-402.74</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5343,22 +5334,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D11" t="n">
-        <v>161.68</v>
+        <v>161.63</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1505.79</v>
+        <v>1505.82</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-366.05</v>
+        <v>-366.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5370,22 +5361,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D12" t="n">
-        <v>118.94</v>
+        <v>118.99</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1400.01</v>
+        <v>1401.06</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>56.22</v>
+        <v>57.27</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5397,22 +5388,22 @@
         <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>43.46</v>
+        <v>43.35</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1392.17</v>
+        <v>1390.47</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>163.83</v>
+        <v>162.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5424,22 +5415,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D14" t="n">
-        <v>433.5</v>
+        <v>437.5</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1195.53</v>
+        <v>1206.85</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>281.04</v>
+        <v>292.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5451,22 +5442,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D15" t="n">
-        <v>115.15</v>
+        <v>114.82</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1168.04</v>
+        <v>1164.69</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>560.85</v>
+        <v>557.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5478,22 +5469,22 @@
         <v>160</v>
       </c>
       <c r="D16" t="n">
-        <v>712.4</v>
+        <v>709.9</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1139.84</v>
+        <v>1135.84</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>386.38</v>
+        <v>382.38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5505,22 +5496,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>330.2</v>
+        <v>330</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1070.89</v>
+        <v>1070.59</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>428.9</v>
+        <v>428.6</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5532,22 +5523,22 @@
         <v>3.05550814</v>
       </c>
       <c r="D18" t="n">
-        <v>313.25</v>
+        <v>313.58</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>708.48</v>
+        <v>709.45</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>490.05</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>218.43</v>
+        <v>219.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5559,22 +5550,22 @@
         <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>47.24</v>
+        <v>46.67</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>699.34</v>
+        <v>691.13</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-168.24</v>
+        <v>-176.45</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5586,22 +5577,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D20" t="n">
-        <v>499.45</v>
+        <v>498.68</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>689.49</v>
+        <v>688.65</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>155.11</v>
+        <v>154.27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5613,22 +5604,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>94.5</v>
+        <v>95.27</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>643.25</v>
+        <v>648.7</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>94.06999999999999</v>
+        <v>99.52</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5640,22 +5631,22 @@
         <v>65</v>
       </c>
       <c r="D22" t="n">
-        <v>983.5</v>
+        <v>986.003</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>639.28</v>
+        <v>640.9</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-23.4</v>
+        <v>-21.78</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5667,22 +5658,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>341.63</v>
+        <v>340</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>589.21</v>
+        <v>586.59</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>99.94</v>
+        <v>97.31999999999999</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5694,22 +5685,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.8325</v>
+        <v>3.8393</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>536.55</v>
+        <v>537.5</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-1.82</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5721,22 +5712,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>354.75</v>
+        <v>356.69</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>525.17</v>
+        <v>528.22</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>117.25</v>
+        <v>120.3</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5748,130 +5739,130 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>237.1</v>
+        <v>236</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>194.85</v>
+        <v>194.01</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-1.67</v>
+        <v>-2.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.7</v>
+        <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>245.78</v>
+        <v>270.96</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>127.35</v>
+        <v>127.24</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>118.76</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>8.59</v>
+        <v>27.39</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.7</v>
       </c>
       <c r="D28" t="n">
-        <v>270</v>
+        <v>242.26</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>126.75</v>
+        <v>125.57</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>118.76</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>26.9</v>
+        <v>6.81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="D29" t="n">
-        <v>403</v>
+        <v>107.76</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>125.32</v>
+        <v>124.32</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>109.16</v>
+        <v>105.28</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>16.16</v>
+        <v>19.04</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.42010405</v>
       </c>
       <c r="D30" t="n">
-        <v>107.66</v>
+        <v>397.01</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>124.16</v>
+        <v>123.5</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>105.28</v>
+        <v>109.16</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>18.88</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5883,22 +5874,22 @@
         <v>2.50421091</v>
       </c>
       <c r="D31" t="n">
-        <v>64.59</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>119.73</v>
+        <v>119.52</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>12.92</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5910,22 +5901,22 @@
         <v>0.43583007</v>
       </c>
       <c r="D32" t="n">
-        <v>366.69</v>
+        <v>367.55</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>118.3</v>
+        <v>118.61</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>14.26</v>
+        <v>14.57</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5937,22 +5928,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D33" t="n">
-        <v>58.94</v>
+        <v>58.78</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>118.11</v>
+        <v>117.83</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>10.47</v>
+        <v>10.19</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5964,49 +5955,49 @@
         <v>0.28038062</v>
       </c>
       <c r="D34" t="n">
-        <v>563.05</v>
+        <v>562.08</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>116.85</v>
+        <v>116.69</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>11.1</v>
+        <v>10.94</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.51881442</v>
+        <v>3.81488812</v>
       </c>
       <c r="D35" t="n">
-        <v>298.9</v>
+        <v>40.61</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>114.79</v>
+        <v>114.71</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>95.94</v>
+        <v>108.23</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>18.85</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -6018,49 +6009,49 @@
         <v>0.59183053</v>
       </c>
       <c r="D36" t="n">
-        <v>260</v>
+        <v>259.71</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>113.9</v>
+        <v>113.81</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>14.05</v>
+        <v>13.96</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.51881442</v>
       </c>
       <c r="D37" t="n">
-        <v>39.85</v>
+        <v>295.48</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>112.53</v>
+        <v>113.51</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>108.23</v>
+        <v>95.94</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4.3</v>
+        <v>17.57</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6072,562 +6063,562 @@
         <v>1.32559468</v>
       </c>
       <c r="D38" t="n">
-        <v>114.43</v>
+        <v>115.34</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>112.28</v>
+        <v>113.21</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-7.45</v>
+        <v>-6.52</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="D39" t="n">
-        <v>273</v>
+        <v>13.33</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.16</v>
+        <v>112.53</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>20.98</v>
+        <v>6.38</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>3.30858696</v>
       </c>
       <c r="D40" t="n">
-        <v>87.16</v>
+        <v>45.9</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>111.87</v>
+        <v>112.45</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>101.53</v>
+        <v>112.71</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>10.34</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.5550481</v>
       </c>
       <c r="D41" t="n">
-        <v>45.6</v>
+        <v>272.85</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.68</v>
+        <v>112.14</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>112.71</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-1.03</v>
+        <v>20.96</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.73400968</v>
       </c>
       <c r="D42" t="n">
-        <v>394.99</v>
+        <v>87</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>110.55</v>
+        <v>111.7</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>101.53</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>15.04</v>
+        <v>10.17</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.35094641</v>
       </c>
       <c r="D43" t="n">
-        <v>352</v>
+        <v>110.34</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.1</v>
+        <v>110.37</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>101.39</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="D44" t="n">
-        <v>109.64</v>
+        <v>392.55</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>109.64</v>
+        <v>109.9</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>12.96</v>
+        <v>14.39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.7905852</v>
       </c>
       <c r="D45" t="n">
-        <v>12.95</v>
+        <v>187.68</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>109.28</v>
+        <v>109.86</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>106.15</v>
+        <v>110.41</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>3.13</v>
+        <v>-0.55</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.42255419</v>
       </c>
       <c r="D46" t="n">
-        <v>186.65</v>
+        <v>350.1</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>109.23</v>
+        <v>109.54</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>110.41</v>
+        <v>101.39</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>-1.18</v>
+        <v>8.15</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.74206342</v>
       </c>
       <c r="D47" t="n">
-        <v>124.61</v>
+        <v>84.29000000000001</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>108.79</v>
+        <v>108.73</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>98.72</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>10.07</v>
+        <v>12.05</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.61215748</v>
       </c>
       <c r="D48" t="n">
-        <v>84.29000000000001</v>
+        <v>239.2</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>108.69</v>
+        <v>108.42</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>12.01</v>
+        <v>20.33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.80409618</v>
       </c>
       <c r="D49" t="n">
-        <v>358.2</v>
+        <v>181.55</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>108.36</v>
+        <v>108.09</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>92.83</v>
+        <v>88.44</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>15.53</v>
+        <v>19.65</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.40867246</v>
       </c>
       <c r="D50" t="n">
-        <v>181.55</v>
+        <v>357.17</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>108.06</v>
+        <v>108.08</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>88.44</v>
+        <v>92.83</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>19.62</v>
+        <v>15.25</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.17949395</v>
       </c>
       <c r="D51" t="n">
-        <v>1133.43</v>
+        <v>123.71</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>107.86</v>
+        <v>108.04</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>98.89</v>
+        <v>98.72</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>8.970000000000001</v>
+        <v>9.32</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.62445608</v>
       </c>
       <c r="D52" t="n">
-        <v>212.09</v>
+        <v>232.99</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>107.53</v>
+        <v>107.73</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>108.77</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>18.07</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.68495686</v>
       </c>
       <c r="D53" t="n">
-        <v>236.4</v>
+        <v>212</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>107.12</v>
+        <v>107.52</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>88.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>19.03</v>
+        <v>18.06</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.50675322</v>
+        <v>13.30225117</v>
       </c>
       <c r="D54" t="n">
-        <v>285.32</v>
+        <v>10.87</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>107.02</v>
+        <v>107.06</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.96</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>10.34</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.50675322</v>
       </c>
       <c r="D55" t="n">
-        <v>10.86</v>
+        <v>285.31</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>106.93</v>
+        <v>107.05</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>106.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>-0.03</v>
+        <v>10.37</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.1285649</v>
       </c>
       <c r="D56" t="n">
-        <v>230.1</v>
+        <v>1111.21</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>106.36</v>
+        <v>105.78</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>108.77</v>
+        <v>98.89</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-2.41</v>
+        <v>6.89</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.90543241</v>
+        <v>2.27580753</v>
       </c>
       <c r="D57" t="n">
-        <v>158.26</v>
+        <v>62.64</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>106.07</v>
+        <v>105.56</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>92.27</v>
+        <v>106.15</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>13.8</v>
+        <v>-0.59</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.90543241</v>
       </c>
       <c r="D58" t="n">
-        <v>62.67</v>
+        <v>157.09</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105.57</v>
+        <v>105.32</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>106.15</v>
+        <v>92.27</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-0.58</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6642,19 +6633,19 @@
         <v>88.84999999999999</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>104.58</v>
+        <v>104.61</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>14.92</v>
+        <v>14.95</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6669,73 +6660,73 @@
         <v>75.63</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>104.07</v>
+        <v>104.11</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-0.91</v>
+        <v>-0.87</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.76637723</v>
       </c>
       <c r="D61" t="n">
-        <v>121.31</v>
+        <v>50.77</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.56</v>
+        <v>103.99</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>89.53</v>
+        <v>112.48</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>14.03</v>
+        <v>-8.49</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.1533463</v>
       </c>
       <c r="D62" t="n">
-        <v>50.54</v>
+        <v>121.51</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>103.49</v>
+        <v>103.77</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>112.48</v>
+        <v>89.53</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-8.99</v>
+        <v>14.24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6747,22 +6738,22 @@
         <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>125</v>
+        <v>125.21</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>103.44</v>
+        <v>103.65</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-1.92</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6774,76 +6765,76 @@
         <v>0.235295</v>
       </c>
       <c r="D64" t="n">
-        <v>591.8</v>
+        <v>594.27</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>103.07</v>
+        <v>103.54</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>119.82</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-16.75</v>
+        <v>-16.28</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.16558147</v>
       </c>
       <c r="D65" t="n">
-        <v>222.82</v>
+        <v>119.15</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>102.5</v>
+        <v>102.83</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>107.82</v>
+        <v>92.77</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-5.32</v>
+        <v>10.06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.6214908</v>
       </c>
       <c r="D66" t="n">
-        <v>117.66</v>
+        <v>222.23</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>101.51</v>
+        <v>102.27</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>92.77</v>
+        <v>107.82</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>8.74</v>
+        <v>-5.55</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6855,76 +6846,76 @@
         <v>0.97307689</v>
       </c>
       <c r="D67" t="n">
-        <v>139.1</v>
+        <v>138.8</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>100.19</v>
+        <v>100.01</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-11.25</v>
+        <v>-11.43</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.10445851</v>
       </c>
       <c r="D68" t="n">
-        <v>145.87</v>
+        <v>1277.55</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>98.94</v>
+        <v>98.81</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-0.91</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D69" t="n">
-        <v>1277.55</v>
+        <v>145.19</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>98.78</v>
+        <v>98.51000000000001</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>88.89</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>9.890000000000001</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6936,22 +6927,22 @@
         <v>5.691347</v>
       </c>
       <c r="D70" t="n">
-        <v>23.25</v>
+        <v>23.29</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>97.95</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-355.01</v>
+        <v>-354.81</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6963,22 +6954,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D71" t="n">
-        <v>111.78</v>
+        <v>111.73</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>97.06</v>
+        <v>97.05</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-13.39</v>
+        <v>-13.4</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6993,19 +6984,19 @@
         <v>68.89</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>94.18000000000001</v>
+        <v>94.20999999999999</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-16.35</v>
+        <v>-16.32</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7017,22 +7008,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D73" t="n">
-        <v>135.16</v>
+        <v>134.81</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>93.5</v>
+        <v>93.29000000000001</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>5.12</v>
+        <v>4.91</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7044,22 +7035,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D74" t="n">
-        <v>114.02</v>
+        <v>114.96</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>53.36</v>
+        <v>53.82</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>5.49</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7071,16 +7062,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D75" t="n">
-        <v>274.53</v>
+        <v>274.19</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>49.25</v>
+        <v>49.21</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>-2.86</v>
+        <v>-2.9</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Snapshots" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HoldingsSnapshots" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Holdings" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Snapshots" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="HoldingsSnapshots" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44183.28</v>
+        <v>43928.54</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44126.32</v>
+        <v>43870.19</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6248.33</v>
+        <v>5992.2</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1649593867045215</v>
+        <v>0.1581974122702921</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>56.96</v>
+        <v>58.35</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-10 10:16:50</t>
+          <t>2026-08-10 18:40:38</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>111.121</v>
+        <v>110.84</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7111.74</v>
+        <v>7093.76</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.161237511401192</v>
+        <v>0.1617750151997034</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1065.97</v>
+        <v>1047.99</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1763166643785655</v>
+        <v>0.1733426842238457</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.973</v>
+        <v>14.614</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4342.17</v>
+        <v>4238.06</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09844576501403511</v>
+        <v>0.09665004467549718</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>911.46</v>
+        <v>807.35</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2656767841059139</v>
+        <v>0.2353302960611652</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1527.6</v>
+        <v>1526.4</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2694.58</v>
+        <v>2692.47</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06109157160855487</v>
+        <v>0.06140246853216703</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1498.62</v>
+        <v>1496.51</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.253068664503829</v>
+        <v>1.251304391451219</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.55</v>
+        <v>24.53</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2090.46</v>
+        <v>2087.97</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04739495089580552</v>
+        <v>0.0476166910758927</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>164.65</v>
+        <v>162.16</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.08549649238502241</v>
+        <v>0.08420352994324466</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-9.06</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>225.05</v>
+        <v>218.58</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1820.69</v>
+        <v>1767.68</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04127872006471501</v>
+        <v>0.04031239552341941</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>568.01</v>
+        <v>515</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4534358335728199</v>
+        <v>0.4111185618034933</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-38.39</v>
+        <v>-38.85</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>488</v>
+        <v>475.45</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1806.68</v>
+        <v>1759.56</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04096108506473882</v>
+        <v>0.04012721684195546</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-91.87</v>
+        <v>-138.99</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.04838956045403071</v>
+        <v>-0.07320850122461879</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-10.53</v>
+        <v>-11.24</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>79.71079663</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>122.08</v>
+        <v>123.98</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1699.95</v>
+        <v>1725.76</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.0385413003718438</v>
+        <v>0.03935639917773368</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>579.95</v>
+        <v>605.76</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.5178125</v>
+        <v>0.5408571428571428</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-10.04</v>
+        <v>-10.45</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>1.15856288</v>
@@ -1111,22 +1111,22 @@
         <v>3299</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3261.9</v>
+        <v>3298</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1649.5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1630.95</v>
+        <v>1649</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03697693099294605</v>
+        <v>0.03760586770123472</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-18.55</v>
+        <v>-0.5</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.01124583207032434</v>
+        <v>-0.0003031221582297666</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>224.15</v>
+        <v>212.99</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1593.32</v>
+        <v>1513.42</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03612378288094718</v>
+        <v>0.03451393104693914</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-402.74</v>
+        <v>-482.64</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2017674819394207</v>
+        <v>-0.2417963387874112</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-16.04</v>
+        <v>-16.78</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>161.63</v>
+        <v>158.81</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1505.82</v>
+        <v>1478.99</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03413998113234497</v>
+        <v>0.03372874607122446</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-366.02</v>
+        <v>-392.85</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.1955402171125737</v>
+        <v>-0.2098737071544577</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-87.5</v>
+        <v>-88.17</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1257,114 +1257,114 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
+          <t>UBS Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IE00BMD8KM66</t>
+          <t>CH0244767585</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>113.04005874</v>
+        <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>118.99</v>
+        <v>43.83</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1401.06</v>
+        <v>1401.55</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03176486031881848</v>
+        <v>0.03196270702041572</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>57.27</v>
+        <v>173.21</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.04261826624695823</v>
+        <v>0.141011446342218</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-12.79</v>
+        <v>-43.59</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UBS Group</t>
+          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CH0244767585</t>
+          <t>IE00BMD8KM66</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>37.05</v>
+        <v>113.04005874</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>43.35</v>
+        <v>118.96</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1390.47</v>
+        <v>1400.18</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.03152476362718765</v>
+        <v>0.03193146381923277</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>162.13</v>
+        <v>56.39</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.131991142517544</v>
+        <v>0.04196340201966081</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-39.94</v>
+        <v>-13.29</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-07-16</t>
         </is>
       </c>
     </row>
@@ -1396,25 +1396,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>437.5</v>
+        <v>437.7</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1206.85</v>
+        <v>1205.03</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02736172731772092</v>
+        <v>0.02748101804488713</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>292.36</v>
+        <v>290.54</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.3196973176305919</v>
+        <v>0.317707137311507</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>-2.23</v>
+        <v>-4.02</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>114.82</v>
+        <v>114.65</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1164.69</v>
+        <v>1162.97</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02640587495519442</v>
+        <v>0.0265218289633141</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>557.5</v>
+        <v>555.78</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.9181640013834219</v>
+        <v>0.9153312801594228</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,22 +1510,22 @@
         <v>470.9125</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>709.9</v>
+        <v>711.8</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1135.84</v>
+        <v>1138.88</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02575178717865529</v>
+        <v>0.02597245033813354</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>382.38</v>
+        <v>385.42</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.5074987391500544</v>
+        <v>0.5115334589759244</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>330</v>
+        <v>334.81</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1070.59</v>
+        <v>1085.78</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02427243787469764</v>
+        <v>0.02476149122658983</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>428.6</v>
+        <v>443.79</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.6676116450412001</v>
+        <v>0.6912724497266313</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-32.5</v>
+        <v>-32.73</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1599,17 +1599,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AAPL_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US0378331005</t>
+          <t>US6701002056</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1618,55 +1618,55 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>3.05550814</v>
+        <v>20</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>207.72976897</v>
+        <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>313.58</v>
+        <v>47.13</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>490.05</v>
+        <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>709.45</v>
+        <v>697.6799999999999</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01608466457766675</v>
+        <v>0.01591077124184199</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>219.4</v>
+        <v>-169.9</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.4477094174063871</v>
+        <v>-0.1958320846492543</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-20.08</v>
+        <v>-11.36</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.46065664</v>
+        <v>0</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US6701002056</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1675,55 +1675,55 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>20</v>
+        <v>1.8650317</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>57.84</v>
+        <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46.67</v>
+        <v>505.14</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>867.58</v>
+        <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>691.13</v>
+        <v>697.3099999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.0156693131715594</v>
+        <v>0.01590233329699696</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-176.45</v>
+        <v>162.93</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>-0.2033818206966504</v>
+        <v>0.3048953927916464</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-11.03</v>
+        <v>-24.36</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0</v>
+        <v>0.3650317</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>AAPL_US_EQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>US0378331005</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1732,38 +1732,38 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.8650317</v>
+        <v>3.05550814</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>369.46288902</v>
+        <v>207.72976897</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>498.68</v>
+        <v>306.68</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>534.38</v>
+        <v>490.05</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>688.65</v>
+        <v>693.58</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01561308656199902</v>
+        <v>0.01581726969085651</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>154.27</v>
+        <v>203.53</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.2886896964706763</v>
+        <v>0.4153249668401183</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-24.17</v>
+        <v>-20.25</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3650317</v>
+        <v>0.46065664</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-01-24</t>
         </is>
       </c>
     </row>
@@ -1795,25 +1795,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>95.27</v>
+        <v>95.89</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>648.7</v>
+        <v>652.6799999999999</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01470733936363721</v>
+        <v>0.01488453470663546</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>99.52</v>
+        <v>103.5</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.1812156305764959</v>
+        <v>0.1884627990822681</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-23.51</v>
+        <v>-23.7</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1852,22 +1852,22 @@
         <v>1019.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>986.003</v>
+        <v>999.25</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>640.9</v>
+        <v>649.51</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01453049760776181</v>
+        <v>0.01481224204404425</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-21.78</v>
+        <v>-13.17</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.03286654192068571</v>
+        <v>-0.01987384559666808</v>
       </c>
       <c r="M22" s="2" t="n">
         <v>0</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>340</v>
+        <v>338.1</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>586.59</v>
+        <v>583.09</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.0132991802024294</v>
+        <v>0.01329751691807942</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1989085780857195</v>
+        <v>0.1917550636662783</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-31</v>
+        <v>-31.18</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.8393</v>
+        <v>3.8225</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>537.5</v>
+        <v>535.15</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01218621074141359</v>
+        <v>0.01220423292923939</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-0.87</v>
+        <v>-3.22</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.001615989003844939</v>
+        <v>-0.005981016772851385</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>356.69</v>
+        <v>354.61</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>528.22</v>
+        <v>524.9400000000001</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01197581439596184</v>
+        <v>0.0119713912620292</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>120.3</v>
+        <v>117.02</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2949107668170229</v>
+        <v>0.2868699745048048</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-8.92</v>
+        <v>-9.07</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>236</v>
+        <v>235.82</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>194.01</v>
+        <v>193.78</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004398598597100747</v>
+        <v>0.004419202573162683</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-2.51</v>
+        <v>-2.74</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.01277223692245064</v>
+        <v>-0.01394260126195807</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.79</v>
+        <v>-1.88</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2112,17 +2112,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2131,55 +2131,55 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.7</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>212.76482689</v>
+        <v>225.62857143</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>270.96</v>
+        <v>252.66</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>118.76</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>127.24</v>
+        <v>130.91</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002884787822767378</v>
+        <v>0.002985436107197475</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>27.39</v>
+        <v>12.15</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.2743114672008012</v>
+        <v>0.1023071741327046</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.06</v>
+        <v>-1.86</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,55 +2188,55 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.7</v>
+        <v>0.63422137</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>225.62857143</v>
+        <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>242.26</v>
+        <v>271.83</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>118.76</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>125.57</v>
+        <v>127.6</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002846925549394056</v>
+        <v>0.002909950708718951</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>6.81</v>
+        <v>27.75</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.05734253957561468</v>
+        <v>0.2779168753129695</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-1.81</v>
+        <v>0.02</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0</v>
+        <v>0.63422137</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.42010405</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>91.20399179</v>
+        <v>350.55601106</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>107.76</v>
+        <v>404.07</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>105.28</v>
+        <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>124.32</v>
+        <v>125.64</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002818585524414024</v>
+        <v>0.002865252406296623</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>19.04</v>
+        <v>16.48</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1808510638297872</v>
+        <v>0.1509710516672774</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.42010405</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>350.55601106</v>
+        <v>91.20399179</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>397.01</v>
+        <v>108.83</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>109.16</v>
+        <v>105.28</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>123.5</v>
+        <v>125.5</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002799994468027124</v>
+        <v>0.002862059670409313</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>14.34</v>
+        <v>20.22</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1313668010260169</v>
+        <v>0.1920592705167173</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-0.11</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2365,25 +2365,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>64.45999999999999</v>
+        <v>65.06</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>119.52</v>
+        <v>120.59</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002709759828490703</v>
+        <v>0.002750085861790112</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>12.71</v>
+        <v>13.78</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1189963486564928</v>
+        <v>0.1290141372530662</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.11</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>2.50421091</v>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.43583007</v>
+        <v>1.32559468</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>322.35040597</v>
+        <v>121.66614911</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>367.55</v>
+        <v>119.43</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>104.04</v>
+        <v>119.73</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>118.61</v>
+        <v>117.18</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.00268912829030524</v>
+        <v>0.002672319937677795</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>14.57</v>
+        <v>-2.55</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1400422914263745</v>
+        <v>-0.02129792032072162</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.36</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.43583007</v>
+        <v>1.32559468</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.43583007</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>53.65641702</v>
+        <v>322.35040597</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>58.78</v>
+        <v>363.2</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>107.64</v>
+        <v>104.04</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>117.83</v>
+        <v>117.16</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.0026714441147177</v>
+        <v>0.002671863832551037</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>10.19</v>
+        <v>13.12</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.09466740988480118</v>
+        <v>0.1261053440984237</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.43583007</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.30858696</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>509.16500577</v>
+        <v>45.93199509</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>562.08</v>
+        <v>47.53</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>105.75</v>
+        <v>112.71</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>116.69</v>
+        <v>116.4</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002645598011935911</v>
+        <v>0.002654531837734216</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>10.94</v>
+        <v>3.69</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.103451536643026</v>
+        <v>0.03273888741016769</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.22</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.30858696</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.28038062</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>38.28159448</v>
+        <v>509.16500577</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>40.61</v>
+        <v>560.29</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>108.23</v>
+        <v>105.75</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>114.71</v>
+        <v>116.28</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002600707412367541</v>
+        <v>0.002651795206973665</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>6.48</v>
+        <v>10.53</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.0598724937632819</v>
+        <v>0.09957446808510638</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.28038062</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>2.70722512</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>228.00445932</v>
+        <v>53.65641702</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>259.71</v>
+        <v>58</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>107.64</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>113.81</v>
+        <v>116.22</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002580302594381919</v>
+        <v>0.002650426891593389</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>13.96</v>
+        <v>8.58</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1398097145718578</v>
+        <v>0.07971014492753624</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.12</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>2.70722512</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.7905852</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>249.91595261</v>
+        <v>188.32884805</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>295.48</v>
+        <v>194.55</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>95.94</v>
+        <v>110.41</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>113.51</v>
+        <v>113.84</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002573500988386711</v>
+        <v>0.002596150381509134</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>17.57</v>
+        <v>3.43</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.1831352928913905</v>
+        <v>0.03106602662802282</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.21</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.7905852</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.59183053</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>121.66614911</v>
+        <v>228.00445932</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>115.34</v>
+        <v>259.52</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>113.21</v>
+        <v>113.68</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002566699382391503</v>
+        <v>0.002592501540495066</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>-6.52</v>
+        <v>13.83</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>-0.05445585901611959</v>
+        <v>0.1385077616424637</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.31</v>
+        <v>0.02</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.59183053</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.51881442</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>12.56856884</v>
+        <v>249.91595261</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>13.33</v>
+        <v>295.16</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>106.15</v>
+        <v>95.94</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.53</v>
+        <v>113.34</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002551282408802366</v>
+        <v>0.002584747753340172</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>6.38</v>
+        <v>17.4</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.06010362694300517</v>
+        <v>0.1813633520950594</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.03</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.51881442</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.5550481</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>45.93199509</v>
+        <v>221.99877812</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>45.9</v>
+        <v>275.49</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>112.71</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112.45</v>
+        <v>113.18</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002549468647203644</v>
+        <v>0.002581098912326104</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-0.26</v>
+        <v>22</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.002306805074971165</v>
+        <v>0.2412809826716385</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.18</v>
+        <v>0.02</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.5550481</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2910,17 +2910,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,34 +2929,34 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.5550481</v>
+        <v>1.73400968</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>221.99877812</v>
+        <v>79.10567143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>272.85</v>
+        <v>86.92</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>101.53</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>112.14</v>
+        <v>111.56</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002542440321008596</v>
+        <v>0.002544154397058669</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>20.96</v>
+        <v>10.03</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.2298749725817065</v>
+        <v>0.09878853540825371</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.06</v>
+        <v>0</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0.5550481</v>
+        <v>1.73400968</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>1.73400968</v>
+        <v>3.81488812</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>79.10567143</v>
+        <v>38.28159448</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>87</v>
+        <v>39.46</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>101.53</v>
+        <v>108.23</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>111.7</v>
+        <v>111.42</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002532464632215625</v>
+        <v>0.00254096166117136</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>10.17</v>
+        <v>3.19</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.1001674381956072</v>
+        <v>0.0294742677630971</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.14</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>1.73400968</v>
+        <v>3.81488812</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>96.717382</v>
+        <v>341.38450299</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>110.34</v>
+        <v>394.55</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.37</v>
+        <v>110.42</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002502310845636872</v>
+        <v>0.002518156404833437</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>13.69</v>
+        <v>14.91</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.1416011584609019</v>
+        <v>0.1561093079258716</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.35094641</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>341.38450299</v>
+        <v>96.717382</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>392.55</v>
+        <v>108.6</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>109.9</v>
+        <v>108.59</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.00249165499624438</v>
+        <v>0.002476422785735038</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>14.39</v>
+        <v>11.91</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.150664851847974</v>
+        <v>0.1231899048407116</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.35094641</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.80409618</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>188.32884805</v>
+        <v>148.63893521</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>187.68</v>
+        <v>182.25</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>110.41</v>
+        <v>88.44</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>109.86</v>
+        <v>108.47</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002490748115445019</v>
+        <v>0.002473686154974488</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>-0.55</v>
+        <v>20.03</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-0.004981432841228151</v>
+        <v>0.2264812302125735</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.17</v>
+        <v>0.03</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.80409618</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3220,25 +3220,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>350.1</v>
+        <v>346.71</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>109.54</v>
+        <v>108.44</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002483493069050131</v>
+        <v>0.00247300199728435</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>8.15</v>
+        <v>7.05</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.08038268073774535</v>
+        <v>0.06953348456455272</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>0.42255419</v>
@@ -3277,25 +3277,25 @@
         <v>74.99726962</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>84.29000000000001</v>
+        <v>84.09</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>108.73</v>
+        <v>108.43</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.00246512873286307</v>
+        <v>0.002472773944720971</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>12.05</v>
+        <v>11.75</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1246379809681423</v>
+        <v>0.1215349606950765</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>1.74206342</v>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>194.45976548</v>
+        <v>306.99401668</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>239.2</v>
+        <v>357.75</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>88.09</v>
+        <v>92.83</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>108.42</v>
+        <v>108.21</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002458100406668022</v>
+        <v>0.002467756788326628</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>20.33</v>
+        <v>15.38</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.2307866954251334</v>
+        <v>0.1656791985349564</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>148.63893521</v>
+        <v>54.82621761</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>181.55</v>
+        <v>52.84</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>88.44</v>
+        <v>112.48</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>108.09</v>
+        <v>108.19</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002450618640073294</v>
+        <v>0.002467300683199869</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>19.65</v>
+        <v>-4.29</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.2221845318860244</v>
+        <v>-0.03814011379800853</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.06</v>
+        <v>-0.22</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.62445608</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>306.99401668</v>
+        <v>235.02053179</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>357.17</v>
+        <v>233.61</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>92.83</v>
+        <v>108.77</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>108.08</v>
+        <v>107.97</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002450391919873454</v>
+        <v>0.002462283526805526</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>15.25</v>
+        <v>-0.8</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1642787891845309</v>
+        <v>-0.007354969201066471</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.15</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.62445608</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1.17949395</v>
+        <v>11.40066159</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>113.12478542</v>
+        <v>12.56856884</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>123.71</v>
+        <v>12.79</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>98.72</v>
+        <v>106.15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>108.04</v>
+        <v>107.93</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002449485039074093</v>
+        <v>0.002461371316552009</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>9.32</v>
+        <v>1.78</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.09440842787682334</v>
+        <v>0.0167687235044748</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>1.17949395</v>
+        <v>11.40066159</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.61215748</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>235.02053179</v>
+        <v>194.45976548</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>232.99</v>
+        <v>237.16</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>108.77</v>
+        <v>88.09</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>107.73</v>
+        <v>107.46</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002442456712879045</v>
+        <v>0.002450652846073186</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>-1.04</v>
+        <v>19.37</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>-0.009561459961386413</v>
+        <v>0.2198887501419003</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.02</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.61215748</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3619,25 +3619,25 @@
         <v>176.50746647</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>212</v>
+        <v>211.73</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>107.52</v>
+        <v>107.34</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002437695588682399</v>
+        <v>0.002447916215312635</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>18.06</v>
+        <v>17.88</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.2018779342723005</v>
+        <v>0.1998658618376928</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>0.68495686</v>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.1285649</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>10.85229847</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>10.87</v>
+        <v>1126.41</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>106.96</v>
+        <v>98.89</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>107.06</v>
+        <v>107.19</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002427266459489748</v>
+        <v>0.002444495426861946</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>0.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.0009349289454001497</v>
+        <v>0.08393164121751441</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.1285649</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.90543241</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>257.81779936</v>
+        <v>137.713206</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>285.31</v>
+        <v>159.41</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>107.05</v>
+        <v>106.83</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002427039739289908</v>
+        <v>0.002436285534580294</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>10.37</v>
+        <v>14.56</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1072610674389739</v>
+        <v>0.1577977674216972</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.90543241</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.50675322</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>257.81779936</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>1111.21</v>
+        <v>283.93</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>98.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>105.78</v>
+        <v>106.5</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002398246273910195</v>
+        <v>0.00242875979998878</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>6.89</v>
+        <v>9.82</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.06967337445646678</v>
+        <v>0.1015721969383533</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.50675322</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>62.95787236</v>
+        <v>113.12478542</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>62.64</v>
+        <v>121.97</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>106.15</v>
+        <v>98.72</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>105.56</v>
+        <v>106.48</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.00239325842951371</v>
+        <v>0.002428303694862021</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>-0.59</v>
+        <v>7.76</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>-0.005558172397550635</v>
+        <v>0.07860615883306321</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.04</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,55 +3898,55 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.90543241</v>
+        <v>5.691347</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>137.713206</v>
+        <v>105.04894536</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>157.09</v>
+        <v>25.12</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>92.27</v>
+        <v>452.96</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>105.32</v>
+        <v>105.82</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002387817144717544</v>
+        <v>0.002413252225678992</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>13.05</v>
+        <v>-347.14</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.141432751706947</v>
+        <v>-0.7663811374072765</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.06</v>
+        <v>-10.44</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1.59010207</v>
+        <v>13.30225117</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>10.85229847</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>88.84999999999999</v>
+        <v>10.69</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>89.66</v>
+        <v>106.96</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>104.61</v>
+        <v>105.25</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002371720010528886</v>
+        <v>0.002400253229566376</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>14.95</v>
+        <v>-1.71</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.1667410216372965</v>
+        <v>-0.01598728496634256</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>1.59010207</v>
+        <v>13.30225117</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.59010207</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>76.24181082</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>75.63</v>
+        <v>88.91</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>104.98</v>
+        <v>89.66</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>104.11</v>
+        <v>104.64</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002360384000536873</v>
+        <v>0.002386342023200243</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>-0.87</v>
+        <v>14.98</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>-0.008287292817679558</v>
+        <v>0.1670756190051305</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.03</v>
+        <v>0.02</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.59010207</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.1533463</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>54.82621761</v>
+        <v>104.90344487</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>50.77</v>
+        <v>121.68</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>112.48</v>
+        <v>89.53</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>103.99</v>
+        <v>103.87</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.00235766335813879</v>
+        <v>0.002368781975820043</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-8.49</v>
+        <v>14.34</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.07548008534850641</v>
+        <v>0.1601697754942477</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.18</v>
+        <v>0.02</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.1533463</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>104.90344487</v>
+        <v>62.95787236</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>121.51</v>
+        <v>61.56</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>89.53</v>
+        <v>106.15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>103.77</v>
+        <v>103.7</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002352675513742305</v>
+        <v>0.002364905082242596</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>14.24</v>
+        <v>-2.45</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.1590528314531442</v>
+        <v>-0.02308054639660857</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.06</v>
+        <v>-0.1</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>FB_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US30303M1027</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,55 +4183,55 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.235295</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>127.23134407</v>
+        <v>627.34014747</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>125.21</v>
+        <v>593.27</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>105.36</v>
+        <v>119.82</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>103.65</v>
+        <v>103.32</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002349954871344222</v>
+        <v>0.002356239084834185</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-1.71</v>
+        <v>-16.5</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.01623006833712984</v>
+        <v>-0.1377065598397597</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.04</v>
+        <v>-10.57</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-01-23</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FB_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US30303M1027</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,55 +4240,55 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.235295</v>
+        <v>1.85908491</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>627.34014747</v>
+        <v>76.24181082</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>594.27</v>
+        <v>74.08</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>119.82</v>
+        <v>104.98</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>103.54</v>
+        <v>101.94</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002347460949145979</v>
+        <v>0.002324767831087851</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-16.28</v>
+        <v>-3.04</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.1358704723752295</v>
+        <v>-0.02895789674223662</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-10.52</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0</v>
+        <v>1.85908491</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1.16558147</v>
+        <v>1.11796351</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>107.56862839</v>
+        <v>127.23134407</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>119.15</v>
+        <v>121.44</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>92.77</v>
+        <v>105.36</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>102.83</v>
+        <v>100.49</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002331363814957321</v>
+        <v>0.002291700209397863</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>10.06</v>
+        <v>-4.87</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>0.1084402285221516</v>
+        <v>-0.04622247532270311</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>0.06</v>
+        <v>-0.08</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>1.16558147</v>
+        <v>1.11796351</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4360,25 +4360,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>222.23</v>
+        <v>218.21</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>102.27</v>
+        <v>100.38</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002318667483766267</v>
+        <v>0.002289191631200692</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-5.55</v>
+        <v>-7.44</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.05147468002225932</v>
+        <v>-0.06900389538119088</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>0.6214908</v>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.16558147</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>154.44822659</v>
+        <v>107.56862839</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>138.8</v>
+        <v>116.14</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>111.44</v>
+        <v>92.77</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>100.01</v>
+        <v>100.2</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.00226742871860237</v>
+        <v>0.002285086685059866</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-11.43</v>
+        <v>7.43</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.1025664034458004</v>
+        <v>0.08009054651288132</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.16</v>
+        <v>0.04</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.16558147</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4474,25 +4474,25 @@
         <v>1150.02597682</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>1277.55</v>
+        <v>1289.73</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>98.81</v>
+        <v>99.72</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002240222294621539</v>
+        <v>0.002274140162017663</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>9.92</v>
+        <v>10.83</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.1115986050174373</v>
+        <v>0.1218359770502869</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.06</v>
+        <v>0.03</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>0.10445851</v>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>147.21071381</v>
+        <v>154.44822659</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>145.19</v>
+        <v>137.48</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>98.51000000000001</v>
+        <v>99.02</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002233420688626332</v>
+        <v>0.002258176482581117</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-1.34</v>
+        <v>-12.42</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.01342013019529294</v>
+        <v>-0.1114501076812635</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.2</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,38 +4582,38 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>105.04894536</v>
+        <v>147.21071381</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>23.29</v>
+        <v>145.99</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>452.96</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>98.15000000000001</v>
+        <v>99.02</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002225258761432083</v>
+        <v>0.002258176482581117</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-354.81</v>
+        <v>-0.83</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.7833141999293536</v>
+        <v>-0.008312468703054582</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-10.27</v>
+        <v>0</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4645,25 +4645,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>111.73</v>
+        <v>111.8</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>97.05</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002200319539449655</v>
+        <v>0.002213706232722168</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-13.4</v>
+        <v>-13.38</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1213218650973291</v>
+        <v>-0.1211407876867361</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.18</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.17308322</v>
@@ -4677,17 +4677,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>PNR_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IE00BLS09M33</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4696,34 +4696,34 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>1.84694851</v>
+        <v>0.93456659</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>80.72233697999999</v>
+        <v>127.79185697</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>68.89</v>
+        <v>135.56</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>110.53</v>
+        <v>88.38</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>94.20999999999999</v>
+        <v>93.77</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.002135931002695023</v>
+        <v>0.002138448886807022</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>-16.32</v>
+        <v>5.39</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>-0.147652221116439</v>
+        <v>0.06098664856302331</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.14</v>
+        <v>0.02</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>1.84694851</v>
+        <v>0.93456659</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -4734,17 +4734,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>PNR_US_EQ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>IE00BLS09M33</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4753,34 +4753,34 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.84694851</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>127.79185697</v>
+        <v>80.72233697999999</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>134.81</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>88.38</v>
+        <v>110.53</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>93.29000000000001</v>
+        <v>91.69</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.00211507274430972</v>
+        <v>0.002091013953624143</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>4.91</v>
+        <v>-18.84</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.05555555555555556</v>
+        <v>-0.1704514611417715</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.18</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.84694851</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -4816,25 +4816,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>114.96</v>
+        <v>113.67</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>53.82</v>
+        <v>53.19</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001220208115540241</v>
+        <v>0.001213011584614114</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>5.95</v>
+        <v>5.32</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.1242949655316482</v>
+        <v>0.1111343221224149</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.03</v>
+        <v>0.01</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.63221571</v>
@@ -4873,25 +4873,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>274.19</v>
+        <v>271.61</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>49.21</v>
+        <v>48.72</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.001115690103413885</v>
+        <v>0.001111072088783599</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>-2.9</v>
+        <v>-3.39</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>-0.0556515064287085</v>
+        <v>-0.06505469199769719</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>0.04</v>
+        <v>0.01</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>0.24236298</v>
@@ -4988,29 +4988,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10 10:16:50</t>
+          <t>2026-08-10 18:40:38</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44183.28</v>
+        <v>43928.54</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>44126.32</v>
+        <v>43870.19</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37877.99</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6248.33</v>
+        <v>5992.2</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1649593867045215</v>
+        <v>0.1581974122702921</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1251.59</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>77.42</v>
+        <v>78.81</v>
       </c>
       <c r="J2" t="n">
         <v>74</v>
@@ -5091,16 +5091,16 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>111.121</v>
+        <v>110.84</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7111.74</v>
+        <v>7093.76</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1065.97</v>
+        <v>1047.99</v>
       </c>
     </row>
     <row r="3">
@@ -5118,16 +5118,16 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.973</v>
+        <v>14.614</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4342.17</v>
+        <v>4238.06</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>911.46</v>
+        <v>807.35</v>
       </c>
     </row>
     <row r="4">
@@ -5145,16 +5145,16 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1527.6</v>
+        <v>1526.4</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2694.58</v>
+        <v>2692.47</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1498.62</v>
+        <v>1496.51</v>
       </c>
     </row>
     <row r="5">
@@ -5172,16 +5172,16 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>24.55</v>
+        <v>24.53</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2090.46</v>
+        <v>2087.97</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>164.65</v>
+        <v>162.16</v>
       </c>
     </row>
     <row r="6">
@@ -5199,16 +5199,16 @@
         <v>10.9260596</v>
       </c>
       <c r="D6" t="n">
-        <v>225.05</v>
+        <v>218.58</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1820.69</v>
+        <v>1767.68</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>568.01</v>
+        <v>515</v>
       </c>
     </row>
     <row r="7">
@@ -5226,16 +5226,16 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>488</v>
+        <v>475.45</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1806.68</v>
+        <v>1759.56</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-91.87</v>
+        <v>-138.99</v>
       </c>
     </row>
     <row r="8">
@@ -5253,16 +5253,16 @@
         <v>18.80610988</v>
       </c>
       <c r="D8" t="n">
-        <v>122.08</v>
+        <v>123.98</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1699.95</v>
+        <v>1725.76</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>579.95</v>
+        <v>605.76</v>
       </c>
     </row>
     <row r="9">
@@ -5280,16 +5280,16 @@
         <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>3261.9</v>
+        <v>3298</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1630.95</v>
+        <v>1649</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1649.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-18.55</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="10">
@@ -5307,16 +5307,16 @@
         <v>9.6</v>
       </c>
       <c r="D10" t="n">
-        <v>224.15</v>
+        <v>212.99</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1593.32</v>
+        <v>1513.42</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-402.74</v>
+        <v>-482.64</v>
       </c>
     </row>
     <row r="11">
@@ -5334,16 +5334,16 @@
         <v>12.5822526</v>
       </c>
       <c r="D11" t="n">
-        <v>161.63</v>
+        <v>158.81</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1505.82</v>
+        <v>1478.99</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-366.02</v>
+        <v>-392.85</v>
       </c>
     </row>
     <row r="12">
@@ -5354,23 +5354,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>118.99</v>
+        <v>43.83</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1401.06</v>
+        <v>1401.55</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>57.27</v>
+        <v>173.21</v>
       </c>
     </row>
     <row r="13">
@@ -5381,23 +5381,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="D13" t="n">
-        <v>43.35</v>
+        <v>118.96</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1390.47</v>
+        <v>1400.18</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>162.13</v>
+        <v>56.39</v>
       </c>
     </row>
     <row r="14">
@@ -5415,16 +5415,16 @@
         <v>3.2220691</v>
       </c>
       <c r="D14" t="n">
-        <v>437.5</v>
+        <v>437.7</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1206.85</v>
+        <v>1205.03</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>292.36</v>
+        <v>290.54</v>
       </c>
     </row>
     <row r="15">
@@ -5442,16 +5442,16 @@
         <v>1014.362806</v>
       </c>
       <c r="D15" t="n">
-        <v>114.82</v>
+        <v>114.65</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1164.69</v>
+        <v>1162.97</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>557.5</v>
+        <v>555.78</v>
       </c>
     </row>
     <row r="16">
@@ -5469,16 +5469,16 @@
         <v>160</v>
       </c>
       <c r="D16" t="n">
-        <v>709.9</v>
+        <v>711.8</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1135.84</v>
+        <v>1138.88</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>382.38</v>
+        <v>385.42</v>
       </c>
     </row>
     <row r="17">
@@ -5496,16 +5496,16 @@
         <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>330</v>
+        <v>334.81</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1070.59</v>
+        <v>1085.78</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>428.6</v>
+        <v>443.79</v>
       </c>
     </row>
     <row r="18">
@@ -5516,23 +5516,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AAPL_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>3.05550814</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>313.58</v>
+        <v>47.13</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>709.45</v>
+        <v>697.6799999999999</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>490.05</v>
+        <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>219.4</v>
+        <v>-169.9</v>
       </c>
     </row>
     <row r="19">
@@ -5543,23 +5543,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>20</v>
+        <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>46.67</v>
+        <v>505.14</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>691.13</v>
+        <v>697.3099999999999</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>867.58</v>
+        <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-176.45</v>
+        <v>162.93</v>
       </c>
     </row>
     <row r="20">
@@ -5570,23 +5570,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>AAPL_US_EQ</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.8650317</v>
+        <v>3.05550814</v>
       </c>
       <c r="D20" t="n">
-        <v>498.68</v>
+        <v>306.68</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>688.65</v>
+        <v>693.58</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>534.38</v>
+        <v>490.05</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>154.27</v>
+        <v>203.53</v>
       </c>
     </row>
     <row r="21">
@@ -5604,16 +5604,16 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>95.27</v>
+        <v>95.89</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>648.7</v>
+        <v>652.6799999999999</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>99.52</v>
+        <v>103.5</v>
       </c>
     </row>
     <row r="22">
@@ -5631,16 +5631,16 @@
         <v>65</v>
       </c>
       <c r="D22" t="n">
-        <v>986.003</v>
+        <v>999.25</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>640.9</v>
+        <v>649.51</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-21.78</v>
+        <v>-13.17</v>
       </c>
     </row>
     <row r="23">
@@ -5658,16 +5658,16 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>340</v>
+        <v>338.1</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>586.59</v>
+        <v>583.09</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>93.81999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -5685,16 +5685,16 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.8393</v>
+        <v>3.8225</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>537.5</v>
+        <v>535.15</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-0.87</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="25">
@@ -5712,16 +5712,16 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>356.69</v>
+        <v>354.61</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>528.22</v>
+        <v>524.9400000000001</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>120.3</v>
+        <v>117.02</v>
       </c>
     </row>
     <row r="26">
@@ -5739,16 +5739,16 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>236</v>
+        <v>235.82</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>194.01</v>
+        <v>193.78</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-2.51</v>
+        <v>-2.74</v>
       </c>
     </row>
     <row r="27">
@@ -5759,23 +5759,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.7</v>
       </c>
       <c r="D27" t="n">
-        <v>270.96</v>
+        <v>252.66</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>127.24</v>
+        <v>130.91</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>118.76</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>27.39</v>
+        <v>12.15</v>
       </c>
     </row>
     <row r="28">
@@ -5786,23 +5786,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7</v>
+        <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>242.26</v>
+        <v>271.83</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>125.57</v>
+        <v>127.6</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>118.76</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>6.81</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="29">
@@ -5813,23 +5813,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.42010405</v>
       </c>
       <c r="D29" t="n">
-        <v>107.76</v>
+        <v>404.07</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>124.32</v>
+        <v>125.64</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>105.28</v>
+        <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>19.04</v>
+        <v>16.48</v>
       </c>
     </row>
     <row r="30">
@@ -5840,23 +5840,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="D30" t="n">
-        <v>397.01</v>
+        <v>108.83</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>123.5</v>
+        <v>125.5</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>109.16</v>
+        <v>105.28</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>14.34</v>
+        <v>20.22</v>
       </c>
     </row>
     <row r="31">
@@ -5874,16 +5874,16 @@
         <v>2.50421091</v>
       </c>
       <c r="D31" t="n">
-        <v>64.45999999999999</v>
+        <v>65.06</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>119.52</v>
+        <v>120.59</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>12.71</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="32">
@@ -5894,23 +5894,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.43583007</v>
+        <v>1.32559468</v>
       </c>
       <c r="D32" t="n">
-        <v>367.55</v>
+        <v>119.43</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>118.61</v>
+        <v>117.18</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>104.04</v>
+        <v>119.73</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>14.57</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="33">
@@ -5921,23 +5921,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.43583007</v>
       </c>
       <c r="D33" t="n">
-        <v>58.78</v>
+        <v>363.2</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>117.83</v>
+        <v>117.16</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>107.64</v>
+        <v>104.04</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>10.19</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="34">
@@ -5948,23 +5948,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>3.30858696</v>
       </c>
       <c r="D34" t="n">
-        <v>562.08</v>
+        <v>47.53</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>116.69</v>
+        <v>116.4</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>105.75</v>
+        <v>112.71</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>10.94</v>
+        <v>3.69</v>
       </c>
     </row>
     <row r="35">
@@ -5975,23 +5975,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.28038062</v>
       </c>
       <c r="D35" t="n">
-        <v>40.61</v>
+        <v>560.29</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>114.71</v>
+        <v>116.28</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>108.23</v>
+        <v>105.75</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>6.48</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="36">
@@ -6002,23 +6002,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>2.70722512</v>
       </c>
       <c r="D36" t="n">
-        <v>259.71</v>
+        <v>58</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>113.81</v>
+        <v>116.22</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>107.64</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>13.96</v>
+        <v>8.58</v>
       </c>
     </row>
     <row r="37">
@@ -6029,23 +6029,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.7905852</v>
       </c>
       <c r="D37" t="n">
-        <v>295.48</v>
+        <v>194.55</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>113.51</v>
+        <v>113.84</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>95.94</v>
+        <v>110.41</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>17.57</v>
+        <v>3.43</v>
       </c>
     </row>
     <row r="38">
@@ -6056,23 +6056,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.59183053</v>
       </c>
       <c r="D38" t="n">
-        <v>115.34</v>
+        <v>259.52</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>113.21</v>
+        <v>113.68</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>-6.52</v>
+        <v>13.83</v>
       </c>
     </row>
     <row r="39">
@@ -6083,23 +6083,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.51881442</v>
       </c>
       <c r="D39" t="n">
-        <v>13.33</v>
+        <v>295.16</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.53</v>
+        <v>113.34</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>106.15</v>
+        <v>95.94</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>6.38</v>
+        <v>17.4</v>
       </c>
     </row>
     <row r="40">
@@ -6110,23 +6110,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.5550481</v>
       </c>
       <c r="D40" t="n">
-        <v>45.9</v>
+        <v>275.49</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>112.45</v>
+        <v>113.18</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>112.71</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-0.26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="41">
@@ -6137,23 +6137,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.5550481</v>
+        <v>1.73400968</v>
       </c>
       <c r="D41" t="n">
-        <v>272.85</v>
+        <v>86.92</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>112.14</v>
+        <v>111.56</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>101.53</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>20.96</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="42">
@@ -6164,23 +6164,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>1.73400968</v>
+        <v>3.81488812</v>
       </c>
       <c r="D42" t="n">
-        <v>87</v>
+        <v>39.46</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>111.7</v>
+        <v>111.42</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>101.53</v>
+        <v>108.23</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>10.17</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="43">
@@ -6191,23 +6191,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="D43" t="n">
-        <v>110.34</v>
+        <v>394.55</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.37</v>
+        <v>110.42</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>13.69</v>
+        <v>14.91</v>
       </c>
     </row>
     <row r="44">
@@ -6218,23 +6218,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.35094641</v>
       </c>
       <c r="D44" t="n">
-        <v>392.55</v>
+        <v>108.6</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>109.9</v>
+        <v>108.59</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>14.39</v>
+        <v>11.91</v>
       </c>
     </row>
     <row r="45">
@@ -6245,23 +6245,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.80409618</v>
       </c>
       <c r="D45" t="n">
-        <v>187.68</v>
+        <v>182.25</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>109.86</v>
+        <v>108.47</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>110.41</v>
+        <v>88.44</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-0.55</v>
+        <v>20.03</v>
       </c>
     </row>
     <row r="46">
@@ -6279,16 +6279,16 @@
         <v>0.42255419</v>
       </c>
       <c r="D46" t="n">
-        <v>350.1</v>
+        <v>346.71</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>109.54</v>
+        <v>108.44</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>8.15</v>
+        <v>7.05</v>
       </c>
     </row>
     <row r="47">
@@ -6306,16 +6306,16 @@
         <v>1.74206342</v>
       </c>
       <c r="D47" t="n">
-        <v>84.29000000000001</v>
+        <v>84.09</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>108.73</v>
+        <v>108.43</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>12.05</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="48">
@@ -6326,23 +6326,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.40867246</v>
       </c>
       <c r="D48" t="n">
-        <v>239.2</v>
+        <v>357.75</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>108.42</v>
+        <v>108.21</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>88.09</v>
+        <v>92.83</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>20.33</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="49">
@@ -6353,23 +6353,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="D49" t="n">
-        <v>181.55</v>
+        <v>52.84</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>108.09</v>
+        <v>108.19</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>88.44</v>
+        <v>112.48</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>19.65</v>
+        <v>-4.29</v>
       </c>
     </row>
     <row r="50">
@@ -6380,23 +6380,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.62445608</v>
       </c>
       <c r="D50" t="n">
-        <v>357.17</v>
+        <v>233.61</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>108.08</v>
+        <v>107.97</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>92.83</v>
+        <v>108.77</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>15.25</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="51">
@@ -6407,23 +6407,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1.17949395</v>
+        <v>11.40066159</v>
       </c>
       <c r="D51" t="n">
-        <v>123.71</v>
+        <v>12.79</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>108.04</v>
+        <v>107.93</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>98.72</v>
+        <v>106.15</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>9.32</v>
+        <v>1.78</v>
       </c>
     </row>
     <row r="52">
@@ -6434,23 +6434,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.61215748</v>
       </c>
       <c r="D52" t="n">
-        <v>232.99</v>
+        <v>237.16</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>107.73</v>
+        <v>107.46</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>108.77</v>
+        <v>88.09</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>-1.04</v>
+        <v>19.37</v>
       </c>
     </row>
     <row r="53">
@@ -6468,16 +6468,16 @@
         <v>0.68495686</v>
       </c>
       <c r="D53" t="n">
-        <v>212</v>
+        <v>211.73</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>107.52</v>
+        <v>107.34</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>18.06</v>
+        <v>17.88</v>
       </c>
     </row>
     <row r="54">
@@ -6488,23 +6488,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.1285649</v>
       </c>
       <c r="D54" t="n">
-        <v>10.87</v>
+        <v>1126.41</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>107.06</v>
+        <v>107.19</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>106.96</v>
+        <v>98.89</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>0.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="55">
@@ -6515,23 +6515,23 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.90543241</v>
       </c>
       <c r="D55" t="n">
-        <v>285.31</v>
+        <v>159.41</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>107.05</v>
+        <v>106.83</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>10.37</v>
+        <v>14.56</v>
       </c>
     </row>
     <row r="56">
@@ -6542,23 +6542,23 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.50675322</v>
       </c>
       <c r="D56" t="n">
-        <v>1111.21</v>
+        <v>283.93</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>105.78</v>
+        <v>106.5</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>98.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>6.89</v>
+        <v>9.82</v>
       </c>
     </row>
     <row r="57">
@@ -6569,23 +6569,23 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="D57" t="n">
-        <v>62.64</v>
+        <v>121.97</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>105.56</v>
+        <v>106.48</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>106.15</v>
+        <v>98.72</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>-0.59</v>
+        <v>7.76</v>
       </c>
     </row>
     <row r="58">
@@ -6596,23 +6596,23 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.90543241</v>
+        <v>5.691347</v>
       </c>
       <c r="D58" t="n">
-        <v>157.09</v>
+        <v>25.12</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105.32</v>
+        <v>105.82</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>92.27</v>
+        <v>452.96</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>13.05</v>
+        <v>-347.14</v>
       </c>
     </row>
     <row r="59">
@@ -6623,23 +6623,23 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1.59010207</v>
+        <v>13.30225117</v>
       </c>
       <c r="D59" t="n">
-        <v>88.84999999999999</v>
+        <v>10.69</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>104.61</v>
+        <v>105.25</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>89.66</v>
+        <v>106.96</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>14.95</v>
+        <v>-1.71</v>
       </c>
     </row>
     <row r="60">
@@ -6650,23 +6650,23 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.59010207</v>
       </c>
       <c r="D60" t="n">
-        <v>75.63</v>
+        <v>88.91</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>104.11</v>
+        <v>104.64</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>104.98</v>
+        <v>89.66</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-0.87</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="61">
@@ -6677,23 +6677,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.1533463</v>
       </c>
       <c r="D61" t="n">
-        <v>50.77</v>
+        <v>121.68</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.99</v>
+        <v>103.87</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>112.48</v>
+        <v>89.53</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-8.49</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="62">
@@ -6704,23 +6704,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="D62" t="n">
-        <v>121.51</v>
+        <v>61.56</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>103.77</v>
+        <v>103.7</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>89.53</v>
+        <v>106.15</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>14.24</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="63">
@@ -6731,23 +6731,23 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>FB_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.235295</v>
       </c>
       <c r="D63" t="n">
-        <v>125.21</v>
+        <v>593.27</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>103.65</v>
+        <v>103.32</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>105.36</v>
+        <v>119.82</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-1.71</v>
+        <v>-16.5</v>
       </c>
     </row>
     <row r="64">
@@ -6758,23 +6758,23 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>FB_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.235295</v>
+        <v>1.85908491</v>
       </c>
       <c r="D64" t="n">
-        <v>594.27</v>
+        <v>74.08</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>103.54</v>
+        <v>101.94</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>119.82</v>
+        <v>104.98</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-16.28</v>
+        <v>-3.04</v>
       </c>
     </row>
     <row r="65">
@@ -6785,23 +6785,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1.16558147</v>
+        <v>1.11796351</v>
       </c>
       <c r="D65" t="n">
-        <v>119.15</v>
+        <v>121.44</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>102.83</v>
+        <v>100.49</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>92.77</v>
+        <v>105.36</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>10.06</v>
+        <v>-4.87</v>
       </c>
     </row>
     <row r="66">
@@ -6819,16 +6819,16 @@
         <v>0.6214908</v>
       </c>
       <c r="D66" t="n">
-        <v>222.23</v>
+        <v>218.21</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>102.27</v>
+        <v>100.38</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-5.55</v>
+        <v>-7.44</v>
       </c>
     </row>
     <row r="67">
@@ -6839,23 +6839,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.16558147</v>
       </c>
       <c r="D67" t="n">
-        <v>138.8</v>
+        <v>116.14</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>100.01</v>
+        <v>100.2</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>111.44</v>
+        <v>92.77</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-11.43</v>
+        <v>7.43</v>
       </c>
     </row>
     <row r="68">
@@ -6873,16 +6873,16 @@
         <v>0.10445851</v>
       </c>
       <c r="D68" t="n">
-        <v>1277.55</v>
+        <v>1289.73</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>98.81</v>
+        <v>99.72</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>9.92</v>
+        <v>10.83</v>
       </c>
     </row>
     <row r="69">
@@ -6893,23 +6893,23 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0.97307689</v>
       </c>
       <c r="D69" t="n">
-        <v>145.19</v>
+        <v>137.48</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>98.51000000000001</v>
+        <v>99.02</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-1.34</v>
+        <v>-12.42</v>
       </c>
     </row>
     <row r="70">
@@ -6920,23 +6920,23 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D70" t="n">
-        <v>23.29</v>
+        <v>145.99</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>98.15000000000001</v>
+        <v>99.02</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>452.96</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-354.81</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="71">
@@ -6954,16 +6954,16 @@
         <v>1.17308322</v>
       </c>
       <c r="D71" t="n">
-        <v>111.73</v>
+        <v>111.8</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>97.05</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-13.4</v>
+        <v>-13.38</v>
       </c>
     </row>
     <row r="72">
@@ -6974,23 +6974,23 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>PNR_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>1.84694851</v>
+        <v>0.93456659</v>
       </c>
       <c r="D72" t="n">
-        <v>68.89</v>
+        <v>135.56</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>94.20999999999999</v>
+        <v>93.77</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>110.53</v>
+        <v>88.38</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>-16.32</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="73">
@@ -7001,23 +7001,23 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>PNR_US_EQ</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.84694851</v>
       </c>
       <c r="D73" t="n">
-        <v>134.81</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>93.29000000000001</v>
+        <v>91.69</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>88.38</v>
+        <v>110.53</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>4.91</v>
+        <v>-18.84</v>
       </c>
     </row>
     <row r="74">
@@ -7035,16 +7035,16 @@
         <v>0.63221571</v>
       </c>
       <c r="D74" t="n">
-        <v>114.96</v>
+        <v>113.67</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>53.82</v>
+        <v>53.19</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>5.95</v>
+        <v>5.32</v>
       </c>
     </row>
     <row r="75">
@@ -7062,16 +7062,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D75" t="n">
-        <v>274.19</v>
+        <v>271.61</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>49.21</v>
+        <v>48.72</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>-2.9</v>
+        <v>-3.39</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43928.54</v>
+        <v>43952.78</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43870.19</v>
+        <v>43895.43</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37877.99</v>
+        <v>37878.99</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5992.2</v>
+        <v>6016.44</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1581974122702921</v>
+        <v>0.1588331684662131</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>58.35</v>
+        <v>57.35</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-10 18:40:38</t>
+          <t>2026-08-10 19:32:21</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         <v>7093.76</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1617750151997034</v>
+        <v>0.1616833138041059</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>1047.99</v>
@@ -778,7 +778,7 @@
         <v>4238.06</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09665004467549718</v>
+        <v>0.0965952590587543</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>807.35</v>
@@ -835,7 +835,7 @@
         <v>2692.47</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06140246853216703</v>
+        <v>0.06136766283580793</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>1496.51</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.53</v>
+        <v>24.69</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2087.97</v>
+        <v>2102.09</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.0476166910758927</v>
+        <v>0.0479115274712526</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>162.16</v>
+        <v>176.28</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.08420352994324466</v>
+        <v>0.09153550973356665</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-9.779999999999999</v>
+        <v>-9.32</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>218.58</v>
+        <v>219.07</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1767.68</v>
+        <v>1772.06</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04031239552341941</v>
+        <v>0.04038937503661017</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>515</v>
+        <v>519.38</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4111185618034933</v>
+        <v>0.4146150652999968</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-38.85</v>
+        <v>-38.56</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>475.45</v>
+        <v>475.28</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1759.56</v>
+        <v>1759.34</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04012721684195546</v>
+        <v>0.04009945660807746</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-138.99</v>
+        <v>-139.21</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.07320850122461879</v>
+        <v>-0.07332437913144242</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-11.24</v>
+        <v>-10.8</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>79.71079663</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>123.98</v>
+        <v>123.83</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1725.76</v>
+        <v>1724.08</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.03935639917773368</v>
+        <v>0.03929579907741209</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>605.76</v>
+        <v>604.08</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.5408571428571428</v>
+        <v>0.5393571428571429</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-10.45</v>
+        <v>-10.19</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>1.15856288</v>
@@ -1120,7 +1120,7 @@
         <v>1649</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03760586770123472</v>
+        <v>0.03758455099453189</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>-0.5</v>
@@ -1168,25 +1168,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>212.99</v>
+        <v>213.75</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1513.42</v>
+        <v>1519.18</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03451393104693914</v>
+        <v>0.03462565080647238</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-482.64</v>
+        <v>-476.88</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2417963387874112</v>
+        <v>-0.2389106539883571</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-16.78</v>
+        <v>-16.31</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>158.81</v>
+        <v>158.28</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1478.99</v>
+        <v>1474.4</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03372874607122446</v>
+        <v>0.03360501030099322</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-392.85</v>
+        <v>-397.44</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.2098737071544577</v>
+        <v>-0.2123258398153688</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-88.17</v>
+        <v>-87.75</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1288,19 +1288,19 @@
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1401.55</v>
+        <v>1401.5</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03196270702041572</v>
+        <v>0.03194344949595903</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>173.21</v>
+        <v>173.16</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.141011446342218</v>
+        <v>0.1409707410000489</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-43.59</v>
+        <v>-43.64</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1345,19 +1345,19 @@
         <v>1343.79</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1400.18</v>
+        <v>1400.51</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.03193146381923277</v>
+        <v>0.03192088508996474</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>56.39</v>
+        <v>56.72</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.04196340201966081</v>
+        <v>0.04220897610489734</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-13.29</v>
+        <v>-12.98</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1402,16 +1402,16 @@
         <v>914.49</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1205.03</v>
+        <v>1205.04</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02748101804488713</v>
+        <v>0.02746566848420297</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>290.54</v>
+        <v>290.55</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.317707137311507</v>
+        <v>0.3177180723682053</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>-4.02</v>
@@ -1462,7 +1462,7 @@
         <v>1162.97</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.0265218289633141</v>
+        <v>0.02650679519109203</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>555.78</v>
@@ -1519,7 +1519,7 @@
         <v>1138.88</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02597245033813354</v>
+        <v>0.02595772797856427</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>385.42</v>
@@ -1567,25 +1567,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>334.81</v>
+        <v>335.22</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1085.78</v>
+        <v>1087.37</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02476149122658983</v>
+        <v>0.0247836950969825</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>443.79</v>
+        <v>445.38</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.6912724497266313</v>
+        <v>0.693749123818128</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-32.73</v>
+        <v>-32.58</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>47.13</v>
+        <v>47.47</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>697.6799999999999</v>
+        <v>702.88</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01591077124184199</v>
+        <v>0.01602027240936117</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-169.9</v>
+        <v>-164.7</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.1958320846492543</v>
+        <v>-0.189838401069642</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-11.36</v>
+        <v>-11.15</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>505.14</v>
+        <v>504.83</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>697.3099999999999</v>
+        <v>697.05</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01590233329699696</v>
+        <v>0.01588739312961701</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>162.93</v>
+        <v>162.67</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.3048953927916464</v>
+        <v>0.3044088476365133</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-24.36</v>
+        <v>-24.24</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1732,31 +1732,31 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.05550814</v>
+        <v>3.05990683</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>207.72976897</v>
+        <v>207.87234231</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>306.68</v>
+        <v>307.13</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>490.05</v>
+        <v>491.05</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>693.58</v>
+        <v>695.76</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01581726969085651</v>
+        <v>0.01585799102483657</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>203.53</v>
+        <v>204.71</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.4153249668401183</v>
+        <v>0.4168821912228897</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-20.25</v>
+        <v>-20.15</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0.46065664</v>
@@ -1795,25 +1795,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>95.89</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>652.6799999999999</v>
+        <v>652.15</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01488453470663546</v>
+        <v>0.01486401754462339</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>103.5</v>
+        <v>102.97</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.1884627990822681</v>
+        <v>0.1874977238792382</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-23.7</v>
+        <v>-23.58</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1861,7 +1861,7 @@
         <v>649.51</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01481224204404425</v>
+        <v>0.01480384579530528</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>-13.17</v>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>338.1</v>
+        <v>337.85</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>583.09</v>
+        <v>582.8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01329751691807942</v>
+        <v>0.01328336950855863</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>93.81999999999999</v>
+        <v>93.53</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1917550636662783</v>
+        <v>0.1911623439000961</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-31.18</v>
+        <v>-31.07</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1975,7 +1975,7 @@
         <v>535.15</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01220423292923939</v>
+        <v>0.01219731501802531</v>
       </c>
       <c r="K24" s="2" t="n">
         <v>-3.22</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>354.61</v>
+        <v>355.28</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>524.9400000000001</v>
+        <v>526.0599999999999</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.0119713912620292</v>
+        <v>0.011990132744805</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>117.02</v>
+        <v>118.14</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2868699745048048</v>
+        <v>0.2896156109040988</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-9.07</v>
+        <v>-8.98</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>235.82</v>
+        <v>236.3</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>193.78</v>
+        <v>194.22</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004419202573162683</v>
+        <v>0.00442672619415281</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-2.74</v>
+        <v>-2.3</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.01394260126195807</v>
+        <v>-0.01170364339507429</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.88</v>
+        <v>-1.83</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>252.66</v>
+        <v>252.24</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>130.91</v>
+        <v>130.72</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002985436107197475</v>
+        <v>0.002979413284417956</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>12.15</v>
+        <v>11.96</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.1023071741327046</v>
+        <v>0.1007073088582014</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-1.86</v>
+        <v>-1.83</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0</v>
@@ -2194,25 +2194,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>271.83</v>
+        <v>271.91</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>127.6</v>
+        <v>127.67</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002909950708718951</v>
+        <v>0.002909896680092108</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>27.75</v>
+        <v>27.82</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2779168753129695</v>
+        <v>0.2786179268903355</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0.63422137</v>
@@ -2251,25 +2251,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>404.07</v>
+        <v>402.98</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>125.64</v>
+        <v>125.33</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002865252406296623</v>
+        <v>0.002856562629560147</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>16.48</v>
+        <v>16.17</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1509710516672774</v>
+        <v>0.1481311835837303</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.42010405</v>
@@ -2308,25 +2308,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>108.83</v>
+        <v>108.3</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>125.5</v>
+        <v>124.92</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002862059670409313</v>
+        <v>0.00284721777455241</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>20.22</v>
+        <v>19.64</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1920592705167173</v>
+        <v>0.1865501519756839</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>1.55804584</v>
@@ -2365,25 +2365,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>65.06</v>
+        <v>65.12</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>120.59</v>
+        <v>120.73</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002750085861790112</v>
+        <v>0.002751717914839196</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>13.78</v>
+        <v>13.92</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1290141372530662</v>
+        <v>0.130324875947945</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>2.50421091</v>
@@ -2422,25 +2422,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>119.43</v>
+        <v>120.28</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>117.18</v>
+        <v>118.04</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002672319937677795</v>
+        <v>0.002690406549056728</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.69</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>-0.02129792032072162</v>
+        <v>-0.01411509229098806</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.33</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>1.32559468</v>
@@ -2479,25 +2479,25 @@
         <v>322.35040597</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>363.2</v>
+        <v>362.33</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>117.16</v>
+        <v>116.91</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002671863832551037</v>
+        <v>0.002664651216962233</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.12</v>
+        <v>12.87</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1261053440984237</v>
+        <v>0.1237024221453287</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>0.43583007</v>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.70722512</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45.93199509</v>
+        <v>53.65641702</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>47.53</v>
+        <v>58.16</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>112.71</v>
+        <v>107.64</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>116.4</v>
+        <v>116.57</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002654531837734216</v>
+        <v>0.002656901825004598</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>3.69</v>
+        <v>8.93</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.03273888741016769</v>
+        <v>0.0829617242660721</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.22</v>
+        <v>-0.1</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.70722512</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2593,25 +2593,25 @@
         <v>509.16500577</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>560.29</v>
+        <v>559.92</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>116.28</v>
+        <v>116.23</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002651795206973665</v>
+        <v>0.002649152433046963</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>10.53</v>
+        <v>10.48</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.09957446808510638</v>
+        <v>0.09910165484633571</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.06</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>0.28038062</v>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2.70722512</v>
+        <v>3.30858696</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>53.65641702</v>
+        <v>45.93199509</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>58</v>
+        <v>47.35</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>107.64</v>
+        <v>112.71</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>116.22</v>
+        <v>115.98</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002650426891593389</v>
+        <v>0.002643454350725172</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>8.58</v>
+        <v>3.27</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.07971014492753624</v>
+        <v>0.02901250998136811</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.2</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>2.70722512</v>
+        <v>3.30858696</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.59183053</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>188.32884805</v>
+        <v>228.00445932</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>194.55</v>
+        <v>259.91</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>110.41</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>113.84</v>
+        <v>113.88</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002596150381509134</v>
+        <v>0.00259559045922213</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3.43</v>
+        <v>14.03</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.03106602662802282</v>
+        <v>0.1405107661492238</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.21</v>
+        <v>0.05</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.59183053</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>228.00445932</v>
+        <v>188.32884805</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>259.52</v>
+        <v>194.3</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>110.41</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>113.68</v>
+        <v>113.72</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002592501540495066</v>
+        <v>0.002591943686536184</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>13.83</v>
+        <v>3.31</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.1385077616424637</v>
+        <v>0.02997916855357305</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.02</v>
+        <v>-0.18</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.5550481</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>249.91595261</v>
+        <v>221.99877812</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>295.16</v>
+        <v>275.37</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>95.94</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.34</v>
+        <v>113.16</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002584747753340172</v>
+        <v>0.002579179982135372</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>17.4</v>
+        <v>21.98</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.1813633520950594</v>
+        <v>0.2410616363237552</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.5550481</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.51881442</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>221.99877812</v>
+        <v>249.91595261</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>275.49</v>
+        <v>294.33</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>113.18</v>
+        <v>113.05</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002581098912326104</v>
+        <v>0.002576672825913784</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>22</v>
+        <v>17.11</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.2412809826716385</v>
+        <v>0.1783406295601418</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.51881442</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2935,25 +2935,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>86.92</v>
+        <v>86.88</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.56</v>
+        <v>111.53</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002544154397058669</v>
+        <v>0.002542028485397296</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.09878853540825371</v>
+        <v>0.09849305623953511</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>1.73400968</v>
@@ -2998,19 +2998,19 @@
         <v>108.23</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>111.42</v>
+        <v>111.45</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.00254096166117136</v>
+        <v>0.002540205099054323</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.0294742677630971</v>
+        <v>0.02975145523422341</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.11</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>3.81488812</v>
@@ -3049,25 +3049,25 @@
         <v>341.38450299</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>394.55</v>
+        <v>394.31</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.42</v>
+        <v>110.38</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002518156404833437</v>
+        <v>0.002515817306717058</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>14.91</v>
+        <v>14.87</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.1561093079258716</v>
+        <v>0.1556905036121872</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>0.37810738</v>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.76637723</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>96.717382</v>
+        <v>54.82621761</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>108.6</v>
+        <v>53.11</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>112.48</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>108.59</v>
+        <v>108.77</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002476422785735038</v>
+        <v>0.002479121656564726</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>11.91</v>
+        <v>-3.71</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1231899048407116</v>
+        <v>-0.03298364153627311</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.2</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.76637723</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3163,25 +3163,25 @@
         <v>148.63893521</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>182.25</v>
+        <v>182.27</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>108.47</v>
+        <v>108.51</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002473686154974488</v>
+        <v>0.002473195650950064</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>20.03</v>
+        <v>20.07</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.2264812302125735</v>
+        <v>0.2269335142469471</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>0.80409618</v>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.40867246</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>324.07677699</v>
+        <v>306.99401668</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>346.71</v>
+        <v>358.33</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>101.39</v>
+        <v>92.83</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>108.44</v>
+        <v>108.42</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.00247300199728435</v>
+        <v>0.002471144341314219</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>7.05</v>
+        <v>15.59</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.06953348456455272</v>
+        <v>0.1679413982548745</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.40867246</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.42255419</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>74.99726962</v>
+        <v>324.07677699</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>84.09</v>
+        <v>345.91</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>108.43</v>
+        <v>108.21</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002472773944720971</v>
+        <v>0.002466357952163915</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>11.75</v>
+        <v>6.82</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1215349606950765</v>
+        <v>0.06726501627379426</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.42255419</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.40867246</v>
+        <v>11.40066159</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>306.99401668</v>
+        <v>12.56856884</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>357.75</v>
+        <v>12.82</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>92.83</v>
+        <v>106.15</v>
       </c>
       <c r="I48" s="2" t="n">
         <v>108.21</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002467756788326628</v>
+        <v>0.002466357952163915</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>15.38</v>
+        <v>2.06</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1656791985349564</v>
+        <v>0.01940650023551578</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.06</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.40867246</v>
+        <v>11.40066159</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.35094641</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>54.82621761</v>
+        <v>96.717382</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>52.84</v>
+        <v>108.07</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>112.48</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>108.19</v>
+        <v>108.09</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002467300683199869</v>
+        <v>0.002463622872649455</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>-4.29</v>
+        <v>11.41</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>-0.03814011379800853</v>
+        <v>0.118018204385602</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.22</v>
+        <v>0.06</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.35094641</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.74206342</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>235.02053179</v>
+        <v>74.99726962</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>233.61</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>108.77</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>107.97</v>
+        <v>108.07</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002462283526805526</v>
+        <v>0.002463167026063712</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>-0.8</v>
+        <v>11.39</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>-0.007354969201066471</v>
+        <v>0.1178113363673976</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.15</v>
+        <v>0.05</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.74206342</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.62445608</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>12.56856884</v>
+        <v>235.02053179</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>12.79</v>
+        <v>233.56</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>106.15</v>
+        <v>108.77</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>107.93</v>
+        <v>107.98</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002461371316552009</v>
+        <v>0.002461115716427867</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1.78</v>
+        <v>-0.79</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.0167687235044748</v>
+        <v>-0.00726303208605314</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.11</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.62445608</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3562,25 +3562,25 @@
         <v>194.45976548</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>237.16</v>
+        <v>236.81</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>88.09</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>107.46</v>
+        <v>107.32</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002450652846073186</v>
+        <v>0.00244607277909834</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>19.37</v>
+        <v>19.23</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.2198887501419003</v>
+        <v>0.2182994664547622</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="N52" s="4" t="n">
         <v>0.61215748</v>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.1285649</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>176.50746647</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>211.73</v>
+        <v>1126.8</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>98.89</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>107.34</v>
+        <v>107.25</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002447916215312635</v>
+        <v>0.002444477316048238</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>17.88</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1998658618376928</v>
+        <v>0.08453837597330366</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.1285649</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.68495686</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>176.50746647</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>1126.41</v>
+        <v>211.15</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>98.89</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>107.19</v>
+        <v>107.07</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002444495426861946</v>
+        <v>0.002440374696776549</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>17.61</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.08393164121751441</v>
+        <v>0.1968477531857813</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.68495686</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
         <v>137.713206</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>159.41</v>
+        <v>159.56</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>92.27</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>106.83</v>
+        <v>106.96</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002436285534580294</v>
+        <v>0.002437867540554961</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>14.56</v>
+        <v>14.69</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1577977674216972</v>
+        <v>0.1592066760593909</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.02</v>
+        <v>0.05</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>0.90543241</v>
@@ -3790,25 +3790,25 @@
         <v>257.81779936</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>283.93</v>
+        <v>282.67</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>106.5</v>
+        <v>106.05</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.00242875979998878</v>
+        <v>0.002417126520903643</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>9.82</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.1015721969383533</v>
+        <v>0.09691766652875464</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.03</v>
+        <v>0.05</v>
       </c>
       <c r="N56" s="4" t="n">
         <v>0.50675322</v>
@@ -3847,25 +3847,25 @@
         <v>113.12478542</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>121.97</v>
+        <v>121.37</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>106.48</v>
+        <v>105.98</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002428303694862021</v>
+        <v>0.002415531057853541</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>7.76</v>
+        <v>7.26</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.07860615883306321</v>
+        <v>0.07354132901134522</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>1.17949395</v>
@@ -3904,25 +3904,25 @@
         <v>105.04894536</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>25.12</v>
+        <v>25.13</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>105.82</v>
+        <v>105.89</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002413252225678992</v>
+        <v>0.002413479748217697</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-347.14</v>
+        <v>-347.07</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.7663811374072765</v>
+        <v>-0.7662265983751325</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-10.44</v>
+        <v>-10.33</v>
       </c>
       <c r="N58" s="4" t="n">
         <v>0</v>
@@ -3961,25 +3961,25 @@
         <v>10.85229847</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>10.69</v>
+        <v>10.7</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>105.25</v>
+        <v>105.38</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002400253229566376</v>
+        <v>0.002401855660281243</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-1.71</v>
+        <v>-1.58</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.01598728496634256</v>
+        <v>-0.01477187733732237</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.08</v>
       </c>
       <c r="N59" s="4" t="n">
         <v>13.30225117</v>
@@ -4018,25 +4018,25 @@
         <v>76.19636644000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>88.91</v>
+        <v>88.7</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>104.64</v>
+        <v>104.42</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002386342023200243</v>
+        <v>0.002379975024165567</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>14.98</v>
+        <v>14.76</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.1670756190051305</v>
+        <v>0.1646219049743475</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>1.59010207</v>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>104.90344487</v>
+        <v>62.95787236</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>121.68</v>
+        <v>61.73</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>89.53</v>
+        <v>106.15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>103.87</v>
+        <v>104.01</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002368781975820043</v>
+        <v>0.00237063016915783</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>14.34</v>
+        <v>-2.14</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.1601697754942477</v>
+        <v>-0.02016015073009892</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.02</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.1533463</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>62.95787236</v>
+        <v>104.90344487</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>61.56</v>
+        <v>121.4</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>106.15</v>
+        <v>89.53</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>103.7</v>
+        <v>103.66</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002364905082242596</v>
+        <v>0.002362652853907323</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-2.45</v>
+        <v>14.13</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.02308054639660857</v>
+        <v>0.1578241930079303</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.04</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.1533463</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4189,7 +4189,7 @@
         <v>627.34014747</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>593.27</v>
+        <v>593.09</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>119.82</v>
@@ -4198,7 +4198,7 @@
         <v>103.32</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002356239084834185</v>
+        <v>0.002354903461949687</v>
       </c>
       <c r="K63" s="2" t="n">
         <v>-16.5</v>
@@ -4207,7 +4207,7 @@
         <v>-0.1377065598397597</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-10.57</v>
+        <v>-10.53</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>0</v>
@@ -4246,25 +4246,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>74.08</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>101.94</v>
+        <v>102.06</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002324767831087851</v>
+        <v>0.002326185127047862</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-3.04</v>
+        <v>-2.92</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.02895789674223662</v>
+        <v>-0.02781482187083254</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>1.85908491</v>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.6214908</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>127.23134407</v>
+        <v>234.11448729</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>121.44</v>
+        <v>218.24</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>105.36</v>
+        <v>107.82</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>100.49</v>
+        <v>100.42</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002291700209397863</v>
+        <v>0.002288805707016915</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-4.87</v>
+        <v>-7.4</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.04622247532270311</v>
+        <v>-0.06863290669634577</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.6214908</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.11796351</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>234.11448729</v>
+        <v>127.23134407</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>218.21</v>
+        <v>120.96</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>107.82</v>
+        <v>105.36</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>100.38</v>
+        <v>100.12</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002289191631200692</v>
+        <v>0.002281968008230766</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-7.44</v>
+        <v>-5.24</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.06900389538119088</v>
+        <v>-0.04973424449506454</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.12</v>
+        <v>-0.05</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.11796351</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.10445851</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>107.56862839</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>116.14</v>
+        <v>1291.97</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>92.77</v>
+        <v>88.89</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>100.2</v>
+        <v>99.91</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002285086685059866</v>
+        <v>0.002277181619080461</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>7.43</v>
+        <v>11.02</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.08009054651288132</v>
+        <v>0.1239734503318708</v>
       </c>
       <c r="M67" s="2" t="n">
         <v>0.04</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.10445851</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4449,17 +4449,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,34 +4468,34 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.16558147</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>1289.73</v>
+        <v>115.58</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>88.89</v>
+        <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>99.72</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002274140162017663</v>
+        <v>0.002273306923101644</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>10.83</v>
+        <v>6.97</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.1218359770502869</v>
+        <v>0.07513204699795192</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.16558147</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4531,25 +4531,25 @@
         <v>154.44822659</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>137.48</v>
+        <v>137.37</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>99.02</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002258176482581117</v>
+        <v>0.002255528906257656</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-12.42</v>
+        <v>-12.48</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.1114501076812635</v>
+        <v>-0.1119885139985643</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>0.97307689</v>
@@ -4588,25 +4588,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>145.99</v>
+        <v>145.64</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>99.02</v>
+        <v>98.81</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002258176482581117</v>
+        <v>0.002252110056864582</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-0.83</v>
+        <v>-1.04</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.008312468703054582</v>
+        <v>-0.01041562343515273</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4645,25 +4645,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>111.8</v>
+        <v>111.93</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>97.06999999999999</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002213706232722168</v>
+        <v>0.002215642330005121</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-13.38</v>
+        <v>-13.24</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1211407876867361</v>
+        <v>-0.1198732458125849</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.15</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.17308322</v>
@@ -4702,25 +4702,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>135.56</v>
+        <v>135.34</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>93.77</v>
+        <v>93.64</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.002138448886807022</v>
+        <v>0.002134273714449949</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>5.39</v>
+        <v>5.26</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.06098664856302331</v>
+        <v>0.05951572754016746</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.93456659</v>
@@ -4759,25 +4759,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>67.06999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>91.69</v>
+        <v>91.34</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.002091013953624143</v>
+        <v>0.002081851357089474</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-18.84</v>
+        <v>-19.19</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.1704514611417715</v>
+        <v>-0.173618022256401</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.15</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>1.84694851</v>
@@ -4816,25 +4816,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>113.67</v>
+        <v>113.78</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>53.19</v>
+        <v>53.26</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001213011584614114</v>
+        <v>0.001213919457834305</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>5.32</v>
+        <v>5.39</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.1111343221224149</v>
+        <v>0.1125966158345519</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.01</v>
+        <v>0.03</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.63221571</v>
@@ -4873,25 +4873,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>271.61</v>
+        <v>272.05</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>48.72</v>
+        <v>48.81</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.001111072088783599</v>
+        <v>0.001112493592506429</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>-3.39</v>
+        <v>-3.3</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>-0.06505469199769719</v>
+        <v>-0.06332757628094415</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>0.24236298</v>
@@ -4988,29 +4988,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10 18:40:38</t>
+          <t>2026-08-10 19:32:21</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43928.54</v>
+        <v>43952.78</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43870.19</v>
+        <v>43895.43</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37877.99</v>
+        <v>37878.99</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5992.2</v>
+        <v>6016.44</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1581974122702921</v>
+        <v>0.1588331684662131</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1251.59</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>78.81</v>
+        <v>77.81</v>
       </c>
       <c r="J2" t="n">
         <v>74</v>
@@ -5172,16 +5172,16 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>24.53</v>
+        <v>24.69</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2087.97</v>
+        <v>2102.09</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>162.16</v>
+        <v>176.28</v>
       </c>
     </row>
     <row r="6">
@@ -5199,16 +5199,16 @@
         <v>10.9260596</v>
       </c>
       <c r="D6" t="n">
-        <v>218.58</v>
+        <v>219.07</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1767.68</v>
+        <v>1772.06</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>515</v>
+        <v>519.38</v>
       </c>
     </row>
     <row r="7">
@@ -5226,16 +5226,16 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>475.45</v>
+        <v>475.28</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1759.56</v>
+        <v>1759.34</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-138.99</v>
+        <v>-139.21</v>
       </c>
     </row>
     <row r="8">
@@ -5253,16 +5253,16 @@
         <v>18.80610988</v>
       </c>
       <c r="D8" t="n">
-        <v>123.98</v>
+        <v>123.83</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1725.76</v>
+        <v>1724.08</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>605.76</v>
+        <v>604.08</v>
       </c>
     </row>
     <row r="9">
@@ -5307,16 +5307,16 @@
         <v>9.6</v>
       </c>
       <c r="D10" t="n">
-        <v>212.99</v>
+        <v>213.75</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1513.42</v>
+        <v>1519.18</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-482.64</v>
+        <v>-476.88</v>
       </c>
     </row>
     <row r="11">
@@ -5334,16 +5334,16 @@
         <v>12.5822526</v>
       </c>
       <c r="D11" t="n">
-        <v>158.81</v>
+        <v>158.28</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1478.99</v>
+        <v>1474.4</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-392.85</v>
+        <v>-397.44</v>
       </c>
     </row>
     <row r="12">
@@ -5364,13 +5364,13 @@
         <v>43.83</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1401.55</v>
+        <v>1401.5</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>173.21</v>
+        <v>173.16</v>
       </c>
     </row>
     <row r="13">
@@ -5391,13 +5391,13 @@
         <v>118.96</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1400.18</v>
+        <v>1400.51</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>56.39</v>
+        <v>56.72</v>
       </c>
     </row>
     <row r="14">
@@ -5418,13 +5418,13 @@
         <v>437.7</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1205.03</v>
+        <v>1205.04</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>290.54</v>
+        <v>290.55</v>
       </c>
     </row>
     <row r="15">
@@ -5496,16 +5496,16 @@
         <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>334.81</v>
+        <v>335.22</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1085.78</v>
+        <v>1087.37</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>443.79</v>
+        <v>445.38</v>
       </c>
     </row>
     <row r="18">
@@ -5523,16 +5523,16 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>47.13</v>
+        <v>47.47</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>697.6799999999999</v>
+        <v>702.88</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-169.9</v>
+        <v>-164.7</v>
       </c>
     </row>
     <row r="19">
@@ -5550,16 +5550,16 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>505.14</v>
+        <v>504.83</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>697.3099999999999</v>
+        <v>697.05</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>162.93</v>
+        <v>162.67</v>
       </c>
     </row>
     <row r="20">
@@ -5574,19 +5574,19 @@
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.05550814</v>
+        <v>3.05990683</v>
       </c>
       <c r="D20" t="n">
-        <v>306.68</v>
+        <v>307.13</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>693.58</v>
+        <v>695.76</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>490.05</v>
+        <v>491.05</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>203.53</v>
+        <v>204.71</v>
       </c>
     </row>
     <row r="21">
@@ -5604,16 +5604,16 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>95.89</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>652.6799999999999</v>
+        <v>652.15</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>103.5</v>
+        <v>102.97</v>
       </c>
     </row>
     <row r="22">
@@ -5658,16 +5658,16 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>338.1</v>
+        <v>337.85</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>583.09</v>
+        <v>582.8</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>93.81999999999999</v>
+        <v>93.53</v>
       </c>
     </row>
     <row r="24">
@@ -5712,16 +5712,16 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>354.61</v>
+        <v>355.28</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>524.9400000000001</v>
+        <v>526.0599999999999</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>117.02</v>
+        <v>118.14</v>
       </c>
     </row>
     <row r="26">
@@ -5739,16 +5739,16 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>235.82</v>
+        <v>236.3</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>193.78</v>
+        <v>194.22</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-2.74</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="27">
@@ -5766,16 +5766,16 @@
         <v>0.7</v>
       </c>
       <c r="D27" t="n">
-        <v>252.66</v>
+        <v>252.24</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>130.91</v>
+        <v>130.72</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>12.15</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="28">
@@ -5793,16 +5793,16 @@
         <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>271.83</v>
+        <v>271.91</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>127.6</v>
+        <v>127.67</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>27.75</v>
+        <v>27.82</v>
       </c>
     </row>
     <row r="29">
@@ -5820,16 +5820,16 @@
         <v>0.42010405</v>
       </c>
       <c r="D29" t="n">
-        <v>404.07</v>
+        <v>402.98</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>125.64</v>
+        <v>125.33</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>16.48</v>
+        <v>16.17</v>
       </c>
     </row>
     <row r="30">
@@ -5847,16 +5847,16 @@
         <v>1.55804584</v>
       </c>
       <c r="D30" t="n">
-        <v>108.83</v>
+        <v>108.3</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>125.5</v>
+        <v>124.92</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>20.22</v>
+        <v>19.64</v>
       </c>
     </row>
     <row r="31">
@@ -5874,16 +5874,16 @@
         <v>2.50421091</v>
       </c>
       <c r="D31" t="n">
-        <v>65.06</v>
+        <v>65.12</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>120.59</v>
+        <v>120.73</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>13.78</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="32">
@@ -5901,16 +5901,16 @@
         <v>1.32559468</v>
       </c>
       <c r="D32" t="n">
-        <v>119.43</v>
+        <v>120.28</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>117.18</v>
+        <v>118.04</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-2.55</v>
+        <v>-1.69</v>
       </c>
     </row>
     <row r="33">
@@ -5928,16 +5928,16 @@
         <v>0.43583007</v>
       </c>
       <c r="D33" t="n">
-        <v>363.2</v>
+        <v>362.33</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>117.16</v>
+        <v>116.91</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.12</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="34">
@@ -5948,23 +5948,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.70722512</v>
       </c>
       <c r="D34" t="n">
-        <v>47.53</v>
+        <v>58.16</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>116.4</v>
+        <v>116.57</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>112.71</v>
+        <v>107.64</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>3.69</v>
+        <v>8.93</v>
       </c>
     </row>
     <row r="35">
@@ -5982,16 +5982,16 @@
         <v>0.28038062</v>
       </c>
       <c r="D35" t="n">
-        <v>560.29</v>
+        <v>559.92</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>116.28</v>
+        <v>116.23</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>10.53</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="36">
@@ -6002,23 +6002,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2.70722512</v>
+        <v>3.30858696</v>
       </c>
       <c r="D36" t="n">
-        <v>58</v>
+        <v>47.35</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>116.22</v>
+        <v>115.98</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>107.64</v>
+        <v>112.71</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.58</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="37">
@@ -6029,23 +6029,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.59183053</v>
       </c>
       <c r="D37" t="n">
-        <v>194.55</v>
+        <v>259.91</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>113.84</v>
+        <v>113.88</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>110.41</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>3.43</v>
+        <v>14.03</v>
       </c>
     </row>
     <row r="38">
@@ -6056,23 +6056,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="D38" t="n">
-        <v>259.52</v>
+        <v>194.3</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>113.68</v>
+        <v>113.72</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>110.41</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>13.83</v>
+        <v>3.31</v>
       </c>
     </row>
     <row r="39">
@@ -6083,23 +6083,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.5550481</v>
       </c>
       <c r="D39" t="n">
-        <v>295.16</v>
+        <v>275.37</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.34</v>
+        <v>113.16</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>95.94</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>17.4</v>
+        <v>21.98</v>
       </c>
     </row>
     <row r="40">
@@ -6110,23 +6110,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.51881442</v>
       </c>
       <c r="D40" t="n">
-        <v>275.49</v>
+        <v>294.33</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>113.18</v>
+        <v>113.05</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>22</v>
+        <v>17.11</v>
       </c>
     </row>
     <row r="41">
@@ -6144,16 +6144,16 @@
         <v>1.73400968</v>
       </c>
       <c r="D41" t="n">
-        <v>86.92</v>
+        <v>86.88</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.56</v>
+        <v>111.53</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>10.03</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42">
@@ -6174,13 +6174,13 @@
         <v>39.46</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>111.42</v>
+        <v>111.45</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3.19</v>
+        <v>3.22</v>
       </c>
     </row>
     <row r="43">
@@ -6198,16 +6198,16 @@
         <v>0.37810738</v>
       </c>
       <c r="D43" t="n">
-        <v>394.55</v>
+        <v>394.31</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.42</v>
+        <v>110.38</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>14.91</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="44">
@@ -6218,23 +6218,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.76637723</v>
       </c>
       <c r="D44" t="n">
-        <v>108.6</v>
+        <v>53.11</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>108.59</v>
+        <v>108.77</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>112.48</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>11.91</v>
+        <v>-3.71</v>
       </c>
     </row>
     <row r="45">
@@ -6252,16 +6252,16 @@
         <v>0.80409618</v>
       </c>
       <c r="D45" t="n">
-        <v>182.25</v>
+        <v>182.27</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>108.47</v>
+        <v>108.51</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>20.03</v>
+        <v>20.07</v>
       </c>
     </row>
     <row r="46">
@@ -6272,23 +6272,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.40867246</v>
       </c>
       <c r="D46" t="n">
-        <v>346.71</v>
+        <v>358.33</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>108.44</v>
+        <v>108.42</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>101.39</v>
+        <v>92.83</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>7.05</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="47">
@@ -6299,23 +6299,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.42255419</v>
       </c>
       <c r="D47" t="n">
-        <v>84.09</v>
+        <v>345.91</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>108.43</v>
+        <v>108.21</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>11.75</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="48">
@@ -6326,23 +6326,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.40867246</v>
+        <v>11.40066159</v>
       </c>
       <c r="D48" t="n">
-        <v>357.75</v>
+        <v>12.82</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>108.21</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>92.83</v>
+        <v>106.15</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>15.38</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="49">
@@ -6353,23 +6353,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.35094641</v>
       </c>
       <c r="D49" t="n">
-        <v>52.84</v>
+        <v>108.07</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>108.19</v>
+        <v>108.09</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>112.48</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-4.29</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="50">
@@ -6380,23 +6380,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.74206342</v>
       </c>
       <c r="D50" t="n">
-        <v>233.61</v>
+        <v>83.79000000000001</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>107.97</v>
+        <v>108.07</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>108.77</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>-0.8</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="51">
@@ -6407,23 +6407,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.62445608</v>
       </c>
       <c r="D51" t="n">
-        <v>12.79</v>
+        <v>233.56</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>107.93</v>
+        <v>107.98</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>106.15</v>
+        <v>108.77</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1.78</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="52">
@@ -6441,16 +6441,16 @@
         <v>0.61215748</v>
       </c>
       <c r="D52" t="n">
-        <v>237.16</v>
+        <v>236.81</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>107.46</v>
+        <v>107.32</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>88.09</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>19.37</v>
+        <v>19.23</v>
       </c>
     </row>
     <row r="53">
@@ -6461,23 +6461,23 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.1285649</v>
       </c>
       <c r="D53" t="n">
-        <v>211.73</v>
+        <v>1126.8</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>107.34</v>
+        <v>107.25</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>98.89</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>17.88</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="54">
@@ -6488,23 +6488,23 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.68495686</v>
       </c>
       <c r="D54" t="n">
-        <v>1126.41</v>
+        <v>211.15</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>107.19</v>
+        <v>107.07</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>98.89</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>17.61</v>
       </c>
     </row>
     <row r="55">
@@ -6522,16 +6522,16 @@
         <v>0.90543241</v>
       </c>
       <c r="D55" t="n">
-        <v>159.41</v>
+        <v>159.56</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>106.83</v>
+        <v>106.96</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>92.27</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>14.56</v>
+        <v>14.69</v>
       </c>
     </row>
     <row r="56">
@@ -6549,16 +6549,16 @@
         <v>0.50675322</v>
       </c>
       <c r="D56" t="n">
-        <v>283.93</v>
+        <v>282.67</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>106.5</v>
+        <v>106.05</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>9.82</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="57">
@@ -6576,16 +6576,16 @@
         <v>1.17949395</v>
       </c>
       <c r="D57" t="n">
-        <v>121.97</v>
+        <v>121.37</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>106.48</v>
+        <v>105.98</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>7.76</v>
+        <v>7.26</v>
       </c>
     </row>
     <row r="58">
@@ -6603,16 +6603,16 @@
         <v>5.691347</v>
       </c>
       <c r="D58" t="n">
-        <v>25.12</v>
+        <v>25.13</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105.82</v>
+        <v>105.89</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-347.14</v>
+        <v>-347.07</v>
       </c>
     </row>
     <row r="59">
@@ -6630,16 +6630,16 @@
         <v>13.30225117</v>
       </c>
       <c r="D59" t="n">
-        <v>10.69</v>
+        <v>10.7</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>105.25</v>
+        <v>105.38</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-1.71</v>
+        <v>-1.58</v>
       </c>
     </row>
     <row r="60">
@@ -6657,16 +6657,16 @@
         <v>1.59010207</v>
       </c>
       <c r="D60" t="n">
-        <v>88.91</v>
+        <v>88.7</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>104.64</v>
+        <v>104.42</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>14.98</v>
+        <v>14.76</v>
       </c>
     </row>
     <row r="61">
@@ -6677,23 +6677,23 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="D61" t="n">
-        <v>121.68</v>
+        <v>61.73</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.87</v>
+        <v>104.01</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>89.53</v>
+        <v>106.15</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>14.34</v>
+        <v>-2.14</v>
       </c>
     </row>
     <row r="62">
@@ -6704,23 +6704,23 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.1533463</v>
       </c>
       <c r="D62" t="n">
-        <v>61.56</v>
+        <v>121.4</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>103.7</v>
+        <v>103.66</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>106.15</v>
+        <v>89.53</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-2.45</v>
+        <v>14.13</v>
       </c>
     </row>
     <row r="63">
@@ -6738,7 +6738,7 @@
         <v>0.235295</v>
       </c>
       <c r="D63" t="n">
-        <v>593.27</v>
+        <v>593.09</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>103.32</v>
@@ -6765,16 +6765,16 @@
         <v>1.85908491</v>
       </c>
       <c r="D64" t="n">
-        <v>74.08</v>
+        <v>74.15000000000001</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101.94</v>
+        <v>102.06</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-3.04</v>
+        <v>-2.92</v>
       </c>
     </row>
     <row r="65">
@@ -6785,23 +6785,23 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.6214908</v>
       </c>
       <c r="D65" t="n">
-        <v>121.44</v>
+        <v>218.24</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>100.49</v>
+        <v>100.42</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>105.36</v>
+        <v>107.82</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-4.87</v>
+        <v>-7.4</v>
       </c>
     </row>
     <row r="66">
@@ -6812,23 +6812,23 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.11796351</v>
       </c>
       <c r="D66" t="n">
-        <v>218.21</v>
+        <v>120.96</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>100.38</v>
+        <v>100.12</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>107.82</v>
+        <v>105.36</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-7.44</v>
+        <v>-5.24</v>
       </c>
     </row>
     <row r="67">
@@ -6839,23 +6839,23 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.10445851</v>
       </c>
       <c r="D67" t="n">
-        <v>116.14</v>
+        <v>1291.97</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>100.2</v>
+        <v>99.91</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>92.77</v>
+        <v>88.89</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>7.43</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="68">
@@ -6866,23 +6866,23 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>1289.73</v>
+        <v>115.58</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>99.72</v>
+        <v>99.73999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>88.89</v>
+        <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>10.83</v>
+        <v>6.97</v>
       </c>
     </row>
     <row r="69">
@@ -6900,16 +6900,16 @@
         <v>0.97307689</v>
       </c>
       <c r="D69" t="n">
-        <v>137.48</v>
+        <v>137.37</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>99.02</v>
+        <v>98.95999999999999</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-12.42</v>
+        <v>-12.48</v>
       </c>
     </row>
     <row r="70">
@@ -6927,16 +6927,16 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D70" t="n">
-        <v>145.99</v>
+        <v>145.64</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>99.02</v>
+        <v>98.81</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-0.83</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="71">
@@ -6954,16 +6954,16 @@
         <v>1.17308322</v>
       </c>
       <c r="D71" t="n">
-        <v>111.8</v>
+        <v>111.93</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>97.06999999999999</v>
+        <v>97.20999999999999</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-13.38</v>
+        <v>-13.24</v>
       </c>
     </row>
     <row r="72">
@@ -6981,16 +6981,16 @@
         <v>0.93456659</v>
       </c>
       <c r="D72" t="n">
-        <v>135.56</v>
+        <v>135.34</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>93.77</v>
+        <v>93.64</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>5.39</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="73">
@@ -7008,16 +7008,16 @@
         <v>1.84694851</v>
       </c>
       <c r="D73" t="n">
-        <v>67.06999999999999</v>
+        <v>66.8</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>91.69</v>
+        <v>91.34</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-18.84</v>
+        <v>-19.19</v>
       </c>
     </row>
     <row r="74">
@@ -7035,16 +7035,16 @@
         <v>0.63221571</v>
       </c>
       <c r="D74" t="n">
-        <v>113.67</v>
+        <v>113.78</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>53.19</v>
+        <v>53.26</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>5.32</v>
+        <v>5.39</v>
       </c>
     </row>
     <row r="75">
@@ -7062,16 +7062,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D75" t="n">
-        <v>271.61</v>
+        <v>272.05</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>48.72</v>
+        <v>48.81</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>-3.39</v>
+        <v>-3.3</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43952.78</v>
+        <v>43867.51</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43895.43</v>
+        <v>43810.16</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37878.99</v>
+        <v>37880.19</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6016.44</v>
+        <v>5929.97</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1588331684662131</v>
+        <v>0.1565454133149807</v>
       </c>
     </row>
     <row r="9">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>20.46</v>
+        <v>21.66</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-10 19:32:21</t>
+          <t>2026-08-11 19:32:40</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>110.84</v>
+        <v>110.74</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7093.76</v>
+        <v>7087.36</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1616833138041059</v>
+        <v>0.1618533332054467</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1047.99</v>
+        <v>1041.59</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1733426842238457</v>
+        <v>0.1722840928450801</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.614</v>
+        <v>14.646</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4238.06</v>
+        <v>4247.34</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0965952590587543</v>
+        <v>0.09699607981770672</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>807.35</v>
+        <v>816.63</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2353302960611652</v>
+        <v>0.2380352754969088</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1526.4</v>
+        <v>1524.2</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2692.47</v>
+        <v>2688.58</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06136766283580793</v>
+        <v>0.0613988332170935</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1496.51</v>
+        <v>1492.62</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.251304391451219</v>
+        <v>1.248051774306833</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.69</v>
+        <v>24.7</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2102.09</v>
+        <v>2103.11</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.0479115274712526</v>
+        <v>0.04802851324014965</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>176.28</v>
+        <v>177.3</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.09153550973356665</v>
+        <v>0.09206515699887322</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-9.32</v>
+        <v>-9.17</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>219.07</v>
+        <v>217.83</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1772.06</v>
+        <v>1762.17</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04038937503661017</v>
+        <v>0.04024250047614936</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>519.38</v>
+        <v>509.49</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4146150652999968</v>
+        <v>0.4067199923364307</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-38.56</v>
+        <v>-38.47</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>475.28</v>
+        <v>475.42</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1759.34</v>
+        <v>1760.01</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04009945660807746</v>
+        <v>0.0401931727716552</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-139.21</v>
+        <v>-138.54</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.07332437913144242</v>
+        <v>-0.07297147823338863</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-10.8</v>
+        <v>-10.64</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>79.71079663</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>123.83</v>
+        <v>120.77</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1724.08</v>
+        <v>1681.61</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.03929579907741209</v>
+        <v>0.03840275979371884</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>604.08</v>
+        <v>561.61</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.5393571428571429</v>
+        <v>0.5014375</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-10.19</v>
+        <v>-10.1</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>1.15856288</v>
@@ -1111,22 +1111,22 @@
         <v>3299</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3298</v>
+        <v>3356</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1649.5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1649</v>
+        <v>1678</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03758455099453189</v>
+        <v>0.03832031858389295</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-0.5</v>
+        <v>28.5</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.0003031221582297666</v>
+        <v>0.0172779630190967</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>213.75</v>
+        <v>211.37</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1519.18</v>
+        <v>1502.39</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03462565080647238</v>
+        <v>0.03430993053471688</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-476.88</v>
+        <v>-493.67</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2389106539883571</v>
+        <v>-0.2473222247828222</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-16.31</v>
+        <v>-16.15</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>158.28</v>
+        <v>157.28</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1474.4</v>
+        <v>1465.21</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03360501030099322</v>
+        <v>0.03346085458421084</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-397.44</v>
+        <v>-406.63</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.2123258398153688</v>
+        <v>-0.2172354474741431</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-87.75</v>
+        <v>-87.59999999999999</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1257,114 +1257,114 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UBS Group</t>
+          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CH0244767585</t>
+          <t>IE00BMD8KM66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>37.05</v>
+        <v>113.04005874</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>43.83</v>
+        <v>119</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1401.5</v>
+        <v>1401.09</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03194344949595903</v>
+        <v>0.03199655254154146</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>173.16</v>
+        <v>57.3</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1409707410000489</v>
+        <v>0.04264059116379791</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-43.64</v>
+        <v>-12.87</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-07-16</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
+          <t>UBS Group</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>IE00BMD8KM66</t>
+          <t>CH0244767585</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>113.04005874</v>
+        <v>37.05</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>118.96</v>
+        <v>43.65</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1400.51</v>
+        <v>1394.25</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.03192088508996474</v>
+        <v>0.03184034814397661</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>56.72</v>
+        <v>165.91</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.04220897610489734</v>
+        <v>0.1350684663855284</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-12.98</v>
+        <v>-44.9</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -1396,25 +1396,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>437.7</v>
+        <v>435.7</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1205.04</v>
+        <v>1199.73</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02746566848420297</v>
+        <v>0.02739811431147431</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>290.55</v>
+        <v>285.24</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.3177180723682053</v>
+        <v>0.3119115572614244</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>-4.02</v>
+        <v>-3.87</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>114.65</v>
+        <v>113.8</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1162.97</v>
+        <v>1154.34</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02650679519109203</v>
+        <v>0.02636154741008997</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>555.78</v>
+        <v>547.15</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.9153312801594228</v>
+        <v>0.9011182661111018</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,22 +1510,22 @@
         <v>470.9125</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>711.8</v>
+        <v>707.4</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1138.88</v>
+        <v>1131.84</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02595772797856427</v>
+        <v>0.02584771715494243</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>385.42</v>
+        <v>378.38</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.5115334589759244</v>
+        <v>0.5021898972739096</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>335.22</v>
+        <v>335.08</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1087.37</v>
+        <v>1087</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.0247836950969825</v>
+        <v>0.02482371054868393</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>445.38</v>
+        <v>445.01</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.693749123818128</v>
+        <v>0.6931727908534401</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-32.58</v>
+        <v>-32.54</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>47.47</v>
+        <v>47.33</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>702.88</v>
+        <v>700.86</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01602027240936117</v>
+        <v>0.0160054698943428</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-164.7</v>
+        <v>-166.72</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.189838401069642</v>
+        <v>-0.1921667166140298</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-11.15</v>
+        <v>-11.09</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>504.83</v>
+        <v>503.04</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>697.05</v>
+        <v>694.63</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01588739312961701</v>
+        <v>0.0158631960059175</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>162.67</v>
+        <v>160.25</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.3044088476365133</v>
+        <v>0.2998802350387365</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-24.24</v>
+        <v>-24.2</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,25 +1738,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>307.13</v>
+        <v>304.64</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>695.76</v>
+        <v>690.1799999999999</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01585799102483657</v>
+        <v>0.01576157179989942</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>204.71</v>
+        <v>199.13</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.4168821912228897</v>
+        <v>0.4055187862743102</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-20.15</v>
+        <v>-20.1</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0.46065664</v>
@@ -1770,114 +1770,114 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US6311031081</t>
+          <t>IE00B43HR379</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>65</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>77.20222067</v>
+        <v>1019.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>95.79000000000001</v>
+        <v>1001</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>652.15</v>
+        <v>650.65</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01486401754462339</v>
+        <v>0.01485882913385575</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>102.97</v>
+        <v>-12.03</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.1874977238792382</v>
+        <v>-0.01815355827850546</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-23.58</v>
+        <v>0</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IE00B43HR379</t>
+          <t>US6311031081</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>65</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1019.5</v>
+        <v>77.20222067</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>999.25</v>
+        <v>95.22</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>649.51</v>
+        <v>648.33</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01480384579530528</v>
+        <v>0.01480584752532498</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-13.17</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.01987384559666808</v>
+        <v>0.1805418988309844</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>-23.53</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-09-26</t>
         </is>
       </c>
     </row>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>337.85</v>
+        <v>340.95</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>582.8</v>
+        <v>588.2</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01328336950855863</v>
+        <v>0.01343266471456843</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>93.53</v>
+        <v>98.93000000000001</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.1911623439000961</v>
+        <v>0.2021991947186625</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-31.07</v>
+        <v>-31.02</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.8225</v>
+        <v>3.817</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>535.15</v>
+        <v>534.38</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01219731501802531</v>
+        <v>0.01220358274425549</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-3.22</v>
+        <v>-3.99</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.005981016772851385</v>
+        <v>-0.007411259914185412</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>355.28</v>
+        <v>344.03</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>526.0599999999999</v>
+        <v>509.44</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.011990132744805</v>
+        <v>0.01163403045254971</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>118.14</v>
+        <v>101.52</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2896156109040988</v>
+        <v>0.2488723279074328</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-8.98</v>
+        <v>-8.949999999999999</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>236.3</v>
+        <v>238.93</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>194.22</v>
+        <v>196.4</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.00442672619415281</v>
+        <v>0.004485167204932404</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-2.3</v>
+        <v>-0.12</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.01170364339507429</v>
+        <v>-0.0006106248727864848</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.83</v>
+        <v>-1.81</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2137,25 +2137,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>252.24</v>
+        <v>250.42</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>130.72</v>
+        <v>129.79</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002979413284417956</v>
+        <v>0.002964001280693364</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>11.96</v>
+        <v>11.03</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.1007073088582014</v>
+        <v>0.09287638935668574</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-1.83</v>
+        <v>-1.82</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0</v>
@@ -2194,25 +2194,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>271.91</v>
+        <v>270.81</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>127.67</v>
+        <v>127.17</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002909896680092108</v>
+        <v>0.002904168602093961</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>27.82</v>
+        <v>27.32</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2786179268903355</v>
+        <v>0.2736104156234352</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0.63422137</v>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>350.55601106</v>
+        <v>91.20399179</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>402.98</v>
+        <v>109.93</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>109.16</v>
+        <v>105.28</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>125.33</v>
+        <v>126.81</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002856562629560147</v>
+        <v>0.0028959473180116</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>16.17</v>
+        <v>21.53</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1481311835837303</v>
+        <v>0.2045022796352584</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.42010405</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>91.20399179</v>
+        <v>350.55601106</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>108.3</v>
+        <v>399.45</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>105.28</v>
+        <v>109.16</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>124.92</v>
+        <v>124.25</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.00284721777455241</v>
+        <v>0.002837484853425923</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>19.64</v>
+        <v>15.09</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1865501519756839</v>
+        <v>0.1382374496152437</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.12</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.42010405</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>2.70722512</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>57.56703616</v>
+        <v>53.65641702</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>65.12</v>
+        <v>59.08</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>106.81</v>
+        <v>107.64</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>120.73</v>
+        <v>118.42</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002751717914839196</v>
+        <v>0.002704345725092135</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>13.92</v>
+        <v>10.78</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.130324875947945</v>
+        <v>0.1001486436269045</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.09</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>2.70722512</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>1.32559468</v>
+        <v>2.50421091</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>121.66614911</v>
+        <v>57.56703616</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>120.28</v>
+        <v>63.75</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>119.73</v>
+        <v>106.81</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>118.04</v>
+        <v>118.2</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002690406549056728</v>
+        <v>0.002699321607041804</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>-1.69</v>
+        <v>11.39</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>-0.01411509229098806</v>
+        <v>0.106637955247636</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>1.32559468</v>
+        <v>2.50421091</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
         <v>322.35040597</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>362.33</v>
+        <v>364.24</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>116.91</v>
+        <v>117.54</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002664651216962233</v>
+        <v>0.002684249252890809</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>12.87</v>
+        <v>13.5</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1237024221453287</v>
+        <v>0.129757785467128</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>0.43583007</v>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>2.70722512</v>
+        <v>3.30858696</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>53.65641702</v>
+        <v>45.93199509</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>58.16</v>
+        <v>47.7</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>107.64</v>
+        <v>112.71</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>116.57</v>
+        <v>116.85</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002656901825004598</v>
+        <v>0.00266849179173295</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>8.93</v>
+        <v>4.14</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.0829617242660721</v>
+        <v>0.03673143465531008</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.19</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>2.70722512</v>
+        <v>3.30858696</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2593,25 +2593,25 @@
         <v>509.16500577</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>559.92</v>
+        <v>562.76</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>116.23</v>
+        <v>116.83</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002649152433046963</v>
+        <v>0.002668035053728375</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>10.48</v>
+        <v>11.08</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.09910165484633571</v>
+        <v>0.1047754137115839</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>0.28038062</v>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>3.30858696</v>
+        <v>1.32559468</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>45.93199509</v>
+        <v>121.66614911</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>47.35</v>
+        <v>117.5</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>112.71</v>
+        <v>119.73</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>115.98</v>
+        <v>115.32</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002643454350725172</v>
+        <v>0.002633551334382917</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>3.27</v>
+        <v>-4.41</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.02901250998136811</v>
+        <v>-0.03683287396642446</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.32</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>3.30858696</v>
+        <v>1.32559468</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>228.00445932</v>
+        <v>188.32884805</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>259.91</v>
+        <v>196.49</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>110.41</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>113.88</v>
+        <v>115.02</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.00259559045922213</v>
+        <v>0.002626700264314283</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>14.03</v>
+        <v>4.61</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.1405107661492238</v>
+        <v>0.04175346436011231</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.17</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.59183053</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>188.32884805</v>
+        <v>228.00445932</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>194.3</v>
+        <v>259.87</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>110.41</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>113.72</v>
+        <v>113.87</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002591943686536184</v>
+        <v>0.002600437829051186</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>3.31</v>
+        <v>14.02</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.02997916855357305</v>
+        <v>0.1404106159238858</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.18</v>
+        <v>0.06</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.59183053</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.51881442</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>221.99877812</v>
+        <v>249.91595261</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>275.37</v>
+        <v>293.11</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.16</v>
+        <v>112.59</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002579179982135372</v>
+        <v>0.002571206596758348</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>21.98</v>
+        <v>16.65</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.2410616363237552</v>
+        <v>0.173545966228893</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.51881442</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.5550481</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>249.91595261</v>
+        <v>221.99877812</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>294.33</v>
+        <v>272.41</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>95.94</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>113.05</v>
+        <v>111.95</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002576672825913784</v>
+        <v>0.002556590980611928</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>17.11</v>
+        <v>20.77</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1783406295601418</v>
+        <v>0.2277911822768151</v>
       </c>
       <c r="M40" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.5550481</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2935,25 +2935,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>86.88</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.53</v>
+        <v>111.14</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002542028485397296</v>
+        <v>0.002538093091426616</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>10</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.09849305623953511</v>
+        <v>0.09465182704619324</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>1.73400968</v>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.90543241</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>38.28159448</v>
+        <v>137.713206</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>39.46</v>
+        <v>164.28</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>108.23</v>
+        <v>92.27</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>111.45</v>
+        <v>110.13</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002540205099054323</v>
+        <v>0.002515027822195548</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>3.22</v>
+        <v>17.86</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.02975145523422341</v>
+        <v>0.1935623713016148</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.11</v>
+        <v>0.05</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.90543241</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.40867246</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>341.38450299</v>
+        <v>306.99401668</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>394.31</v>
+        <v>362.38</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.38</v>
+        <v>109.65</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002515817306717058</v>
+        <v>0.002504066110085734</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>14.87</v>
+        <v>16.82</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.1556905036121872</v>
+        <v>0.1811914251858236</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.40867246</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.37810738</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>54.82621761</v>
+        <v>341.38450299</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>53.11</v>
+        <v>391.6</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>112.48</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>108.77</v>
+        <v>109.63</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002479121656564726</v>
+        <v>0.002503609372081158</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>-3.71</v>
+        <v>14.12</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>-0.03298364153627311</v>
+        <v>0.1478379227306041</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.2</v>
+        <v>0.06</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.37810738</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>148.63893521</v>
+        <v>54.82621761</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>182.27</v>
+        <v>53.52</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>88.44</v>
+        <v>112.48</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>108.51</v>
+        <v>109.62</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002473195650950064</v>
+        <v>0.002503381003078871</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>20.07</v>
+        <v>-2.86</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.2269335142469471</v>
+        <v>-0.02542674253200569</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.18</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.1285649</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>306.99401668</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>358.33</v>
+        <v>1145.78</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>92.83</v>
+        <v>98.89</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>108.42</v>
+        <v>109.07</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002471144341314219</v>
+        <v>0.002490820707953041</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>15.59</v>
+        <v>10.18</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1679413982548745</v>
+        <v>0.1029426635655779</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.1285649</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3277,25 +3277,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>345.91</v>
+        <v>348.53</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>108.21</v>
+        <v>109.04</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002466357952163915</v>
+        <v>0.002490135600946178</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>6.82</v>
+        <v>7.65</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.06726501627379426</v>
+        <v>0.0754512279317487</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>0.42255419</v>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.61215748</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>12.56856884</v>
+        <v>194.45976548</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>12.82</v>
+        <v>240.29</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>106.15</v>
+        <v>88.09</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>108.21</v>
+        <v>108.91</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002466357952163915</v>
+        <v>0.002487166803916437</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.06</v>
+        <v>20.82</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.01940650023551578</v>
+        <v>0.2363491883301169</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.06</v>
+        <v>0.05</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.61215748</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1.35094641</v>
+        <v>1.74206342</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>96.717382</v>
+        <v>74.99726962</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>108.07</v>
+        <v>84.31</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>108.09</v>
+        <v>108.75</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002463622872649455</v>
+        <v>0.002483512899879832</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>11.41</v>
+        <v>12.07</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.118018204385602</v>
+        <v>0.1248448489863467</v>
       </c>
       <c r="M49" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>1.35094641</v>
+        <v>1.74206342</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>1.74206342</v>
+        <v>11.40066159</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>74.99726962</v>
+        <v>12.56856884</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>83.79000000000001</v>
+        <v>12.87</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>108.07</v>
+        <v>108.64</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002463167026063712</v>
+        <v>0.002481000840854666</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>11.39</v>
+        <v>2.49</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1178113363673976</v>
+        <v>0.02345737164390014</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>1.74206342</v>
+        <v>11.40066159</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.35094641</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>235.02053179</v>
+        <v>96.717382</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>233.56</v>
+        <v>108.25</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>108.77</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>107.98</v>
+        <v>108.28</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002461115716427867</v>
+        <v>0.002472779556772305</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>-0.79</v>
+        <v>11.6</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-0.00726303208605314</v>
+        <v>0.1199834505585436</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.11</v>
+        <v>0.06</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.35094641</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.80409618</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>194.45976548</v>
+        <v>148.63893521</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>236.81</v>
+        <v>181.63</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>88.09</v>
+        <v>88.44</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>107.32</v>
+        <v>108.13</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.00244607277909834</v>
+        <v>0.002469354021737988</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>19.23</v>
+        <v>19.69</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.2182994664547622</v>
+        <v>0.222636815920398</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.80409618</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.62445608</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>235.02053179</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>1126.8</v>
+        <v>233.54</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>98.89</v>
+        <v>108.77</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>107.25</v>
+        <v>107.98</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002444477316048238</v>
+        <v>0.002465928486703671</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>-0.79</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.08453837597330366</v>
+        <v>-0.00726303208605314</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.11</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.62445608</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.68495686</v>
+        <v>3.81488812</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>176.50746647</v>
+        <v>38.28159448</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>211.15</v>
+        <v>38.1</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>108.23</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>107.07</v>
+        <v>107.62</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002440374696776549</v>
+        <v>0.00245770720262131</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>17.61</v>
+        <v>-0.61</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.1968477531857813</v>
+        <v>-0.00563614524623487</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.68495686</v>
+        <v>3.81488812</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.90543241</v>
+        <v>13.30225117</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>137.713206</v>
+        <v>10.85229847</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>159.56</v>
+        <v>10.87</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>92.27</v>
+        <v>106.96</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>106.96</v>
+        <v>107.06</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002437867540554961</v>
+        <v>0.002444918538493194</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>14.69</v>
+        <v>0.1</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1592066760593909</v>
+        <v>0.0009349289454001497</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.05</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.90543241</v>
+        <v>13.30225117</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.68495686</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>257.81779936</v>
+        <v>176.50746647</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>282.67</v>
+        <v>210.85</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>106.05</v>
+        <v>106.93</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002417126520903643</v>
+        <v>0.002441949741463452</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>17.47</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.09691766652875464</v>
+        <v>0.1952828079588643</v>
       </c>
       <c r="M56" s="2" t="n">
         <v>0.05</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.68495686</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.50675322</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>113.12478542</v>
+        <v>257.81779936</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>121.37</v>
+        <v>284.57</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>98.72</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>105.98</v>
+        <v>106.77</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002415531057853541</v>
+        <v>0.002438295837426847</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>7.26</v>
+        <v>10.09</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.07354132901134522</v>
+        <v>0.1043649151841125</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.50675322</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,55 +3898,55 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.17949395</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>105.04894536</v>
+        <v>113.12478542</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>25.13</v>
+        <v>121.62</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>452.96</v>
+        <v>98.72</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>105.89</v>
+        <v>106.21</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002413479748217697</v>
+        <v>0.00242550717329873</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-347.07</v>
+        <v>7.49</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.7662265983751325</v>
+        <v>0.07587115072933549</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-10.33</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0</v>
+        <v>1.17949395</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,38 +3955,38 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>13.30225117</v>
+        <v>5.691347</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>10.85229847</v>
+        <v>105.04894536</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>10.7</v>
+        <v>25.08</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>106.96</v>
+        <v>452.96</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>105.38</v>
+        <v>105.68</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002401855660281243</v>
+        <v>0.002413403616177477</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-1.58</v>
+        <v>-347.28</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.01477187733732237</v>
+        <v>-0.7666902154715648</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.08</v>
+        <v>-10.3</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
@@ -4018,25 +4018,25 @@
         <v>76.19636644000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>88.7</v>
+        <v>89.05</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>104.42</v>
+        <v>104.84</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002379975024165567</v>
+        <v>0.002394220619985302</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>14.76</v>
+        <v>15.18</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.1646219049743475</v>
+        <v>0.1693062681240241</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>1.59010207</v>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>FB_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US30303M1027</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,55 +4069,55 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.235295</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>62.95787236</v>
+        <v>627.34014747</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>61.73</v>
+        <v>601.74</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>106.15</v>
+        <v>119.82</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>104.01</v>
+        <v>104.83</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.00237063016915783</v>
+        <v>0.002393992250983014</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-2.14</v>
+        <v>-14.99</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.02016015073009892</v>
+        <v>-0.1251043231513938</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-10.53</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-01-23</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>104.90344487</v>
+        <v>62.95787236</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>121.4</v>
+        <v>61.84</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>89.53</v>
+        <v>106.15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>103.66</v>
+        <v>104.2</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002362652853907323</v>
+        <v>0.002379605003838883</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>14.13</v>
+        <v>-1.95</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.1578241930079303</v>
+        <v>-0.01837023080546396</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FB_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US30303M1027</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,55 +4183,55 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.235295</v>
+        <v>1.1533463</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>627.34014747</v>
+        <v>104.90344487</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>593.09</v>
+        <v>121.59</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>119.82</v>
+        <v>89.53</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>103.32</v>
+        <v>103.83</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002354903461949687</v>
+        <v>0.002371155350754234</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-16.5</v>
+        <v>14.3</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.1377065598397597</v>
+        <v>0.1597229978778063</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-10.53</v>
+        <v>0.05</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0</v>
+        <v>1.1533463</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>76.24181082</v>
+        <v>127.23134407</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>74.15000000000001</v>
+        <v>123.17</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>104.98</v>
+        <v>105.36</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>102.06</v>
+        <v>101.95</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002326185127047862</v>
+        <v>0.002328221978324128</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-2.92</v>
+        <v>-3.41</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.02781482187083254</v>
+        <v>-0.03236522399392559</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.05</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4303,25 +4303,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>218.24</v>
+        <v>221.14</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>100.42</v>
+        <v>101.76</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002288805707016915</v>
+        <v>0.002323882967280659</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-7.4</v>
+        <v>-6.06</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.06863290669634577</v>
+        <v>-0.0562047857540345</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>0.6214908</v>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.85908491</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>127.23134407</v>
+        <v>76.24181082</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>120.96</v>
+        <v>73.61</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>105.36</v>
+        <v>104.98</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>100.12</v>
+        <v>101.32</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002281968008230766</v>
+        <v>0.002313834731179996</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-5.24</v>
+        <v>-3.66</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.04973424449506454</v>
+        <v>-0.03486378357782435</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.85908491</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4417,25 +4417,25 @@
         <v>1150.02597682</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>1291.97</v>
+        <v>1300.25</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>99.91</v>
+        <v>100.56</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002277181619080461</v>
+        <v>0.002296478687006123</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>11.02</v>
+        <v>11.67</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.1239734503318708</v>
+        <v>0.1312858589267634</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>0.10445851</v>
@@ -4474,25 +4474,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>115.58</v>
+        <v>116.09</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>99.73999999999999</v>
+        <v>100.19</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002273306923101644</v>
+        <v>0.002288029033921475</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>6.97</v>
+        <v>7.42</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.07513204699795192</v>
+        <v>0.07998275304516547</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.16558147</v>
@@ -4531,25 +4531,25 @@
         <v>154.44822659</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>137.37</v>
+        <v>138.12</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>98.95999999999999</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002255528906257656</v>
+        <v>0.002272499941765904</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-12.48</v>
+        <v>-11.93</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.1119885139985643</v>
+        <v>-0.1070531227566403</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>0.97307689</v>
@@ -4588,22 +4588,22 @@
         <v>147.21071381</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>145.64</v>
+        <v>145.08</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>98.81</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002252110056864582</v>
+        <v>0.002247836089518822</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-1.04</v>
+        <v>-1.42</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.01041562343515273</v>
+        <v>-0.014221331997997</v>
       </c>
       <c r="M70" s="2" t="n">
         <v>0.03</v>
@@ -4645,22 +4645,22 @@
         <v>126.99866255</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>111.93</v>
+        <v>112.87</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>97.20999999999999</v>
+        <v>98.03</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002215642330005121</v>
+        <v>0.00223870132942731</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-13.24</v>
+        <v>-12.42</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1198732458125849</v>
+        <v>-0.1124490719782707</v>
       </c>
       <c r="M71" s="2" t="n">
         <v>-0.15</v>
@@ -4702,25 +4702,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>135.34</v>
+        <v>136.03</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>93.64</v>
+        <v>94.13</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.002134273714449949</v>
+        <v>0.002149637418535067</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>5.26</v>
+        <v>5.75</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.05951572754016746</v>
+        <v>0.06505996831862412</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.93456659</v>
@@ -4759,25 +4759,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>66.8</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>91.34</v>
+        <v>91.87</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.002081851357089474</v>
+        <v>0.002098026024018024</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-19.19</v>
+        <v>-18.66</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.173618022256401</v>
+        <v>-0.1688229439971048</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>1.84694851</v>
@@ -4816,22 +4816,22 @@
         <v>102.32267085</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>113.78</v>
+        <v>114.04</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>53.26</v>
+        <v>53.38</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.001213919457834305</v>
+        <v>0.00121903373421228</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>5.39</v>
+        <v>5.51</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.1125966158345519</v>
+        <v>0.1151034050553583</v>
       </c>
       <c r="M74" s="2" t="n">
         <v>0.03</v>
@@ -4873,25 +4873,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>272.05</v>
+        <v>273.04</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>48.81</v>
+        <v>49</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.001112493592506429</v>
+        <v>0.001119008111210223</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>-3.3</v>
+        <v>-3.11</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>-0.06332757628094415</v>
+        <v>-0.05968144310113222</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>0.24236298</v>
@@ -4983,34 +4983,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-10 19:32:21</t>
+          <t>2026-08-11 19:32:40</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43952.78</v>
+        <v>43867.51</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43895.43</v>
+        <v>43810.16</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37878.99</v>
+        <v>37880.19</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6016.44</v>
+        <v>5929.97</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1588331684662131</v>
+        <v>0.1565454133149807</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1251.59</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>77.81</v>
+        <v>79.01000000000001</v>
       </c>
       <c r="J2" t="n">
         <v>74</v>
@@ -5079,7 +5079,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5091,22 +5091,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>110.84</v>
+        <v>110.74</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7093.76</v>
+        <v>7087.36</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1047.99</v>
+        <v>1041.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5118,22 +5118,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.614</v>
+        <v>14.646</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4238.06</v>
+        <v>4247.34</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>807.35</v>
+        <v>816.63</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5145,22 +5145,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1526.4</v>
+        <v>1524.2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2692.47</v>
+        <v>2688.58</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1496.51</v>
+        <v>1492.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5172,22 +5172,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>24.69</v>
+        <v>24.7</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2102.09</v>
+        <v>2103.11</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>176.28</v>
+        <v>177.3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5199,22 +5199,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D6" t="n">
-        <v>219.07</v>
+        <v>217.83</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1772.06</v>
+        <v>1762.17</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>519.38</v>
+        <v>509.49</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5226,22 +5226,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>475.28</v>
+        <v>475.42</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1759.34</v>
+        <v>1760.01</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-139.21</v>
+        <v>-138.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5253,22 +5253,22 @@
         <v>18.80610988</v>
       </c>
       <c r="D8" t="n">
-        <v>123.83</v>
+        <v>120.77</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1724.08</v>
+        <v>1681.61</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>604.08</v>
+        <v>561.61</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5280,22 +5280,22 @@
         <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>3298</v>
+        <v>3356</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1649</v>
+        <v>1678</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1649.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.5</v>
+        <v>28.5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5307,22 +5307,22 @@
         <v>9.6</v>
       </c>
       <c r="D10" t="n">
-        <v>213.75</v>
+        <v>211.37</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1519.18</v>
+        <v>1502.39</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-476.88</v>
+        <v>-493.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5334,76 +5334,76 @@
         <v>12.5822526</v>
       </c>
       <c r="D11" t="n">
-        <v>158.28</v>
+        <v>157.28</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1474.4</v>
+        <v>1465.21</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-397.44</v>
+        <v>-406.63</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="D12" t="n">
-        <v>43.83</v>
+        <v>119</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1401.5</v>
+        <v>1401.09</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>173.16</v>
+        <v>57.3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="D13" t="n">
-        <v>118.96</v>
+        <v>43.65</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1400.51</v>
+        <v>1394.25</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>56.72</v>
+        <v>165.91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5415,22 +5415,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D14" t="n">
-        <v>437.7</v>
+        <v>435.7</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1205.04</v>
+        <v>1199.73</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>290.55</v>
+        <v>285.24</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5442,22 +5442,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D15" t="n">
-        <v>114.65</v>
+        <v>113.8</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1162.97</v>
+        <v>1154.34</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>555.78</v>
+        <v>547.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5469,22 +5469,22 @@
         <v>160</v>
       </c>
       <c r="D16" t="n">
-        <v>711.8</v>
+        <v>707.4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1138.88</v>
+        <v>1131.84</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>385.42</v>
+        <v>378.38</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5496,22 +5496,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>335.22</v>
+        <v>335.08</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1087.37</v>
+        <v>1087</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>445.38</v>
+        <v>445.01</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5523,22 +5523,22 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>47.47</v>
+        <v>47.33</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>702.88</v>
+        <v>700.86</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-164.7</v>
+        <v>-166.72</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5550,22 +5550,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>504.83</v>
+        <v>503.04</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>697.05</v>
+        <v>694.63</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>162.67</v>
+        <v>160.25</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5577,76 +5577,76 @@
         <v>3.05990683</v>
       </c>
       <c r="D20" t="n">
-        <v>307.13</v>
+        <v>304.64</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>695.76</v>
+        <v>690.1799999999999</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>204.71</v>
+        <v>199.13</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>95.79000000000001</v>
+        <v>1001</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>652.15</v>
+        <v>650.65</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>102.97</v>
+        <v>-12.03</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>65</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>999.25</v>
+        <v>95.22</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>649.51</v>
+        <v>648.33</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-13.17</v>
+        <v>99.15000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5658,22 +5658,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>337.85</v>
+        <v>340.95</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>582.8</v>
+        <v>588.2</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>93.53</v>
+        <v>98.93000000000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5685,22 +5685,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.8225</v>
+        <v>3.817</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>535.15</v>
+        <v>534.38</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-3.22</v>
+        <v>-3.99</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5712,22 +5712,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>355.28</v>
+        <v>344.03</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>526.0599999999999</v>
+        <v>509.44</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>118.14</v>
+        <v>101.52</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5739,22 +5739,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>236.3</v>
+        <v>238.93</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>194.22</v>
+        <v>196.4</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-2.3</v>
+        <v>-0.12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5766,22 +5766,22 @@
         <v>0.7</v>
       </c>
       <c r="D27" t="n">
-        <v>252.24</v>
+        <v>250.42</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>130.72</v>
+        <v>129.79</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>11.96</v>
+        <v>11.03</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5793,130 +5793,130 @@
         <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>271.91</v>
+        <v>270.81</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>127.67</v>
+        <v>127.17</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>27.82</v>
+        <v>27.32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.55804584</v>
       </c>
       <c r="D29" t="n">
-        <v>402.98</v>
+        <v>109.93</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>125.33</v>
+        <v>126.81</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>109.16</v>
+        <v>105.28</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>16.17</v>
+        <v>21.53</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.42010405</v>
       </c>
       <c r="D30" t="n">
-        <v>108.3</v>
+        <v>399.45</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>124.92</v>
+        <v>124.25</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>105.28</v>
+        <v>109.16</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>19.64</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>2.70722512</v>
       </c>
       <c r="D31" t="n">
-        <v>65.12</v>
+        <v>59.08</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>120.73</v>
+        <v>118.42</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>106.81</v>
+        <v>107.64</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>13.92</v>
+        <v>10.78</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>1.32559468</v>
+        <v>2.50421091</v>
       </c>
       <c r="D32" t="n">
-        <v>120.28</v>
+        <v>63.75</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>118.04</v>
+        <v>118.2</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>119.73</v>
+        <v>106.81</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>-1.69</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5928,49 +5928,49 @@
         <v>0.43583007</v>
       </c>
       <c r="D33" t="n">
-        <v>362.33</v>
+        <v>364.24</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>116.91</v>
+        <v>117.54</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>12.87</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2.70722512</v>
+        <v>3.30858696</v>
       </c>
       <c r="D34" t="n">
-        <v>58.16</v>
+        <v>47.7</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>116.57</v>
+        <v>116.85</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>107.64</v>
+        <v>112.71</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>8.93</v>
+        <v>4.14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5982,157 +5982,157 @@
         <v>0.28038062</v>
       </c>
       <c r="D35" t="n">
-        <v>559.92</v>
+        <v>562.76</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>116.23</v>
+        <v>116.83</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>10.48</v>
+        <v>11.08</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>3.30858696</v>
+        <v>1.32559468</v>
       </c>
       <c r="D36" t="n">
-        <v>47.35</v>
+        <v>117.5</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>115.98</v>
+        <v>115.32</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>112.71</v>
+        <v>119.73</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>3.27</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="D37" t="n">
-        <v>259.91</v>
+        <v>196.49</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>113.88</v>
+        <v>115.02</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>110.41</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>14.03</v>
+        <v>4.61</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.59183053</v>
       </c>
       <c r="D38" t="n">
-        <v>194.3</v>
+        <v>259.87</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>113.72</v>
+        <v>113.87</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>110.41</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>3.31</v>
+        <v>14.02</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.51881442</v>
       </c>
       <c r="D39" t="n">
-        <v>275.37</v>
+        <v>293.11</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.16</v>
+        <v>112.59</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>21.98</v>
+        <v>16.65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.5550481</v>
       </c>
       <c r="D40" t="n">
-        <v>294.33</v>
+        <v>272.41</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>113.05</v>
+        <v>111.95</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>95.94</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>17.11</v>
+        <v>20.77</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6144,157 +6144,157 @@
         <v>1.73400968</v>
       </c>
       <c r="D41" t="n">
-        <v>86.88</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.53</v>
+        <v>111.14</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>10</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.90543241</v>
       </c>
       <c r="D42" t="n">
-        <v>39.46</v>
+        <v>164.28</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>111.45</v>
+        <v>110.13</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>108.23</v>
+        <v>92.27</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>3.22</v>
+        <v>17.86</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.40867246</v>
       </c>
       <c r="D43" t="n">
-        <v>394.31</v>
+        <v>362.38</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.38</v>
+        <v>109.65</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>14.87</v>
+        <v>16.82</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.37810738</v>
       </c>
       <c r="D44" t="n">
-        <v>53.11</v>
+        <v>391.6</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>108.77</v>
+        <v>109.63</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>112.48</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>-3.71</v>
+        <v>14.12</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="D45" t="n">
-        <v>182.27</v>
+        <v>53.52</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>108.51</v>
+        <v>109.62</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>88.44</v>
+        <v>112.48</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>20.07</v>
+        <v>-2.86</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.1285649</v>
       </c>
       <c r="D46" t="n">
-        <v>358.33</v>
+        <v>1145.78</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>108.42</v>
+        <v>109.07</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>92.83</v>
+        <v>98.89</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>15.59</v>
+        <v>10.18</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6306,346 +6306,346 @@
         <v>0.42255419</v>
       </c>
       <c r="D47" t="n">
-        <v>345.91</v>
+        <v>348.53</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>108.21</v>
+        <v>109.04</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>6.82</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.61215748</v>
       </c>
       <c r="D48" t="n">
-        <v>12.82</v>
+        <v>240.29</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>108.21</v>
+        <v>108.91</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>106.15</v>
+        <v>88.09</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2.06</v>
+        <v>20.82</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1.35094641</v>
+        <v>1.74206342</v>
       </c>
       <c r="D49" t="n">
-        <v>108.07</v>
+        <v>84.31</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>108.09</v>
+        <v>108.75</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>11.41</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1.74206342</v>
+        <v>11.40066159</v>
       </c>
       <c r="D50" t="n">
-        <v>83.79000000000001</v>
+        <v>12.87</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>108.07</v>
+        <v>108.64</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>11.39</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.35094641</v>
       </c>
       <c r="D51" t="n">
-        <v>233.56</v>
+        <v>108.25</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>107.98</v>
+        <v>108.28</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>108.77</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-0.79</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.80409618</v>
       </c>
       <c r="D52" t="n">
-        <v>236.81</v>
+        <v>181.63</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>107.32</v>
+        <v>108.13</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>88.09</v>
+        <v>88.44</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>19.23</v>
+        <v>19.69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.62445608</v>
       </c>
       <c r="D53" t="n">
-        <v>1126.8</v>
+        <v>233.54</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>107.25</v>
+        <v>107.98</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>98.89</v>
+        <v>108.77</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>-0.79</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.68495686</v>
+        <v>3.81488812</v>
       </c>
       <c r="D54" t="n">
-        <v>211.15</v>
+        <v>38.1</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>107.07</v>
+        <v>107.62</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>108.23</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>17.61</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.90543241</v>
+        <v>13.30225117</v>
       </c>
       <c r="D55" t="n">
-        <v>159.56</v>
+        <v>10.87</v>
       </c>
       <c r="E55" s="2" t="n">
+        <v>107.06</v>
+      </c>
+      <c r="F55" s="2" t="n">
         <v>106.96</v>
       </c>
-      <c r="F55" s="2" t="n">
-        <v>92.27</v>
-      </c>
       <c r="G55" s="2" t="n">
-        <v>14.69</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.68495686</v>
       </c>
       <c r="D56" t="n">
-        <v>282.67</v>
+        <v>210.85</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>106.05</v>
+        <v>106.93</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>17.47</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.50675322</v>
       </c>
       <c r="D57" t="n">
-        <v>121.37</v>
+        <v>284.57</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>105.98</v>
+        <v>106.77</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>98.72</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>7.26</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.17949395</v>
       </c>
       <c r="D58" t="n">
-        <v>25.13</v>
+        <v>121.62</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105.89</v>
+        <v>106.21</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>452.96</v>
+        <v>98.72</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-347.07</v>
+        <v>7.49</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>13.30225117</v>
+        <v>5.691347</v>
       </c>
       <c r="D59" t="n">
-        <v>10.7</v>
+        <v>25.08</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>105.38</v>
+        <v>105.68</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>106.96</v>
+        <v>452.96</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-1.58</v>
+        <v>-347.28</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6657,130 +6657,130 @@
         <v>1.59010207</v>
       </c>
       <c r="D60" t="n">
-        <v>88.7</v>
+        <v>89.05</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>104.42</v>
+        <v>104.84</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>14.76</v>
+        <v>15.18</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>FB_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.235295</v>
       </c>
       <c r="D61" t="n">
-        <v>61.73</v>
+        <v>601.74</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>104.01</v>
+        <v>104.83</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>106.15</v>
+        <v>119.82</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-2.14</v>
+        <v>-14.99</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="D62" t="n">
-        <v>121.4</v>
+        <v>61.84</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>103.66</v>
+        <v>104.2</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>89.53</v>
+        <v>106.15</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>14.13</v>
+        <v>-1.95</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>FB_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.235295</v>
+        <v>1.1533463</v>
       </c>
       <c r="D63" t="n">
-        <v>593.09</v>
+        <v>121.59</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>103.32</v>
+        <v>103.83</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>119.82</v>
+        <v>89.53</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-16.5</v>
+        <v>14.3</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="D64" t="n">
-        <v>74.15000000000001</v>
+        <v>123.17</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>102.06</v>
+        <v>101.95</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>104.98</v>
+        <v>105.36</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-2.92</v>
+        <v>-3.41</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6792,49 +6792,49 @@
         <v>0.6214908</v>
       </c>
       <c r="D65" t="n">
-        <v>218.24</v>
+        <v>221.14</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>100.42</v>
+        <v>101.76</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-7.4</v>
+        <v>-6.06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.85908491</v>
       </c>
       <c r="D66" t="n">
-        <v>120.96</v>
+        <v>73.61</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>100.12</v>
+        <v>101.32</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>105.36</v>
+        <v>104.98</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-5.24</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6846,22 +6846,22 @@
         <v>0.10445851</v>
       </c>
       <c r="D67" t="n">
-        <v>1291.97</v>
+        <v>1300.25</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>99.91</v>
+        <v>100.56</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>11.02</v>
+        <v>11.67</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6873,22 +6873,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>115.58</v>
+        <v>116.09</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>99.73999999999999</v>
+        <v>100.19</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>6.97</v>
+        <v>7.42</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6900,22 +6900,22 @@
         <v>0.97307689</v>
       </c>
       <c r="D69" t="n">
-        <v>137.37</v>
+        <v>138.12</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>98.95999999999999</v>
+        <v>99.51000000000001</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-12.48</v>
+        <v>-11.93</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6927,22 +6927,22 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D70" t="n">
-        <v>145.64</v>
+        <v>145.08</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>98.81</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-1.04</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6954,22 +6954,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D71" t="n">
-        <v>111.93</v>
+        <v>112.87</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>97.20999999999999</v>
+        <v>98.03</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-13.24</v>
+        <v>-12.42</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6981,22 +6981,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D72" t="n">
-        <v>135.34</v>
+        <v>136.03</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>93.64</v>
+        <v>94.13</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>5.26</v>
+        <v>5.75</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7008,22 +7008,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D73" t="n">
-        <v>66.8</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>91.34</v>
+        <v>91.87</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-19.19</v>
+        <v>-18.66</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7035,22 +7035,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D74" t="n">
-        <v>113.78</v>
+        <v>114.04</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>53.26</v>
+        <v>53.38</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>5.39</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7062,16 +7062,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D75" t="n">
-        <v>272.05</v>
+        <v>273.04</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>48.81</v>
+        <v>49</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>-3.3</v>
+        <v>-3.11</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43867.51</v>
+        <v>44196.49</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43810.16</v>
+        <v>44139.13</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5929.97</v>
+        <v>6258.94</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1565454133149807</v>
+        <v>0.1652298998500271</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>57.35</v>
+        <v>57.36</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-11 19:32:40</t>
+          <t>2026-08-12 19:34:51</t>
         </is>
       </c>
     </row>
@@ -721,7 +721,7 @@
         <v>7087.36</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1618533332054467</v>
+        <v>0.1606399705527235</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>1041.59</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.646</v>
+        <v>15.134</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4247.34</v>
+        <v>4388.86</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09699607981770672</v>
+        <v>0.09947658100618932</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>816.63</v>
+        <v>958.15</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2380352754969088</v>
+        <v>0.279286211891999</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1524.2</v>
+        <v>1537.8</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2688.58</v>
+        <v>2712.57</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.0613988332170935</v>
+        <v>0.06148229593560947</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1492.62</v>
+        <v>1516.61</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.248051774306833</v>
+        <v>1.268110973611158</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.7</v>
+        <v>24.97</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2103.11</v>
+        <v>2128.4</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04802851324014965</v>
+        <v>0.04824167437867086</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>177.3</v>
+        <v>202.59</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.09206515699887322</v>
+        <v>0.1051972936063267</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-9.17</v>
+        <v>-7.1</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>217.83</v>
+        <v>222.52</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1762.17</v>
+        <v>1802.06</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04024250047614936</v>
+        <v>0.04084495007086431</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>509.49</v>
+        <v>549.38</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4067199923364307</v>
+        <v>0.4385637193856372</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-38.47</v>
+        <v>-37.15</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>475.42</v>
+        <v>482.88</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1760.01</v>
+        <v>1789.56</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.0401931727716552</v>
+        <v>0.04056162882968155</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-138.54</v>
+        <v>-108.99</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.07297147823338863</v>
+        <v>-0.05740696847594216</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-10.64</v>
+        <v>-8.59</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>79.71079663</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>120.77</v>
+        <v>123.69</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1681.61</v>
+        <v>1724.13</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.03840275979371884</v>
+        <v>0.03907861212483452</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>561.61</v>
+        <v>604.13</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.5014375</v>
+        <v>0.5394017857142858</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-10.1</v>
+        <v>-8.9</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>1.15856288</v>
@@ -1111,22 +1111,22 @@
         <v>3299</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3356</v>
+        <v>3322.5</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1649.5</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1678</v>
+        <v>1661.25</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03832031858389295</v>
+        <v>0.03765339295318876</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>28.5</v>
+        <v>11.75</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.0172779630190967</v>
+        <v>0.007123370718399515</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>211.37</v>
+        <v>220.47</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1502.39</v>
+        <v>1568.76</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03430993053471688</v>
+        <v>0.03555704242542929</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-493.67</v>
+        <v>-427.3</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2473222247828222</v>
+        <v>-0.2140717212909432</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-16.15</v>
+        <v>-14.01</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>157.28</v>
+        <v>153.61</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1465.21</v>
+        <v>1432.57</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03346085458421084</v>
+        <v>0.03247020083849488</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-406.63</v>
+        <v>-439.27</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.2172354474741431</v>
+        <v>-0.2346728352850671</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-87.59999999999999</v>
+        <v>-85.67</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>119</v>
+        <v>119.04</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1401.09</v>
+        <v>1403.08</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03199655254154146</v>
+        <v>0.03180178936629651</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>57.3</v>
+        <v>59.29</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.04264059116379791</v>
+        <v>0.04412147731416367</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-12.87</v>
+        <v>-11.43</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1345,19 +1345,19 @@
         <v>1228.34</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1394.25</v>
+        <v>1391.51</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.03184034814397661</v>
+        <v>0.03153954722545775</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>165.91</v>
+        <v>163.17</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.1350684663855284</v>
+        <v>0.1328378136346614</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-44.9</v>
+        <v>-47.23</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,25 +1396,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>435.7</v>
+        <v>438.9</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1199.73</v>
+        <v>1207.67</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02739811431147431</v>
+        <v>0.02737268506713467</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>285.24</v>
+        <v>293.18</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.3119115572614244</v>
+        <v>0.32059399227985</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>-3.87</v>
+        <v>-4.52</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>113.8</v>
+        <v>115.2</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1154.34</v>
+        <v>1168.55</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02636154741008997</v>
+        <v>0.0264860029107291</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>547.15</v>
+        <v>561.36</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.9011182661111018</v>
+        <v>0.924521154827978</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,22 +1510,22 @@
         <v>470.9125</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>707.4</v>
+        <v>714.6</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1131.84</v>
+        <v>1143.36</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02584771715494243</v>
+        <v>0.0259150539454976</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>378.38</v>
+        <v>389.9</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.5021898972739096</v>
+        <v>0.5174793618772064</v>
       </c>
       <c r="M16" s="2" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>335.08</v>
+        <v>333.87</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1087</v>
+        <v>1084.25</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02482371054868393</v>
+        <v>0.02457528446019257</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>445.01</v>
+        <v>442.26</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.6931727908534401</v>
+        <v>0.6888892350348136</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-32.54</v>
+        <v>-31.88</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0</v>
@@ -1624,25 +1624,25 @@
         <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>47.33</v>
+        <v>46.25</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>700.86</v>
+        <v>685.61</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.0160054698943428</v>
+        <v>0.01553983009338495</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-166.72</v>
+        <v>-181.97</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.1921667166140298</v>
+        <v>-0.2097443463427004</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-11.09</v>
+        <v>-10.16</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -1656,17 +1656,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>AAPL_US_EQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>US0378331005</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1675,55 +1675,55 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.8650317</v>
+        <v>3.05990683</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>369.46288902</v>
+        <v>207.87234231</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>503.04</v>
+        <v>301.92</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>534.38</v>
+        <v>491.05</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>694.63</v>
+        <v>684.76</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.0158631960059175</v>
+        <v>0.01552056424898452</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>160.25</v>
+        <v>193.71</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2998802350387365</v>
+        <v>0.3944812137256898</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-24.2</v>
+        <v>-19.59</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3650317</v>
+        <v>0.46065664</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-01-24</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AAPL_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US0378331005</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1732,152 +1732,152 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>3.05990683</v>
+        <v>1.8650317</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>207.87234231</v>
+        <v>369.46288902</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>304.64</v>
+        <v>494.29</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>491.05</v>
+        <v>534.38</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>690.1799999999999</v>
+        <v>683.29</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01576157179989942</v>
+        <v>0.01548724567102143</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>199.13</v>
+        <v>148.91</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.4055187862743102</v>
+        <v>0.2786593809648565</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-20.1</v>
+        <v>-23.65</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.46065664</v>
+        <v>0.3650317</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IE00B43HR379</t>
+          <t>US6311031081</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>65</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1019.5</v>
+        <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1001</v>
+        <v>96</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>650.65</v>
+        <v>654.34</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01485882913385575</v>
+        <v>0.01483107367644216</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-12.03</v>
+        <v>105.16</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.01815355827850546</v>
+        <v>0.1914854874540224</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>-22.97</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-09-26</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>US6311031081</t>
+          <t>IE00B43HR379</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>65</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>77.20222067</v>
+        <v>1019.5</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>95.22</v>
+        <v>1005.5</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>648.33</v>
+        <v>653.58</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01480584752532498</v>
+        <v>0.01481384774497825</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>-9.1</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1805418988309844</v>
+        <v>-0.01373211806603489</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-23.53</v>
+        <v>0</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
@@ -1909,25 +1909,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>340.95</v>
+        <v>343.63</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>588.2</v>
+        <v>593.46</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01343266471456843</v>
+        <v>0.01345118590338564</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>98.93000000000001</v>
+        <v>104.19</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.2021991947186625</v>
+        <v>0.2129499049604513</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-31.02</v>
+        <v>-30.53</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
@@ -1966,22 +1966,22 @@
         <v>3.8455</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.817</v>
+        <v>3.828</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>534.38</v>
+        <v>535.92</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01220358274425549</v>
+        <v>0.01214700156597316</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-3.99</v>
+        <v>-2.45</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.007411259914185412</v>
+        <v>-0.004550773631517359</v>
       </c>
       <c r="M24" s="2" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>269.43</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>344.03</v>
+        <v>343.82</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>509.44</v>
+        <v>509.68</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01163403045254971</v>
+        <v>0.01155225361648232</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>101.52</v>
+        <v>101.76</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2488723279074328</v>
+        <v>0.2494606785644244</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-8.949999999999999</v>
+        <v>-8.52</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>0</v>
@@ -2080,25 +2080,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>238.93</v>
+        <v>235.43</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>196.4</v>
+        <v>193.74</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004485167204932404</v>
+        <v>0.004391252581339829</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-0.12</v>
+        <v>-2.78</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.0006106248727864848</v>
+        <v>-0.01414614288622023</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.81</v>
+        <v>-1.59</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.11022215</v>
@@ -2112,17 +2112,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2131,55 +2131,55 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.7</v>
+        <v>1.55804584</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>225.62857143</v>
+        <v>91.20399179</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>250.42</v>
+        <v>111.04</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>118.76</v>
+        <v>105.28</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>129.79</v>
+        <v>128.23</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002964001280693364</v>
+        <v>0.002906422620549221</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>11.03</v>
+        <v>22.95</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.09287638935668574</v>
+        <v>0.2179901215805471</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-1.82</v>
+        <v>0.04</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0</v>
+        <v>1.55804584</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,55 +2188,55 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.7</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>212.76482689</v>
+        <v>225.62857143</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>270.81</v>
+        <v>243.72</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>118.76</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>127.17</v>
+        <v>126.45</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002904168602093961</v>
+        <v>0.002866077675804797</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>27.32</v>
+        <v>7.69</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2736104156234352</v>
+        <v>0.0647524418996295</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>0.06</v>
+        <v>-1.7</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.63422137</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>91.20399179</v>
+        <v>212.76482689</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>109.93</v>
+        <v>268.17</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>126.81</v>
+        <v>126.06</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.0028959473180116</v>
+        <v>0.002857238053079895</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>21.53</v>
+        <v>26.21</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.2045022796352584</v>
+        <v>0.2624937406109164</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.63422137</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2308,25 +2308,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>399.45</v>
+        <v>394.75</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>124.25</v>
+        <v>122.92</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002837484853425923</v>
+        <v>0.002786067757294786</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>15.09</v>
+        <v>13.76</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1382374496152437</v>
+        <v>0.1260534994503481</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>0.42010405</v>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.70722512</v>
+        <v>2.50421091</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>53.65641702</v>
+        <v>57.56703616</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>59.08</v>
+        <v>63.91</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>107.64</v>
+        <v>106.81</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>118.42</v>
+        <v>118.63</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002704345725092135</v>
+        <v>0.002688831907320862</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>10.78</v>
+        <v>11.82</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1001486436269045</v>
+        <v>0.1106637955247636</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.09</v>
+        <v>0.05</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.70722512</v>
+        <v>2.50421091</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.50421091</v>
+        <v>2.70722512</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>57.56703616</v>
+        <v>53.65641702</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>63.75</v>
+        <v>58.55</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>106.81</v>
+        <v>107.64</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>118.2</v>
+        <v>117.49</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002699321607041804</v>
+        <v>0.002662993010124994</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>11.39</v>
+        <v>9.85</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.106637955247636</v>
+        <v>0.09150873281308064</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.03</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.50421091</v>
+        <v>2.70722512</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.43583007</v>
+        <v>1.32559468</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>322.35040597</v>
+        <v>121.66614911</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>364.24</v>
+        <v>119.12</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>104.04</v>
+        <v>119.73</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>117.54</v>
+        <v>117.04</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002684249252890809</v>
+        <v>0.002652793445442415</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.5</v>
+        <v>-2.69</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.129757785467128</v>
+        <v>-0.02246721790695732</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.19</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.43583007</v>
+        <v>1.32559468</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2536,25 +2536,25 @@
         <v>45.93199509</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>47.7</v>
+        <v>47.68</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>116.85</v>
+        <v>116.93</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.00266849179173295</v>
+        <v>0.002650300218520007</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>4.14</v>
+        <v>4.22</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.03673143465531008</v>
+        <v>0.03744122083222429</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>3.30858696</v>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.43583007</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>509.16500577</v>
+        <v>322.35040597</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>562.76</v>
+        <v>361.92</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>105.75</v>
+        <v>104.04</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>116.83</v>
+        <v>116.91</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002668035053728375</v>
+        <v>0.002649846904534115</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>11.08</v>
+        <v>12.87</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1047754137115839</v>
+        <v>0.1237024221453287</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.09</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.43583007</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.28038062</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>121.66614911</v>
+        <v>509.16500577</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>117.5</v>
+        <v>561.05</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>119.73</v>
+        <v>105.75</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>115.32</v>
+        <v>116.6</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002633551334382917</v>
+        <v>0.002642820537752782</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>-4.41</v>
+        <v>10.85</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>-0.03683287396642446</v>
+        <v>0.1026004728132388</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.32</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.28038062</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>196.49</v>
+        <v>196.71</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>115.02</v>
+        <v>115.27</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002626700264314283</v>
+        <v>0.002612675157690936</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>4.61</v>
+        <v>4.86</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.04175346436011231</v>
+        <v>0.04401775201521602</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.05</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>0.7905852</v>
@@ -2764,25 +2764,25 @@
         <v>228.00445932</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>259.87</v>
+        <v>260.92</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>113.87</v>
+        <v>114.46</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002600437829051186</v>
+        <v>0.002594315941262294</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>14.02</v>
+        <v>14.61</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.1404106159238858</v>
+        <v>0.1463194792188282</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>0.59183053</v>
@@ -2821,25 +2821,25 @@
         <v>249.91595261</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>293.11</v>
+        <v>293.48</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.59</v>
+        <v>112.86</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002571206596758348</v>
+        <v>0.0025580508223909</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>16.65</v>
+        <v>16.92</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.173545966228893</v>
+        <v>0.176360225140713</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>0.51881442</v>
@@ -2878,25 +2878,25 @@
         <v>221.99877812</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>272.41</v>
+        <v>271.84</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>111.95</v>
+        <v>111.84</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002556590980611928</v>
+        <v>0.002534931809110387</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>20.77</v>
+        <v>20.66</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.2277911822768151</v>
+        <v>0.2265847773634569</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>0.5550481</v>
@@ -2935,25 +2935,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>86.56999999999999</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.14</v>
+        <v>111.62</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002538093091426616</v>
+        <v>0.002529945355265571</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>9.609999999999999</v>
+        <v>10.09</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.09465182704619324</v>
+        <v>0.09937949374569092</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.03</v>
+        <v>0.14</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>1.73400968</v>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.40867246</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>137.713206</v>
+        <v>306.99401668</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>164.28</v>
+        <v>365.84</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>92.27</v>
+        <v>92.83</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>110.13</v>
+        <v>110.82</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002515027822195548</v>
+        <v>0.002511812795829874</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>17.86</v>
+        <v>17.99</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.1935623713016148</v>
+        <v>0.1937951093396531</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.05</v>
+        <v>0.17</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.40867246</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.37810738</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>306.99401668</v>
+        <v>341.38450299</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>362.38</v>
+        <v>395.17</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>92.83</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>109.65</v>
+        <v>110.75</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002504066110085734</v>
+        <v>0.002510226196879251</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>16.82</v>
+        <v>15.24</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.1811914251858236</v>
+        <v>0.1595644435137682</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.06</v>
+        <v>0.17</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.37810738</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.1285649</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>341.38450299</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>391.6</v>
+        <v>1162.05</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>109.63</v>
+        <v>110.73</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002503609372081158</v>
+        <v>0.002509772882893358</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>14.12</v>
+        <v>11.84</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1478379227306041</v>
+        <v>0.1197289918090808</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.1285649</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.90543241</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>54.82621761</v>
+        <v>137.713206</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>53.52</v>
+        <v>164.34</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>112.48</v>
+        <v>92.27</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>109.62</v>
+        <v>110.29</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002503381003078871</v>
+        <v>0.002499799975203725</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>-2.86</v>
+        <v>18.02</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-0.02542674253200569</v>
+        <v>0.1952964127018533</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.18</v>
+        <v>0.15</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.90543241</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.1285649</v>
+        <v>11.40066159</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>12.56856884</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>1145.78</v>
+        <v>13.04</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>98.89</v>
+        <v>106.15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>109.07</v>
+        <v>110.19</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002490820707953041</v>
+        <v>0.002497533405274263</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>10.18</v>
+        <v>4.04</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1029426635655779</v>
+        <v>0.03805934997644842</v>
       </c>
       <c r="M46" s="2" t="n">
         <v>0.06</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.1285649</v>
+        <v>11.40066159</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.80409618</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>324.07677699</v>
+        <v>148.63893521</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>348.53</v>
+        <v>183.95</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>101.39</v>
+        <v>88.44</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>109.04</v>
+        <v>109.63</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002490135600946178</v>
+        <v>0.002484840613669275</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>7.65</v>
+        <v>21.19</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.0754512279317487</v>
+        <v>0.2395974672094075</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.80409618</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.74206342</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>194.45976548</v>
+        <v>74.99726962</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>240.29</v>
+        <v>84.77</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>88.09</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>108.91</v>
+        <v>109.46</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002487166803916437</v>
+        <v>0.002480987444789189</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>20.82</v>
+        <v>12.78</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.2363491883301169</v>
+        <v>0.1321886636326024</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.74206342</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1.74206342</v>
+        <v>1.35094641</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>74.99726962</v>
+        <v>96.717382</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>84.31</v>
+        <v>109.27</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>108.75</v>
+        <v>109.41</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002483512899879832</v>
+        <v>0.002479854159824459</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>12.07</v>
+        <v>12.73</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1248448489863467</v>
+        <v>0.1316714935870914</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.06</v>
+        <v>0.16</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>1.74206342</v>
+        <v>1.35094641</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>11.40066159</v>
+        <v>3.81488812</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>12.56856884</v>
+        <v>38.28159448</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>12.87</v>
+        <v>38.65</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>106.15</v>
+        <v>108.23</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>108.64</v>
+        <v>109.29</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002481000840854666</v>
+        <v>0.002477134275909104</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2.49</v>
+        <v>1.06</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.02345737164390014</v>
+        <v>0.009793957313129447</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>11.40066159</v>
+        <v>3.81488812</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.76637723</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>96.717382</v>
+        <v>54.82621761</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>108.25</v>
+        <v>52.83</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>112.48</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>108.28</v>
+        <v>108.32</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002472779556772305</v>
+        <v>0.002455148547593322</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>11.6</v>
+        <v>-4.16</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.1199834505585436</v>
+        <v>-0.03698435277382646</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.76637723</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.68495686</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>148.63893521</v>
+        <v>176.50746647</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>181.63</v>
+        <v>213.36</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>88.44</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>108.13</v>
+        <v>108.32</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002469354021737988</v>
+        <v>0.002455148547593322</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>19.69</v>
+        <v>18.86</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.222636815920398</v>
+        <v>0.2108204784261122</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.68495686</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3619,25 +3619,25 @@
         <v>235.02053179</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>233.54</v>
+        <v>233.58</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>107.98</v>
+        <v>108.11</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002465928486703671</v>
+        <v>0.002450388750741452</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>-0.79</v>
+        <v>-0.66</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>-0.00726303208605314</v>
+        <v>-0.006067849590879838</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.11</v>
+        <v>0.01</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>0.62445608</v>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.42255419</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>38.28159448</v>
+        <v>324.07677699</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>38.1</v>
+        <v>344.03</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>108.23</v>
+        <v>101.39</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>107.62</v>
+        <v>107.75</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.00245770720262131</v>
+        <v>0.002442229098995388</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>-0.61</v>
+        <v>6.36</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>-0.00563614524623487</v>
+        <v>0.06272807969227735</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.1</v>
+        <v>0.11</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.42255419</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
         <v>10.85229847</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>10.87</v>
+        <v>10.92</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>107.06</v>
+        <v>107.67</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002444918538493194</v>
+        <v>0.002440415843051818</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.1</v>
+        <v>0.71</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.0009349289454001497</v>
+        <v>0.006637995512341062</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>13.30225117</v>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.61215748</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>176.50746647</v>
+        <v>194.45976548</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>210.85</v>
+        <v>234.84</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>88.09</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>106.93</v>
+        <v>106.55</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002441949741463452</v>
+        <v>0.002415030259841843</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>17.47</v>
+        <v>18.46</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.1952828079588643</v>
+        <v>0.2095584061755023</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.61215748</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.59010207</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>257.81779936</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>284.57</v>
+        <v>90.3</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>106.77</v>
+        <v>106.43</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002438295837426847</v>
+        <v>0.002412310375926489</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>10.09</v>
+        <v>16.77</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.1043649151841125</v>
+        <v>0.1870399286192282</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.59010207</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3904,25 +3904,25 @@
         <v>113.12478542</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>121.62</v>
+        <v>120.86</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>106.21</v>
+        <v>105.66</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.00242550717329873</v>
+        <v>0.002394857787469631</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>7.49</v>
+        <v>6.94</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.07587115072933549</v>
+        <v>0.07029983792544571</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.18</v>
       </c>
       <c r="N58" s="4" t="n">
         <v>1.17949395</v>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,55 +3955,55 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.1533463</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>105.04894536</v>
+        <v>104.90344487</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>25.08</v>
+        <v>123.41</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>452.96</v>
+        <v>89.53</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>105.68</v>
+        <v>105.5</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002413403616177477</v>
+        <v>0.002391231275582491</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-347.28</v>
+        <v>15.97</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.7666902154715648</v>
+        <v>0.1783759633642354</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-10.3</v>
+        <v>0.15</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0</v>
+        <v>1.1533463</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.50675322</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>257.81779936</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>89.05</v>
+        <v>280.58</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>89.66</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>104.84</v>
+        <v>105.39</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002394220619985302</v>
+        <v>0.002388738048660083</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>15.18</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.1693062681240241</v>
+        <v>0.09009102192800993</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.05</v>
+        <v>0.16</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.50675322</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FB_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US30303M1027</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,55 +4069,55 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.235295</v>
+        <v>2.27580753</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>627.34014747</v>
+        <v>62.95787236</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>601.74</v>
+        <v>62.42</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>119.82</v>
+        <v>106.15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>104.83</v>
+        <v>105.29</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002393992250983014</v>
+        <v>0.002386471478730621</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-14.99</v>
+        <v>-0.86</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.1251043231513938</v>
+        <v>-0.008101742816768722</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-10.53</v>
+        <v>0.05</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0</v>
+        <v>2.27580753</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.85908491</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>62.95787236</v>
+        <v>76.24181082</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>61.84</v>
+        <v>74.25</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>106.15</v>
+        <v>104.98</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>104.2</v>
+        <v>102.31</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002379605003838883</v>
+        <v>0.002318927694832651</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-1.95</v>
+        <v>-2.67</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.01837023080546396</v>
+        <v>-0.02543341588874071</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.85908491</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.11796351</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>104.90344487</v>
+        <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>121.59</v>
+        <v>123.41</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>89.53</v>
+        <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>103.83</v>
+        <v>102.26</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002371155350754234</v>
+        <v>0.00231779440986792</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>14.3</v>
+        <v>-3.1</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.1597229978778063</v>
+        <v>-0.02942293090356872</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.11796351</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>127.23134407</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>123.17</v>
+        <v>1309.49</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>105.36</v>
+        <v>88.89</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>101.95</v>
+        <v>101.39</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002328221978324128</v>
+        <v>0.0022980752514816</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-3.41</v>
+        <v>12.5</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.03236522399392559</v>
+        <v>0.1406232422094724</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.05</v>
+        <v>0.15</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>FB_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Meta Platforms</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US30303M1027</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,55 +4297,55 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.6214908</v>
+        <v>0.235295</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>234.11448729</v>
+        <v>627.34014747</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>221.14</v>
+        <v>580.47</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>107.82</v>
+        <v>119.82</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>101.76</v>
+        <v>101.23</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002323882967280659</v>
+        <v>0.002294448739594461</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-6.06</v>
+        <v>-18.59</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.0562047857540345</v>
+        <v>-0.1551493907527959</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.09</v>
+        <v>-10.42</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.6214908</v>
+        <v>0</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-01-23</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.17308322</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>76.24181082</v>
+        <v>126.99866255</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>73.61</v>
+        <v>115.56</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>104.98</v>
+        <v>110.45</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>101.32</v>
+        <v>100.48</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002313834731179996</v>
+        <v>0.002277449465123495</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-3.66</v>
+        <v>-9.970000000000001</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.03486378357782435</v>
+        <v>-0.09026708918062472</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.17308322</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.6214908</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>234.11448729</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>1300.25</v>
+        <v>217.25</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>88.89</v>
+        <v>107.82</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>100.56</v>
+        <v>100.08</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002296478687006123</v>
+        <v>0.002268383185405647</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>11.67</v>
+        <v>-7.74</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.1312858589267634</v>
+        <v>-0.07178631051752922</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.6214908</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4449,17 +4449,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,34 +4468,34 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.97307689</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>107.56862839</v>
+        <v>154.44822659</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>116.09</v>
+        <v>138.7</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>92.77</v>
+        <v>111.44</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>100.19</v>
+        <v>100.04</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002288029033921475</v>
+        <v>0.002267476557433862</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>7.42</v>
+        <v>-11.4</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.07998275304516547</v>
+        <v>-0.10229720028715</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.04</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.97307689</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.16558147</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>154.44822659</v>
+        <v>107.56862839</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>138.12</v>
+        <v>114.99</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>111.44</v>
+        <v>92.77</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.34</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002272499941765904</v>
+        <v>0.002251610567927627</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-11.93</v>
+        <v>6.57</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.1070531227566403</v>
+        <v>0.07082030828931768</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.17</v>
+        <v>0.16</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.16558147</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,55 +4582,55 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>5.691347</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>147.21071381</v>
+        <v>105.04894536</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>145.08</v>
+        <v>23.53</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>452.96</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>98.43000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002247836089518822</v>
+        <v>0.002249797311984058</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-1.42</v>
+        <v>-353.7</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.014221331997997</v>
+        <v>-0.7808636524196397</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.03</v>
+        <v>-9.82</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>0</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4639,34 +4639,34 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>126.99866255</v>
+        <v>147.21071381</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>112.87</v>
+        <v>144.48</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>110.45</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>98.03</v>
+        <v>98.13</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.00223870132942731</v>
+        <v>0.002224185071781136</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-12.42</v>
+        <v>-1.72</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1124490719782707</v>
+        <v>-0.01722583875813721</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.15</v>
+        <v>0.13</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4702,25 +4702,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>136.03</v>
+        <v>138.06</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>94.13</v>
+        <v>95.63</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.002149637418535067</v>
+        <v>0.002167520823544585</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>5.75</v>
+        <v>7.25</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.06505996831862412</v>
+        <v>0.08203213396696085</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>0.05</v>
+        <v>0.14</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.93456659</v>
@@ -4759,25 +4759,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>67.18000000000001</v>
+        <v>66.17</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>91.87</v>
+        <v>90.58</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.002098026024018024</v>
+        <v>0.002053059042106749</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-18.66</v>
+        <v>-19.95</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.1688229439971048</v>
+        <v>-0.1804939835338822</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.03</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>1.84694851</v>
@@ -4816,25 +4816,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>114.04</v>
+        <v>111.3</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>53.38</v>
+        <v>52.16</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.00121903373421228</v>
+        <v>0.001182242875207419</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>5.51</v>
+        <v>4.29</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.1151034050553583</v>
+        <v>0.08961771464382703</v>
       </c>
       <c r="M74" s="2" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="N74" s="4" t="n">
         <v>0.63221571</v>
@@ -4873,25 +4873,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>273.04</v>
+        <v>275.27</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>49</v>
+        <v>49.45</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.001119008111210223</v>
+        <v>0.001120818830118997</v>
       </c>
       <c r="K75" s="2" t="n">
-        <v>-3.11</v>
+        <v>-2.66</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>-0.05968144310113222</v>
+        <v>-0.05104586451736711</v>
       </c>
       <c r="M75" s="2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="N75" s="4" t="n">
         <v>0.24236298</v>
@@ -4983,34 +4983,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-11 19:32:40</t>
+          <t>2026-08-12 19:34:51</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43867.51</v>
+        <v>44196.49</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43810.16</v>
+        <v>44139.13</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>37880.19</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5929.97</v>
+        <v>6258.94</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1565454133149807</v>
+        <v>0.1652298998500271</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1251.59</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>79.01000000000001</v>
+        <v>79.02</v>
       </c>
       <c r="J2" t="n">
         <v>74</v>
@@ -5079,7 +5079,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5106,7 +5106,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5118,22 +5118,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.646</v>
+        <v>15.134</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4247.34</v>
+        <v>4388.86</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>816.63</v>
+        <v>958.15</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5145,22 +5145,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1524.2</v>
+        <v>1537.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2688.58</v>
+        <v>2712.57</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1492.62</v>
+        <v>1516.61</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5172,22 +5172,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>24.7</v>
+        <v>24.97</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2103.11</v>
+        <v>2128.4</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>177.3</v>
+        <v>202.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5199,22 +5199,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D6" t="n">
-        <v>217.83</v>
+        <v>222.52</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1762.17</v>
+        <v>1802.06</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>509.49</v>
+        <v>549.38</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5226,22 +5226,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>475.42</v>
+        <v>482.88</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1760.01</v>
+        <v>1789.56</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-138.54</v>
+        <v>-108.99</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5253,22 +5253,22 @@
         <v>18.80610988</v>
       </c>
       <c r="D8" t="n">
-        <v>120.77</v>
+        <v>123.69</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1681.61</v>
+        <v>1724.13</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1120</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>561.61</v>
+        <v>604.13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5280,22 +5280,22 @@
         <v>50</v>
       </c>
       <c r="D9" t="n">
-        <v>3356</v>
+        <v>3322.5</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1678</v>
+        <v>1661.25</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1649.5</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>28.5</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5307,22 +5307,22 @@
         <v>9.6</v>
       </c>
       <c r="D10" t="n">
-        <v>211.37</v>
+        <v>220.47</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1502.39</v>
+        <v>1568.76</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-493.67</v>
+        <v>-427.3</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5334,22 +5334,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D11" t="n">
-        <v>157.28</v>
+        <v>153.61</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1465.21</v>
+        <v>1432.57</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-406.63</v>
+        <v>-439.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5361,22 +5361,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D12" t="n">
-        <v>119</v>
+        <v>119.04</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1401.09</v>
+        <v>1403.08</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>57.3</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5391,19 +5391,19 @@
         <v>43.65</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1394.25</v>
+        <v>1391.51</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>165.91</v>
+        <v>163.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5415,22 +5415,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D14" t="n">
-        <v>435.7</v>
+        <v>438.9</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1199.73</v>
+        <v>1207.67</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>285.24</v>
+        <v>293.18</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5442,22 +5442,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D15" t="n">
-        <v>113.8</v>
+        <v>115.2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1154.34</v>
+        <v>1168.55</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>547.15</v>
+        <v>561.36</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5469,22 +5469,22 @@
         <v>160</v>
       </c>
       <c r="D16" t="n">
-        <v>707.4</v>
+        <v>714.6</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1131.84</v>
+        <v>1143.36</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>378.38</v>
+        <v>389.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5496,22 +5496,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D17" t="n">
-        <v>335.08</v>
+        <v>333.87</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1087</v>
+        <v>1084.25</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>445.01</v>
+        <v>442.26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5523,130 +5523,130 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>47.33</v>
+        <v>46.25</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>700.86</v>
+        <v>685.61</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-166.72</v>
+        <v>-181.97</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>AAPL_US_EQ</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.8650317</v>
+        <v>3.05990683</v>
       </c>
       <c r="D19" t="n">
-        <v>503.04</v>
+        <v>301.92</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>694.63</v>
+        <v>684.76</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>534.38</v>
+        <v>491.05</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>160.25</v>
+        <v>193.71</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AAPL_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>3.05990683</v>
+        <v>1.8650317</v>
       </c>
       <c r="D20" t="n">
-        <v>304.64</v>
+        <v>494.29</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>690.1799999999999</v>
+        <v>683.29</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>491.05</v>
+        <v>534.38</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>199.13</v>
+        <v>148.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>65</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>1001</v>
+        <v>96</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>650.65</v>
+        <v>654.34</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-12.03</v>
+        <v>105.16</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>65</v>
       </c>
       <c r="D22" t="n">
-        <v>95.22</v>
+        <v>1005.5</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>648.33</v>
+        <v>653.58</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5658,22 +5658,22 @@
         <v>2.330043</v>
       </c>
       <c r="D23" t="n">
-        <v>340.95</v>
+        <v>343.63</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>588.2</v>
+        <v>593.46</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>98.93000000000001</v>
+        <v>104.19</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5685,22 +5685,22 @@
         <v>140</v>
       </c>
       <c r="D24" t="n">
-        <v>3.817</v>
+        <v>3.828</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>534.38</v>
+        <v>535.92</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-3.99</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5712,22 +5712,22 @@
         <v>2</v>
       </c>
       <c r="D25" t="n">
-        <v>344.03</v>
+        <v>343.82</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>509.44</v>
+        <v>509.68</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>101.52</v>
+        <v>101.76</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5739,103 +5739,103 @@
         <v>1.11022215</v>
       </c>
       <c r="D26" t="n">
-        <v>238.93</v>
+        <v>235.43</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>196.4</v>
+        <v>193.74</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-0.12</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.7</v>
+        <v>1.55804584</v>
       </c>
       <c r="D27" t="n">
-        <v>250.42</v>
+        <v>111.04</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>129.79</v>
+        <v>128.23</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>118.76</v>
+        <v>105.28</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>11.03</v>
+        <v>22.95</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.7</v>
       </c>
       <c r="D28" t="n">
-        <v>270.81</v>
+        <v>243.72</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>127.17</v>
+        <v>126.45</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>118.76</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>27.32</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.63422137</v>
       </c>
       <c r="D29" t="n">
-        <v>109.93</v>
+        <v>268.17</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>126.81</v>
+        <v>126.06</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>21.53</v>
+        <v>26.21</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5847,103 +5847,103 @@
         <v>0.42010405</v>
       </c>
       <c r="D30" t="n">
-        <v>399.45</v>
+        <v>394.75</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>124.25</v>
+        <v>122.92</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>15.09</v>
+        <v>13.76</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.70722512</v>
+        <v>2.50421091</v>
       </c>
       <c r="D31" t="n">
-        <v>59.08</v>
+        <v>63.91</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>118.42</v>
+        <v>118.63</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>107.64</v>
+        <v>106.81</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>10.78</v>
+        <v>11.82</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.50421091</v>
+        <v>2.70722512</v>
       </c>
       <c r="D32" t="n">
-        <v>63.75</v>
+        <v>58.55</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>118.2</v>
+        <v>117.49</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>106.81</v>
+        <v>107.64</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>11.39</v>
+        <v>9.85</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.43583007</v>
+        <v>1.32559468</v>
       </c>
       <c r="D33" t="n">
-        <v>364.24</v>
+        <v>119.12</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>117.54</v>
+        <v>117.04</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>104.04</v>
+        <v>119.73</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.5</v>
+        <v>-2.69</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5955,76 +5955,76 @@
         <v>3.30858696</v>
       </c>
       <c r="D34" t="n">
-        <v>47.7</v>
+        <v>47.68</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>116.85</v>
+        <v>116.93</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>4.14</v>
+        <v>4.22</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.43583007</v>
       </c>
       <c r="D35" t="n">
-        <v>562.76</v>
+        <v>361.92</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>116.83</v>
+        <v>116.91</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>105.75</v>
+        <v>104.04</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>11.08</v>
+        <v>12.87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.28038062</v>
       </c>
       <c r="D36" t="n">
-        <v>117.5</v>
+        <v>561.05</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>115.32</v>
+        <v>116.6</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>119.73</v>
+        <v>105.75</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>-4.41</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -6036,22 +6036,22 @@
         <v>0.7905852</v>
       </c>
       <c r="D37" t="n">
-        <v>196.49</v>
+        <v>196.71</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>115.02</v>
+        <v>115.27</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4.61</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -6063,22 +6063,22 @@
         <v>0.59183053</v>
       </c>
       <c r="D38" t="n">
-        <v>259.87</v>
+        <v>260.92</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>113.87</v>
+        <v>114.46</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>14.02</v>
+        <v>14.61</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -6090,22 +6090,22 @@
         <v>0.51881442</v>
       </c>
       <c r="D39" t="n">
-        <v>293.11</v>
+        <v>293.48</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.59</v>
+        <v>112.86</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>16.65</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6117,22 +6117,22 @@
         <v>0.5550481</v>
       </c>
       <c r="D40" t="n">
-        <v>272.41</v>
+        <v>271.84</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>111.95</v>
+        <v>111.84</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>20.77</v>
+        <v>20.66</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6144,319 +6144,319 @@
         <v>1.73400968</v>
       </c>
       <c r="D41" t="n">
-        <v>86.56999999999999</v>
+        <v>86.84999999999999</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.14</v>
+        <v>111.62</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>9.609999999999999</v>
+        <v>10.09</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.40867246</v>
       </c>
       <c r="D42" t="n">
-        <v>164.28</v>
+        <v>365.84</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>110.13</v>
+        <v>110.82</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>92.27</v>
+        <v>92.83</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>17.86</v>
+        <v>17.99</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.37810738</v>
       </c>
       <c r="D43" t="n">
-        <v>362.38</v>
+        <v>395.17</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>109.65</v>
+        <v>110.75</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>92.83</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>16.82</v>
+        <v>15.24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.1285649</v>
       </c>
       <c r="D44" t="n">
-        <v>391.6</v>
+        <v>1162.05</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>109.63</v>
+        <v>110.73</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>14.12</v>
+        <v>11.84</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.90543241</v>
       </c>
       <c r="D45" t="n">
-        <v>53.52</v>
+        <v>164.34</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>109.62</v>
+        <v>110.29</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>112.48</v>
+        <v>92.27</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-2.86</v>
+        <v>18.02</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.1285649</v>
+        <v>11.40066159</v>
       </c>
       <c r="D46" t="n">
-        <v>1145.78</v>
+        <v>13.04</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>109.07</v>
+        <v>110.19</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>98.89</v>
+        <v>106.15</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>10.18</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.80409618</v>
       </c>
       <c r="D47" t="n">
-        <v>348.53</v>
+        <v>183.95</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>109.04</v>
+        <v>109.63</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>101.39</v>
+        <v>88.44</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>7.65</v>
+        <v>21.19</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.74206342</v>
       </c>
       <c r="D48" t="n">
-        <v>240.29</v>
+        <v>84.77</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>108.91</v>
+        <v>109.46</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>88.09</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>20.82</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1.74206342</v>
+        <v>1.35094641</v>
       </c>
       <c r="D49" t="n">
-        <v>84.31</v>
+        <v>109.27</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>108.75</v>
+        <v>109.41</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>12.07</v>
+        <v>12.73</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>11.40066159</v>
+        <v>3.81488812</v>
       </c>
       <c r="D50" t="n">
-        <v>12.87</v>
+        <v>38.65</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>108.64</v>
+        <v>109.29</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>106.15</v>
+        <v>108.23</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>2.49</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.76637723</v>
       </c>
       <c r="D51" t="n">
-        <v>108.25</v>
+        <v>52.83</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>108.28</v>
+        <v>108.32</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>112.48</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>11.6</v>
+        <v>-4.16</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.68495686</v>
       </c>
       <c r="D52" t="n">
-        <v>181.63</v>
+        <v>213.36</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>108.13</v>
+        <v>108.32</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>88.44</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>19.69</v>
+        <v>18.86</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6468,49 +6468,49 @@
         <v>0.62445608</v>
       </c>
       <c r="D53" t="n">
-        <v>233.54</v>
+        <v>233.58</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>107.98</v>
+        <v>108.11</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>-0.79</v>
+        <v>-0.66</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.42255419</v>
       </c>
       <c r="D54" t="n">
-        <v>38.1</v>
+        <v>344.03</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>107.62</v>
+        <v>107.75</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>108.23</v>
+        <v>101.39</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>-0.61</v>
+        <v>6.36</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6522,76 +6522,76 @@
         <v>13.30225117</v>
       </c>
       <c r="D55" t="n">
-        <v>10.87</v>
+        <v>10.92</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>107.06</v>
+        <v>107.67</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.1</v>
+        <v>0.71</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.61215748</v>
       </c>
       <c r="D56" t="n">
-        <v>210.85</v>
+        <v>234.84</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>106.93</v>
+        <v>106.55</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>88.09</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>17.47</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.59010207</v>
       </c>
       <c r="D57" t="n">
-        <v>284.57</v>
+        <v>90.3</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>106.77</v>
+        <v>106.43</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.66</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>10.09</v>
+        <v>16.77</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6603,373 +6603,373 @@
         <v>1.17949395</v>
       </c>
       <c r="D58" t="n">
-        <v>121.62</v>
+        <v>120.86</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>106.21</v>
+        <v>105.66</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>7.49</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.1533463</v>
       </c>
       <c r="D59" t="n">
-        <v>25.08</v>
+        <v>123.41</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>105.68</v>
+        <v>105.5</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>452.96</v>
+        <v>89.53</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-347.28</v>
+        <v>15.97</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.50675322</v>
       </c>
       <c r="D60" t="n">
-        <v>89.05</v>
+        <v>280.58</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>104.84</v>
+        <v>105.39</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>89.66</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>15.18</v>
+        <v>8.710000000000001</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FB_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.235295</v>
+        <v>2.27580753</v>
       </c>
       <c r="D61" t="n">
-        <v>601.74</v>
+        <v>62.42</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>104.83</v>
+        <v>105.29</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>119.82</v>
+        <v>106.15</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-14.99</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.85908491</v>
       </c>
       <c r="D62" t="n">
-        <v>61.84</v>
+        <v>74.25</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>104.2</v>
+        <v>102.31</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>106.15</v>
+        <v>104.98</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-1.95</v>
+        <v>-2.67</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>121.59</v>
+        <v>123.41</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>103.83</v>
+        <v>102.26</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>89.53</v>
+        <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>14.3</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="D64" t="n">
-        <v>123.17</v>
+        <v>1309.49</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101.95</v>
+        <v>101.39</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>105.36</v>
+        <v>88.89</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-3.41</v>
+        <v>12.5</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>FB_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.6214908</v>
+        <v>0.235295</v>
       </c>
       <c r="D65" t="n">
-        <v>221.14</v>
+        <v>580.47</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>101.76</v>
+        <v>101.23</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>107.82</v>
+        <v>119.82</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-6.06</v>
+        <v>-18.59</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.17308322</v>
       </c>
       <c r="D66" t="n">
-        <v>73.61</v>
+        <v>115.56</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>101.32</v>
+        <v>100.48</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>104.98</v>
+        <v>110.45</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-3.66</v>
+        <v>-9.970000000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.6214908</v>
       </c>
       <c r="D67" t="n">
-        <v>1300.25</v>
+        <v>217.25</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>100.56</v>
+        <v>100.08</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>88.89</v>
+        <v>107.82</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>11.67</v>
+        <v>-7.74</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.97307689</v>
       </c>
       <c r="D68" t="n">
-        <v>116.09</v>
+        <v>138.7</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>100.19</v>
+        <v>100.04</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>92.77</v>
+        <v>111.44</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>7.42</v>
+        <v>-11.4</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.16558147</v>
       </c>
       <c r="D69" t="n">
-        <v>138.12</v>
+        <v>114.99</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>99.51000000000001</v>
+        <v>99.34</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>111.44</v>
+        <v>92.77</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-11.93</v>
+        <v>6.57</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>5.691347</v>
       </c>
       <c r="D70" t="n">
-        <v>145.08</v>
+        <v>23.53</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>98.43000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>452.96</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-1.42</v>
+        <v>-353.7</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D71" t="n">
-        <v>112.87</v>
+        <v>144.48</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>98.03</v>
+        <v>98.13</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>110.45</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-12.42</v>
+        <v>-1.72</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6981,22 +6981,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D72" t="n">
-        <v>136.03</v>
+        <v>138.06</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>94.13</v>
+        <v>95.63</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>5.75</v>
+        <v>7.25</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -7008,22 +7008,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D73" t="n">
-        <v>67.18000000000001</v>
+        <v>66.17</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>91.87</v>
+        <v>90.58</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-18.66</v>
+        <v>-19.95</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -7035,22 +7035,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D74" t="n">
-        <v>114.04</v>
+        <v>111.3</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>53.38</v>
+        <v>52.16</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>5.51</v>
+        <v>4.29</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -7062,16 +7062,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D75" t="n">
-        <v>273.04</v>
+        <v>275.27</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>49</v>
+        <v>49.45</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>-3.11</v>
+        <v>-2.66</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44196.49</v>
+        <v>44346.99</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>44139.13</v>
+        <v>43055.46</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>37880.19</v>
+        <v>36637.52</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6258.94</v>
+        <v>6417.94</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1652298998500271</v>
+        <v>0.1751739746576733</v>
       </c>
     </row>
     <row r="9">
@@ -531,7 +531,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>1251.59</v>
+        <v>1243.5</v>
       </c>
     </row>
     <row r="10">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>57.36</v>
+        <v>1291.53</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>21.66</v>
+        <v>21.74</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-12 19:34:51</t>
+          <t>2026-08-13 19:33:04</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O75"/>
+  <dimension ref="A1:O73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>110.74</v>
+        <v>111.44</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7087.36</v>
+        <v>7132.16</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1606399705527235</v>
+        <v>0.1657348357886264</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1041.59</v>
+        <v>1086.39</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1722840928450801</v>
+        <v>0.1796942324964397</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15.134</v>
+        <v>15.456</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4388.86</v>
+        <v>4482.24</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09947658100618932</v>
+        <v>0.1041568487478145</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>958.15</v>
+        <v>1051.53</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.279286211891999</v>
+        <v>0.3065050674641692</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1537.8</v>
+        <v>1525.8</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2712.57</v>
+        <v>2691.41</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06148229593560947</v>
+        <v>0.06254211829093387</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1516.61</v>
+        <v>1495.45</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.268110973611158</v>
+        <v>1.250418074183083</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.97</v>
+        <v>25.56</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2128.4</v>
+        <v>2179.34</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04824167437867086</v>
+        <v>0.05064280064210352</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>202.59</v>
+        <v>253.53</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1051972936063267</v>
+        <v>0.1316485011501654</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-7.1</v>
+        <v>-6.52</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -915,17 +915,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>CSCO_US_EQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US67066G1040</t>
+          <t>US17275R1023</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -934,55 +934,55 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>10.9260596</v>
+        <v>24.80610988</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>150.09436705</v>
+        <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>222.52</v>
+        <v>112.8</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1252.68</v>
+        <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1802.06</v>
+        <v>2074.59</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04084495007086431</v>
+        <v>0.04820865389709799</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>549.38</v>
+        <v>428.02</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.4385637193856372</v>
+        <v>0.2599464341024068</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-37.15</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>0</v>
+        <v>1.15856288</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2024-10-15</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US0079031078</t>
+          <t>US67066G1040</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -991,55 +991,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>509.97</v>
+        <v>150.09436705</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>482.88</v>
+        <v>225.88</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1789.56</v>
+        <v>1829.81</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04056162882968155</v>
+        <v>0.04252053513583352</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-108.99</v>
+        <v>577.13</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.05740696847594216</v>
+        <v>0.4607162244148545</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-8.59</v>
+        <v>-36.8</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>CSCO_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US17275R1023</t>
+          <t>US0079031078</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,112 +1048,112 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>18.80610988</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>79.71079663</v>
+        <v>509.97</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>123.69</v>
+        <v>487.13</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1120</v>
+        <v>1898.55</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1724.13</v>
+        <v>1805.84</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.03907861212483452</v>
+        <v>0.04196352800000744</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>604.13</v>
+        <v>-92.70999999999999</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.5394017857142858</v>
+        <v>-0.04883200337099365</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-8.9</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="N8" s="4" t="n">
-        <v>1.15856288</v>
+        <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SHELl_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Shell</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GB00BP6MXD84</t>
+          <t>US5738741041</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>50</v>
+        <v>9.6</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>3299</v>
+        <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>3322.5</v>
+        <v>222.9</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1649.5</v>
+        <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1661.25</v>
+        <v>1586.52</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03765339295318876</v>
+        <v>0.03686704051442641</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>11.75</v>
+        <v>-409.54</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.007123370718399515</v>
+        <v>-0.2051741931605263</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>-13.43</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US5738741041</t>
+          <t>US75734B1008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1162,55 +1162,55 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.6</v>
+        <v>12.5822526</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>278.55208333</v>
+        <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>220.47</v>
+        <v>158.42</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1996.06</v>
+        <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1568.76</v>
+        <v>1477.86</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03555704242542929</v>
+        <v>0.03434203444939252</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-427.3</v>
+        <v>-393.98</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2140717212909432</v>
+        <v>-0.2104773912300197</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-14.01</v>
+        <v>-85.15000000000001</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-03-22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>US75734B1008</t>
+          <t>IE00BMD8KM66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1219,226 +1219,226 @@
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>12.5822526</v>
+        <v>15.9020618</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>191.52532353</v>
+        <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>153.61</v>
+        <v>119.08</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1871.84</v>
+        <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1432.57</v>
+        <v>1403.97</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03247020083849488</v>
+        <v>0.03262500243995617</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>-439.27</v>
+        <v>60.18</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>-0.2346728352850671</v>
+        <v>0.04478378318040765</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-85.67</v>
+        <v>-11.03</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-07-16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
+          <t>UBS Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>IE00BMD8KM66</t>
+          <t>CH0244767585</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>113.04005874</v>
+        <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>119.04</v>
+        <v>43.49</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1403.08</v>
+        <v>1386.08</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03180178936629651</v>
+        <v>0.03220928038489031</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>59.29</v>
+        <v>157.74</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.04412147731416367</v>
+        <v>0.1284172134750965</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-11.43</v>
+        <v>-47.51</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>ALVd_EQ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UBS Group</t>
+          <t>Allianz</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CH0244767585</t>
+          <t>DE0008404005</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>35</v>
+        <v>3.2220691</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>37.05</v>
+        <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>43.65</v>
+        <v>437.8</v>
       </c>
       <c r="H13" s="2" t="n">
-        <v>1228.34</v>
+        <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1391.51</v>
+        <v>1205.88</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.03153954722545775</v>
+        <v>0.02802185085314811</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>163.17</v>
+        <v>291.39</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.1328378136346614</v>
+        <v>0.3186366171308598</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-47.23</v>
+        <v>-3.59</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-06-25</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ALVd_EQ</t>
+          <t>LLOYl_EQ</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Allianz</t>
+          <t>Lloyds Banking Group</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>DE0008404005</t>
+          <t>GB0008706128</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EUR</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
-        <v>3.2220691</v>
+        <v>1014.362806</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>330.7067499</v>
+        <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>438.9</v>
+        <v>115.3</v>
       </c>
       <c r="H14" s="2" t="n">
-        <v>914.49</v>
+        <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1207.67</v>
+        <v>1169.56</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02737268506713467</v>
+        <v>0.02717785839702781</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>293.18</v>
+        <v>562.37</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.32059399227985</v>
+        <v>0.9261845550816054</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>-4.52</v>
+        <v>0</v>
       </c>
       <c r="N14" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2024-06-25</t>
+          <t>2024-08-08</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>LLOYl_EQ</t>
+          <t>RBSl_EQ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Lloyds Banking Group</t>
+          <t>NatWest</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>GB0008706128</t>
+          <t>GB00BM8PJY71</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1447,28 +1447,28 @@
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>1014.362806</v>
+        <v>160</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>59.85909543</v>
+        <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>115.2</v>
+        <v>705.6</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>607.1900000000001</v>
+        <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1168.55</v>
+        <v>1128.96</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.0264860029107291</v>
+        <v>0.0262344086801092</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>561.36</v>
+        <v>375.5</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.924521154827978</v>
+        <v>0.4983675311230855</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1478,81 +1478,81 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2024-08-08</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RBSl_EQ</t>
+          <t>SNOW_US_EQ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>NatWest</t>
+          <t>Snowflake</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>GB00BM8PJY71</t>
+          <t>US8334451098</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
-        <v>160</v>
+        <v>4.3814255</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>470.9125</v>
+        <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>714.6</v>
+        <v>338.47</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>753.46</v>
+        <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1143.36</v>
+        <v>1099.51</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.0259150539454976</v>
+        <v>0.02555005907017686</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>389.9</v>
+        <v>457.52</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.5174793618772064</v>
+        <v>0.7126590756865371</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>0</v>
+        <v>-31.7</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-11-21</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SNOW_US_EQ</t>
+          <t>AAPL_US_EQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Snowflake</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US8334451098</t>
+          <t>US0378331005</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1561,38 +1561,38 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>4.3814255</v>
+        <v>3.05990683</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>187.8703632</v>
+        <v>207.87234231</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>333.87</v>
+        <v>304.37</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>641.99</v>
+        <v>491.05</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>1084.25</v>
+        <v>690.52</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.02457528446019257</v>
+        <v>0.01604608124449848</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>442.26</v>
+        <v>199.47</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.6888892350348136</v>
+        <v>0.4062111801242236</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-31.88</v>
+        <v>-19.45</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0</v>
+        <v>0.46065664</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2024-11-21</t>
+          <t>2024-01-24</t>
         </is>
       </c>
     </row>
@@ -1624,25 +1624,25 @@
         <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46.25</v>
+        <v>46.5</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>685.61</v>
+        <v>689.52</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01553983009338495</v>
+        <v>0.01602284356674186</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-181.97</v>
+        <v>-178.06</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.2097443463427004</v>
+        <v>-0.205237557343415</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-10.16</v>
+        <v>-9.91</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -1656,17 +1656,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>AAPL_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US0378331005</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1675,55 +1675,55 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>3.05990683</v>
+        <v>1.8650317</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>207.87234231</v>
+        <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>301.92</v>
+        <v>497.89</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>491.05</v>
+        <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>684.76</v>
+        <v>688.47</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01552056424898452</v>
+        <v>0.01599844400509742</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>193.71</v>
+        <v>154.09</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.3944812137256898</v>
+        <v>0.2883528575171226</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-19.59</v>
+        <v>-23.5</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.46065664</v>
+        <v>0.3650317</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>US6311031081</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1732,283 +1732,283 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.8650317</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>369.46288902</v>
+        <v>77.20222067</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>494.29</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>534.38</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>683.29</v>
+        <v>663.54</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01548724567102143</v>
+        <v>0.01541912869862498</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>148.91</v>
+        <v>114.36</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.2786593809648565</v>
+        <v>0.2082377362613351</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-23.65</v>
+        <v>-22.81</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3650317</v>
+        <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-09-26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US6311031081</t>
+          <t>IE00B43HR379</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>65</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>77.20222067</v>
+        <v>1019.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>96</v>
+        <v>1008.5</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>654.34</v>
+        <v>655.53</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01483107367644216</v>
+        <v>0.01523299489979449</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>105.16</v>
+        <v>-7.15</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.1914854874540224</v>
+        <v>-0.01078952133759884</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-22.97</v>
+        <v>0</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>AXP_US_EQ</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IE00B43HR379</t>
+          <t>US0258161092</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>65</v>
+        <v>2.330043</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>1019.5</v>
+        <v>265.62170741</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>1005.5</v>
+        <v>344.76</v>
       </c>
       <c r="H22" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>489.27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>653.58</v>
+        <v>595.59</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01481384774497825</v>
+        <v>0.01384012849506292</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>-9.1</v>
+        <v>106.32</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>-0.01373211806603489</v>
+        <v>0.2173033294499969</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>0</v>
+        <v>-30.39</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-04-08</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AXP_US_EQ</t>
+          <t>EMHGl_EQ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>iShares J.P. Morgan USD EM Bond (Dist)</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US0258161092</t>
+          <t>IE00BDFGJ734</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBP</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>2.330043</v>
+        <v>140</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>265.62170741</v>
+        <v>3.8455</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>343.63</v>
+        <v>3.8385</v>
       </c>
       <c r="H23" s="2" t="n">
-        <v>489.27</v>
+        <v>538.37</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>593.46</v>
+        <v>537.39</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01345118590338564</v>
+        <v>0.01248769564962787</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>104.19</v>
+        <v>-0.98</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.2129499049604513</v>
+        <v>-0.001820309452606943</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>-30.53</v>
+        <v>0</v>
       </c>
       <c r="N23" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2024-04-08</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>EMHGl_EQ</t>
+          <t>GOOGL_US_EQ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>iShares J.P. Morgan USD EM Bond (Dist)</t>
+          <t>Alphabet (Class A)</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>IE00BDFGJ734</t>
+          <t>US02079K3059</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>GBP</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>3.8455</v>
+        <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>3.828</v>
+        <v>346.34</v>
       </c>
       <c r="H24" s="2" t="n">
-        <v>538.37</v>
+        <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>535.92</v>
+        <v>513.5700000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01214700156597316</v>
+        <v>0.01193417416546528</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>-2.45</v>
+        <v>105.65</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>-0.004550773631517359</v>
+        <v>0.2589968621298294</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>0</v>
+        <v>-8.4</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-29</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>GOOGL_US_EQ</t>
+          <t>IBM_US_EQ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Alphabet (Class A)</t>
+          <t>IBM</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US02079K3059</t>
+          <t>US4592001014</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2017,55 +2017,55 @@
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>2</v>
+        <v>1.11022215</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>269.43</v>
+        <v>236.87151261</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>343.82</v>
+        <v>237.62</v>
       </c>
       <c r="H25" s="2" t="n">
-        <v>407.92</v>
+        <v>196.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>509.68</v>
+        <v>195.6</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.01155225361648232</v>
+        <v>0.00454528976919409</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>101.76</v>
+        <v>-0.92</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.2494606785644244</v>
+        <v>-0.004681457358029717</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-8.52</v>
+        <v>-1.54</v>
       </c>
       <c r="N25" s="4" t="n">
-        <v>0</v>
+        <v>1.11022215</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2025-10-29</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IBM_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IBM</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US4592001014</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2074,34 +2074,34 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.11022215</v>
+        <v>0.63422137</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>236.87151261</v>
+        <v>212.76482689</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>235.43</v>
+        <v>275.9</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>196.52</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>193.74</v>
+        <v>129.74</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.004391252581339829</v>
+        <v>0.00301485631214336</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>-2.78</v>
+        <v>29.89</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>-0.01414614288622023</v>
+        <v>0.299349023535303</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.59</v>
+        <v>0.2</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.11022215</v>
+        <v>0.63422137</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2137,25 +2137,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>111.04</v>
+        <v>111.19</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>128.23</v>
+        <v>128.44</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002906422620549221</v>
+        <v>0.002984647331059759</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>22.95</v>
+        <v>23.16</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.2179901215805471</v>
+        <v>0.2199848024316109</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.04</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>1.55804584</v>
@@ -2194,25 +2194,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>243.72</v>
+        <v>242.73</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>126.45</v>
+        <v>125.98</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002866077675804797</v>
+        <v>0.002927482643778484</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>7.69</v>
+        <v>7.22</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.0647524418996295</v>
+        <v>0.06079488043112159</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-1.7</v>
+        <v>-1.66</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.42010405</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>212.76482689</v>
+        <v>350.55601106</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>268.17</v>
+        <v>399.64</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>126.06</v>
+        <v>124.48</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002857238053079895</v>
+        <v>0.00289262612714356</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>26.21</v>
+        <v>15.32</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.2624937406109164</v>
+        <v>0.1403444485159399</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.16</v>
+        <v>0.03</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.42010405</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>350.55601106</v>
+        <v>57.56703616</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>394.75</v>
+        <v>64.61</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>109.16</v>
+        <v>106.81</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>122.92</v>
+        <v>119.96</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002786067757294786</v>
+        <v>0.002787591823683655</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>13.76</v>
+        <v>13.15</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1260534994503481</v>
+        <v>0.1231158131261118</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>2.70722512</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>57.56703616</v>
+        <v>53.65641702</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>63.91</v>
+        <v>59.33</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>106.81</v>
+        <v>107.64</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>118.63</v>
+        <v>119.09</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002688831907320862</v>
+        <v>0.0027673750440354</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>11.82</v>
+        <v>11.45</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1106637955247636</v>
+        <v>0.1063730955035303</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>2.70722512</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>53.65641702</v>
+        <v>509.16500577</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>58.55</v>
+        <v>567.0700000000001</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>107.64</v>
+        <v>105.75</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>117.49</v>
+        <v>117.88</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002662993010124994</v>
+        <v>0.002739257453949894</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>9.85</v>
+        <v>12.13</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.09150873281308064</v>
+        <v>0.1147044917257683</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.03</v>
+        <v>0.09</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>1.32559468</v>
+        <v>3.30858696</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>121.66614911</v>
+        <v>45.93199509</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>119.12</v>
+        <v>47.6</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>119.73</v>
+        <v>112.71</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>117.04</v>
+        <v>116.77</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002652793445442415</v>
+        <v>0.00271346363164005</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>-2.69</v>
+        <v>4.06</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>-0.02246721790695732</v>
+        <v>0.03602164847839588</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.03</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>1.32559468</v>
+        <v>3.30858696</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.43583007</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>45.93199509</v>
+        <v>322.35040597</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>47.68</v>
+        <v>360.59</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>112.71</v>
+        <v>104.04</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>116.93</v>
+        <v>116.52</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002650300218520007</v>
+        <v>0.002707654212200896</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>4.22</v>
+        <v>12.48</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.03744122083222429</v>
+        <v>0.1199538638985006</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.43583007</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.7905852</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>322.35040597</v>
+        <v>188.32884805</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>361.92</v>
+        <v>197.42</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>104.04</v>
+        <v>110.41</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>116.91</v>
+        <v>115.72</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002649846904534115</v>
+        <v>0.002689064069995604</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>12.87</v>
+        <v>5.31</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.1237024221453287</v>
+        <v>0.04809346979440268</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.02</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.7905852</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.59183053</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>509.16500577</v>
+        <v>228.00445932</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>561.05</v>
+        <v>261.6</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>105.75</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>116.6</v>
+        <v>114.79</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002642820537752782</v>
+        <v>0.002667453029681951</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>10.85</v>
+        <v>14.94</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1026004728132388</v>
+        <v>0.1496244366549825</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.59183053</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.7905852</v>
+        <v>1.32559468</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>188.32884805</v>
+        <v>121.66614911</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>196.71</v>
+        <v>116.41</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>110.41</v>
+        <v>119.73</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>115.27</v>
+        <v>114.41</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002612675157690936</v>
+        <v>0.002658622712134437</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>4.86</v>
+        <v>-5.32</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.04401775201521602</v>
+        <v>-0.04443330827695648</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.05</v>
+        <v>-0.15</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.7905852</v>
+        <v>1.32559468</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.1285649</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>228.00445932</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>260.92</v>
+        <v>1181.97</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>98.89</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>114.46</v>
+        <v>112.67</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002594315941262294</v>
+        <v>0.002618189152837925</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>14.61</v>
+        <v>13.78</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.1463194792188282</v>
+        <v>0.1393467489129336</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.17</v>
+        <v>0.2</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.1285649</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.73400968</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>249.91595261</v>
+        <v>79.10567143</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>293.48</v>
+        <v>87.52</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>95.94</v>
+        <v>101.53</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.86</v>
+        <v>112.52</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.0025580508223909</v>
+        <v>0.002614703501174432</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>16.92</v>
+        <v>10.99</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.176360225140713</v>
+        <v>0.1082438688072491</v>
       </c>
       <c r="M39" s="2" t="n">
         <v>0.17</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.73400968</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2878,25 +2878,25 @@
         <v>221.99877812</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>271.84</v>
+        <v>272.69</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>111.84</v>
+        <v>112.22</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002534931809110387</v>
+        <v>0.002607732197847447</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>20.66</v>
+        <v>21.04</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.2265847773634569</v>
+        <v>0.2307523579732397</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>0.5550481</v>
@@ -2910,17 +2910,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,34 +2929,34 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>1.73400968</v>
+        <v>0.51881442</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>79.10567143</v>
+        <v>249.91595261</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>86.84999999999999</v>
+        <v>290.76</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>101.53</v>
+        <v>95.94</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.62</v>
+        <v>111.84</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002529945355265571</v>
+        <v>0.002598901880299933</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>10.09</v>
+        <v>15.9</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.09937949374569092</v>
+        <v>0.1657285803627267</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>1.73400968</v>
+        <v>0.51881442</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.40867246</v>
+        <v>11.40066159</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>306.99401668</v>
+        <v>12.56856884</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>365.84</v>
+        <v>13.18</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>92.83</v>
+        <v>106.15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>110.82</v>
+        <v>111.41</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002511812795829874</v>
+        <v>0.002588909678864589</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>17.99</v>
+        <v>5.26</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.1937951093396531</v>
+        <v>0.04955252001884126</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.17</v>
+        <v>0.09</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.40867246</v>
+        <v>11.40066159</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,55 +3043,55 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.37810738</v>
+        <v>5.691347</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>341.38450299</v>
+        <v>105.04894536</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>395.17</v>
+        <v>26.36</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>452.96</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.75</v>
+        <v>111.23</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002510226196879251</v>
+        <v>0.002584726896868398</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>15.24</v>
+        <v>-341.73</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.1595644435137682</v>
+        <v>-0.7544374779229955</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>0.17</v>
+        <v>-9.69</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.35094641</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>96.717382</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>1162.05</v>
+        <v>110.91</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>98.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>110.73</v>
+        <v>111.09</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002509772882893358</v>
+        <v>0.002581473621982472</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>11.84</v>
+        <v>14.41</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1197289918090808</v>
+        <v>0.1490484071162598</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.35094641</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.90543241</v>
+        <v>3.81488812</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>137.713206</v>
+        <v>38.28159448</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>164.34</v>
+        <v>38.98</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>92.27</v>
+        <v>108.23</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>110.29</v>
+        <v>110.25</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002499799975203725</v>
+        <v>0.002561953972666914</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>18.02</v>
+        <v>2.02</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1952964127018533</v>
+        <v>0.01866395638917121</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.90543241</v>
+        <v>3.81488812</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.40867246</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>12.56856884</v>
+        <v>306.99401668</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>13.04</v>
+        <v>363.42</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>106.15</v>
+        <v>92.83</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>110.19</v>
+        <v>110.12</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002497533405274263</v>
+        <v>0.002558933074558554</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>4.04</v>
+        <v>17.29</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.03805934997644842</v>
+        <v>0.1862544436065927</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.40867246</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.37810738</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>148.63893521</v>
+        <v>341.38450299</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>183.95</v>
+        <v>392.5</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>88.44</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>109.63</v>
+        <v>110.03</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002484840613669275</v>
+        <v>0.002556841683560458</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>21.19</v>
+        <v>14.52</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.2395974672094075</v>
+        <v>0.1520259658674484</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.37810738</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.80409618</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>74.99726962</v>
+        <v>148.63893521</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>84.77</v>
+        <v>184.02</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>109.46</v>
+        <v>109.71</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002480987444789189</v>
+        <v>0.002549405626678341</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>12.78</v>
+        <v>21.27</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1321886636326024</v>
+        <v>0.2405020352781547</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.80409618</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.90543241</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>96.717382</v>
+        <v>137.713206</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>109.27</v>
+        <v>163.32</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>109.41</v>
+        <v>109.64</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002479854159824459</v>
+        <v>0.002547778989235378</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>12.73</v>
+        <v>17.37</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1316714935870914</v>
+        <v>0.1882518695133847</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.16</v>
+        <v>0.18</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.90543241</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.68495686</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>38.28159448</v>
+        <v>176.50746647</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>38.65</v>
+        <v>214.71</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>108.23</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>109.29</v>
+        <v>109.04</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002477134275909104</v>
+        <v>0.002533836382581409</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1.06</v>
+        <v>19.58</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.009793957313129447</v>
+        <v>0.2188687681645428</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.02</v>
+        <v>0.18</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.68495686</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2.76637723</v>
+        <v>13.30225117</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>54.82621761</v>
+        <v>10.85229847</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>52.83</v>
+        <v>10.98</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>112.48</v>
+        <v>106.96</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>108.32</v>
+        <v>108.29</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002455148547593322</v>
+        <v>0.002516408124263947</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>-4.16</v>
+        <v>1.33</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-0.03698435277382646</v>
+        <v>0.01243455497382199</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>2.76637723</v>
+        <v>13.30225117</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.42255419</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>176.50746647</v>
+        <v>324.07677699</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>213.36</v>
+        <v>344.74</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>101.39</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>108.32</v>
+        <v>108</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002455148547593322</v>
+        <v>0.002509669197714528</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>18.86</v>
+        <v>6.61</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.2108204784261122</v>
+        <v>0.06519380609527567</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.42255419</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.74206342</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>235.02053179</v>
+        <v>74.99726962</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>233.58</v>
+        <v>83.59</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>108.77</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>108.11</v>
+        <v>107.97</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002450388750741452</v>
+        <v>0.00250897206738183</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>-0.66</v>
+        <v>11.29</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>-0.006067849590879838</v>
+        <v>0.1167769962763757</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.01</v>
+        <v>0.19</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.74206342</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.59010207</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>324.07677699</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>344.03</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>101.39</v>
+        <v>89.66</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>107.75</v>
+        <v>106.94</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002442229098995388</v>
+        <v>0.002485037259292515</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>6.36</v>
+        <v>17.28</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.06272807969227735</v>
+        <v>0.1927280838724069</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.11</v>
+        <v>0.17</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.59010207</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>13.30225117</v>
+        <v>2.76637723</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>10.85229847</v>
+        <v>54.82621761</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>10.92</v>
+        <v>52.02</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>106.96</v>
+        <v>112.48</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>107.67</v>
+        <v>106.7</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002440415843051818</v>
+        <v>0.002479460216630927</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>0.71</v>
+        <v>-5.78</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.006637995512341062</v>
+        <v>-0.05138691322901849</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>13.30225117</v>
+        <v>2.76637723</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>194.45976548</v>
+        <v>62.95787236</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>234.84</v>
+        <v>63.13</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>88.09</v>
+        <v>106.15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>106.55</v>
+        <v>106.52</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002415030259841843</v>
+        <v>0.002475277434634736</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>18.46</v>
+        <v>0.37</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.2095584061755023</v>
+        <v>0.003485633537447009</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.14</v>
+        <v>0.08</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1.59010207</v>
+        <v>1.17949395</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>113.12478542</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>90.3</v>
+        <v>121.16</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>89.66</v>
+        <v>98.72</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>106.43</v>
+        <v>105.95</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002412310375926489</v>
+        <v>0.002462031958313465</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>16.77</v>
+        <v>7.23</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.1870399286192282</v>
+        <v>0.07323743922204215</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.15</v>
+        <v>0.2</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>1.59010207</v>
+        <v>1.17949395</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.1533463</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>113.12478542</v>
+        <v>104.90344487</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>120.86</v>
+        <v>123.16</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>98.72</v>
+        <v>89.53</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>105.66</v>
+        <v>105.32</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002394857787469631</v>
+        <v>0.002447392221326797</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>6.94</v>
+        <v>15.79</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.07029983792544571</v>
+        <v>0.1763654640902491</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>0.18</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.1533463</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.62445608</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>104.90344487</v>
+        <v>235.02053179</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>123.41</v>
+        <v>226.12</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>89.53</v>
+        <v>108.77</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>105.5</v>
+        <v>104.69</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002391231275582491</v>
+        <v>0.002432752484340129</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>15.97</v>
+        <v>-4.08</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.1783759633642354</v>
+        <v>-0.037510342925439</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.15</v>
+        <v>0.04</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.62445608</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.61215748</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>257.81779936</v>
+        <v>194.45976548</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>280.58</v>
+        <v>230.08</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>105.39</v>
+        <v>104.43</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002388738048660083</v>
+        <v>0.002426710688123409</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>16.34</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.09009102192800993</v>
+        <v>0.185492110341696</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.61215748</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.50675322</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>62.95787236</v>
+        <v>257.81779936</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>62.42</v>
+        <v>276.33</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>106.15</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>105.29</v>
+        <v>103.82</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002386471478730621</v>
+        <v>0.002412535704691873</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-0.86</v>
+        <v>7.14</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.008101742816768722</v>
+        <v>0.07385188249896565</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.05</v>
+        <v>0.18</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.50675322</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4132,25 +4132,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>74.25</v>
+        <v>74.98</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>102.31</v>
+        <v>103.35</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002318927694832651</v>
+        <v>0.002401613996146263</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-2.67</v>
+        <v>-1.63</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.02543341588874071</v>
+        <v>-0.01552676700323871</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.11</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>1.85908491</v>
@@ -4189,25 +4189,25 @@
         <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>123.41</v>
+        <v>124.31</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>102.26</v>
+        <v>103.04</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.00231779440986792</v>
+        <v>0.002394410316041713</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-3.1</v>
+        <v>-2.32</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.02942293090356872</v>
+        <v>-0.02201974183750949</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.1</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>1.11796351</v>
@@ -4246,25 +4246,25 @@
         <v>1150.02597682</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1309.49</v>
+        <v>1316.66</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>101.39</v>
+        <v>101.97</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.0022980752514816</v>
+        <v>0.002369546000842133</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>12.5</v>
+        <v>13.08</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1406232422094724</v>
+        <v>0.1471481606479919</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>0.10445851</v>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FB_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Meta Platforms</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US30303M1027</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,38 +4297,38 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.235295</v>
+        <v>0.97307689</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>627.34014747</v>
+        <v>154.44822659</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>580.47</v>
+        <v>140.37</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>119.82</v>
+        <v>111.44</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>101.23</v>
+        <v>101.27</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002294448739594461</v>
+        <v>0.002353279626412502</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-18.59</v>
+        <v>-10.17</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.1551493907527959</v>
+        <v>-0.09125987078248385</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-10.42</v>
+        <v>-0.01</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0</v>
+        <v>0.97307689</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>2025-01-23</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -4360,7 +4360,7 @@
         <v>126.99866255</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>115.56</v>
+        <v>115.53</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>110.45</v>
@@ -4369,7 +4369,7 @@
         <v>100.48</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002277449465123495</v>
+        <v>0.002334921860984776</v>
       </c>
       <c r="K66" s="2" t="n">
         <v>-9.970000000000001</v>
@@ -4378,7 +4378,7 @@
         <v>-0.09026708918062472</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>1.17308322</v>
@@ -4417,25 +4417,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>217.25</v>
+        <v>217.01</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>100.08</v>
+        <v>100</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002268383185405647</v>
+        <v>0.0023237677756616</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-7.74</v>
+        <v>-7.82</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.07178631051752922</v>
+        <v>-0.07252828788721945</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.03</v>
+        <v>0.06</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>0.6214908</v>
@@ -4449,17 +4449,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,34 +4468,34 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.16558147</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>154.44822659</v>
+        <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>138.7</v>
+        <v>114.65</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>111.44</v>
+        <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>100.04</v>
+        <v>99.08</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002267476557433862</v>
+        <v>0.002302389112125513</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-11.4</v>
+        <v>6.31</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.10229720028715</v>
+        <v>0.06801767812870541</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.04</v>
+        <v>0.19</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.16558147</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>107.56862839</v>
+        <v>147.21071381</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>114.99</v>
+        <v>144.57</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>92.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>99.34</v>
+        <v>98.22</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002251610567927627</v>
+        <v>0.002282404709254824</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>6.57</v>
+        <v>-1.63</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.07082030828931768</v>
+        <v>-0.01632448673009514</v>
       </c>
       <c r="M69" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,55 +4582,55 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.93456659</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>105.04894536</v>
+        <v>127.79185697</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>23.53</v>
+        <v>138.67</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>452.96</v>
+        <v>88.38</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>99.26000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002249797311984058</v>
+        <v>0.002232908455633232</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-353.7</v>
+        <v>7.71</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.7808636524196397</v>
+        <v>0.08723693143245079</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-9.82</v>
+        <v>0.17</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0</v>
+        <v>0.93456659</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PNR_US_EQ</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Pentair</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>IE00BLS09M33</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -4639,34 +4639,34 @@
         </is>
       </c>
       <c r="E71" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.84694851</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>147.21071381</v>
+        <v>80.72233697999999</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>144.48</v>
+        <v>66.66</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>110.53</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>98.13</v>
+        <v>91.28</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002224185071781136</v>
+        <v>0.002121135225623909</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-1.72</v>
+        <v>-19.25</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.01722583875813721</v>
+        <v>-0.1741608613046232</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="N71" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.84694851</v>
       </c>
       <c r="O71" t="inlineStr">
         <is>
@@ -4677,17 +4677,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>TROW_US_EQ</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>T Rowe Price</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US74144T1088</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4696,34 +4696,34 @@
         </is>
       </c>
       <c r="E72" s="4" t="n">
-        <v>0.93456659</v>
+        <v>0.63221571</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>127.79185697</v>
+        <v>102.32267085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>138.06</v>
+        <v>111.24</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>88.38</v>
+        <v>47.87</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>95.63</v>
+        <v>52.14</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.002167520823544585</v>
+        <v>0.001211612518229958</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>7.25</v>
+        <v>4.27</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.08203213396696085</v>
+        <v>0.08919991644035931</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>0.14</v>
+        <v>0.09</v>
       </c>
       <c r="N72" s="4" t="n">
-        <v>0.93456659</v>
+        <v>0.63221571</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
@@ -4734,17 +4734,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>PNR_US_EQ</t>
+          <t>MCD_US_EQ</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pentair</t>
+          <t>McDonald's</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>IE00BLS09M33</t>
+          <t>US5801351017</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -4753,150 +4753,36 @@
         </is>
       </c>
       <c r="E73" s="4" t="n">
-        <v>1.84694851</v>
+        <v>0.24236298</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>80.72233697999999</v>
+        <v>290.55592566</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>66.17</v>
+        <v>272.67</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>110.53</v>
+        <v>52.11</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>90.58</v>
+        <v>49</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.002053059042106749</v>
+        <v>0.001138646210074184</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-19.95</v>
+        <v>-3.11</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.1804939835338822</v>
+        <v>-0.05968144310113222</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.03</v>
+        <v>0.1</v>
       </c>
       <c r="N73" s="4" t="n">
-        <v>1.84694851</v>
+        <v>0.24236298</v>
       </c>
       <c r="O73" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>TROW_US_EQ</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>T Rowe Price</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>US74144T1088</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E74" s="4" t="n">
-        <v>0.63221571</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>102.32267085</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>111.3</v>
-      </c>
-      <c r="H74" s="2" t="n">
-        <v>47.87</v>
-      </c>
-      <c r="I74" s="2" t="n">
-        <v>52.16</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>0.001182242875207419</v>
-      </c>
-      <c r="K74" s="2" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>0.08961771464382703</v>
-      </c>
-      <c r="M74" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="N74" s="4" t="n">
-        <v>0.63221571</v>
-      </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>2026-04-30</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>MCD_US_EQ</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>McDonald's</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>US5801351017</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="E75" s="4" t="n">
-        <v>0.24236298</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>290.55592566</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>275.27</v>
-      </c>
-      <c r="H75" s="2" t="n">
-        <v>52.11</v>
-      </c>
-      <c r="I75" s="2" t="n">
-        <v>49.45</v>
-      </c>
-      <c r="J75" s="3" t="n">
-        <v>0.001120818830118997</v>
-      </c>
-      <c r="K75" s="2" t="n">
-        <v>-2.66</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>-0.05104586451736711</v>
-      </c>
-      <c r="M75" s="2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="N75" s="4" t="n">
-        <v>0.24236298</v>
-      </c>
-      <c r="O75" t="inlineStr">
         <is>
           <t>2026-04-30</t>
         </is>
@@ -4983,37 +4869,37 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-12 19:34:51</t>
+          <t>2026-08-13 19:33:04</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44196.49</v>
+        <v>44346.99</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>44139.13</v>
+        <v>43055.46</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>37880.19</v>
+        <v>36637.52</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6258.94</v>
+        <v>6417.94</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1652298998500271</v>
+        <v>0.1751739746576733</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1251.59</v>
+        <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>79.02</v>
+        <v>1313.27</v>
       </c>
       <c r="J2" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
   </sheetData>
@@ -5027,7 +4913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -5079,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5091,22 +4977,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>110.74</v>
+        <v>111.44</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7087.36</v>
+        <v>7132.16</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1041.59</v>
+        <v>1086.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5118,22 +5004,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>15.134</v>
+        <v>15.456</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4388.86</v>
+        <v>4482.24</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>958.15</v>
+        <v>1051.53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5145,22 +5031,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1537.8</v>
+        <v>1525.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2712.57</v>
+        <v>2691.41</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1516.61</v>
+        <v>1495.45</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5172,346 +5058,346 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>24.97</v>
+        <v>25.56</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2128.4</v>
+        <v>2179.34</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>202.59</v>
+        <v>253.53</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>CSCO_US_EQ</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>10.9260596</v>
+        <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>222.52</v>
+        <v>112.8</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1802.06</v>
+        <v>2074.59</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1252.68</v>
+        <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>549.38</v>
+        <v>428.02</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="D7" t="n">
-        <v>482.88</v>
+        <v>225.88</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1789.56</v>
+        <v>1829.81</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-108.99</v>
+        <v>577.13</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CSCO_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>18.80610988</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>123.69</v>
+        <v>487.13</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1724.13</v>
+        <v>1805.84</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1120</v>
+        <v>1898.55</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>604.13</v>
+        <v>-92.70999999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SHELl_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>50</v>
+        <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>3322.5</v>
+        <v>222.9</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1661.25</v>
+        <v>1586.52</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1649.5</v>
+        <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>11.75</v>
+        <v>-409.54</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.6</v>
+        <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>220.47</v>
+        <v>158.42</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1568.76</v>
+        <v>1477.86</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1996.06</v>
+        <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-427.3</v>
+        <v>-393.98</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>12.5822526</v>
+        <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>153.61</v>
+        <v>119.08</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1432.57</v>
+        <v>1403.97</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1871.84</v>
+        <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-439.27</v>
+        <v>60.18</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>119.04</v>
+        <v>43.49</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1403.08</v>
+        <v>1386.08</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>59.29</v>
+        <v>157.74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>ALVd_EQ</t>
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>35</v>
+        <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>43.65</v>
+        <v>437.8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1391.51</v>
+        <v>1205.88</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>1228.34</v>
+        <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>163.17</v>
+        <v>291.39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ALVd_EQ</t>
+          <t>LLOYl_EQ</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>3.2220691</v>
+        <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>438.9</v>
+        <v>115.3</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1207.67</v>
+        <v>1169.56</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>914.49</v>
+        <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>293.18</v>
+        <v>562.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LLOYl_EQ</t>
+          <t>RBSl_EQ</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>1014.362806</v>
+        <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>115.2</v>
+        <v>705.6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1168.55</v>
+        <v>1128.96</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>607.1900000000001</v>
+        <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>561.36</v>
+        <v>375.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RBSl_EQ</t>
+          <t>SNOW_US_EQ</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>160</v>
+        <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>714.6</v>
+        <v>338.47</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1143.36</v>
+        <v>1099.51</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>753.46</v>
+        <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>389.9</v>
+        <v>457.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SNOW_US_EQ</t>
+          <t>AAPL_US_EQ</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>4.3814255</v>
+        <v>3.05990683</v>
       </c>
       <c r="D17" t="n">
-        <v>333.87</v>
+        <v>304.37</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1084.25</v>
+        <v>690.52</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>641.99</v>
+        <v>491.05</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>442.26</v>
+        <v>199.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5523,238 +5409,238 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>46.25</v>
+        <v>46.5</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>685.61</v>
+        <v>689.52</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-181.97</v>
+        <v>-178.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AAPL_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>3.05990683</v>
+        <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>301.92</v>
+        <v>497.89</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>684.76</v>
+        <v>688.47</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>491.05</v>
+        <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>193.71</v>
+        <v>154.09</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.8650317</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>494.29</v>
+        <v>97.31999999999999</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>683.29</v>
+        <v>663.54</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>534.38</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>148.91</v>
+        <v>114.36</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>96</v>
+        <v>1008.5</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>654.34</v>
+        <v>655.53</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>105.16</v>
+        <v>-7.15</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>AXP_US_EQ</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>65</v>
+        <v>2.330043</v>
       </c>
       <c r="D22" t="n">
-        <v>1005.5</v>
+        <v>344.76</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>653.58</v>
+        <v>595.59</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>489.27</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>-9.1</v>
+        <v>106.32</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AXP_US_EQ</t>
+          <t>EMHGl_EQ</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>2.330043</v>
+        <v>140</v>
       </c>
       <c r="D23" t="n">
-        <v>343.63</v>
+        <v>3.8385</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>593.46</v>
+        <v>537.39</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>489.27</v>
+        <v>538.37</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>104.19</v>
+        <v>-0.98</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>EMHGl_EQ</t>
+          <t>GOOGL_US_EQ</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>140</v>
+        <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>3.828</v>
+        <v>346.34</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>535.92</v>
+        <v>513.5700000000001</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>538.37</v>
+        <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>-2.45</v>
+        <v>105.65</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GOOGL_US_EQ</t>
+          <t>IBM_US_EQ</t>
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>2</v>
+        <v>1.11022215</v>
       </c>
       <c r="D25" t="n">
-        <v>343.82</v>
+        <v>237.62</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>509.68</v>
+        <v>195.6</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>407.92</v>
+        <v>196.52</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>101.76</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>IBM_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.11022215</v>
+        <v>0.63422137</v>
       </c>
       <c r="D26" t="n">
-        <v>235.43</v>
+        <v>275.9</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>193.74</v>
+        <v>129.74</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>196.52</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>-2.78</v>
+        <v>29.89</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5766,22 +5652,22 @@
         <v>1.55804584</v>
       </c>
       <c r="D27" t="n">
-        <v>111.04</v>
+        <v>111.19</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>128.23</v>
+        <v>128.44</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>22.95</v>
+        <v>23.16</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5793,319 +5679,319 @@
         <v>0.7</v>
       </c>
       <c r="D28" t="n">
-        <v>243.72</v>
+        <v>242.73</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>126.45</v>
+        <v>125.98</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7.69</v>
+        <v>7.22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.42010405</v>
       </c>
       <c r="D29" t="n">
-        <v>268.17</v>
+        <v>399.64</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>126.06</v>
+        <v>124.48</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>26.21</v>
+        <v>15.32</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="D30" t="n">
-        <v>394.75</v>
+        <v>64.61</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>122.92</v>
+        <v>119.96</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>109.16</v>
+        <v>106.81</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>13.76</v>
+        <v>13.15</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>2.70722512</v>
       </c>
       <c r="D31" t="n">
-        <v>63.91</v>
+        <v>59.33</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>118.63</v>
+        <v>119.09</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>106.81</v>
+        <v>107.64</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>11.82</v>
+        <v>11.45</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="D32" t="n">
-        <v>58.55</v>
+        <v>567.0700000000001</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>117.49</v>
+        <v>117.88</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>107.64</v>
+        <v>105.75</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>9.85</v>
+        <v>12.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>1.32559468</v>
+        <v>3.30858696</v>
       </c>
       <c r="D33" t="n">
-        <v>119.12</v>
+        <v>47.6</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>117.04</v>
+        <v>116.77</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>119.73</v>
+        <v>112.71</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>-2.69</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.43583007</v>
       </c>
       <c r="D34" t="n">
-        <v>47.68</v>
+        <v>360.59</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>116.93</v>
+        <v>116.52</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>112.71</v>
+        <v>104.04</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>4.22</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.7905852</v>
       </c>
       <c r="D35" t="n">
-        <v>361.92</v>
+        <v>197.42</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>116.91</v>
+        <v>115.72</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>104.04</v>
+        <v>110.41</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>12.87</v>
+        <v>5.31</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.59183053</v>
       </c>
       <c r="D36" t="n">
-        <v>561.05</v>
+        <v>261.6</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>116.6</v>
+        <v>114.79</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>105.75</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>10.85</v>
+        <v>14.94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.7905852</v>
+        <v>1.32559468</v>
       </c>
       <c r="D37" t="n">
-        <v>196.71</v>
+        <v>116.41</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>115.27</v>
+        <v>114.41</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>110.41</v>
+        <v>119.73</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4.86</v>
+        <v>-5.32</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.1285649</v>
       </c>
       <c r="D38" t="n">
-        <v>260.92</v>
+        <v>1181.97</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>114.46</v>
+        <v>112.67</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>98.89</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>14.61</v>
+        <v>13.78</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.73400968</v>
       </c>
       <c r="D39" t="n">
-        <v>293.48</v>
+        <v>87.52</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.86</v>
+        <v>112.52</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>95.94</v>
+        <v>101.53</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>16.92</v>
+        <v>10.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6117,589 +6003,589 @@
         <v>0.5550481</v>
       </c>
       <c r="D40" t="n">
-        <v>271.84</v>
+        <v>272.69</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>111.84</v>
+        <v>112.22</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>20.66</v>
+        <v>21.04</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>1.73400968</v>
+        <v>0.51881442</v>
       </c>
       <c r="D41" t="n">
-        <v>86.84999999999999</v>
+        <v>290.76</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.62</v>
+        <v>111.84</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>101.53</v>
+        <v>95.94</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>10.09</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.40867246</v>
+        <v>11.40066159</v>
       </c>
       <c r="D42" t="n">
-        <v>365.84</v>
+        <v>13.18</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>110.82</v>
+        <v>111.41</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>92.83</v>
+        <v>106.15</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>17.99</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.37810738</v>
+        <v>5.691347</v>
       </c>
       <c r="D43" t="n">
-        <v>395.17</v>
+        <v>26.36</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.75</v>
+        <v>111.23</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>452.96</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>15.24</v>
+        <v>-341.73</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.35094641</v>
       </c>
       <c r="D44" t="n">
-        <v>1162.05</v>
+        <v>110.91</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>110.73</v>
+        <v>111.09</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>98.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>11.84</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.90543241</v>
+        <v>3.81488812</v>
       </c>
       <c r="D45" t="n">
-        <v>164.34</v>
+        <v>38.98</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>110.29</v>
+        <v>110.25</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>92.27</v>
+        <v>108.23</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>18.02</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.40867246</v>
       </c>
       <c r="D46" t="n">
-        <v>13.04</v>
+        <v>363.42</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>110.19</v>
+        <v>110.12</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>106.15</v>
+        <v>92.83</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>4.04</v>
+        <v>17.29</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.37810738</v>
       </c>
       <c r="D47" t="n">
-        <v>183.95</v>
+        <v>392.5</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>109.63</v>
+        <v>110.03</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>88.44</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>21.19</v>
+        <v>14.52</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.80409618</v>
       </c>
       <c r="D48" t="n">
-        <v>84.77</v>
+        <v>184.02</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>109.46</v>
+        <v>109.71</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>12.78</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.90543241</v>
       </c>
       <c r="D49" t="n">
-        <v>109.27</v>
+        <v>163.32</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>109.41</v>
+        <v>109.64</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>12.73</v>
+        <v>17.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.68495686</v>
       </c>
       <c r="D50" t="n">
-        <v>38.65</v>
+        <v>214.71</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>109.29</v>
+        <v>109.04</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>108.23</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>1.06</v>
+        <v>19.58</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>2.76637723</v>
+        <v>13.30225117</v>
       </c>
       <c r="D51" t="n">
-        <v>52.83</v>
+        <v>10.98</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>108.32</v>
+        <v>108.29</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>112.48</v>
+        <v>106.96</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-4.16</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.42255419</v>
       </c>
       <c r="D52" t="n">
-        <v>213.36</v>
+        <v>344.74</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>108.32</v>
+        <v>108</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>101.39</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>18.86</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.74206342</v>
       </c>
       <c r="D53" t="n">
-        <v>233.58</v>
+        <v>83.59</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>108.11</v>
+        <v>107.97</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>108.77</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>-0.66</v>
+        <v>11.29</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.59010207</v>
       </c>
       <c r="D54" t="n">
-        <v>344.03</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>107.75</v>
+        <v>106.94</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>101.39</v>
+        <v>89.66</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>6.36</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>13.30225117</v>
+        <v>2.76637723</v>
       </c>
       <c r="D55" t="n">
-        <v>10.92</v>
+        <v>52.02</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>107.67</v>
+        <v>106.7</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>106.96</v>
+        <v>112.48</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>0.71</v>
+        <v>-5.78</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="D56" t="n">
-        <v>234.84</v>
+        <v>63.13</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>106.55</v>
+        <v>106.52</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>88.09</v>
+        <v>106.15</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>18.46</v>
+        <v>0.37</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1.59010207</v>
+        <v>1.17949395</v>
       </c>
       <c r="D57" t="n">
-        <v>90.3</v>
+        <v>121.16</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>106.43</v>
+        <v>105.95</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>89.66</v>
+        <v>98.72</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>16.77</v>
+        <v>7.23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.1533463</v>
       </c>
       <c r="D58" t="n">
-        <v>120.86</v>
+        <v>123.16</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105.66</v>
+        <v>105.32</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>98.72</v>
+        <v>89.53</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>6.94</v>
+        <v>15.79</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1.1533463</v>
+        <v>0.62445608</v>
       </c>
       <c r="D59" t="n">
-        <v>123.41</v>
+        <v>226.12</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>105.5</v>
+        <v>104.69</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>89.53</v>
+        <v>108.77</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>15.97</v>
+        <v>-4.08</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.61215748</v>
       </c>
       <c r="D60" t="n">
-        <v>280.58</v>
+        <v>230.08</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>105.39</v>
+        <v>104.43</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>88.09</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>8.710000000000001</v>
+        <v>16.34</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.50675322</v>
       </c>
       <c r="D61" t="n">
-        <v>62.42</v>
+        <v>276.33</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>105.29</v>
+        <v>103.82</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>106.15</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-0.86</v>
+        <v>7.14</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6711,22 +6597,22 @@
         <v>1.85908491</v>
       </c>
       <c r="D62" t="n">
-        <v>74.25</v>
+        <v>74.98</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>102.31</v>
+        <v>103.35</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-2.67</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6738,22 +6624,22 @@
         <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>123.41</v>
+        <v>124.31</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>102.26</v>
+        <v>103.04</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-3.1</v>
+        <v>-2.32</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6765,49 +6651,49 @@
         <v>0.10445851</v>
       </c>
       <c r="D64" t="n">
-        <v>1309.49</v>
+        <v>1316.66</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101.39</v>
+        <v>101.97</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>12.5</v>
+        <v>13.08</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FB_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.235295</v>
+        <v>0.97307689</v>
       </c>
       <c r="D65" t="n">
-        <v>580.47</v>
+        <v>140.37</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>101.23</v>
+        <v>101.27</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>119.82</v>
+        <v>111.44</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-18.59</v>
+        <v>-10.17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6819,7 +6705,7 @@
         <v>1.17308322</v>
       </c>
       <c r="D66" t="n">
-        <v>115.56</v>
+        <v>115.53</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>100.48</v>
@@ -6834,7 +6720,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6846,232 +6732,178 @@
         <v>0.6214908</v>
       </c>
       <c r="D67" t="n">
-        <v>217.25</v>
+        <v>217.01</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>100.08</v>
+        <v>100</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-7.74</v>
+        <v>-7.82</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>138.7</v>
+        <v>114.65</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>100.04</v>
+        <v>99.08</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>111.44</v>
+        <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-11.4</v>
+        <v>6.31</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D69" t="n">
-        <v>114.99</v>
+        <v>144.57</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>99.34</v>
+        <v>98.22</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>92.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>6.57</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.93456659</v>
       </c>
       <c r="D70" t="n">
-        <v>23.53</v>
+        <v>138.67</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>99.26000000000001</v>
+        <v>96.09</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>452.96</v>
+        <v>88.38</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-353.7</v>
+        <v>7.71</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PNR_US_EQ</t>
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.84694851</v>
       </c>
       <c r="D71" t="n">
-        <v>144.48</v>
+        <v>66.66</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>98.13</v>
+        <v>91.28</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>110.53</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-1.72</v>
+        <v>-19.25</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>TROW_US_EQ</t>
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>0.93456659</v>
+        <v>0.63221571</v>
       </c>
       <c r="D72" t="n">
-        <v>138.06</v>
+        <v>111.24</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>95.63</v>
+        <v>52.14</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>88.38</v>
+        <v>47.87</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>7.25</v>
+        <v>4.27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>PNR_US_EQ</t>
+          <t>MCD_US_EQ</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>1.84694851</v>
+        <v>0.24236298</v>
       </c>
       <c r="D73" t="n">
-        <v>66.17</v>
+        <v>272.67</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>90.58</v>
+        <v>49</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>110.53</v>
+        <v>52.11</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-19.95</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>TROW_US_EQ</t>
-        </is>
-      </c>
-      <c r="C74" s="4" t="n">
-        <v>0.63221571</v>
-      </c>
-      <c r="D74" t="n">
-        <v>111.3</v>
-      </c>
-      <c r="E74" s="2" t="n">
-        <v>52.16</v>
-      </c>
-      <c r="F74" s="2" t="n">
-        <v>47.87</v>
-      </c>
-      <c r="G74" s="2" t="n">
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>MCD_US_EQ</t>
-        </is>
-      </c>
-      <c r="C75" s="4" t="n">
-        <v>0.24236298</v>
-      </c>
-      <c r="D75" t="n">
-        <v>275.27</v>
-      </c>
-      <c r="E75" s="2" t="n">
-        <v>49.45</v>
-      </c>
-      <c r="F75" s="2" t="n">
-        <v>52.11</v>
-      </c>
-      <c r="G75" s="2" t="n">
-        <v>-2.66</v>
+        <v>-3.11</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44346.99</v>
+        <v>44290.32</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43055.46</v>
+        <v>42998.66</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>36637.52</v>
+        <v>36638.67</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6417.94</v>
+        <v>6359.99</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1751739746576733</v>
+        <v>0.1735868141501861</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1291.53</v>
+        <v>1291.66</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>21.74</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-13 19:33:04</t>
+          <t>2026-08-14 19:26:50</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>111.44</v>
+        <v>110.98</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7132.16</v>
+        <v>7102.72</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1657348357886264</v>
+        <v>0.1652688184803092</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1086.39</v>
+        <v>1056.95</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1796942324964397</v>
+        <v>0.1748247121541177</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15.456</v>
+        <v>15.062</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4482.24</v>
+        <v>4367.98</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.1041568487478145</v>
+        <v>0.1016358372208986</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1051.53</v>
+        <v>937.27</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.3065050674641692</v>
+        <v>0.2732000081615759</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1525.8</v>
+        <v>1527.8</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2691.41</v>
+        <v>2694.94</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06254211829093387</v>
+        <v>0.06270689956457871</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1495.45</v>
+        <v>1498.98</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.250418074183083</v>
+        <v>1.253369677915649</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>25.56</v>
+        <v>25.57</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2179.34</v>
+        <v>2172.23</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05064280064210352</v>
+        <v>0.05054428241117236</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>253.53</v>
+        <v>246.42</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1316485011501654</v>
+        <v>0.1279565481537639</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-6.52</v>
+        <v>-13.53</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>112.8</v>
+        <v>111.71</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2074.59</v>
+        <v>2047.05</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04820865389709799</v>
+        <v>0.04763154606546745</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>428.02</v>
+        <v>400.48</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2599464341024068</v>
+        <v>0.2432207558743327</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-8.619999999999999</v>
+        <v>-14.59</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -972,17 +972,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US67066G1040</t>
+          <t>US0079031078</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -991,55 +991,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.9260596</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>150.09436705</v>
+        <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>225.88</v>
+        <v>508.75</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1252.68</v>
+        <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1829.81</v>
+        <v>1879.11</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04252053513583352</v>
+        <v>0.04372385360742559</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>577.13</v>
+        <v>-19.44</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.4607162244148545</v>
+        <v>-0.01023939322114245</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-36.8</v>
+        <v>-14.93</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US0079031078</t>
+          <t>US67066G1040</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,55 +1048,55 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>509.97</v>
+        <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>487.13</v>
+        <v>225.15</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1805.84</v>
+        <v>1817.24</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04196352800000744</v>
+        <v>0.04228423867126357</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-92.70999999999999</v>
+        <v>564.5599999999999</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0.04883200337099365</v>
+        <v>0.4506817383529712</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-8.039999999999999</v>
+        <v>-41.23</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US5738741041</t>
+          <t>US75734B1008</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1105,55 +1105,55 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.6</v>
+        <v>12.5822526</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>278.55208333</v>
+        <v>191.52532353</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>222.9</v>
+        <v>176.4</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1996.06</v>
+        <v>1871.84</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1586.52</v>
+        <v>1639.59</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03686704051442641</v>
+        <v>0.03815061020174387</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-409.54</v>
+        <v>-232.25</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.2051741931605263</v>
+        <v>-0.1240757757073254</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-13.43</v>
+        <v>-91.66</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-03-22</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US75734B1008</t>
+          <t>US5738741041</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1162,38 +1162,38 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>12.5822526</v>
+        <v>9.6</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>191.52532353</v>
+        <v>278.55208333</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>158.42</v>
+        <v>220.16</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1871.84</v>
+        <v>1996.06</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1477.86</v>
+        <v>1561.3</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03434203444939252</v>
+        <v>0.03632892839550296</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-393.98</v>
+        <v>-434.76</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2104773912300197</v>
+        <v>-0.2178090838952737</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-85.15000000000001</v>
+        <v>-20.66</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
@@ -1231,19 +1231,19 @@
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1403.97</v>
+        <v>1398.85</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03262500243995617</v>
+        <v>0.03254897936722559</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>60.18</v>
+        <v>55.06</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.04478378318040765</v>
+        <v>0.04097366403976812</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-11.03</v>
+        <v>-15.89</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>43.49</v>
+        <v>43.55</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1386.08</v>
+        <v>1384.86</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03220928038489031</v>
+        <v>0.0322234546709769</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>157.74</v>
+        <v>156.52</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1284172134750965</v>
+        <v>0.1274240031261703</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-47.51</v>
+        <v>-50.18</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>437.8</v>
+        <v>442.7</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1205.88</v>
+        <v>1218.95</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02802185085314811</v>
+        <v>0.02836299703304832</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>291.39</v>
+        <v>304.46</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3186366171308598</v>
+        <v>0.3329287362354973</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-3.59</v>
+        <v>-3.91</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>115.3</v>
+        <v>115.2</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1169.56</v>
+        <v>1168.55</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02717785839702781</v>
+        <v>0.0271902704647185</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>562.37</v>
+        <v>561.36</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.9261845550816054</v>
+        <v>0.924521154827978</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>705.6</v>
+        <v>707.8</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1128.96</v>
+        <v>1132.48</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.0262344086801092</v>
+        <v>0.02635097984329674</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>375.5</v>
+        <v>379.02</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4983675311230855</v>
+        <v>0.5030393119740928</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>338.47</v>
+        <v>328.51</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1099.51</v>
+        <v>1063.27</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02555005907017686</v>
+        <v>0.02474057496642953</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>457.52</v>
+        <v>421.28</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.7126590756865371</v>
+        <v>0.656209598280347</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-31.7</v>
+        <v>-33.92</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>304.37</v>
+        <v>305.49</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>690.52</v>
+        <v>690.53</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.01604608124449848</v>
+        <v>0.01606751740533316</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>199.47</v>
+        <v>199.48</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4062111801242236</v>
+        <v>0.406231544649221</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-19.45</v>
+        <v>-21.18</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.46065664</v>
@@ -1599,17 +1599,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US6701002056</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1618,55 +1618,55 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>20</v>
+        <v>1.8650317</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>57.84</v>
+        <v>369.46288902</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46.5</v>
+        <v>495.2</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>867.58</v>
+        <v>534.38</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>689.52</v>
+        <v>682.25</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01602284356674186</v>
+        <v>0.01587485518339326</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-178.06</v>
+        <v>147.87</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.205237557343415</v>
+        <v>0.2767132003443243</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-9.91</v>
+        <v>-25.36</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0</v>
+        <v>0.3650317</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>US6701002056</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1675,38 +1675,38 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.8650317</v>
+        <v>20</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>369.46288902</v>
+        <v>57.84</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>497.89</v>
+        <v>45.97</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>534.38</v>
+        <v>867.58</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>688.47</v>
+        <v>679.1799999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01599844400509742</v>
+        <v>0.01580342124361602</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>154.09</v>
+        <v>-188.4</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2883528575171226</v>
+        <v>-0.2171557666151825</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-23.5</v>
+        <v>-13.03</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3650317</v>
+        <v>0</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
@@ -1738,25 +1738,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>97.31999999999999</v>
+        <v>96.95</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>663.54</v>
+        <v>658.6</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01541912869862498</v>
+        <v>0.01532455789488135</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>114.36</v>
+        <v>109.42</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.2082377362613351</v>
+        <v>0.199242507010452</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-22.81</v>
+        <v>-24.73</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
         <v>1019.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1008.5</v>
+        <v>996</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>655.53</v>
+        <v>647.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01523299489979449</v>
+        <v>0.01506395199080806</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-7.15</v>
+        <v>-15.28</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.01078952133759884</v>
+        <v>-0.02305788615923221</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>344.76</v>
+        <v>342.64</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>595.59</v>
+        <v>589.77</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01384012849506292</v>
+        <v>0.01372299500404521</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>106.32</v>
+        <v>100.5</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.2173033294499969</v>
+        <v>0.2054080569010976</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-30.39</v>
+        <v>-32.07</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,22 +1909,22 @@
         <v>3.8455</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3.8385</v>
+        <v>3.8295</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>537.39</v>
+        <v>536.13</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01248769564962787</v>
+        <v>0.01247487887060847</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-0.98</v>
+        <v>-2.24</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.001820309452606943</v>
+        <v>-0.004160707320244442</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -1966,25 +1966,25 @@
         <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>346.34</v>
+        <v>345.41</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>513.5700000000001</v>
+        <v>510.32</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01193417416546528</v>
+        <v>0.01187432187202528</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>105.65</v>
+        <v>102.4</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.2589968621298294</v>
+        <v>0.2510296136497353</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-8.4</v>
+        <v>-9.859999999999999</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>237.62</v>
+        <v>234.8</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>195.6</v>
+        <v>192.57</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.00454528976919409</v>
+        <v>0.00448079276316019</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-0.92</v>
+        <v>-3.95</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.004681457358029717</v>
+        <v>-0.02009973539588846</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-1.54</v>
+        <v>-2.25</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>1.11022215</v>
@@ -2055,17 +2055,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2074,34 +2074,34 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.55804584</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>212.76482689</v>
+        <v>91.20399179</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>275.9</v>
+        <v>111.23</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.28</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>129.74</v>
+        <v>128.02</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.00301485631214336</v>
+        <v>0.002978818557094914</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>29.89</v>
+        <v>22.74</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.299349023535303</v>
+        <v>0.2159954407294833</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.31</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.55804584</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2112,17 +2112,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2131,34 +2131,34 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.63422137</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>91.20399179</v>
+        <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>111.19</v>
+        <v>272.68</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>128.44</v>
+        <v>127.75</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002984647331059759</v>
+        <v>0.002972536093336004</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>23.16</v>
+        <v>27.9</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.2199848024316109</v>
+        <v>0.2794191286930396</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.17</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.63422137</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2194,25 +2194,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>242.73</v>
+        <v>246.37</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>125.98</v>
+        <v>127.4</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002927482643778484</v>
+        <v>0.002964392158833714</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>7.22</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.06079488043112159</v>
+        <v>0.07275176827214551</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-1.66</v>
+        <v>-2.09</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
@@ -2251,25 +2251,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>399.64</v>
+        <v>399.81</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>124.48</v>
+        <v>124.08</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.00289262612714356</v>
+        <v>0.002887141122983416</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>15.32</v>
+        <v>14.92</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1403444485159399</v>
+        <v>0.1366801026016856</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>0.03</v>
+        <v>-0.37</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.42010405</v>
@@ -2308,25 +2308,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>64.61</v>
+        <v>64.22</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>119.96</v>
+        <v>118.8</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002787591823683655</v>
+        <v>0.002764284053920292</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>13.15</v>
+        <v>11.99</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1231158131261118</v>
+        <v>0.1122554067971164</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.32</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>2.50421091</v>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>53.65641702</v>
+        <v>509.16500577</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>59.33</v>
+        <v>569.87</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>107.64</v>
+        <v>105.75</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>119.09</v>
+        <v>118.03</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.0027673750440354</v>
+        <v>0.002746367398015253</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>11.45</v>
+        <v>12.28</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1063730955035303</v>
+        <v>0.1161229314420804</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>0.06</v>
+        <v>-0.29</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.28038062</v>
+        <v>2.70722512</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>509.16500577</v>
+        <v>53.65641702</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>567.0700000000001</v>
+        <v>58.93</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>105.75</v>
+        <v>107.64</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>117.88</v>
+        <v>117.85</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002739257453949894</v>
+        <v>0.002742179088842646</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>12.13</v>
+        <v>10.21</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1147044917257683</v>
+        <v>0.09485321441843182</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.34</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.28038062</v>
+        <v>2.70722512</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
         <v>45.93199509</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>47.6</v>
+        <v>48.21</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>116.77</v>
+        <v>117.83</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.00271346363164005</v>
+        <v>0.002741713721156802</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>4.06</v>
+        <v>5.12</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.03602164847839588</v>
+        <v>0.0454263153225091</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.45</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>3.30858696</v>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.7905852</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>322.35040597</v>
+        <v>188.32884805</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>360.59</v>
+        <v>200.37</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>104.04</v>
+        <v>110.41</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>116.52</v>
+        <v>117.02</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002707654212200896</v>
+        <v>0.002722866329880072</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>12.48</v>
+        <v>6.61</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1199538638985006</v>
+        <v>0.05986776560094195</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>0.12</v>
+        <v>-0.42</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.7905852</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.7905852</v>
+        <v>1.32559468</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>188.32884805</v>
+        <v>121.66614911</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>197.42</v>
+        <v>118.3</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>110.41</v>
+        <v>119.73</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>115.72</v>
+        <v>115.84</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002689064069995604</v>
+        <v>0.002695409636415208</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>5.31</v>
+        <v>-3.89</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.04809346979440268</v>
+        <v>-0.03248976864612044</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.59</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.7905852</v>
+        <v>1.32559468</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.43583007</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>228.00445932</v>
+        <v>322.35040597</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>261.6</v>
+        <v>358.88</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>104.04</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>114.79</v>
+        <v>115.54</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002667453029681951</v>
+        <v>0.00268842912112753</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>14.94</v>
+        <v>11.5</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1496244366549825</v>
+        <v>0.1105344098423683</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.26</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.43583007</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.59183053</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>121.66614911</v>
+        <v>228.00445932</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>116.41</v>
+        <v>261.01</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>114.41</v>
+        <v>114.11</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002658622712134437</v>
+        <v>0.0026551553315896</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>-5.32</v>
+        <v>14.26</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>-0.04443330827695648</v>
+        <v>0.142814221331998</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.59183053</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.1285649</v>
+        <v>3.81488812</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>38.28159448</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>1181.97</v>
+        <v>40.36</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>98.89</v>
+        <v>108.23</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>112.67</v>
+        <v>113.74</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002618189152837925</v>
+        <v>0.002646546029401465</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>13.78</v>
+        <v>5.51</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.1393467489129336</v>
+        <v>0.05091009886353137</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.35</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.1285649</v>
+        <v>3.81488812</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2821,25 +2821,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>87.52</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.52</v>
+        <v>112.17</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002614703501174432</v>
+        <v>0.002610014666062619</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>10.99</v>
+        <v>10.64</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.1082438688072491</v>
+        <v>0.1047966118388654</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>0.17</v>
+        <v>-0.2</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>1.73400968</v>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>221.99877812</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>272.69</v>
+        <v>1174.69</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112.22</v>
+        <v>111.56</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002607732197847447</v>
+        <v>0.002595820951644341</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>21.04</v>
+        <v>12.67</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.2307523579732397</v>
+        <v>0.1281221559308322</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2935,25 +2935,25 @@
         <v>249.91595261</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>290.76</v>
+        <v>290.38</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.84</v>
+        <v>111.29</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002598901880299933</v>
+        <v>0.002589538487885432</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>15.9</v>
+        <v>15.35</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.1657285803627267</v>
+        <v>0.159995830727538</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>0.19</v>
+        <v>-0.16</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0.51881442</v>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.37810738</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>12.56856884</v>
+        <v>341.38450299</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>13.18</v>
+        <v>395.35</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>106.15</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>111.41</v>
+        <v>110.43</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002588909678864589</v>
+        <v>0.00256952767739409</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>5.26</v>
+        <v>14.92</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.04955252001884126</v>
+        <v>0.1562140090042927</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.15</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.37810738</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,38 +3043,38 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.5550481</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>105.04894536</v>
+        <v>221.99877812</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>26.36</v>
+        <v>268.88</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>452.96</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>111.23</v>
+        <v>110.25</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002584726896868398</v>
+        <v>0.002565339368221483</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>-341.73</v>
+        <v>19.07</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>-0.7544374779229955</v>
+        <v>0.2091467427067339</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-9.69</v>
+        <v>-0.15</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0</v>
+        <v>0.5550481</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -3106,25 +3106,25 @@
         <v>96.717382</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>110.91</v>
+        <v>110.34</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>111.09</v>
+        <v>110.12</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002581473621982472</v>
+        <v>0.00256231447826349</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>14.41</v>
+        <v>13.44</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1490484071162598</v>
+        <v>0.1390153082333471</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>0.19</v>
+        <v>-0.15</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>1.35094641</v>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>3.81488812</v>
+        <v>2.76637723</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>38.28159448</v>
+        <v>54.82621761</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>38.98</v>
+        <v>53.81</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>108.23</v>
+        <v>112.48</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>110.25</v>
+        <v>109.96</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002561953972666914</v>
+        <v>0.002558591536776728</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.02</v>
+        <v>-2.52</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.01866395638917121</v>
+        <v>-0.02240398293029872</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.44</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>3.81488812</v>
+        <v>2.76637723</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.80409618</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>306.99401668</v>
+        <v>148.63893521</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>363.42</v>
+        <v>185.11</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>92.83</v>
+        <v>88.44</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>110.12</v>
+        <v>109.96</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002558933074558554</v>
+        <v>0.002558591536776728</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>17.29</v>
+        <v>21.52</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1862544436065927</v>
+        <v>0.2433288104929896</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>0.19</v>
+        <v>-0.14</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.80409618</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.40867246</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>341.38450299</v>
+        <v>306.99401668</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>392.5</v>
+        <v>363.08</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>110.03</v>
+        <v>109.61</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002556841683560458</v>
+        <v>0.002550447602274438</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>14.52</v>
+        <v>16.78</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1520259658674484</v>
+        <v>0.1807605300010773</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>0.19</v>
+        <v>-0.15</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.40867246</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.68495686</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>148.63893521</v>
+        <v>176.50746647</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>184.02</v>
+        <v>216.1</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>88.44</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>109.71</v>
+        <v>109.34</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002549405626678341</v>
+        <v>0.002544165138515528</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>21.27</v>
+        <v>19.88</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.2405020352781547</v>
+        <v>0.2222222222222222</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>0.18</v>
+        <v>-0.15</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.68495686</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.90543241</v>
+        <v>11.40066159</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>137.713206</v>
+        <v>12.56856884</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>163.32</v>
+        <v>12.96</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>92.27</v>
+        <v>106.15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>109.64</v>
+        <v>109.15</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002547778989235378</v>
+        <v>0.002539744145499999</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>17.37</v>
+        <v>3</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1882518695133847</v>
+        <v>0.02826189354686764</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>0.18</v>
+        <v>-0.3</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.90543241</v>
+        <v>11.40066159</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.90543241</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>176.50746647</v>
+        <v>137.713206</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>214.71</v>
+        <v>163.15</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>109.04</v>
+        <v>109.12</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002533836382581409</v>
+        <v>0.002539046093971232</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>19.58</v>
+        <v>16.85</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.2188687681645428</v>
+        <v>0.1826162349626098</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>0.18</v>
+        <v>-0.16</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.90543241</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3505,25 +3505,25 @@
         <v>10.85229847</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>10.98</v>
+        <v>10.97</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>108.29</v>
+        <v>107.8</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002516408124263947</v>
+        <v>0.00250833182670545</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>1.33</v>
+        <v>0.84</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.01243455497382199</v>
+        <v>0.007853403141361256</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>0.07000000000000001</v>
+        <v>-0.32</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>13.30225117</v>
@@ -3562,25 +3562,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>344.74</v>
+        <v>344.9</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>108</v>
+        <v>107.66</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002509669197714528</v>
+        <v>0.002505074252904534</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>6.61</v>
+        <v>6.27</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.06519380609527567</v>
+        <v>0.06184041818719795</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>0.14</v>
+        <v>-0.23</v>
       </c>
       <c r="N52" s="4" t="n">
         <v>0.42255419</v>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,38 +3613,38 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1.74206342</v>
+        <v>5.691347</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>74.99726962</v>
+        <v>105.04894536</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>83.59</v>
+        <v>25.56</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>452.96</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>107.97</v>
+        <v>107.46</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.00250897206738183</v>
+        <v>0.002500420576046082</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>11.29</v>
+        <v>-345.5</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1167769962763757</v>
+        <v>-0.7627605086541859</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>0.19</v>
+        <v>-11.31</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
@@ -3676,25 +3676,25 @@
         <v>76.19636644000001</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>90.70999999999999</v>
+        <v>91.27</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>106.94</v>
+        <v>107.21</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002485037259292515</v>
+        <v>0.002494603479973018</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>17.28</v>
+        <v>17.55</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.1927280838724069</v>
+        <v>0.1957394601829132</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>0.17</v>
+        <v>-0.16</v>
       </c>
       <c r="N54" s="4" t="n">
         <v>1.59010207</v>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.74206342</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>54.82621761</v>
+        <v>74.99726962</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>52.02</v>
+        <v>83.28</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>112.48</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>106.7</v>
+        <v>107.17</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002479460216630927</v>
+        <v>0.002493672744601327</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>-5.78</v>
+        <v>10.49</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>-0.05138691322901849</v>
+        <v>0.1085022755482002</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.17</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.74206342</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.62445608</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>62.95787236</v>
+        <v>235.02053179</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>63.13</v>
+        <v>230.78</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>106.15</v>
+        <v>108.77</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>106.52</v>
+        <v>106.46</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002475277434634736</v>
+        <v>0.002477152191753824</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>0.37</v>
+        <v>-2.31</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.003485633537447009</v>
+        <v>-0.02123747356807943</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>0.08</v>
+        <v>-0.35</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.62445608</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3847,25 +3847,25 @@
         <v>113.12478542</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>121.16</v>
+        <v>121.71</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>105.95</v>
+        <v>106.05</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002462031958313465</v>
+        <v>0.002467612154193998</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.07323743922204215</v>
+        <v>0.07425040518638575</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.15</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>1.17949395</v>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>104.90344487</v>
+        <v>62.95787236</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>123.16</v>
+        <v>62.9</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>89.53</v>
+        <v>106.15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>105.32</v>
+        <v>105.75</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002447392221326797</v>
+        <v>0.002460631638906321</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>15.79</v>
+        <v>-0.4</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.1763654640902491</v>
+        <v>-0.003768252472915685</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>0.18</v>
+        <v>-0.3</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.61215748</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>235.02053179</v>
+        <v>194.45976548</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>226.12</v>
+        <v>233.71</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>108.77</v>
+        <v>88.09</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>104.69</v>
+        <v>105.69</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002432752484340129</v>
+        <v>0.002459235535848785</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-4.08</v>
+        <v>17.6</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.037510342925439</v>
+        <v>0.1997956635259394</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>0.04</v>
+        <v>-0.15</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.61215748</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.1533463</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>194.45976548</v>
+        <v>104.90344487</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>230.08</v>
+        <v>123.8</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>88.09</v>
+        <v>89.53</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>104.43</v>
+        <v>105.48</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002426710688123409</v>
+        <v>0.002454349175147411</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>16.34</v>
+        <v>15.95</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.185492110341696</v>
+        <v>0.1781525745560147</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.1533463</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4075,25 +4075,25 @@
         <v>257.81779936</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>276.33</v>
+        <v>276.43</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>103.82</v>
+        <v>103.48</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002412535704691873</v>
+        <v>0.002407812406562894</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>7.14</v>
+        <v>6.8</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.07385188249896565</v>
+        <v>0.0703351261894911</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>0.50675322</v>
@@ -4132,25 +4132,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>74.98</v>
+        <v>74.81</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>103.35</v>
+        <v>102.74</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002401613996146263</v>
+        <v>0.002390593802186623</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-1.63</v>
+        <v>-2.24</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.01552676700323871</v>
+        <v>-0.02133739759954277</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>0.11</v>
+        <v>-0.27</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>1.85908491</v>
@@ -4189,25 +4189,25 @@
         <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>124.31</v>
+        <v>124.18</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>103.04</v>
+        <v>102.56</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002394410316041713</v>
+        <v>0.002386405493014017</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-2.32</v>
+        <v>-2.8</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.02201974183750949</v>
+        <v>-0.02657555049354594</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.28</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>1.11796351</v>
@@ -4246,25 +4246,25 @@
         <v>1150.02597682</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1316.66</v>
+        <v>1318.66</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>101.97</v>
+        <v>101.75</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002369546000842133</v>
+        <v>0.002367558101737287</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>13.08</v>
+        <v>12.86</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1471481606479919</v>
+        <v>0.1446731915851052</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>0.10445851</v>
@@ -4303,25 +4303,25 @@
         <v>154.44822659</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>140.37</v>
+        <v>140.84</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>101.27</v>
+        <v>101.24</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002353279626412502</v>
+        <v>0.002355691225748235</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-10.17</v>
+        <v>-10.2</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.09125987078248385</v>
+        <v>-0.09152907394113424</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.42</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>0.97307689</v>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.6214908</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>126.99866255</v>
+        <v>234.11448729</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>115.53</v>
+        <v>218.1</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>110.45</v>
+        <v>107.82</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>100.48</v>
+        <v>100.13</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002334921860984776</v>
+        <v>0.002329863319183828</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-9.970000000000001</v>
+        <v>-7.69</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.09026708918062472</v>
+        <v>-0.07132257466147283</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>0</v>
+        <v>-0.34</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.6214908</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>234.11448729</v>
+        <v>126.99866255</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>217.01</v>
+        <v>115.45</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>107.82</v>
+        <v>110.45</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>100</v>
+        <v>100.05</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.0023237677756616</v>
+        <v>0.002328001848440448</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-7.82</v>
+        <v>-10.4</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.07252828788721945</v>
+        <v>-0.09416025350837483</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>0.06</v>
+        <v>-0.39</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4474,25 +4474,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>114.65</v>
+        <v>114.31</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>99.08</v>
+        <v>98.42</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002302389112125513</v>
+        <v>0.002290074382044067</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>6.31</v>
+        <v>5.65</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.06801767812870541</v>
+        <v>0.06090330925945888</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>0.19</v>
+        <v>-0.15</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.16558147</v>
@@ -4531,25 +4531,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>144.57</v>
+        <v>144.59</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>98.22</v>
+        <v>97.88</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002282404709254824</v>
+        <v>0.002277509454526247</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-1.63</v>
+        <v>-1.97</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.01632448673009514</v>
+        <v>-0.01972959439158738</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>0.16</v>
+        <v>-0.2</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4588,25 +4588,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>138.67</v>
+        <v>139.15</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>96.09</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002232908455633232</v>
+        <v>0.002235393678957259</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>7.71</v>
+        <v>7.69</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.08723693143245079</v>
+        <v>0.08701063589047296</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>0.93456659</v>
@@ -4645,25 +4645,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>66.66</v>
+        <v>66.16</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>91.28</v>
+        <v>90.27</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002121135225623909</v>
+        <v>0.002100437050062161</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-19.25</v>
+        <v>-20.26</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1741608613046232</v>
+        <v>-0.1832986519496969</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>0.01</v>
+        <v>-0.39</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.84694851</v>
@@ -4702,25 +4702,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>111.24</v>
+        <v>110.47</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>52.14</v>
+        <v>51.59</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001211612518229958</v>
+        <v>0.001200415945637608</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4.27</v>
+        <v>3.72</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.08919991644035931</v>
+        <v>0.07771046584499687</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>0.09</v>
+        <v>-0.09</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.63221571</v>
@@ -4759,25 +4759,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>272.67</v>
+        <v>273.77</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>49</v>
+        <v>49.02</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001138646210074184</v>
+        <v>0.001140616198006504</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-3.11</v>
+        <v>-3.09</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.05968144310113222</v>
+        <v>-0.05929763960852043</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.24236298</v>
@@ -4810,7 +4810,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4869,34 +4869,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-13 19:33:04</t>
+          <t>2026-08-14 19:26:50</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44346.99</v>
+        <v>44290.32</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43055.46</v>
+        <v>42998.66</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>36637.52</v>
+        <v>36638.67</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6417.94</v>
+        <v>6359.99</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1751739746576733</v>
+        <v>0.1735868141501861</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1313.27</v>
+        <v>1314.55</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4977,22 +4977,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>111.44</v>
+        <v>110.98</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7132.16</v>
+        <v>7102.72</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1086.39</v>
+        <v>1056.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5004,22 +5004,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>15.456</v>
+        <v>15.062</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4482.24</v>
+        <v>4367.98</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1051.53</v>
+        <v>937.27</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5031,22 +5031,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1525.8</v>
+        <v>1527.8</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2691.41</v>
+        <v>2694.94</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1495.45</v>
+        <v>1498.98</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5058,22 +5058,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>25.56</v>
+        <v>25.57</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2179.34</v>
+        <v>2172.23</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>253.53</v>
+        <v>246.42</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5085,130 +5085,130 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>112.8</v>
+        <v>111.71</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2074.59</v>
+        <v>2047.05</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>428.02</v>
+        <v>400.48</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.9260596</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>225.88</v>
+        <v>508.75</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1829.81</v>
+        <v>1879.11</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1252.68</v>
+        <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>577.13</v>
+        <v>-19.44</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>487.13</v>
+        <v>225.15</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1805.84</v>
+        <v>1817.24</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-92.70999999999999</v>
+        <v>564.5599999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.6</v>
+        <v>12.5822526</v>
       </c>
       <c r="D9" t="n">
-        <v>222.9</v>
+        <v>176.4</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1586.52</v>
+        <v>1639.59</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1996.06</v>
+        <v>1871.84</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-409.54</v>
+        <v>-232.25</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>12.5822526</v>
+        <v>9.6</v>
       </c>
       <c r="D10" t="n">
-        <v>158.42</v>
+        <v>220.16</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1477.86</v>
+        <v>1561.3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1871.84</v>
+        <v>1996.06</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-393.98</v>
+        <v>-434.76</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5223,19 +5223,19 @@
         <v>119.08</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1403.97</v>
+        <v>1398.85</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>60.18</v>
+        <v>55.06</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5247,22 +5247,22 @@
         <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>43.49</v>
+        <v>43.55</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1386.08</v>
+        <v>1384.86</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>157.74</v>
+        <v>156.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5274,22 +5274,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>437.8</v>
+        <v>442.7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1205.88</v>
+        <v>1218.95</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>291.39</v>
+        <v>304.46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5301,22 +5301,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>115.3</v>
+        <v>115.2</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1169.56</v>
+        <v>1168.55</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>562.37</v>
+        <v>561.36</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5328,22 +5328,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>705.6</v>
+        <v>707.8</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1128.96</v>
+        <v>1132.48</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>375.5</v>
+        <v>379.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5355,22 +5355,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>338.47</v>
+        <v>328.51</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1099.51</v>
+        <v>1063.27</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>457.52</v>
+        <v>421.28</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5382,76 +5382,76 @@
         <v>3.05990683</v>
       </c>
       <c r="D17" t="n">
-        <v>304.37</v>
+        <v>305.49</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>690.52</v>
+        <v>690.53</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>199.47</v>
+        <v>199.48</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>20</v>
+        <v>1.8650317</v>
       </c>
       <c r="D18" t="n">
-        <v>46.5</v>
+        <v>495.2</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>689.52</v>
+        <v>682.25</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>867.58</v>
+        <v>534.38</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-178.06</v>
+        <v>147.87</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.8650317</v>
+        <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>497.89</v>
+        <v>45.97</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>688.47</v>
+        <v>679.1799999999999</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>534.38</v>
+        <v>867.58</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>154.09</v>
+        <v>-188.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5463,22 +5463,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>97.31999999999999</v>
+        <v>96.95</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>663.54</v>
+        <v>658.6</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>114.36</v>
+        <v>109.42</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5490,22 +5490,22 @@
         <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>1008.5</v>
+        <v>996</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>655.53</v>
+        <v>647.4</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-7.15</v>
+        <v>-15.28</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5517,22 +5517,22 @@
         <v>2.330043</v>
       </c>
       <c r="D22" t="n">
-        <v>344.76</v>
+        <v>342.64</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>595.59</v>
+        <v>589.77</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>106.32</v>
+        <v>100.5</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5544,22 +5544,22 @@
         <v>140</v>
       </c>
       <c r="D23" t="n">
-        <v>3.8385</v>
+        <v>3.8295</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>537.39</v>
+        <v>536.13</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-0.98</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5571,22 +5571,22 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>346.34</v>
+        <v>345.41</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>513.5700000000001</v>
+        <v>510.32</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>105.65</v>
+        <v>102.4</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5598,76 +5598,76 @@
         <v>1.11022215</v>
       </c>
       <c r="D25" t="n">
-        <v>237.62</v>
+        <v>234.8</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>195.6</v>
+        <v>192.57</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-0.92</v>
+        <v>-3.95</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.55804584</v>
       </c>
       <c r="D26" t="n">
-        <v>275.9</v>
+        <v>111.23</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>129.74</v>
+        <v>128.02</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.28</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>29.89</v>
+        <v>22.74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>111.19</v>
+        <v>272.68</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>128.44</v>
+        <v>127.75</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>23.16</v>
+        <v>27.9</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5679,22 +5679,22 @@
         <v>0.7</v>
       </c>
       <c r="D28" t="n">
-        <v>242.73</v>
+        <v>246.37</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>125.98</v>
+        <v>127.4</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7.22</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5706,22 +5706,22 @@
         <v>0.42010405</v>
       </c>
       <c r="D29" t="n">
-        <v>399.64</v>
+        <v>399.81</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>124.48</v>
+        <v>124.08</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>15.32</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5733,76 +5733,76 @@
         <v>2.50421091</v>
       </c>
       <c r="D30" t="n">
-        <v>64.61</v>
+        <v>64.22</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>119.96</v>
+        <v>118.8</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>13.15</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="D31" t="n">
-        <v>59.33</v>
+        <v>569.87</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>119.09</v>
+        <v>118.03</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>107.64</v>
+        <v>105.75</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>11.45</v>
+        <v>12.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.28038062</v>
+        <v>2.70722512</v>
       </c>
       <c r="D32" t="n">
-        <v>567.0700000000001</v>
+        <v>58.93</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>117.88</v>
+        <v>117.85</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>105.75</v>
+        <v>107.64</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>12.13</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5814,157 +5814,157 @@
         <v>3.30858696</v>
       </c>
       <c r="D33" t="n">
-        <v>47.6</v>
+        <v>48.21</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>116.77</v>
+        <v>117.83</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>4.06</v>
+        <v>5.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.7905852</v>
       </c>
       <c r="D34" t="n">
-        <v>360.59</v>
+        <v>200.37</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>116.52</v>
+        <v>117.02</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>104.04</v>
+        <v>110.41</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12.48</v>
+        <v>6.61</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.7905852</v>
+        <v>1.32559468</v>
       </c>
       <c r="D35" t="n">
-        <v>197.42</v>
+        <v>118.3</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>115.72</v>
+        <v>115.84</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>110.41</v>
+        <v>119.73</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>5.31</v>
+        <v>-3.89</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.43583007</v>
       </c>
       <c r="D36" t="n">
-        <v>261.6</v>
+        <v>358.88</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>114.79</v>
+        <v>115.54</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>104.04</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>14.94</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.59183053</v>
       </c>
       <c r="D37" t="n">
-        <v>116.41</v>
+        <v>261.01</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>114.41</v>
+        <v>114.11</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>-5.32</v>
+        <v>14.26</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.1285649</v>
+        <v>3.81488812</v>
       </c>
       <c r="D38" t="n">
-        <v>1181.97</v>
+        <v>40.36</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>112.67</v>
+        <v>113.74</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>98.89</v>
+        <v>108.23</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>13.78</v>
+        <v>5.51</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5976,49 +5976,49 @@
         <v>1.73400968</v>
       </c>
       <c r="D39" t="n">
-        <v>87.52</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.52</v>
+        <v>112.17</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>10.99</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="D40" t="n">
-        <v>272.69</v>
+        <v>1174.69</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>112.22</v>
+        <v>111.56</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>21.04</v>
+        <v>12.67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6030,76 +6030,76 @@
         <v>0.51881442</v>
       </c>
       <c r="D41" t="n">
-        <v>290.76</v>
+        <v>290.38</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.84</v>
+        <v>111.29</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15.9</v>
+        <v>15.35</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.37810738</v>
       </c>
       <c r="D42" t="n">
-        <v>13.18</v>
+        <v>395.35</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>111.41</v>
+        <v>110.43</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>106.15</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>5.26</v>
+        <v>14.92</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.5550481</v>
       </c>
       <c r="D43" t="n">
-        <v>26.36</v>
+        <v>268.88</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>111.23</v>
+        <v>110.25</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>452.96</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>-341.73</v>
+        <v>19.07</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6111,184 +6111,184 @@
         <v>1.35094641</v>
       </c>
       <c r="D44" t="n">
-        <v>110.91</v>
+        <v>110.34</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>111.09</v>
+        <v>110.12</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>14.41</v>
+        <v>13.44</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>3.81488812</v>
+        <v>2.76637723</v>
       </c>
       <c r="D45" t="n">
-        <v>38.98</v>
+        <v>53.81</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>110.25</v>
+        <v>109.96</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>108.23</v>
+        <v>112.48</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>2.02</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.80409618</v>
       </c>
       <c r="D46" t="n">
-        <v>363.42</v>
+        <v>185.11</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>110.12</v>
+        <v>109.96</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>92.83</v>
+        <v>88.44</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>17.29</v>
+        <v>21.52</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.40867246</v>
       </c>
       <c r="D47" t="n">
-        <v>392.5</v>
+        <v>363.08</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>110.03</v>
+        <v>109.61</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>14.52</v>
+        <v>16.78</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.68495686</v>
       </c>
       <c r="D48" t="n">
-        <v>184.02</v>
+        <v>216.1</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>109.71</v>
+        <v>109.34</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>88.44</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>21.27</v>
+        <v>19.88</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.90543241</v>
+        <v>11.40066159</v>
       </c>
       <c r="D49" t="n">
-        <v>163.32</v>
+        <v>12.96</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>109.64</v>
+        <v>109.15</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>92.27</v>
+        <v>106.15</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>17.37</v>
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.90543241</v>
       </c>
       <c r="D50" t="n">
-        <v>214.71</v>
+        <v>163.15</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>109.04</v>
+        <v>109.12</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>19.58</v>
+        <v>16.85</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6300,22 +6300,22 @@
         <v>13.30225117</v>
       </c>
       <c r="D51" t="n">
-        <v>10.98</v>
+        <v>10.97</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>108.29</v>
+        <v>107.8</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>1.33</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6327,49 +6327,49 @@
         <v>0.42255419</v>
       </c>
       <c r="D52" t="n">
-        <v>344.74</v>
+        <v>344.9</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>108</v>
+        <v>107.66</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>6.61</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1.74206342</v>
+        <v>5.691347</v>
       </c>
       <c r="D53" t="n">
-        <v>83.59</v>
+        <v>25.56</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>107.97</v>
+        <v>107.46</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>452.96</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>11.29</v>
+        <v>-345.5</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6381,76 +6381,76 @@
         <v>1.59010207</v>
       </c>
       <c r="D54" t="n">
-        <v>90.70999999999999</v>
+        <v>91.27</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>106.94</v>
+        <v>107.21</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>17.28</v>
+        <v>17.55</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>2.76637723</v>
+        <v>1.74206342</v>
       </c>
       <c r="D55" t="n">
-        <v>52.02</v>
+        <v>83.28</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>106.7</v>
+        <v>107.17</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>112.48</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>-5.78</v>
+        <v>10.49</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.62445608</v>
       </c>
       <c r="D56" t="n">
-        <v>63.13</v>
+        <v>230.78</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>106.52</v>
+        <v>106.46</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>106.15</v>
+        <v>108.77</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>0.37</v>
+        <v>-2.31</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6462,103 +6462,103 @@
         <v>1.17949395</v>
       </c>
       <c r="D57" t="n">
-        <v>121.16</v>
+        <v>121.71</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>105.95</v>
+        <v>106.05</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>7.23</v>
+        <v>7.33</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="D58" t="n">
-        <v>123.16</v>
+        <v>62.9</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105.32</v>
+        <v>105.75</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>89.53</v>
+        <v>106.15</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>15.79</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.61215748</v>
       </c>
       <c r="D59" t="n">
-        <v>226.12</v>
+        <v>233.71</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>104.69</v>
+        <v>105.69</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>108.77</v>
+        <v>88.09</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-4.08</v>
+        <v>17.6</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.1533463</v>
       </c>
       <c r="D60" t="n">
-        <v>230.08</v>
+        <v>123.8</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>104.43</v>
+        <v>105.48</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>88.09</v>
+        <v>89.53</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>16.34</v>
+        <v>15.95</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6570,22 +6570,22 @@
         <v>0.50675322</v>
       </c>
       <c r="D61" t="n">
-        <v>276.33</v>
+        <v>276.43</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.82</v>
+        <v>103.48</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>7.14</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6597,22 +6597,22 @@
         <v>1.85908491</v>
       </c>
       <c r="D62" t="n">
-        <v>74.98</v>
+        <v>74.81</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>103.35</v>
+        <v>102.74</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-1.63</v>
+        <v>-2.24</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6624,22 +6624,22 @@
         <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>124.31</v>
+        <v>124.18</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>103.04</v>
+        <v>102.56</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-2.32</v>
+        <v>-2.8</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6651,22 +6651,22 @@
         <v>0.10445851</v>
       </c>
       <c r="D64" t="n">
-        <v>1316.66</v>
+        <v>1318.66</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101.97</v>
+        <v>101.75</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>13.08</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6678,76 +6678,76 @@
         <v>0.97307689</v>
       </c>
       <c r="D65" t="n">
-        <v>140.37</v>
+        <v>140.84</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>101.27</v>
+        <v>101.24</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-10.17</v>
+        <v>-10.2</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.6214908</v>
       </c>
       <c r="D66" t="n">
-        <v>115.53</v>
+        <v>218.1</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>100.48</v>
+        <v>100.13</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>110.45</v>
+        <v>107.82</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-9.970000000000001</v>
+        <v>-7.69</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="D67" t="n">
-        <v>217.01</v>
+        <v>115.45</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>100</v>
+        <v>100.05</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>107.82</v>
+        <v>110.45</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-7.82</v>
+        <v>-10.4</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6759,22 +6759,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>114.65</v>
+        <v>114.31</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>99.08</v>
+        <v>98.42</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>6.31</v>
+        <v>5.65</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6786,22 +6786,22 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D69" t="n">
-        <v>144.57</v>
+        <v>144.59</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>98.22</v>
+        <v>97.88</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-1.63</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6813,22 +6813,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D70" t="n">
-        <v>138.67</v>
+        <v>139.15</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>96.09</v>
+        <v>96.06999999999999</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>7.71</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6840,22 +6840,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D71" t="n">
-        <v>66.66</v>
+        <v>66.16</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>91.28</v>
+        <v>90.27</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-19.25</v>
+        <v>-20.26</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6867,22 +6867,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D72" t="n">
-        <v>111.24</v>
+        <v>110.47</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>52.14</v>
+        <v>51.59</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>4.27</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6894,16 +6894,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D73" t="n">
-        <v>272.67</v>
+        <v>273.77</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>49</v>
+        <v>49.02</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-3.11</v>
+        <v>-3.09</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44290.32</v>
+        <v>44310.54</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>42998.66</v>
+        <v>43018.74</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6359.99</v>
+        <v>6380.07</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1735868141501861</v>
+        <v>0.1741348689785956</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1291.66</v>
+        <v>1291.8</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-14 19:26:50</t>
+          <t>2026-08-15 18:54:32</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -721,7 +721,7 @@
         <v>7102.72</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1652688184803092</v>
+        <v>0.1651954781682418</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>1056.95</v>
@@ -778,7 +778,7 @@
         <v>4367.98</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.1016358372208986</v>
+        <v>0.1015907349197655</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>937.27</v>
@@ -835,7 +835,7 @@
         <v>2694.94</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06270689956457871</v>
+        <v>0.06267907251513809</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>1498.98</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>25.57</v>
+        <v>25.59</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2172.23</v>
+        <v>2171.33</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05054428241117236</v>
+        <v>0.05050092043767015</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>246.42</v>
+        <v>245.52</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1279565481537639</v>
+        <v>0.1274892123314346</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-13.53</v>
+        <v>-15.82</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>111.71</v>
+        <v>111.55</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2047.05</v>
+        <v>2041.67</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04763154606546745</v>
+        <v>0.0474852805561467</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>400.48</v>
+        <v>395.1</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2432207558743327</v>
+        <v>0.2399533575857692</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-14.59</v>
+        <v>-16.55</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>508.75</v>
+        <v>515.5</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1879.11</v>
+        <v>1901.76</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04372385360742559</v>
+        <v>0.04423124557370072</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-19.44</v>
+        <v>3.21</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.01023939322114245</v>
+        <v>0.001690764004108398</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-14.93</v>
+        <v>-17.19</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>225.15</v>
+        <v>224.72</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1817.24</v>
+        <v>1811.6</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04228423867126357</v>
+        <v>0.04213429900792751</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>564.5599999999999</v>
+        <v>558.92</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4506817383529712</v>
+        <v>0.4461793913848708</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-41.23</v>
+        <v>-42.68</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>176.4</v>
+        <v>178.26</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1639.59</v>
+        <v>1654.9</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03815061020174387</v>
+        <v>0.03848976122114112</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-232.25</v>
+        <v>-216.94</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1240757757073254</v>
+        <v>-0.1158966578340029</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-91.66</v>
+        <v>-93.79000000000001</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>220.16</v>
+        <v>221.6</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1561.3</v>
+        <v>1569.64</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03632892839550296</v>
+        <v>0.03650677914263819</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-434.76</v>
+        <v>-426.42</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2178090838952737</v>
+        <v>-0.2136308527799766</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-20.66</v>
+        <v>-23.02</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1231,19 +1231,19 @@
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1398.85</v>
+        <v>1397.17</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03254897936722559</v>
+        <v>0.03249546177131049</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>55.06</v>
+        <v>53.38</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.04097366403976812</v>
+        <v>0.03972346869674578</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-15.89</v>
+        <v>-17.49</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1288,19 +1288,19 @@
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1384.86</v>
+        <v>1382.7</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.0322234546709769</v>
+        <v>0.03215891766298375</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>156.52</v>
+        <v>154.36</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1274240031261703</v>
+        <v>0.1256655323444649</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-50.18</v>
+        <v>-52.01</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1345,19 +1345,19 @@
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1218.95</v>
+        <v>1218.61</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02836299703304832</v>
+        <v>0.02834250282294687</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>304.46</v>
+        <v>304.12</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3329287362354973</v>
+        <v>0.3325569443077562</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-3.91</v>
+        <v>-4.16</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>1168.55</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.0271902704647185</v>
+        <v>0.02717820440809985</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>561.36</v>
@@ -1462,7 +1462,7 @@
         <v>1132.48</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02635097984329674</v>
+        <v>0.02633928623343881</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>379.02</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>328.51</v>
+        <v>328.92</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1063.27</v>
+        <v>1063.32</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02474057496642953</v>
+        <v>0.02473075889882395</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>421.28</v>
+        <v>421.33</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.656209598280347</v>
+        <v>0.656287481113413</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-33.92</v>
+        <v>-34.65</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>305.49</v>
+        <v>305.77</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>690.53</v>
+        <v>690.34</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.01606751740533316</v>
+        <v>0.01605596819227902</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>199.48</v>
+        <v>199.29</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.406231544649221</v>
+        <v>0.4058446186742694</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-21.18</v>
+        <v>-21.73</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.46065664</v>
@@ -1624,25 +1624,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>495.2</v>
+        <v>495.26</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>682.25</v>
+        <v>681.52</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01587485518339326</v>
+        <v>0.01585083211519251</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>147.87</v>
+        <v>147.14</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.2767132003443243</v>
+        <v>0.2753471312549122</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-25.36</v>
+        <v>-25.97</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0.3650317</v>
@@ -1681,25 +1681,25 @@
         <v>57.84</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>45.97</v>
+        <v>45.89</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>679.1799999999999</v>
+        <v>677.1799999999999</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01580342124361602</v>
+        <v>0.01574989214075312</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-188.4</v>
+        <v>-190.4</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>-0.2171557666151825</v>
+        <v>-0.2194610295304179</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-13.03</v>
+        <v>-14.06</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0</v>
@@ -1738,25 +1738,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>96.95</v>
+        <v>97</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>658.6</v>
+        <v>658.15</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01532455789488135</v>
+        <v>0.01530729128508914</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>109.42</v>
+        <v>108.97</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.199242507010452</v>
+        <v>0.1984231035361812</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-24.73</v>
+        <v>-25.36</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -1804,7 +1804,7 @@
         <v>647.4</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01506395199080806</v>
+        <v>0.01505726715485332</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>-15.28</v>
@@ -1852,25 +1852,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>342.64</v>
+        <v>342.22</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>589.77</v>
+        <v>588.34</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01372299500404521</v>
+        <v>0.01368364621236701</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>100.5</v>
+        <v>99.06999999999999</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.2054080569010976</v>
+        <v>0.2024853352954401</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-32.07</v>
+        <v>-32.62</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>536.13</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01247487887060847</v>
+        <v>0.01246934297147283</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>-2.24</v>
@@ -1966,25 +1966,25 @@
         <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>345.41</v>
+        <v>347.27</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>510.32</v>
+        <v>512.45</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01187432187202528</v>
+        <v>0.01191859214319522</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>102.4</v>
+        <v>104.53</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.2510296136497353</v>
+        <v>0.2562512257305354</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-9.859999999999999</v>
+        <v>-10.34</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>234.8</v>
+        <v>234.58</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>192.57</v>
+        <v>192.16</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.00448079276316019</v>
+        <v>0.004469268545685223</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-3.95</v>
+        <v>-4.36</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.02009973539588846</v>
+        <v>-0.02218603704457562</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-2.25</v>
+        <v>-2.48</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>1.11022215</v>
@@ -2055,17 +2055,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2074,34 +2074,34 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.63422137</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>91.20399179</v>
+        <v>212.76482689</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>111.23</v>
+        <v>272.96</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>128.02</v>
+        <v>127.73</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.002978818557094914</v>
+        <v>0.002970751828374134</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>22.74</v>
+        <v>27.88</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.2159954407294833</v>
+        <v>0.2792188282423635</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.29</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.63422137</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2112,17 +2112,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2131,34 +2131,34 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.55804584</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>212.76482689</v>
+        <v>91.20399179</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>272.68</v>
+        <v>111</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.28</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>127.75</v>
+        <v>127.6</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002972536093336004</v>
+        <v>0.002967728280752677</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>27.9</v>
+        <v>22.32</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.2794191286930396</v>
+        <v>0.2120060790273556</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.44</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.55804584</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2194,25 +2194,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>246.37</v>
+        <v>246.68</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>127.4</v>
+        <v>127.41</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002964392158833714</v>
+        <v>0.002963309249613626</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>8.65</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.07275176827214551</v>
+        <v>0.07283597170764568</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-2.09</v>
+        <v>-2.22</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0</v>
@@ -2251,25 +2251,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>399.81</v>
+        <v>399.34</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>124.08</v>
+        <v>123.78</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002887141122983416</v>
+        <v>0.00287888249679911</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>14.92</v>
+        <v>14.62</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1366801026016856</v>
+        <v>0.1339318431659949</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.5</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.42010405</v>
@@ -2308,25 +2308,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>64.22</v>
+        <v>63.98</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>118.8</v>
+        <v>118.22</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002764284053920292</v>
+        <v>0.002749567690835278</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>11.99</v>
+        <v>11.41</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1122554067971164</v>
+        <v>0.1068252036326187</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.44</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>2.50421091</v>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.28038062</v>
+        <v>2.70722512</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>509.16500577</v>
+        <v>53.65641702</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>569.87</v>
+        <v>59</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>105.75</v>
+        <v>107.64</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>118.03</v>
+        <v>117.85</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002746367398015253</v>
+        <v>0.00274096220914344</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>12.28</v>
+        <v>10.21</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1161229314420804</v>
+        <v>0.09485321441843182</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.46</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0.28038062</v>
+        <v>2.70722512</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>53.65641702</v>
+        <v>509.16500577</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>58.93</v>
+        <v>569</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>107.64</v>
+        <v>105.75</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>117.85</v>
+        <v>117.71</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002742179088842646</v>
+        <v>0.002737706080935718</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>10.21</v>
+        <v>11.96</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.09485321441843182</v>
+        <v>0.113096926713948</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.42</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2479,25 +2479,25 @@
         <v>45.93199509</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>48.21</v>
+        <v>48.16</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>117.83</v>
+        <v>117.57</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002741713721156802</v>
+        <v>0.002734449952727996</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>5.12</v>
+        <v>4.86</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.0454263153225091</v>
+        <v>0.04311951024753793</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.58</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>3.30858696</v>
@@ -2536,25 +2536,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>200.37</v>
+        <v>200.17</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>117.02</v>
+        <v>116.76</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002722866329880072</v>
+        <v>0.00271561092524046</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>6.61</v>
+        <v>6.35</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.05986776560094195</v>
+        <v>0.05751290643963409</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>0.7905852</v>
@@ -2599,19 +2599,19 @@
         <v>119.73</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>115.84</v>
+        <v>115.71</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002695409636415208</v>
+        <v>0.002691189963682541</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>-3.89</v>
+        <v>-4.02</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-0.03248976864612044</v>
+        <v>-0.03357554497619644</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.59</v>
+        <v>-0.73</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>1.32559468</v>
@@ -2650,25 +2650,25 @@
         <v>322.35040597</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>358.88</v>
+        <v>359.1</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>115.54</v>
+        <v>115.48</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.00268842912112753</v>
+        <v>0.002685840610198426</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>11.5</v>
+        <v>11.44</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1105344098423683</v>
+        <v>0.1099577085736255</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.38</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>0.43583007</v>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>0.59183053</v>
+        <v>3.81488812</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>228.00445932</v>
+        <v>38.28159448</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>261.01</v>
+        <v>40.47</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>108.23</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>114.11</v>
+        <v>113.91</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.0026551553315896</v>
+        <v>0.002649325458154682</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>14.26</v>
+        <v>5.68</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.142814221331998</v>
+        <v>0.05248082786658043</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.48</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>0.59183053</v>
+        <v>3.81488812</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.59183053</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>38.28159448</v>
+        <v>228.00445932</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>40.36</v>
+        <v>260.55</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>108.23</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>113.74</v>
+        <v>113.77</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002646546029401465</v>
+        <v>0.00264606932994696</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>5.51</v>
+        <v>13.92</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.05091009886353137</v>
+        <v>0.1394091136705058</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.29</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.59183053</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2821,25 +2821,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>87.56999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.17</v>
+        <v>112.2</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002610014666062619</v>
+        <v>0.002609554177903217</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.1047966118388654</v>
+        <v>0.105092091007584</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.33</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>1.73400968</v>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>249.91595261</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>1174.69</v>
+        <v>290.81</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>111.56</v>
+        <v>111.32</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002595820951644341</v>
+        <v>0.002589087086311818</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>12.67</v>
+        <v>15.38</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1281221559308322</v>
+        <v>0.1603085261621847</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.27</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2910,17 +2910,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,34 +2929,34 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>249.91595261</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>290.38</v>
+        <v>1172.23</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>95.94</v>
+        <v>98.89</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.29</v>
+        <v>111.2</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002589538487885432</v>
+        <v>0.002586296119276628</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>15.35</v>
+        <v>12.31</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.159995830727538</v>
+        <v>0.1244817473960967</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.28</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.80409618</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>341.38450299</v>
+        <v>148.63893521</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>395.35</v>
+        <v>185.81</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>110.43</v>
+        <v>110.24</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.00256952767739409</v>
+        <v>0.002563968382995103</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>14.92</v>
+        <v>21.8</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.1562140090042927</v>
+        <v>0.2464947987336047</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.80409618</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3049,25 +3049,25 @@
         <v>221.99877812</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>268.88</v>
+        <v>268.84</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.25</v>
+        <v>110.1</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002565339368221483</v>
+        <v>0.002560712254787381</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>19.07</v>
+        <v>18.92</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.2091467427067339</v>
+        <v>0.2075016450976091</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>0.5550481</v>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>96.717382</v>
+        <v>341.38450299</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>110.34</v>
+        <v>394</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>110.12</v>
+        <v>109.92</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.00256231447826349</v>
+        <v>0.002556525804234595</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>13.44</v>
+        <v>14.41</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1390153082333471</v>
+        <v>0.1508742540048162</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.27</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3163,25 +3163,25 @@
         <v>54.82621761</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>53.81</v>
+        <v>53.77</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>109.96</v>
+        <v>109.75</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002558591536776728</v>
+        <v>0.002552571934268075</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>-2.52</v>
+        <v>-2.73</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-0.02240398293029872</v>
+        <v>-0.02427098150782361</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.57</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>2.76637723</v>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.35094641</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>148.63893521</v>
+        <v>96.717382</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>185.11</v>
+        <v>110</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>88.44</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>109.96</v>
+        <v>109.65</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002558591536776728</v>
+        <v>0.002550246128405416</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>21.52</v>
+        <v>12.97</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.2433288104929896</v>
+        <v>0.1341539098055441</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.27</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.35094641</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3277,25 +3277,25 @@
         <v>306.99401668</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>363.08</v>
+        <v>362.63</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>109.61</v>
+        <v>109.34</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002550447602274438</v>
+        <v>0.002543036130231174</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>16.78</v>
+        <v>16.51</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1807605300010773</v>
+        <v>0.1778519875040397</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.27</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>0.40867246</v>
@@ -3334,25 +3334,25 @@
         <v>176.50746647</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>216.1</v>
+        <v>216</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>109.34</v>
+        <v>109.16</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002544165138515528</v>
+        <v>0.002538849679678387</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>19.88</v>
+        <v>19.7</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2202101497876146</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>0.68495686</v>
@@ -3391,25 +3391,25 @@
         <v>12.56856884</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>12.96</v>
+        <v>12.93</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>109.15</v>
+        <v>108.76</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002539744145499999</v>
+        <v>0.002529546456227752</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>3</v>
+        <v>2.61</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.02826189354686764</v>
+        <v>0.02458784738577485</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.43</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>11.40066159</v>
@@ -3448,25 +3448,25 @@
         <v>137.713206</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>163.15</v>
+        <v>162</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>92.27</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>109.12</v>
+        <v>108.23</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002539046093971232</v>
+        <v>0.002517219685155661</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>16.85</v>
+        <v>15.96</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1826162349626098</v>
+        <v>0.1729706296737835</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.26</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>0.90543241</v>
@@ -3505,25 +3505,25 @@
         <v>10.85229847</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>10.97</v>
+        <v>10.96</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>107.8</v>
+        <v>107.57</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.00250833182670545</v>
+        <v>0.002501869366462112</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.007853403141361256</v>
+        <v>0.005703066566940912</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.45</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>13.30225117</v>
@@ -3562,25 +3562,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>344.9</v>
+        <v>344.5</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>107.66</v>
+        <v>107.41</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002505074252904534</v>
+        <v>0.002498148077081858</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>6.27</v>
+        <v>6.02</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.06184041818719795</v>
+        <v>0.05937469178419962</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.35</v>
       </c>
       <c r="N52" s="4" t="n">
         <v>0.42255419</v>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,55 +3613,55 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.59010207</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>105.04894536</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>25.56</v>
+        <v>91.55</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>452.96</v>
+        <v>89.66</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>107.46</v>
+        <v>107.41</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002500420576046082</v>
+        <v>0.002498148077081858</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>-345.5</v>
+        <v>17.75</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>-0.7627605086541859</v>
+        <v>0.1979701093018068</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-11.31</v>
+        <v>-0.26</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0</v>
+        <v>1.59010207</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,38 +3670,38 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>1.59010207</v>
+        <v>5.691347</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>105.04894536</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>91.27</v>
+        <v>25.43</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>89.66</v>
+        <v>452.96</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>107.21</v>
+        <v>106.79</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002494603479973018</v>
+        <v>0.002483728080733373</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>17.55</v>
+        <v>-346.17</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.1957394601829132</v>
+        <v>-0.7642396679618511</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.16</v>
+        <v>-11.83</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
@@ -3733,25 +3733,25 @@
         <v>74.99726962</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>83.28</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>107.17</v>
+        <v>106.67</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002493672744601327</v>
+        <v>0.002480937113698183</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>10.49</v>
+        <v>9.99</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1085022755482002</v>
+        <v>0.1033305750930906</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.28</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>1.74206342</v>
@@ -3790,25 +3790,25 @@
         <v>235.02053179</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>230.78</v>
+        <v>231.34</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>106.46</v>
+        <v>106.59</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002477152191753824</v>
+        <v>0.002479076469008056</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>-2.31</v>
+        <v>-2.18</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.02123747356807943</v>
+        <v>-0.02004229107290613</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.48</v>
       </c>
       <c r="N56" s="4" t="n">
         <v>0.62445608</v>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.61215748</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>113.12478542</v>
+        <v>194.45976548</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>121.71</v>
+        <v>235.17</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>98.72</v>
+        <v>88.09</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>106.05</v>
+        <v>106.22</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002467612154193998</v>
+        <v>0.002470470987316218</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>7.33</v>
+        <v>18.13</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.07425040518638575</v>
+        <v>0.205812237484391</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.61215748</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>62.95787236</v>
+        <v>113.12478542</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>62.9</v>
+        <v>122.01</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>106.15</v>
+        <v>98.72</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>105.75</v>
+        <v>106.18</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002460631638906321</v>
+        <v>0.002469540664971155</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-0.4</v>
+        <v>7.46</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.003768252472915685</v>
+        <v>0.07556726094003241</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.27</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>194.45976548</v>
+        <v>62.95787236</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>233.71</v>
+        <v>62.85</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>88.09</v>
+        <v>106.15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>105.69</v>
+        <v>105.54</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002459235535848785</v>
+        <v>0.002454655507450138</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>17.6</v>
+        <v>-0.61</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.1997956635259394</v>
+        <v>-0.00574658502119642</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.43</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4018,25 +4018,25 @@
         <v>104.90344487</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>123.8</v>
+        <v>124</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>105.48</v>
+        <v>105.52</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002454349175147411</v>
+        <v>0.002454190346277606</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>15.95</v>
+        <v>15.99</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.1781525745560147</v>
+        <v>0.1785993521724561</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>1.1533463</v>
@@ -4075,25 +4075,25 @@
         <v>257.81779936</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>276.43</v>
+        <v>275.5</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>103.48</v>
+        <v>103.01</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002407812406562894</v>
+        <v>0.002395812619124869</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>6.8</v>
+        <v>6.33</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.0703351261894911</v>
+        <v>0.06547372776168804</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.28</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>0.50675322</v>
@@ -4132,25 +4132,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>74.81</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>102.74</v>
+        <v>102.52</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002390593802186623</v>
+        <v>0.002384416170397841</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-2.24</v>
+        <v>-2.46</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.02133739759954277</v>
+        <v>-0.02343303486378358</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.4</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>1.85908491</v>
@@ -4189,25 +4189,25 @@
         <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>124.18</v>
+        <v>124.15</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>102.56</v>
+        <v>102.41</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002386405493014017</v>
+        <v>0.002381857783948916</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-2.8</v>
+        <v>-2.95</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.02657555049354594</v>
+        <v>-0.02799924069855733</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.41</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>1.11796351</v>
@@ -4246,25 +4246,25 @@
         <v>1150.02597682</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1318.66</v>
+        <v>1322.64</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>101.75</v>
+        <v>101.94</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002367558101737287</v>
+        <v>0.00237092649639442</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>12.86</v>
+        <v>13.05</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1446731915851052</v>
+        <v>0.1468106648666892</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.25</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>0.10445851</v>
@@ -4303,25 +4303,25 @@
         <v>154.44822659</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>140.84</v>
+        <v>140.83</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>101.24</v>
+        <v>101.11</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002355691225748235</v>
+        <v>0.002351622307734351</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-10.2</v>
+        <v>-10.33</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.09152907394113424</v>
+        <v>-0.09269562096195262</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.55</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>0.97307689</v>
@@ -4360,25 +4360,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>218.1</v>
+        <v>218.33</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>100.13</v>
+        <v>100.12</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002329863319183828</v>
+        <v>0.002328596829694029</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-7.69</v>
+        <v>-7.7</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.07132257466147283</v>
+        <v>-0.07141532183268411</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.46</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>0.6214908</v>
@@ -4417,25 +4417,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>115.45</v>
+        <v>115.3</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>100.05</v>
+        <v>99.8</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002328001848440448</v>
+        <v>0.00232115425093352</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-10.4</v>
+        <v>-10.65</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.09416025350837483</v>
+        <v>-0.09642372114078769</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.52</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>1.17308322</v>
@@ -4474,25 +4474,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>114.31</v>
+        <v>114.11</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>98.42</v>
+        <v>98.14</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002290074382044067</v>
+        <v>0.002282545873613384</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>5.65</v>
+        <v>5.37</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.06090330925945888</v>
+        <v>0.0578850921634149</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.16558147</v>
@@ -4531,25 +4531,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>144.59</v>
+        <v>144.47</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>97.88</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002277509454526247</v>
+        <v>0.002271847166645153</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-1.97</v>
+        <v>-2.17</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.01972959439158738</v>
+        <v>-0.02173259889834752</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.32</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4588,25 +4588,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>139.15</v>
+        <v>139.27</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>96.06999999999999</v>
+        <v>96.03</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002235393678957259</v>
+        <v>0.002233471369911282</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>7.69</v>
+        <v>7.65</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.08701063589047296</v>
+        <v>0.08655804480651733</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.26</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>0.93456659</v>
@@ -4651,19 +4651,19 @@
         <v>110.53</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>90.27</v>
+        <v>90.16</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002100437050062161</v>
+        <v>0.002096946565773208</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-20.26</v>
+        <v>-20.37</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1832986519496969</v>
+        <v>-0.1842938568714376</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.39</v>
+        <v>-0.53</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.84694851</v>
@@ -4702,25 +4702,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>110.47</v>
+        <v>111</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>51.59</v>
+        <v>51.78</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001200415945637608</v>
+        <v>0.001204302275684746</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3.72</v>
+        <v>3.91</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.07771046584499687</v>
+        <v>0.08167954877794026</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.14</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.63221571</v>
@@ -4759,25 +4759,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>273.77</v>
+        <v>273.11</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>49.02</v>
+        <v>48.84</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001140616198006504</v>
+        <v>0.001135923583322576</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-3.09</v>
+        <v>-3.27</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.05929763960852043</v>
+        <v>-0.06275187104202648</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.15</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.24236298</v>
@@ -4810,7 +4810,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4869,34 +4869,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-14 19:26:50</t>
+          <t>2026-08-15 18:54:32</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44290.32</v>
+        <v>44310.54</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>42998.66</v>
+        <v>43018.74</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>36638.67</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6359.99</v>
+        <v>6380.07</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1735868141501861</v>
+        <v>0.1741348689785956</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1314.55</v>
+        <v>1314.69</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4992,7 +4992,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5058,22 +5058,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>25.57</v>
+        <v>25.59</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2172.23</v>
+        <v>2171.33</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>246.42</v>
+        <v>245.52</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5085,22 +5085,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>111.71</v>
+        <v>111.55</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2047.05</v>
+        <v>2041.67</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>400.48</v>
+        <v>395.1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5112,22 +5112,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>508.75</v>
+        <v>515.5</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1879.11</v>
+        <v>1901.76</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-19.44</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5139,22 +5139,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>225.15</v>
+        <v>224.72</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1817.24</v>
+        <v>1811.6</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>564.5599999999999</v>
+        <v>558.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5166,22 +5166,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D9" t="n">
-        <v>176.4</v>
+        <v>178.26</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1639.59</v>
+        <v>1654.9</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-232.25</v>
+        <v>-216.94</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5193,22 +5193,22 @@
         <v>9.6</v>
       </c>
       <c r="D10" t="n">
-        <v>220.16</v>
+        <v>221.6</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1561.3</v>
+        <v>1569.64</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-434.76</v>
+        <v>-426.42</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5223,19 +5223,19 @@
         <v>119.08</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1398.85</v>
+        <v>1397.17</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>55.06</v>
+        <v>53.38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5250,19 +5250,19 @@
         <v>43.55</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1384.86</v>
+        <v>1382.7</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>156.52</v>
+        <v>154.36</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5277,19 +5277,19 @@
         <v>442.7</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1218.95</v>
+        <v>1218.61</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>304.46</v>
+        <v>304.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5316,7 +5316,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5343,7 +5343,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5355,22 +5355,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>328.51</v>
+        <v>328.92</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1063.27</v>
+        <v>1063.32</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>421.28</v>
+        <v>421.33</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5382,22 +5382,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D17" t="n">
-        <v>305.49</v>
+        <v>305.77</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>690.53</v>
+        <v>690.34</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>199.48</v>
+        <v>199.29</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5409,22 +5409,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D18" t="n">
-        <v>495.2</v>
+        <v>495.26</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>682.25</v>
+        <v>681.52</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>147.87</v>
+        <v>147.14</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5436,22 +5436,22 @@
         <v>20</v>
       </c>
       <c r="D19" t="n">
-        <v>45.97</v>
+        <v>45.89</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>679.1799999999999</v>
+        <v>677.1799999999999</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-188.4</v>
+        <v>-190.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5463,22 +5463,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>96.95</v>
+        <v>97</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>658.6</v>
+        <v>658.15</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>109.42</v>
+        <v>108.97</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5505,7 +5505,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5517,22 +5517,22 @@
         <v>2.330043</v>
       </c>
       <c r="D22" t="n">
-        <v>342.64</v>
+        <v>342.22</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>589.77</v>
+        <v>588.34</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>100.5</v>
+        <v>99.06999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5559,7 +5559,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5571,22 +5571,22 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>345.41</v>
+        <v>347.27</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>510.32</v>
+        <v>512.45</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>102.4</v>
+        <v>104.53</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5598,76 +5598,76 @@
         <v>1.11022215</v>
       </c>
       <c r="D25" t="n">
-        <v>234.8</v>
+        <v>234.58</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>192.57</v>
+        <v>192.16</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-3.95</v>
+        <v>-4.36</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.63422137</v>
       </c>
       <c r="D26" t="n">
-        <v>111.23</v>
+        <v>272.96</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>128.02</v>
+        <v>127.73</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>105.28</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>22.74</v>
+        <v>27.88</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.55804584</v>
       </c>
       <c r="D27" t="n">
-        <v>272.68</v>
+        <v>111</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>127.75</v>
+        <v>127.6</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.28</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>27.9</v>
+        <v>22.32</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5679,22 +5679,22 @@
         <v>0.7</v>
       </c>
       <c r="D28" t="n">
-        <v>246.37</v>
+        <v>246.68</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>127.4</v>
+        <v>127.41</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>8.65</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5706,22 +5706,22 @@
         <v>0.42010405</v>
       </c>
       <c r="D29" t="n">
-        <v>399.81</v>
+        <v>399.34</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>124.08</v>
+        <v>123.78</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>14.92</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5733,76 +5733,76 @@
         <v>2.50421091</v>
       </c>
       <c r="D30" t="n">
-        <v>64.22</v>
+        <v>63.98</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>118.8</v>
+        <v>118.22</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.99</v>
+        <v>11.41</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.28038062</v>
+        <v>2.70722512</v>
       </c>
       <c r="D31" t="n">
-        <v>569.87</v>
+        <v>59</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>118.03</v>
+        <v>117.85</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>105.75</v>
+        <v>107.64</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>12.28</v>
+        <v>10.21</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="D32" t="n">
-        <v>58.93</v>
+        <v>569</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>117.85</v>
+        <v>117.71</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>107.64</v>
+        <v>105.75</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>10.21</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5814,22 +5814,22 @@
         <v>3.30858696</v>
       </c>
       <c r="D33" t="n">
-        <v>48.21</v>
+        <v>48.16</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>117.83</v>
+        <v>117.57</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>5.12</v>
+        <v>4.86</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5841,22 +5841,22 @@
         <v>0.7905852</v>
       </c>
       <c r="D34" t="n">
-        <v>200.37</v>
+        <v>200.17</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>117.02</v>
+        <v>116.76</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6.61</v>
+        <v>6.35</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5871,19 +5871,19 @@
         <v>118.3</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>115.84</v>
+        <v>115.71</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-3.89</v>
+        <v>-4.02</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5895,76 +5895,76 @@
         <v>0.43583007</v>
       </c>
       <c r="D36" t="n">
-        <v>358.88</v>
+        <v>359.1</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>115.54</v>
+        <v>115.48</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>11.5</v>
+        <v>11.44</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>0.59183053</v>
+        <v>3.81488812</v>
       </c>
       <c r="D37" t="n">
-        <v>261.01</v>
+        <v>40.47</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>114.11</v>
+        <v>113.91</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>108.23</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>14.26</v>
+        <v>5.68</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.59183053</v>
       </c>
       <c r="D38" t="n">
-        <v>40.36</v>
+        <v>260.55</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>113.74</v>
+        <v>113.77</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>108.23</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>5.51</v>
+        <v>13.92</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5976,103 +5976,103 @@
         <v>1.73400968</v>
       </c>
       <c r="D39" t="n">
-        <v>87.56999999999999</v>
+        <v>87.7</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.17</v>
+        <v>112.2</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>10.64</v>
+        <v>10.67</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="D40" t="n">
-        <v>1174.69</v>
+        <v>290.81</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>111.56</v>
+        <v>111.32</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>12.67</v>
+        <v>15.38</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="D41" t="n">
-        <v>290.38</v>
+        <v>1172.23</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.29</v>
+        <v>111.2</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>95.94</v>
+        <v>98.89</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15.35</v>
+        <v>12.31</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.80409618</v>
       </c>
       <c r="D42" t="n">
-        <v>395.35</v>
+        <v>185.81</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>110.43</v>
+        <v>110.24</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>14.92</v>
+        <v>21.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6084,49 +6084,49 @@
         <v>0.5550481</v>
       </c>
       <c r="D43" t="n">
-        <v>268.88</v>
+        <v>268.84</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.25</v>
+        <v>110.1</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>19.07</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.37810738</v>
       </c>
       <c r="D44" t="n">
-        <v>110.34</v>
+        <v>394</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>110.12</v>
+        <v>109.92</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>13.44</v>
+        <v>14.41</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6138,49 +6138,49 @@
         <v>2.76637723</v>
       </c>
       <c r="D45" t="n">
-        <v>53.81</v>
+        <v>53.77</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>109.96</v>
+        <v>109.75</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-2.52</v>
+        <v>-2.73</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.80409618</v>
+        <v>1.35094641</v>
       </c>
       <c r="D46" t="n">
-        <v>185.11</v>
+        <v>110</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>109.96</v>
+        <v>109.65</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>88.44</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>21.52</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6192,22 +6192,22 @@
         <v>0.40867246</v>
       </c>
       <c r="D47" t="n">
-        <v>363.08</v>
+        <v>362.63</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>109.61</v>
+        <v>109.34</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>16.78</v>
+        <v>16.51</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6219,22 +6219,22 @@
         <v>0.68495686</v>
       </c>
       <c r="D48" t="n">
-        <v>216.1</v>
+        <v>216</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>109.34</v>
+        <v>109.16</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>19.88</v>
+        <v>19.7</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6246,22 +6246,22 @@
         <v>11.40066159</v>
       </c>
       <c r="D49" t="n">
-        <v>12.96</v>
+        <v>12.93</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>109.15</v>
+        <v>108.76</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>3</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6273,22 +6273,22 @@
         <v>0.90543241</v>
       </c>
       <c r="D50" t="n">
-        <v>163.15</v>
+        <v>162</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>109.12</v>
+        <v>108.23</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>92.27</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>16.85</v>
+        <v>15.96</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6300,22 +6300,22 @@
         <v>13.30225117</v>
       </c>
       <c r="D51" t="n">
-        <v>10.97</v>
+        <v>10.96</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>107.8</v>
+        <v>107.57</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.84</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6327,76 +6327,76 @@
         <v>0.42255419</v>
       </c>
       <c r="D52" t="n">
-        <v>344.9</v>
+        <v>344.5</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>107.66</v>
+        <v>107.41</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>6.27</v>
+        <v>6.02</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.59010207</v>
       </c>
       <c r="D53" t="n">
-        <v>25.56</v>
+        <v>91.55</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>107.46</v>
+        <v>107.41</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>452.96</v>
+        <v>89.66</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>-345.5</v>
+        <v>17.75</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>1.59010207</v>
+        <v>5.691347</v>
       </c>
       <c r="D54" t="n">
-        <v>91.27</v>
+        <v>25.43</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>107.21</v>
+        <v>106.79</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>89.66</v>
+        <v>452.96</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>17.55</v>
+        <v>-346.17</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6408,22 +6408,22 @@
         <v>1.74206342</v>
       </c>
       <c r="D55" t="n">
-        <v>83.28</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>107.17</v>
+        <v>106.67</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>10.49</v>
+        <v>9.99</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6435,103 +6435,103 @@
         <v>0.62445608</v>
       </c>
       <c r="D56" t="n">
-        <v>230.78</v>
+        <v>231.34</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>106.46</v>
+        <v>106.59</v>
       </c>
       <c r="F56" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-2.31</v>
+        <v>-2.18</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.61215748</v>
       </c>
       <c r="D57" t="n">
-        <v>121.71</v>
+        <v>235.17</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>106.05</v>
+        <v>106.22</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>98.72</v>
+        <v>88.09</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>7.33</v>
+        <v>18.13</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.17949395</v>
       </c>
       <c r="D58" t="n">
-        <v>62.9</v>
+        <v>122.01</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105.75</v>
+        <v>106.18</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>106.15</v>
+        <v>98.72</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-0.4</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="D59" t="n">
-        <v>233.71</v>
+        <v>62.85</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>105.69</v>
+        <v>105.54</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>88.09</v>
+        <v>106.15</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>17.6</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6543,22 +6543,22 @@
         <v>1.1533463</v>
       </c>
       <c r="D60" t="n">
-        <v>123.8</v>
+        <v>124</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>105.48</v>
+        <v>105.52</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>15.95</v>
+        <v>15.99</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6570,22 +6570,22 @@
         <v>0.50675322</v>
       </c>
       <c r="D61" t="n">
-        <v>276.43</v>
+        <v>275.5</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.48</v>
+        <v>103.01</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>6.8</v>
+        <v>6.33</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6597,22 +6597,22 @@
         <v>1.85908491</v>
       </c>
       <c r="D62" t="n">
-        <v>74.81</v>
+        <v>74.73999999999999</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>102.74</v>
+        <v>102.52</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-2.24</v>
+        <v>-2.46</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6624,22 +6624,22 @@
         <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>124.18</v>
+        <v>124.15</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>102.56</v>
+        <v>102.41</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-2.8</v>
+        <v>-2.95</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6651,22 +6651,22 @@
         <v>0.10445851</v>
       </c>
       <c r="D64" t="n">
-        <v>1318.66</v>
+        <v>1322.64</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101.75</v>
+        <v>101.94</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>12.86</v>
+        <v>13.05</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6678,22 +6678,22 @@
         <v>0.97307689</v>
       </c>
       <c r="D65" t="n">
-        <v>140.84</v>
+        <v>140.83</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>101.24</v>
+        <v>101.11</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-10.2</v>
+        <v>-10.33</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6705,22 +6705,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D66" t="n">
-        <v>218.1</v>
+        <v>218.33</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>100.13</v>
+        <v>100.12</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-7.69</v>
+        <v>-7.7</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6732,22 +6732,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D67" t="n">
-        <v>115.45</v>
+        <v>115.3</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>100.05</v>
+        <v>99.8</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-10.4</v>
+        <v>-10.65</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6759,22 +6759,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>114.31</v>
+        <v>114.11</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>98.42</v>
+        <v>98.14</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>5.65</v>
+        <v>5.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6786,22 +6786,22 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D69" t="n">
-        <v>144.59</v>
+        <v>144.47</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>97.88</v>
+        <v>97.68000000000001</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-1.97</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6813,22 +6813,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D70" t="n">
-        <v>139.15</v>
+        <v>139.27</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>96.06999999999999</v>
+        <v>96.03</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>7.69</v>
+        <v>7.65</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6843,19 +6843,19 @@
         <v>66.16</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>90.27</v>
+        <v>90.16</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-20.26</v>
+        <v>-20.37</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6867,22 +6867,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D72" t="n">
-        <v>110.47</v>
+        <v>111</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>51.59</v>
+        <v>51.78</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>3.72</v>
+        <v>3.91</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6894,16 +6894,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D73" t="n">
-        <v>273.77</v>
+        <v>273.11</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>49.02</v>
+        <v>48.84</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-3.09</v>
+        <v>-3.27</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44310.54</v>
+        <v>44310.67</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1291.8</v>
+        <v>1291.93</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-15 18:54:32</t>
+          <t>2026-08-16 18:53:27</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4869,16 +4869,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-15 18:54:32</t>
+          <t>2026-08-16 18:53:27</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44310.54</v>
+        <v>44310.67</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>43018.74</v>
@@ -4896,7 +4896,7 @@
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1314.69</v>
+        <v>1314.82</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4992,7 +4992,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5073,7 +5073,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5100,7 +5100,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5127,7 +5127,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5154,7 +5154,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5181,7 +5181,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5208,7 +5208,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5235,7 +5235,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5262,7 +5262,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5289,7 +5289,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5316,7 +5316,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5343,7 +5343,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5370,7 +5370,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5424,7 +5424,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5451,7 +5451,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5478,7 +5478,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5505,7 +5505,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5532,7 +5532,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5559,7 +5559,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5586,7 +5586,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5613,7 +5613,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5640,7 +5640,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5667,7 +5667,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5748,7 +5748,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5775,7 +5775,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5802,7 +5802,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5829,7 +5829,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5883,7 +5883,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5910,7 +5910,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5937,7 +5937,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5964,7 +5964,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5991,7 +5991,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6018,7 +6018,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6072,7 +6072,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6099,7 +6099,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6126,7 +6126,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6153,7 +6153,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6180,7 +6180,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6207,7 +6207,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6234,7 +6234,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6261,7 +6261,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6288,7 +6288,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6315,7 +6315,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6342,7 +6342,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6369,7 +6369,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6396,7 +6396,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6423,7 +6423,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6450,7 +6450,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6477,7 +6477,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6504,7 +6504,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6531,7 +6531,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6558,7 +6558,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6585,7 +6585,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6612,7 +6612,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6639,7 +6639,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6666,7 +6666,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6693,7 +6693,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6720,7 +6720,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6747,7 +6747,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6774,7 +6774,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6801,7 +6801,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6828,7 +6828,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6855,7 +6855,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6882,7 +6882,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44310.67</v>
+        <v>44341.92</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43018.74</v>
+        <v>43049.85</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>36638.67</v>
+        <v>36639.92</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6380.07</v>
+        <v>6409.93</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1741348689785956</v>
+        <v>0.1749438863403632</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1291.93</v>
+        <v>1292.07</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>22.89</v>
+        <v>24.14</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-16 18:53:27</t>
+          <t>2026-08-17 19:06:46</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>110.98</v>
+        <v>110.8</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7102.72</v>
+        <v>7091.2</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1651954781682418</v>
+        <v>0.164809139618758</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1056.95</v>
+        <v>1045.43</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1748247121541177</v>
+        <v>0.1729192476723395</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15.062</v>
+        <v>15.578</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4367.98</v>
+        <v>4517.62</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.1015907349197655</v>
+        <v>0.1049956375965272</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>937.27</v>
+        <v>1086.91</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2732000081615759</v>
+        <v>0.3168178015629418</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1527.8</v>
+        <v>1531</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2694.94</v>
+        <v>2700.58</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06267907251513809</v>
+        <v>0.06276515487810602</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1498.98</v>
+        <v>1504.62</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.253369677915649</v>
+        <v>1.258085554700826</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>25.59</v>
+        <v>24.79</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2171.33</v>
+        <v>2105.84</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.05050092043767015</v>
+        <v>0.04894258779540351</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>245.52</v>
+        <v>180.03</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.1274892123314346</v>
+        <v>0.09348274232660543</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-15.82</v>
+        <v>-13.65</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>111.55</v>
+        <v>112.65</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2041.67</v>
+        <v>2064.15</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.0474852805561467</v>
+        <v>0.04797365545240006</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>395.1</v>
+        <v>417.58</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2399533575857692</v>
+        <v>0.2536059809179081</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-16.55</v>
+        <v>-14.69</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>515.5</v>
+        <v>509.7</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1901.76</v>
+        <v>1882.51</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04423124557370072</v>
+        <v>0.04375209462766642</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>3.21</v>
+        <v>-16.04</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.001690764004108398</v>
+        <v>-0.0084485528429591</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-17.19</v>
+        <v>-15.04</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>224.72</v>
+        <v>225.63</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1811.6</v>
+        <v>1821.01</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04213429900792751</v>
+        <v>0.04232275092186858</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>558.92</v>
+        <v>568.33</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4461793913848708</v>
+        <v>0.4536912858830667</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-42.68</v>
+        <v>-41.3</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1086,17 +1086,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US75734B1008</t>
+          <t>US5738741041</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1105,55 +1105,55 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>12.5822526</v>
+        <v>9.6</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>191.52532353</v>
+        <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>178.26</v>
+        <v>235.11</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1871.84</v>
+        <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1654.9</v>
+        <v>1667.23</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03848976122114112</v>
+        <v>0.0387486944165419</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-216.94</v>
+        <v>-328.83</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1158966578340029</v>
+        <v>-0.1647395368876687</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-93.79000000000001</v>
+        <v>-20.77</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US5738741041</t>
+          <t>US75734B1008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1162,38 +1162,38 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>9.6</v>
+        <v>12.5822526</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>278.55208333</v>
+        <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>221.6</v>
+        <v>168.77</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1996.06</v>
+        <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1569.64</v>
+        <v>1568.58</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03650677914263819</v>
+        <v>0.03645593414699788</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-426.42</v>
+        <v>-303.26</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2136308527799766</v>
+        <v>-0.1620117104025985</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-23.02</v>
+        <v>-91.77</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2024-03-22</t>
         </is>
       </c>
     </row>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.08</v>
+        <v>119.06</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1397.17</v>
+        <v>1398.53</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03249546177131049</v>
+        <v>0.03250374069706419</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>53.38</v>
+        <v>54.74</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.03972346869674578</v>
+        <v>0.04073553159347815</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-17.49</v>
+        <v>-15.97</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1288,19 +1288,19 @@
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1382.7</v>
+        <v>1387.27</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03215891766298375</v>
+        <v>0.03224204297141731</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>154.36</v>
+        <v>158.93</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1256655323444649</v>
+        <v>0.1293860006187212</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-52.01</v>
+        <v>-48.13</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>442.7</v>
+        <v>438.6</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1218.61</v>
+        <v>1208.14</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02834250282294687</v>
+        <v>0.02807881796296907</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>304.12</v>
+        <v>293.65</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3325569443077562</v>
+        <v>0.3211079399446686</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-4.16</v>
+        <v>-3.55</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>115.2</v>
+        <v>114.7</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1168.55</v>
+        <v>1163.47</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02717820440809985</v>
+        <v>0.02704062636397737</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>561.36</v>
+        <v>556.28</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.924521154827978</v>
+        <v>0.9161547456315156</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>707.8</v>
+        <v>709</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1132.48</v>
+        <v>1134.4</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02633928623343881</v>
+        <v>0.02636499999767586</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>379.02</v>
+        <v>380.94</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.5030393119740928</v>
+        <v>0.5055875560746423</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>328.92</v>
+        <v>333.88</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1063.32</v>
+        <v>1080.58</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02473075889882395</v>
+        <v>0.02511414994489473</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>421.33</v>
+        <v>438.59</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.656287481113413</v>
+        <v>0.6831726350877739</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-34.65</v>
+        <v>-33.96</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>305.77</v>
+        <v>305.68</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>690.34</v>
+        <v>690.92</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.01605596819227902</v>
+        <v>0.01605792119040392</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>199.29</v>
+        <v>199.87</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4058446186742694</v>
+        <v>0.4070257611241218</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-21.73</v>
+        <v>-21.2</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.46065664</v>
@@ -1599,17 +1599,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>US6701002056</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1618,55 +1618,55 @@
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>1.8650317</v>
+        <v>20</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>369.46288902</v>
+        <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>495.26</v>
+        <v>44.8</v>
       </c>
       <c r="H18" s="2" t="n">
-        <v>534.38</v>
+        <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>681.52</v>
+        <v>661.85</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01585083211519251</v>
+        <v>0.01538229482410241</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>147.14</v>
+        <v>-205.73</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.2753471312549122</v>
+        <v>-0.2371308697756979</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-25.97</v>
+        <v>-13.08</v>
       </c>
       <c r="N18" s="4" t="n">
-        <v>0.3650317</v>
+        <v>0</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US6701002056</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1675,38 +1675,38 @@
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>20</v>
+        <v>1.8650317</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>57.84</v>
+        <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>45.89</v>
+        <v>480.36</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>867.58</v>
+        <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>677.1799999999999</v>
+        <v>661.77</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01574989214075312</v>
+        <v>0.01538043551521681</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>-190.4</v>
+        <v>127.39</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>-0.2194610295304179</v>
+        <v>0.2383884127399978</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-14.06</v>
+        <v>-25.39</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0</v>
+        <v>0.3650317</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
@@ -1738,25 +1738,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>97</v>
+        <v>96.62</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>658.15</v>
+        <v>656.3200000000001</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01530729128508914</v>
+        <v>0.01525377009738595</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>108.97</v>
+        <v>107.14</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.1984231035361812</v>
+        <v>0.1950908627408136</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-25.36</v>
+        <v>-24.76</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
         <v>1019.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>996</v>
+        <v>997.75</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>647.4</v>
+        <v>648.54</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01505726715485332</v>
+        <v>0.01507295230826225</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-15.28</v>
+        <v>-14.14</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.02305788615923221</v>
+        <v>-0.0213375988410696</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>342.22</v>
+        <v>337.55</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>588.34</v>
+        <v>580.97</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01368364621236701</v>
+        <v>0.01350253354077023</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>99.06999999999999</v>
+        <v>91.7</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.2024853352954401</v>
+        <v>0.1874220777893597</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-32.62</v>
+        <v>-32.1</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,22 +1909,22 @@
         <v>3.8455</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3.8295</v>
+        <v>3.82</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>536.13</v>
+        <v>534.8</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01246934297147283</v>
+        <v>0.0124294799001737</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-2.24</v>
+        <v>-3.57</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.004160707320244442</v>
+        <v>-0.006631127291639578</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -1966,25 +1966,25 @@
         <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>347.27</v>
+        <v>343.85</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>512.45</v>
+        <v>507.99</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01191859214319522</v>
+        <v>0.01180637900989013</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>104.53</v>
+        <v>100.07</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.2562512257305354</v>
+        <v>0.2453177093547754</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-10.34</v>
+        <v>-9.869999999999999</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>234.58</v>
+        <v>228.15</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>192.16</v>
+        <v>187.1</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.004469268545685223</v>
+        <v>0.004348458656175206</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-4.36</v>
+        <v>-9.42</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.02218603704457562</v>
+        <v>-0.04793405251373906</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-2.48</v>
+        <v>-2.27</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>1.11022215</v>
@@ -2055,17 +2055,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Abbott Laboratories</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US0028241000</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2074,34 +2074,34 @@
         </is>
       </c>
       <c r="E26" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.55804584</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>212.76482689</v>
+        <v>91.20399179</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>272.96</v>
+        <v>110.03</v>
       </c>
       <c r="H26" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.28</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>127.73</v>
+        <v>126.63</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.002970751828374134</v>
+        <v>0.00294305355227935</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>27.88</v>
+        <v>21.35</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.2792188282423635</v>
+        <v>0.2027925531914894</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.32</v>
       </c>
       <c r="N26" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.55804584</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2112,17 +2112,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Abbott Laboratories</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US0028241000</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2131,55 +2131,55 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.7</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>91.20399179</v>
+        <v>225.62857143</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>111</v>
+        <v>242.43</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>105.28</v>
+        <v>118.76</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>127.6</v>
+        <v>125.35</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002967728280752677</v>
+        <v>0.002913304610109899</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>22.32</v>
+        <v>6.59</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.2120060790273556</v>
+        <v>0.05549006399461098</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.44</v>
+        <v>-2.1</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,38 +2188,38 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.7</v>
+        <v>0.63422137</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>225.62857143</v>
+        <v>212.76482689</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>246.68</v>
+        <v>266.36</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>118.76</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>127.41</v>
+        <v>124.78</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002963309249613626</v>
+        <v>0.002900057034300065</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>8.65</v>
+        <v>24.93</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.07283597170764568</v>
+        <v>0.2496745117676515</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-2.22</v>
+        <v>-0.18</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0</v>
+        <v>0.63422137</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2251,25 +2251,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>399.34</v>
+        <v>391.08</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>123.78</v>
+        <v>121.36</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.00287888249679911</v>
+        <v>0.002820571579441063</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>14.62</v>
+        <v>12.2</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1339318431659949</v>
+        <v>0.1117625503847563</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.38</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.42010405</v>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.30858696</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>57.56703616</v>
+        <v>45.93199509</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>63.98</v>
+        <v>49.23</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>106.81</v>
+        <v>112.71</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>118.22</v>
+        <v>120.32</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002749567690835278</v>
+        <v>0.002796400563928385</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>11.41</v>
+        <v>7.61</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1068252036326187</v>
+        <v>0.06751841007896373</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.45</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.30858696</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.70722512</v>
+        <v>2.50421091</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>53.65641702</v>
+        <v>57.56703616</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>59</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>107.64</v>
+        <v>106.81</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>117.85</v>
+        <v>119.18</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.00274096220914344</v>
+        <v>0.002769905412308718</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>10.21</v>
+        <v>12.37</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.09485321441843182</v>
+        <v>0.1158131261117873</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.33</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.70722512</v>
+        <v>2.50421091</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.7905852</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>509.16500577</v>
+        <v>188.32884805</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>569</v>
+        <v>203.3</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>105.75</v>
+        <v>110.41</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>117.71</v>
+        <v>118.72</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002737706080935718</v>
+        <v>0.002759214386216571</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>11.96</v>
+        <v>8.31</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.113096926713948</v>
+        <v>0.07526492165564715</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.7905852</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.70722512</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>45.93199509</v>
+        <v>53.65641702</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>48.16</v>
+        <v>58.48</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>112.71</v>
+        <v>107.64</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>117.57</v>
+        <v>116.95</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002734449952727996</v>
+        <v>0.002718077177122877</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>4.86</v>
+        <v>9.31</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.04311951024753793</v>
+        <v>0.08649201040505389</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.58</v>
+        <v>-0.34</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.70722512</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.28038062</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>188.32884805</v>
+        <v>509.16500577</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>200.17</v>
+        <v>563.8</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>110.41</v>
+        <v>105.75</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>116.76</v>
+        <v>116.77</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.00271561092524046</v>
+        <v>0.002713893732130298</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>6.35</v>
+        <v>11.02</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.05751290643963409</v>
+        <v>0.1042080378250591</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.3</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.28038062</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2593,25 +2593,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>118.3</v>
+        <v>118.06</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>115.71</v>
+        <v>115.6</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002691189963682541</v>
+        <v>0.002686701339678535</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>-4.02</v>
+        <v>-4.13</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-0.03357554497619644</v>
+        <v>-0.03449427879395306</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.73</v>
+        <v>-0.6</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>1.32559468</v>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.59183053</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>322.35040597</v>
+        <v>228.00445932</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>359.1</v>
+        <v>261.68</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>104.04</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>115.48</v>
+        <v>114.4</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002685840610198426</v>
+        <v>0.002658811706394674</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>11.44</v>
+        <v>14.55</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1099577085736255</v>
+        <v>0.1457185778668002</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.17</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.59183053</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
         <v>38.28159448</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>40.47</v>
+        <v>40.16</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>113.91</v>
+        <v>113.17</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002649325458154682</v>
+        <v>0.002630224832278718</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>5.68</v>
+        <v>4.94</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.05248082786658043</v>
+        <v>0.04564353691213158</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.35</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>3.81488812</v>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.43583007</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>228.00445932</v>
+        <v>322.35040597</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>260.55</v>
+        <v>349.28</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>104.04</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>113.77</v>
+        <v>112.45</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.00264606932994696</v>
+        <v>0.002613491052308401</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>13.92</v>
+        <v>8.41</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.1394091136705058</v>
+        <v>0.08083429450211457</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.26</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.43583007</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>0.5550481</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>79.10567143</v>
+        <v>221.99877812</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>87.7</v>
+        <v>271.76</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>101.53</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.2</v>
+        <v>111.42</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002609554177903217</v>
+        <v>0.002589552450406422</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>10.67</v>
+        <v>20.24</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.105092091007584</v>
+        <v>0.2219785040579074</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.16</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>0.5550481</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,34 +2872,34 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.73400968</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>249.91595261</v>
+        <v>79.10567143</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>290.81</v>
+        <v>86.86</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>95.94</v>
+        <v>101.53</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>111.32</v>
+        <v>111.26</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002589087086311818</v>
+        <v>0.00258583383263524</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>15.38</v>
+        <v>9.73</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.1603085261621847</v>
+        <v>0.09583374372106766</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.2</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.73400968</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -2910,17 +2910,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,34 +2929,34 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>249.91595261</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1172.23</v>
+        <v>288.5</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.2</v>
+        <v>110.56</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002586296119276628</v>
+        <v>0.002569564879886322</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>12.31</v>
+        <v>14.62</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.1244817473960967</v>
+        <v>0.1523869084844695</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2992,25 +2992,25 @@
         <v>148.63893521</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>185.81</v>
+        <v>185.27</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>110.24</v>
+        <v>110.04</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002563968382995103</v>
+        <v>0.002557479372129982</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.2464947987336047</v>
+        <v>0.2442333785617368</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.16</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>0.80409618</v>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>221.99877812</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>268.84</v>
+        <v>1154.58</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>110.1</v>
+        <v>109.65</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002560712254787381</v>
+        <v>0.002548415241312728</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>18.92</v>
+        <v>10.76</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.2075016450976091</v>
+        <v>0.1088077662048741</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.17</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.68495686</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>341.38450299</v>
+        <v>176.50746647</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>394</v>
+        <v>216.43</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>109.92</v>
+        <v>109.5</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002556525804234595</v>
+        <v>0.002544929037152245</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>14.41</v>
+        <v>20.04</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1508742540048162</v>
+        <v>0.2240107310529846</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.16</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.68495686</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.40867246</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>54.82621761</v>
+        <v>306.99401668</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>53.77</v>
+        <v>362.7</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>112.48</v>
+        <v>92.83</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>109.75</v>
+        <v>109.49</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002552571934268075</v>
+        <v>0.002544696623541546</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>-2.73</v>
+        <v>16.66</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-0.02427098150782361</v>
+        <v>0.1794678444468383</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.16</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.40867246</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.76637723</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>96.717382</v>
+        <v>54.82621761</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>110</v>
+        <v>53.57</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>112.48</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>109.65</v>
+        <v>109.47</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002550246128405416</v>
+        <v>0.002544231796320148</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>12.97</v>
+        <v>-3.01</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1341539098055441</v>
+        <v>-0.02676031294452347</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.44</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.76637723</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.37810738</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>306.99401668</v>
+        <v>341.38450299</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>362.63</v>
+        <v>390.44</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>92.83</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>109.34</v>
+        <v>109.05</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002543036130231174</v>
+        <v>0.002534470424670797</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>16.51</v>
+        <v>13.54</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1778519875040397</v>
+        <v>0.1417652601821799</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.16</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.37810738</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.62445608</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>176.50746647</v>
+        <v>235.02053179</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>216</v>
+        <v>235.02</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>108.77</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>109.16</v>
+        <v>108.41</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002538849679678387</v>
+        <v>0.002519595953586072</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>19.7</v>
+        <v>-0.36</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.2202101497876146</v>
+        <v>-0.003309736140479912</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.36</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.62445608</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.90543241</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>12.56856884</v>
+        <v>137.713206</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>12.93</v>
+        <v>161.85</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>106.15</v>
+        <v>92.27</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>108.76</v>
+        <v>108.25</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002529546456227752</v>
+        <v>0.002515877335814891</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2.61</v>
+        <v>15.98</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.02458784738577485</v>
+        <v>0.1731873848488133</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.16</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.90543241</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.90543241</v>
+        <v>11.40066159</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>137.713206</v>
+        <v>12.56856884</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>162</v>
+        <v>12.81</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>92.27</v>
+        <v>106.15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>108.23</v>
+        <v>107.88</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002517219685155661</v>
+        <v>0.002507278032219034</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>15.96</v>
+        <v>1.73</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.1729706296737835</v>
+        <v>0.01629769194536034</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.3</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.90543241</v>
+        <v>11.40066159</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3505,25 +3505,25 @@
         <v>10.85229847</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>10.96</v>
+        <v>10.94</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>107.57</v>
+        <v>107.5</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002501869366462112</v>
+        <v>0.002498446315012478</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.005703066566940912</v>
+        <v>0.005048616305160809</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.32</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>13.30225117</v>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.35094641</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>324.07677699</v>
+        <v>96.717382</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>344.5</v>
+        <v>107.61</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>101.39</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>107.41</v>
+        <v>107.38</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002498148077081858</v>
+        <v>0.002495657351684092</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>6.02</v>
+        <v>10.7</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.05937469178419962</v>
+        <v>0.1106743897393463</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.17</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.35094641</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3619,25 +3619,25 @@
         <v>76.19636644000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>91.55</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>107.41</v>
+        <v>107.36</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002498148077081858</v>
+        <v>0.002495192524462694</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>17.75</v>
+        <v>17.7</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1979701093018068</v>
+        <v>0.1974124470220834</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.16</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>1.59010207</v>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,55 +3670,55 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.42255419</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>105.04894536</v>
+        <v>324.07677699</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>25.43</v>
+        <v>341.98</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>452.96</v>
+        <v>101.39</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>106.79</v>
+        <v>106.74</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002483728080733373</v>
+        <v>0.002480782880599366</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>-346.17</v>
+        <v>5.35</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>-0.7642396679618511</v>
+        <v>0.05276654502416411</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-11.83</v>
+        <v>-0.24</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0</v>
+        <v>0.42255419</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.74206342</v>
+        <v>1.1533463</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>74.99726962</v>
+        <v>104.90344487</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>82.98999999999999</v>
+        <v>124.57</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>106.67</v>
+        <v>106.13</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002480937113698183</v>
+        <v>0.002466605650346738</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>9.99</v>
+        <v>16.6</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1033305750930906</v>
+        <v>0.1854127108231878</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.15</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1.74206342</v>
+        <v>1.1533463</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.61215748</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>235.02053179</v>
+        <v>194.45976548</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>231.34</v>
+        <v>234.5</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>108.77</v>
+        <v>88.09</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>106.59</v>
+        <v>106.04</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002479076469008056</v>
+        <v>0.002464513927850448</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>-2.18</v>
+        <v>17.95</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>-0.02004229107290613</v>
+        <v>0.2037688727437847</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.48</v>
+        <v>-0.16</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.61215748</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.17949395</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>194.45976548</v>
+        <v>113.12478542</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>235.17</v>
+        <v>121.39</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>88.09</v>
+        <v>98.72</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>106.22</v>
+        <v>105.76</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002470470987316218</v>
+        <v>0.002458006346750881</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>18.13</v>
+        <v>7.04</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.205812237484391</v>
+        <v>0.07131280388978931</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.16</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.17949395</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,55 +3898,55 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>5.691347</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>113.12478542</v>
+        <v>105.04894536</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>122.01</v>
+        <v>25.13</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>98.72</v>
+        <v>452.96</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>106.18</v>
+        <v>105.65</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002469540664971155</v>
+        <v>0.002455449797033194</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>7.46</v>
+        <v>-347.31</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.07556726094003241</v>
+        <v>-0.7667564464853409</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.27</v>
+        <v>-11.33</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.74206342</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>62.95787236</v>
+        <v>74.99726962</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>62.85</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>106.15</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>105.54</v>
+        <v>105.25</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002454655507450138</v>
+        <v>0.00244615325260524</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-0.61</v>
+        <v>8.57</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.00574658502119642</v>
+        <v>0.08864294580057923</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.17</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.74206342</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>104.90344487</v>
+        <v>62.95787236</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>124</v>
+        <v>62.27</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>89.53</v>
+        <v>106.15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>105.52</v>
+        <v>104.68</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002454190346277606</v>
+        <v>0.002432905676795407</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>15.99</v>
+        <v>-1.47</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.1785993521724561</v>
+        <v>-0.01384832783796514</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.31</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4075,25 +4075,25 @@
         <v>257.81779936</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>275.5</v>
+        <v>276.52</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>103.01</v>
+        <v>103.51</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002395812619124869</v>
+        <v>0.002405713284343643</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>6.33</v>
+        <v>6.83</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.06547372776168804</v>
+        <v>0.07064542821679767</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.17</v>
       </c>
       <c r="N61" s="4" t="n">
         <v>0.50675322</v>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>76.24181082</v>
+        <v>127.23134407</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>74.73999999999999</v>
+        <v>123.67</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>104.98</v>
+        <v>105.36</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>102.52</v>
+        <v>102.13</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002384416170397841</v>
+        <v>0.002373640206067203</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-2.46</v>
+        <v>-3.23</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.02343303486378358</v>
+        <v>-0.03065679574791192</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.29</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.85908491</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>127.23134407</v>
+        <v>76.24181082</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>124.15</v>
+        <v>74.11</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>105.36</v>
+        <v>104.98</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>102.41</v>
+        <v>101.77</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002381857783948916</v>
+        <v>0.002365273316082045</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-2.95</v>
+        <v>-3.21</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.02799924069855733</v>
+        <v>-0.03057725281005906</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.28</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.85908491</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4246,25 +4246,25 @@
         <v>1150.02597682</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1322.64</v>
+        <v>1318.17</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>101.94</v>
+        <v>101.71</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.00237092649639442</v>
+        <v>0.002363878834417852</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>13.05</v>
+        <v>12.82</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1468106648666892</v>
+        <v>0.1442231972100349</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.15</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>0.10445851</v>
@@ -4303,25 +4303,25 @@
         <v>154.44822659</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>140.83</v>
+        <v>137.98</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>101.11</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002351622307734351</v>
+        <v>0.002305078190911047</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-10.33</v>
+        <v>-12.26</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.09269562096195262</v>
+        <v>-0.1100143575017947</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.55</v>
+        <v>-0.42</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>0.97307689</v>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>234.11448729</v>
+        <v>126.99866255</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>218.33</v>
+        <v>113.94</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>107.82</v>
+        <v>110.45</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>100.12</v>
+        <v>98.73</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002328596829694029</v>
+        <v>0.0022946195784296</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-7.7</v>
+        <v>-11.72</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.07141532183268411</v>
+        <v>-0.1061113626075147</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.46</v>
+        <v>-0.4</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.6214908</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>126.99866255</v>
+        <v>234.11448729</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>115.3</v>
+        <v>215.02</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>110.45</v>
+        <v>107.82</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>99.8</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.00232115425093352</v>
+        <v>0.002294154751208202</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-10.65</v>
+        <v>-9.109999999999999</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.09642372114078769</v>
+        <v>-0.08449267297347431</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.34</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.6214908</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4474,25 +4474,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>114.11</v>
+        <v>112.94</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>98.14</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002282545873613384</v>
+        <v>0.002259989950435473</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>5.37</v>
+        <v>4.47</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.0578850921634149</v>
+        <v>0.04818368006898782</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.15</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.16558147</v>
@@ -4531,25 +4531,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>144.47</v>
+        <v>142.82</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>97.68000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002271847166645153</v>
+        <v>0.002246742374625639</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-2.17</v>
+        <v>-3.18</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.02173259889834752</v>
+        <v>-0.03184777165748624</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.21</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4588,25 +4588,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>139.27</v>
+        <v>138.9</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>96.03</v>
+        <v>95.89</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002233471369911282</v>
+        <v>0.00222861411299113</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>7.65</v>
+        <v>7.51</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.08655804480651733</v>
+        <v>0.08497397601267255</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.16</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>0.93456659</v>
@@ -4645,25 +4645,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>66.16</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>90.16</v>
+        <v>87.41</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002096946565773208</v>
+        <v>0.002031527371118518</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-20.37</v>
+        <v>-23.12</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1842938568714376</v>
+        <v>-0.2091739799149552</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.53</v>
+        <v>-0.4</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.84694851</v>
@@ -4702,25 +4702,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>111</v>
+        <v>110.81</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>51.78</v>
+        <v>51.75</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001204302275684746</v>
+        <v>0.001202740435366472</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.08167954877794026</v>
+        <v>0.08105285147273866</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.08</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.63221571</v>
@@ -4759,25 +4759,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>273.11</v>
+        <v>265.46</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>48.84</v>
+        <v>47.52</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001135923583322576</v>
+        <v>0.001104429478040865</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-3.27</v>
+        <v>-4.59</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.06275187104202648</v>
+        <v>-0.08808290155440414</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.1</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.24236298</v>
@@ -4808,9 +4808,9 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4869,34 +4869,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-16 18:53:27</t>
+          <t>2026-08-17 19:06:46</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44310.67</v>
+        <v>44341.92</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43018.74</v>
+        <v>43049.85</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>36638.67</v>
+        <v>36639.92</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6380.07</v>
+        <v>6409.93</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1741348689785956</v>
+        <v>0.1749438863403632</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1314.82</v>
+        <v>1316.21</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4977,22 +4977,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>110.98</v>
+        <v>110.8</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7102.72</v>
+        <v>7091.2</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1056.95</v>
+        <v>1045.43</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5004,22 +5004,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>15.062</v>
+        <v>15.578</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4367.98</v>
+        <v>4517.62</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>937.27</v>
+        <v>1086.91</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5031,22 +5031,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1527.8</v>
+        <v>1531</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2694.94</v>
+        <v>2700.58</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1498.98</v>
+        <v>1504.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5058,22 +5058,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>25.59</v>
+        <v>24.79</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2171.33</v>
+        <v>2105.84</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>245.52</v>
+        <v>180.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5085,22 +5085,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>111.55</v>
+        <v>112.65</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2041.67</v>
+        <v>2064.15</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>395.1</v>
+        <v>417.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5112,22 +5112,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>515.5</v>
+        <v>509.7</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1901.76</v>
+        <v>1882.51</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>3.21</v>
+        <v>-16.04</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5139,76 +5139,76 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>224.72</v>
+        <v>225.63</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1811.6</v>
+        <v>1821.01</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>558.92</v>
+        <v>568.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>12.5822526</v>
+        <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>178.26</v>
+        <v>235.11</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1654.9</v>
+        <v>1667.23</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1871.84</v>
+        <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-216.94</v>
+        <v>-328.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>9.6</v>
+        <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>221.6</v>
+        <v>168.77</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1569.64</v>
+        <v>1568.58</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1996.06</v>
+        <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-426.42</v>
+        <v>-303.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5220,22 +5220,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.08</v>
+        <v>119.06</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1397.17</v>
+        <v>1398.53</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>53.38</v>
+        <v>54.74</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5250,19 +5250,19 @@
         <v>43.55</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1382.7</v>
+        <v>1387.27</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>154.36</v>
+        <v>158.93</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5274,22 +5274,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>442.7</v>
+        <v>438.6</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1218.61</v>
+        <v>1208.14</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>304.12</v>
+        <v>293.65</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5301,22 +5301,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>115.2</v>
+        <v>114.7</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1168.55</v>
+        <v>1163.47</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>561.36</v>
+        <v>556.28</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5328,22 +5328,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>707.8</v>
+        <v>709</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1132.48</v>
+        <v>1134.4</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>379.02</v>
+        <v>380.94</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5355,22 +5355,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>328.92</v>
+        <v>333.88</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1063.32</v>
+        <v>1080.58</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>421.33</v>
+        <v>438.59</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5382,76 +5382,76 @@
         <v>3.05990683</v>
       </c>
       <c r="D17" t="n">
-        <v>305.77</v>
+        <v>305.68</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>690.34</v>
+        <v>690.92</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>199.29</v>
+        <v>199.87</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>1.8650317</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>495.26</v>
+        <v>44.8</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>681.52</v>
+        <v>661.85</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>534.38</v>
+        <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>147.14</v>
+        <v>-205.73</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>20</v>
+        <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>45.89</v>
+        <v>480.36</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>677.1799999999999</v>
+        <v>661.77</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>867.58</v>
+        <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>-190.4</v>
+        <v>127.39</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5463,22 +5463,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>97</v>
+        <v>96.62</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>658.15</v>
+        <v>656.3200000000001</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>108.97</v>
+        <v>107.14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5490,22 +5490,22 @@
         <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>996</v>
+        <v>997.75</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>647.4</v>
+        <v>648.54</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-15.28</v>
+        <v>-14.14</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5517,22 +5517,22 @@
         <v>2.330043</v>
       </c>
       <c r="D22" t="n">
-        <v>342.22</v>
+        <v>337.55</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>588.34</v>
+        <v>580.97</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>99.06999999999999</v>
+        <v>91.7</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5544,22 +5544,22 @@
         <v>140</v>
       </c>
       <c r="D23" t="n">
-        <v>3.8295</v>
+        <v>3.82</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>536.13</v>
+        <v>534.8</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-2.24</v>
+        <v>-3.57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5571,22 +5571,22 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>347.27</v>
+        <v>343.85</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>512.45</v>
+        <v>507.99</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>104.53</v>
+        <v>100.07</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5598,103 +5598,103 @@
         <v>1.11022215</v>
       </c>
       <c r="D25" t="n">
-        <v>234.58</v>
+        <v>228.15</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>192.16</v>
+        <v>187.1</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-4.36</v>
+        <v>-9.42</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>ABT_US_EQ</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>0.63422137</v>
+        <v>1.55804584</v>
       </c>
       <c r="D26" t="n">
-        <v>272.96</v>
+        <v>110.03</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>127.73</v>
+        <v>126.63</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.28</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>27.88</v>
+        <v>21.35</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ABT_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>1.55804584</v>
+        <v>0.7</v>
       </c>
       <c r="D27" t="n">
-        <v>111</v>
+        <v>242.43</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>127.6</v>
+        <v>125.35</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>105.28</v>
+        <v>118.76</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>22.32</v>
+        <v>6.59</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7</v>
+        <v>0.63422137</v>
       </c>
       <c r="D28" t="n">
-        <v>246.68</v>
+        <v>266.36</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>127.41</v>
+        <v>124.78</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>118.76</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>8.65</v>
+        <v>24.93</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5706,157 +5706,157 @@
         <v>0.42010405</v>
       </c>
       <c r="D29" t="n">
-        <v>399.34</v>
+        <v>391.08</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>123.78</v>
+        <v>121.36</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>14.62</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.30858696</v>
       </c>
       <c r="D30" t="n">
-        <v>63.98</v>
+        <v>49.23</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>118.22</v>
+        <v>120.32</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>106.81</v>
+        <v>112.71</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.41</v>
+        <v>7.61</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.70722512</v>
+        <v>2.50421091</v>
       </c>
       <c r="D31" t="n">
-        <v>59</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>117.85</v>
+        <v>119.18</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>107.64</v>
+        <v>106.81</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>10.21</v>
+        <v>12.37</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.7905852</v>
       </c>
       <c r="D32" t="n">
-        <v>569</v>
+        <v>203.3</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>117.71</v>
+        <v>118.72</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>105.75</v>
+        <v>110.41</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>11.96</v>
+        <v>8.31</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.70722512</v>
       </c>
       <c r="D33" t="n">
-        <v>48.16</v>
+        <v>58.48</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>117.57</v>
+        <v>116.95</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>112.71</v>
+        <v>107.64</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>4.86</v>
+        <v>9.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.28038062</v>
       </c>
       <c r="D34" t="n">
-        <v>200.17</v>
+        <v>563.8</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>116.76</v>
+        <v>116.77</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>110.41</v>
+        <v>105.75</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>6.35</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5868,49 +5868,49 @@
         <v>1.32559468</v>
       </c>
       <c r="D35" t="n">
-        <v>118.3</v>
+        <v>118.06</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>115.71</v>
+        <v>115.6</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-4.02</v>
+        <v>-4.13</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.59183053</v>
       </c>
       <c r="D36" t="n">
-        <v>359.1</v>
+        <v>261.68</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>115.48</v>
+        <v>114.4</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>104.04</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>11.44</v>
+        <v>14.55</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5922,130 +5922,130 @@
         <v>3.81488812</v>
       </c>
       <c r="D37" t="n">
-        <v>40.47</v>
+        <v>40.16</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>113.91</v>
+        <v>113.17</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>5.68</v>
+        <v>4.94</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.43583007</v>
       </c>
       <c r="D38" t="n">
-        <v>260.55</v>
+        <v>349.28</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>113.77</v>
+        <v>112.45</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>104.04</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>13.92</v>
+        <v>8.41</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>1.73400968</v>
+        <v>0.5550481</v>
       </c>
       <c r="D39" t="n">
-        <v>87.7</v>
+        <v>271.76</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.2</v>
+        <v>111.42</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>101.53</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>10.67</v>
+        <v>20.24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.73400968</v>
       </c>
       <c r="D40" t="n">
-        <v>290.81</v>
+        <v>86.86</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>111.32</v>
+        <v>111.26</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>95.94</v>
+        <v>101.53</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>15.38</v>
+        <v>9.73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.51881442</v>
       </c>
       <c r="D41" t="n">
-        <v>1172.23</v>
+        <v>288.5</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.2</v>
+        <v>110.56</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>98.89</v>
+        <v>95.94</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>12.31</v>
+        <v>14.62</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6057,238 +6057,238 @@
         <v>0.80409618</v>
       </c>
       <c r="D42" t="n">
-        <v>185.81</v>
+        <v>185.27</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>110.24</v>
+        <v>110.04</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.1285649</v>
       </c>
       <c r="D43" t="n">
-        <v>268.84</v>
+        <v>1154.58</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>110.1</v>
+        <v>109.65</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>18.92</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.68495686</v>
       </c>
       <c r="D44" t="n">
-        <v>394</v>
+        <v>216.43</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>109.92</v>
+        <v>109.5</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>14.41</v>
+        <v>20.04</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.40867246</v>
       </c>
       <c r="D45" t="n">
-        <v>53.77</v>
+        <v>362.7</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>109.75</v>
+        <v>109.49</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>112.48</v>
+        <v>92.83</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-2.73</v>
+        <v>16.66</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>1.35094641</v>
+        <v>2.76637723</v>
       </c>
       <c r="D46" t="n">
-        <v>110</v>
+        <v>53.57</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>109.65</v>
+        <v>109.47</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>112.48</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>12.97</v>
+        <v>-3.01</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.37810738</v>
       </c>
       <c r="D47" t="n">
-        <v>362.63</v>
+        <v>390.44</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>109.34</v>
+        <v>109.05</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>92.83</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>16.51</v>
+        <v>13.54</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.62445608</v>
       </c>
       <c r="D48" t="n">
-        <v>216</v>
+        <v>235.02</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>109.16</v>
+        <v>108.41</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>108.77</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>19.7</v>
+        <v>-0.36</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.90543241</v>
       </c>
       <c r="D49" t="n">
-        <v>12.93</v>
+        <v>161.85</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>108.76</v>
+        <v>108.25</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>106.15</v>
+        <v>92.27</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>2.61</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.90543241</v>
+        <v>11.40066159</v>
       </c>
       <c r="D50" t="n">
-        <v>162</v>
+        <v>12.81</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>108.23</v>
+        <v>107.88</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>92.27</v>
+        <v>106.15</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>15.96</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6300,49 +6300,49 @@
         <v>13.30225117</v>
       </c>
       <c r="D51" t="n">
-        <v>10.96</v>
+        <v>10.94</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>107.57</v>
+        <v>107.5</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.61</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.42255419</v>
+        <v>1.35094641</v>
       </c>
       <c r="D52" t="n">
-        <v>344.5</v>
+        <v>107.61</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>107.41</v>
+        <v>107.38</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>101.39</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>6.02</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6354,211 +6354,211 @@
         <v>1.59010207</v>
       </c>
       <c r="D53" t="n">
-        <v>91.55</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>107.41</v>
+        <v>107.36</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>17.75</v>
+        <v>17.7</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.42255419</v>
       </c>
       <c r="D54" t="n">
-        <v>25.43</v>
+        <v>341.98</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>106.79</v>
+        <v>106.74</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>452.96</v>
+        <v>101.39</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>-346.17</v>
+        <v>5.35</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1.74206342</v>
+        <v>1.1533463</v>
       </c>
       <c r="D55" t="n">
-        <v>82.98999999999999</v>
+        <v>124.57</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>106.67</v>
+        <v>106.13</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>9.99</v>
+        <v>16.6</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.61215748</v>
       </c>
       <c r="D56" t="n">
-        <v>231.34</v>
+        <v>234.5</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>106.59</v>
+        <v>106.04</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>108.77</v>
+        <v>88.09</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>-2.18</v>
+        <v>17.95</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.17949395</v>
       </c>
       <c r="D57" t="n">
-        <v>235.17</v>
+        <v>121.39</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>106.22</v>
+        <v>105.76</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>88.09</v>
+        <v>98.72</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>18.13</v>
+        <v>7.04</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1.17949395</v>
+        <v>5.691347</v>
       </c>
       <c r="D58" t="n">
-        <v>122.01</v>
+        <v>25.13</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>106.18</v>
+        <v>105.65</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>98.72</v>
+        <v>452.96</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>7.46</v>
+        <v>-347.31</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.74206342</v>
       </c>
       <c r="D59" t="n">
-        <v>62.85</v>
+        <v>81.79000000000001</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>105.54</v>
+        <v>105.25</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>106.15</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-0.61</v>
+        <v>8.57</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1.1533463</v>
+        <v>2.27580753</v>
       </c>
       <c r="D60" t="n">
-        <v>124</v>
+        <v>62.27</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>105.52</v>
+        <v>104.68</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>89.53</v>
+        <v>106.15</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>15.99</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6570,76 +6570,76 @@
         <v>0.50675322</v>
       </c>
       <c r="D61" t="n">
-        <v>275.5</v>
+        <v>276.52</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.01</v>
+        <v>103.51</v>
       </c>
       <c r="F61" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>6.33</v>
+        <v>6.83</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.11796351</v>
       </c>
       <c r="D62" t="n">
-        <v>74.73999999999999</v>
+        <v>123.67</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>102.52</v>
+        <v>102.13</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>104.98</v>
+        <v>105.36</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-2.46</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.85908491</v>
       </c>
       <c r="D63" t="n">
-        <v>124.15</v>
+        <v>74.11</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>102.41</v>
+        <v>101.77</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>105.36</v>
+        <v>104.98</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-2.95</v>
+        <v>-3.21</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6651,22 +6651,22 @@
         <v>0.10445851</v>
       </c>
       <c r="D64" t="n">
-        <v>1322.64</v>
+        <v>1318.17</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101.94</v>
+        <v>101.71</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>13.05</v>
+        <v>12.82</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6678,76 +6678,76 @@
         <v>0.97307689</v>
       </c>
       <c r="D65" t="n">
-        <v>140.83</v>
+        <v>137.98</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>101.11</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-10.33</v>
+        <v>-12.26</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="D66" t="n">
-        <v>218.33</v>
+        <v>113.94</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>100.12</v>
+        <v>98.73</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>107.82</v>
+        <v>110.45</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-7.7</v>
+        <v>-11.72</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.6214908</v>
       </c>
       <c r="D67" t="n">
-        <v>115.3</v>
+        <v>215.02</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>99.8</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>110.45</v>
+        <v>107.82</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-10.65</v>
+        <v>-9.109999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6759,22 +6759,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>114.11</v>
+        <v>112.94</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>98.14</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>5.37</v>
+        <v>4.47</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6786,22 +6786,22 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D69" t="n">
-        <v>144.47</v>
+        <v>142.82</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>97.68000000000001</v>
+        <v>96.67</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-2.17</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6813,22 +6813,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D70" t="n">
-        <v>139.27</v>
+        <v>138.9</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>96.03</v>
+        <v>95.89</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>7.65</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6840,22 +6840,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D71" t="n">
-        <v>66.16</v>
+        <v>64.06999999999999</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>90.16</v>
+        <v>87.41</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-20.37</v>
+        <v>-23.12</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6867,22 +6867,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D72" t="n">
-        <v>111</v>
+        <v>110.81</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>51.78</v>
+        <v>51.75</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>3.91</v>
+        <v>3.88</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6894,16 +6894,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D73" t="n">
-        <v>273.11</v>
+        <v>265.46</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>48.84</v>
+        <v>47.52</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-3.27</v>
+        <v>-4.59</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>44341.92</v>
+        <v>43500.7</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>43049.85</v>
+        <v>42208.5</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>6409.93</v>
+        <v>5568.58</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1749438863403632</v>
+        <v>0.1519812270332468</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1292.07</v>
+        <v>1292.2</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-17 19:06:46</t>
+          <t>2026-08-18 19:05:52</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>110.8</v>
+        <v>109.88</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7091.2</v>
+        <v>7032.32</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.164809139618758</v>
+        <v>0.1667065713821081</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1045.43</v>
+        <v>986.55</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1729192476723395</v>
+        <v>0.1631802069876955</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>15.578</v>
+        <v>14.544</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4517.62</v>
+        <v>4217.76</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.1049956375965272</v>
+        <v>0.09998525501009629</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1086.91</v>
+        <v>787.05</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.3168178015629418</v>
+        <v>0.229413153545476</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1531</v>
+        <v>1514.6</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2700.58</v>
+        <v>2671.65</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06276515487810602</v>
+        <v>0.0633335245598905</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1504.62</v>
+        <v>1475.69</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.258085554700826</v>
+        <v>1.233895782467641</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.79</v>
+        <v>24.3</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2105.84</v>
+        <v>2064.77</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04894258779540351</v>
+        <v>0.04894696592200517</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>180.03</v>
+        <v>138.96</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.09348274232660543</v>
+        <v>0.07215665096764479</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-13.65</v>
+        <v>-13.14</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>112.65</v>
+        <v>111.82</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2064.15</v>
+        <v>2049.49</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04797365545240006</v>
+        <v>0.0485847417327307</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>417.58</v>
+        <v>402.92</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2536059809179081</v>
+        <v>0.2447026242431236</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-14.69</v>
+        <v>-14.25</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -972,17 +972,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US0079031078</t>
+          <t>US67066G1040</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -991,55 +991,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>509.97</v>
+        <v>150.09436705</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>509.7</v>
+        <v>219.76</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1882.51</v>
+        <v>1774.11</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04375209462766642</v>
+        <v>0.04205664636346353</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-16.04</v>
+        <v>521.4299999999999</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.0084485528429591</v>
+        <v>0.4162515566625155</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-15.04</v>
+        <v>-40.98</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US67066G1040</t>
+          <t>US0079031078</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,38 +1048,38 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.9260596</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>150.09436705</v>
+        <v>509.97</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>225.63</v>
+        <v>479.64</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1252.68</v>
+        <v>1898.55</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1821.01</v>
+        <v>1771.96</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04232275092186858</v>
+        <v>0.04200567895463237</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>568.33</v>
+        <v>-126.59</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.4536912858830667</v>
+        <v>-0.06667720102183246</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-41.3</v>
+        <v>-14.54</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>235.11</v>
+        <v>213.4</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1667.23</v>
+        <v>1513.68</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.0387486944165419</v>
+        <v>0.03588295227885953</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-328.83</v>
+        <v>-482.38</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1647395368876687</v>
+        <v>-0.2416660821818983</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-20.77</v>
+        <v>-20.25</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>168.77</v>
+        <v>160.11</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1568.58</v>
+        <v>1488.48</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03645593414699788</v>
+        <v>0.03528556683581525</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-303.26</v>
+        <v>-383.36</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.1620117104025985</v>
+        <v>-0.2048038293871271</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-91.77</v>
+        <v>-91.3</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.06</v>
+        <v>119.08</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1398.53</v>
+        <v>1399.14</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03250374069706419</v>
+        <v>0.033167693205594</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>54.74</v>
+        <v>55.35</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.04073553159347815</v>
+        <v>0.04118947156921841</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-15.97</v>
+        <v>-15.62</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>43.55</v>
+        <v>43.07</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1387.27</v>
+        <v>1370.65</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03224204297141731</v>
+        <v>0.03249231577415227</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>158.93</v>
+        <v>142.31</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1293860006187212</v>
+        <v>0.1158555448817103</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-48.13</v>
+        <v>-49.27</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>438.6</v>
+        <v>442</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1208.14</v>
+        <v>1217.98</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02807881796296907</v>
+        <v>0.02887315563170903</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>293.65</v>
+        <v>303.49</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3211079399446686</v>
+        <v>0.3318680357357653</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-3.55</v>
+        <v>-3.19</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>114.7</v>
+        <v>112.75</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1163.47</v>
+        <v>1143.69</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02704062636397737</v>
+        <v>0.02711205386330589</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>556.28</v>
+        <v>536.5</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.9161547456315156</v>
+        <v>0.8835784515555262</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>709</v>
+        <v>693.2</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1134.4</v>
+        <v>1109.12</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02636499999767586</v>
+        <v>0.02629254534084395</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>380.94</v>
+        <v>355.66</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.5055875560746423</v>
+        <v>0.4720356754174077</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>333.88</v>
+        <v>324.62</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1080.58</v>
+        <v>1050.89</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02511414994489473</v>
+        <v>0.02491215826352379</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>438.59</v>
+        <v>408.9</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6831726350877739</v>
+        <v>0.6369258088132214</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-33.96</v>
+        <v>-33.8</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>305.68</v>
+        <v>310.17</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>690.92</v>
+        <v>701.25</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.01605792119040392</v>
+        <v>0.01662367229899995</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>199.87</v>
+        <v>210.2</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4070257611241218</v>
+        <v>0.4280623154464922</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-21.2</v>
+        <v>-21.08</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.46065664</v>
@@ -1624,25 +1624,25 @@
         <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>44.8</v>
+        <v>45.77</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>661.85</v>
+        <v>676.36</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01538229482410241</v>
+        <v>0.01603363564513598</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-205.73</v>
+        <v>-191.22</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.2371308697756979</v>
+        <v>-0.2204061873256645</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-13.08</v>
+        <v>-12.86</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -1681,25 +1681,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>480.36</v>
+        <v>482.7</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>661.77</v>
+        <v>665.17</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01538043551521681</v>
+        <v>0.01576836806149846</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>127.39</v>
+        <v>130.79</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2383884127399978</v>
+        <v>0.2447509263071223</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-25.39</v>
+        <v>-25.25</v>
       </c>
       <c r="N19" s="4" t="n">
         <v>0.3650317</v>
@@ -1738,25 +1738,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>96.62</v>
+        <v>97.66</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>656.3200000000001</v>
+        <v>663.5599999999999</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01525377009738595</v>
+        <v>0.01573020176930396</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>107.14</v>
+        <v>114.38</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.1950908627408136</v>
+        <v>0.2082741541935249</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-24.76</v>
+        <v>-24.62</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
         <v>1019.5</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>997.75</v>
+        <v>1011</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>648.54</v>
+        <v>657.15</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01507295230826225</v>
+        <v>0.01557824777367246</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-14.14</v>
+        <v>-5.53</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.0213375988410696</v>
+        <v>-0.008344902517051972</v>
       </c>
       <c r="M21" s="2" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>337.55</v>
+        <v>338.07</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>580.97</v>
+        <v>582.02</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01350253354077023</v>
+        <v>0.01379723315716784</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>91.7</v>
+        <v>92.75</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1874220777893597</v>
+        <v>0.189568132115192</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-32.1</v>
+        <v>-31.98</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,22 +1909,22 @@
         <v>3.8455</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3.82</v>
+        <v>3.811</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>534.8</v>
+        <v>533.54</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.0124294799001737</v>
+        <v>0.01264797735245409</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-3.57</v>
+        <v>-4.83</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.006631127291639578</v>
+        <v>-0.008971525159277077</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -1966,25 +1966,25 @@
         <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>343.85</v>
+        <v>342.81</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>507.99</v>
+        <v>506.58</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01180637900989013</v>
+        <v>0.01200886975148291</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>100.07</v>
+        <v>98.66</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.2453177093547754</v>
+        <v>0.24186114924495</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-9.869999999999999</v>
+        <v>-9.779999999999999</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>228.15</v>
+        <v>233.96</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>187.1</v>
+        <v>191.92</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.004348458656175206</v>
+        <v>0.004549611675756249</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-9.42</v>
+        <v>-4.6</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.04793405251373906</v>
+        <v>-0.02340728679014858</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-2.27</v>
+        <v>-2.21</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>1.11022215</v>
@@ -2080,25 +2080,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>110.03</v>
+        <v>113.23</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>126.63</v>
+        <v>130.35</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.00294305355227935</v>
+        <v>0.003090047321461167</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>21.35</v>
+        <v>25.07</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.2027925531914894</v>
+        <v>0.2381268996960486</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.29</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.55804584</v>
@@ -2112,17 +2112,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Automatic Data Processing</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US0530151036</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2131,55 +2131,55 @@
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>0.7</v>
+        <v>0.63422137</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>225.62857143</v>
+        <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>242.43</v>
+        <v>271.43</v>
       </c>
       <c r="H27" s="2" t="n">
-        <v>118.76</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>125.35</v>
+        <v>127.19</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.002913304610109899</v>
+        <v>0.003015137083365138</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>6.59</v>
+        <v>27.34</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.05549006399461098</v>
+        <v>0.2738107160741112</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-2.1</v>
+        <v>-0.15</v>
       </c>
       <c r="N27" s="4" t="n">
-        <v>0</v>
+        <v>0.63422137</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Automatic Data Processing</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US0530151036</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,38 +2188,38 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.7</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>212.76482689</v>
+        <v>225.62857143</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>266.36</v>
+        <v>244.18</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>118.76</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>124.78</v>
+        <v>126.29</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.002900057034300065</v>
+        <v>0.0029938018889707</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>24.93</v>
+        <v>7.53</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.2496745117676515</v>
+        <v>0.06340518693162681</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-0.18</v>
+        <v>-2.06</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
@@ -2251,25 +2251,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>391.08</v>
+        <v>399.48</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>121.36</v>
+        <v>124</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002820571579441063</v>
+        <v>0.002939515672122629</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>12.2</v>
+        <v>14.84</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1117625503847563</v>
+        <v>0.1359472334188347</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.35</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.42010405</v>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,34 +2302,34 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.50421091</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45.93199509</v>
+        <v>57.56703616</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>49.23</v>
+        <v>66.27</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>112.71</v>
+        <v>106.81</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>120.32</v>
+        <v>122.62</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002796400563928385</v>
+        <v>0.00290680170738449</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>7.61</v>
+        <v>15.81</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.06751841007896373</v>
+        <v>0.1480198483288082</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.45</v>
+        <v>-0.29</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.50421091</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.30858696</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>57.56703616</v>
+        <v>45.93199509</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>64.43000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>106.81</v>
+        <v>112.71</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>119.18</v>
+        <v>121.01</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002769905412308718</v>
+        <v>0.002868635415189995</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>12.37</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1158131261117873</v>
+        <v>0.07364031585484873</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.42</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.30858696</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2422,25 +2422,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>203.3</v>
+        <v>205.42</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>118.72</v>
+        <v>119.99</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002759214386216571</v>
+        <v>0.002844455528209631</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>8.31</v>
+        <v>9.58</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.07526492165564715</v>
+        <v>0.08676750294357395</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.4</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>0.7905852</v>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>53.65641702</v>
+        <v>509.16500577</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>58.48</v>
+        <v>576.51</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>107.64</v>
+        <v>105.75</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>116.95</v>
+        <v>119.43</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002718077177122877</v>
+        <v>0.002831180296141981</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>9.31</v>
+        <v>13.68</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.08649201040505389</v>
+        <v>0.1293617021276596</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.27</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.59183053</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>509.16500577</v>
+        <v>228.00445932</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>563.8</v>
+        <v>270.62</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>105.75</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>116.77</v>
+        <v>118.34</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002713893732130298</v>
+        <v>0.002805341005153161</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>11.02</v>
+        <v>18.49</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1042080378250591</v>
+        <v>0.185177766649975</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.15</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.59183053</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2593,25 +2593,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>118.06</v>
+        <v>120.43</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>115.6</v>
+        <v>117.95</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002686701339678535</v>
+        <v>0.002796095754248904</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>-4.13</v>
+        <v>-1.78</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-0.03449427879395306</v>
+        <v>-0.01486678359642529</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.6</v>
+        <v>-0.57</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>1.32559468</v>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>2.70722512</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>228.00445932</v>
+        <v>53.65641702</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>261.68</v>
+        <v>58.13</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>107.64</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>114.4</v>
+        <v>116.28</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002658811706394674</v>
+        <v>0.002756507115761446</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>14.55</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1457185778668002</v>
+        <v>0.0802675585284281</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.31</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>2.70722512</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>3.81488812</v>
+        <v>1.73400968</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>38.28159448</v>
+        <v>79.10567143</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>40.16</v>
+        <v>88.91</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>108.23</v>
+        <v>101.53</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>113.17</v>
+        <v>113.91</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002630224832278718</v>
+        <v>0.002700324437189425</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>4.94</v>
+        <v>12.38</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.04564353691213158</v>
+        <v>0.1219344036245445</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.18</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>3.81488812</v>
+        <v>1.73400968</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.43583007</v>
+        <v>3.81488812</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>322.35040597</v>
+        <v>38.28159448</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>349.28</v>
+        <v>39.9</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>104.04</v>
+        <v>108.23</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>112.45</v>
+        <v>112.47</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002613491052308401</v>
+        <v>0.002666188126158323</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>8.41</v>
+        <v>4.24</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.08083429450211457</v>
+        <v>0.03917582925251779</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.26</v>
+        <v>-0.32</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.43583007</v>
+        <v>3.81488812</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.43583007</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>221.99877812</v>
+        <v>322.35040597</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>271.76</v>
+        <v>347.89</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>111.42</v>
+        <v>112.03</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002589552450406422</v>
+        <v>0.002655757586676598</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>20.24</v>
+        <v>7.99</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.2219785040579074</v>
+        <v>0.07679738562091502</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.23</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.43583007</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,55 +2872,55 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>5.691347</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>79.10567143</v>
+        <v>105.04894536</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>86.86</v>
+        <v>26.25</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>101.53</v>
+        <v>452.96</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>111.26</v>
+        <v>110.39</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.00258583383263524</v>
+        <v>0.002616880121335621</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>9.73</v>
+        <v>-342.57</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.09583374372106766</v>
+        <v>-0.7562919463087249</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.2</v>
+        <v>-11.21</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>0</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,34 +2929,34 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>249.91595261</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>288.5</v>
+        <v>1159.99</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>95.94</v>
+        <v>98.89</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>110.56</v>
+        <v>110.19</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002569564879886322</v>
+        <v>0.002612138967025746</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>14.62</v>
+        <v>11.3</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.1523869084844695</v>
+        <v>0.1142683790069774</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.37810738</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>148.63893521</v>
+        <v>341.38450299</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>185.27</v>
+        <v>394.05</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>88.44</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>110.04</v>
+        <v>110.09</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002557479372129982</v>
+        <v>0.002609768389870809</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>21.6</v>
+        <v>14.58</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.2442333785617368</v>
+        <v>0.1526541723379751</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.37810738</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.40867246</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>306.99401668</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1154.58</v>
+        <v>362.04</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>98.89</v>
+        <v>92.83</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>109.65</v>
+        <v>109.32</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002548415241312728</v>
+        <v>0.002591514945777789</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>10.76</v>
+        <v>16.49</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.1088077662048741</v>
+        <v>0.1776365399116665</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.40867246</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.51881442</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>176.50746647</v>
+        <v>249.91595261</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>216.43</v>
+        <v>285.17</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>95.94</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>109.5</v>
+        <v>109.32</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002544929037152245</v>
+        <v>0.002591514945777789</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>20.04</v>
+        <v>13.38</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.2240107310529846</v>
+        <v>0.1394621638524078</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.51881442</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.76637723</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>306.99401668</v>
+        <v>54.82621761</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>362.7</v>
+        <v>53.34</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>92.83</v>
+        <v>112.48</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>109.49</v>
+        <v>109.03</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002544696623541546</v>
+        <v>0.00258464027202847</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>16.66</v>
+        <v>-3.45</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1794678444468383</v>
+        <v>-0.03067211948790896</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.41</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.76637723</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.5550481</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>54.82621761</v>
+        <v>221.99877812</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>53.57</v>
+        <v>264.46</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>112.48</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>109.47</v>
+        <v>108.46</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002544231796320148</v>
+        <v>0.002571127982245325</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>-3.01</v>
+        <v>17.28</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>-0.02676031294452347</v>
+        <v>0.1895152445711779</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.44</v>
+        <v>-0.13</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.5550481</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.80409618</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>341.38450299</v>
+        <v>148.63893521</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>390.44</v>
+        <v>182.12</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>109.05</v>
+        <v>108.2</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002534470424670797</v>
+        <v>0.002564964481642487</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>13.54</v>
+        <v>19.76</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1417652601821799</v>
+        <v>0.2234283129805518</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.80409618</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.62445608</v>
+        <v>11.40066159</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>235.02053179</v>
+        <v>12.56856884</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>235.02</v>
+        <v>12.84</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>108.77</v>
+        <v>106.15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>108.41</v>
+        <v>108.16</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002519595953586072</v>
+        <v>0.002564016250780512</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>-0.36</v>
+        <v>2.01</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>-0.003309736140479912</v>
+        <v>0.01893546867640132</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.28</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.62445608</v>
+        <v>11.40066159</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.35094641</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>137.713206</v>
+        <v>96.717382</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>161.85</v>
+        <v>108.26</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>92.27</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>108.25</v>
+        <v>108.06</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002515877335814891</v>
+        <v>0.002561645673625575</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>15.98</v>
+        <v>11.38</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1731873848488133</v>
+        <v>0.1177079023582954</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.35094641</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.42255419</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>12.56856884</v>
+        <v>324.07677699</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>12.81</v>
+        <v>345.2</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>106.15</v>
+        <v>101.39</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>107.88</v>
+        <v>107.78</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002507278032219034</v>
+        <v>0.00255500805759175</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>1.73</v>
+        <v>6.39</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.01629769194536034</v>
+        <v>0.06302396686063715</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.42255419</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3505,25 +3505,25 @@
         <v>10.85229847</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>10.94</v>
+        <v>10.95</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>107.5</v>
+        <v>107.62</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002498446315012478</v>
+        <v>0.00255121513414385</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.005048616305160809</v>
+        <v>0.006170531039640988</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.3</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>13.30225117</v>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.68495686</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>96.717382</v>
+        <v>176.50746647</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>107.61</v>
+        <v>211.66</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>107.38</v>
+        <v>107.12</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002495657351684092</v>
+        <v>0.002539362248369161</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>10.7</v>
+        <v>17.66</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1106743897393463</v>
+        <v>0.1974066621953946</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.68495686</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.62445608</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>235.02053179</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>91.40000000000001</v>
+        <v>231.6</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>89.66</v>
+        <v>108.77</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>107.36</v>
+        <v>106.86</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002495192524462694</v>
+        <v>0.002533198747766324</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>17.7</v>
+        <v>-1.91</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.1974124470220834</v>
+        <v>-0.0175599889675462</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.33</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.62445608</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.61215748</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>324.07677699</v>
+        <v>194.45976548</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>341.98</v>
+        <v>235.41</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>101.39</v>
+        <v>88.09</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>106.74</v>
+        <v>106.48</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002480782880599366</v>
+        <v>0.002524190554577561</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5.35</v>
+        <v>18.39</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.05276654502416411</v>
+        <v>0.2087637643319332</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.24</v>
+        <v>-0.13</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.61215748</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.74206342</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>104.90344487</v>
+        <v>74.99726962</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>124.57</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>106.13</v>
+        <v>106.24</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002466605650346738</v>
+        <v>0.002518501169405711</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>16.6</v>
+        <v>9.56</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1854127108231878</v>
+        <v>0.09888291270169632</v>
       </c>
       <c r="M55" s="2" t="n">
         <v>-0.15</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.74206342</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.17949395</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>194.45976548</v>
+        <v>113.12478542</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>234.5</v>
+        <v>121.89</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>88.09</v>
+        <v>98.72</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>106.04</v>
+        <v>106.23</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002464513927850448</v>
+        <v>0.002518264111690217</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>17.95</v>
+        <v>7.51</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.2037688727437847</v>
+        <v>0.07607374392220421</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.17949395</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.90543241</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>113.12478542</v>
+        <v>137.713206</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>121.39</v>
+        <v>158.51</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>98.72</v>
+        <v>92.27</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>105.76</v>
+        <v>106.04</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002458006346750881</v>
+        <v>0.002513760015095835</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>7.04</v>
+        <v>13.77</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.07131280388978931</v>
+        <v>0.1492359380080199</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.14</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.90543241</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,55 +3898,55 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.59010207</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>105.04894536</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>25.13</v>
+        <v>89.78</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>452.96</v>
+        <v>89.66</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>105.65</v>
+        <v>105.48</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002455449797033194</v>
+        <v>0.002500484783028185</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-347.31</v>
+        <v>15.82</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.7667564464853409</v>
+        <v>0.1764443453044836</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-11.33</v>
+        <v>-0.14</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0</v>
+        <v>1.59010207</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.50675322</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>74.99726962</v>
+        <v>257.81779936</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>81.79000000000001</v>
+        <v>280.76</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>105.25</v>
+        <v>105.12</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.00244615325260524</v>
+        <v>0.00249195070527041</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>8.57</v>
+        <v>8.44</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.08864294580057923</v>
+        <v>0.08729830368225071</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.50675322</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4018,25 +4018,25 @@
         <v>62.95787236</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>62.27</v>
+        <v>62.33</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>104.68</v>
+        <v>104.81</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002432905676795407</v>
+        <v>0.002484601916090103</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>-1.47</v>
+        <v>-1.34</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>-0.01384832783796514</v>
+        <v>-0.01262364578426755</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.28</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>2.27580753</v>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.1533463</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>257.81779936</v>
+        <v>104.90344487</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>276.52</v>
+        <v>121.45</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>103.51</v>
+        <v>103.5</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002405713284343643</v>
+        <v>0.00245354735536042</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>6.83</v>
+        <v>13.97</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.07064542821679767</v>
+        <v>0.1560370825421646</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.13</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.1533463</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4132,25 +4132,25 @@
         <v>127.23134407</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>123.67</v>
+        <v>124.37</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>102.13</v>
+        <v>102.73</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002373640206067203</v>
+        <v>0.002435293911267401</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-3.23</v>
+        <v>-2.63</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.03065679574791192</v>
+        <v>-0.02496203492786636</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.27</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>1.11796351</v>
@@ -4189,25 +4189,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>74.11</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>101.77</v>
+        <v>102.2</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002365273316082045</v>
+        <v>0.002422729852346232</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-3.21</v>
+        <v>-2.78</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.03057725281005906</v>
+        <v>-0.02648123452086111</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.25</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>1.85908491</v>
@@ -4246,25 +4246,25 @@
         <v>1150.02597682</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1318.17</v>
+        <v>1313.82</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>101.71</v>
+        <v>101.4</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002363878834417852</v>
+        <v>0.002403765235106731</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>12.82</v>
+        <v>12.51</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1442231972100349</v>
+        <v>0.1407357408032399</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.13</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>0.10445851</v>
@@ -4303,25 +4303,25 @@
         <v>154.44822659</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>137.98</v>
+        <v>140.58</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>101.07</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002305078190911047</v>
+        <v>0.002395942330495436</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-12.26</v>
+        <v>-10.37</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.1100143575017947</v>
+        <v>-0.0930545585068198</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.42</v>
+        <v>-0.4</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>0.97307689</v>
@@ -4360,25 +4360,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>113.94</v>
+        <v>115.73</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>98.73</v>
+        <v>100.31</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.0022946195784296</v>
+        <v>0.002377925944117911</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-11.72</v>
+        <v>-10.14</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.1061113626075147</v>
+        <v>-0.09180624717066546</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.37</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>1.17308322</v>
@@ -4417,25 +4417,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>215.02</v>
+        <v>217.38</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>98.70999999999999</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002294154751208202</v>
+        <v>0.002366310116058716</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-9.109999999999999</v>
+        <v>-8</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.08449267297347431</v>
+        <v>-0.07419773696902245</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.32</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>0.6214908</v>
@@ -4449,17 +4449,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,34 +4468,34 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>107.56862839</v>
+        <v>147.21071381</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>112.94</v>
+        <v>143.67</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>92.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>97.23999999999999</v>
+        <v>97.28</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002259989950435473</v>
+        <v>0.002306097456323301</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>4.47</v>
+        <v>-2.57</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.04818368006898782</v>
+        <v>-0.0257386079118678</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.17</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.16558147</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>147.21071381</v>
+        <v>107.56862839</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>142.82</v>
+        <v>112.95</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>92.77</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>96.67</v>
+        <v>97.27</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002246742374625639</v>
+        <v>0.002305860398607807</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>-3.18</v>
+        <v>4.5</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>-0.03184777165748624</v>
+        <v>0.04850706047213539</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.21</v>
+        <v>-0.13</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.16558147</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4588,25 +4588,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>138.9</v>
+        <v>137.21</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>95.89</v>
+        <v>94.75</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.00222861411299113</v>
+        <v>0.00224612185430338</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>7.51</v>
+        <v>6.37</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.08497397601267255</v>
+        <v>0.07207513011993665</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.16</v>
+        <v>-0.13</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>0.93456659</v>
@@ -4645,25 +4645,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>64.06999999999999</v>
+        <v>63.99</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>87.41</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002031527371118518</v>
+        <v>0.002069987971691516</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-23.12</v>
+        <v>-23.21</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.2091739799149552</v>
+        <v>-0.2099882384872885</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.84694851</v>
@@ -4702,25 +4702,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>110.81</v>
+        <v>111.13</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>51.75</v>
+        <v>51.91</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001202740435366472</v>
+        <v>0.00123056660112811</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3.88</v>
+        <v>4.04</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.08105285147273866</v>
+        <v>0.08439523710048047</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.63221571</v>
@@ -4759,25 +4759,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>265.46</v>
+        <v>268.94</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>47.52</v>
+        <v>48.16</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001104429478040865</v>
+        <v>0.00114166995781795</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-4.59</v>
+        <v>-3.95</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.08808290155440414</v>
+        <v>-0.0758011897908271</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.24236298</v>
@@ -4810,7 +4810,7 @@
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4869,34 +4869,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-17 19:06:46</t>
+          <t>2026-08-18 19:05:52</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>44341.92</v>
+        <v>43500.7</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>43049.85</v>
+        <v>42208.5</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>36639.92</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>6409.93</v>
+        <v>5568.58</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1749438863403632</v>
+        <v>0.1519812270332468</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1316.21</v>
+        <v>1316.34</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4977,22 +4977,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>110.8</v>
+        <v>109.88</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7091.2</v>
+        <v>7032.32</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1045.43</v>
+        <v>986.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5004,22 +5004,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>15.578</v>
+        <v>14.544</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4517.62</v>
+        <v>4217.76</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1086.91</v>
+        <v>787.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5031,22 +5031,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1531</v>
+        <v>1514.6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2700.58</v>
+        <v>2671.65</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1504.62</v>
+        <v>1475.69</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5058,22 +5058,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>24.79</v>
+        <v>24.3</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2105.84</v>
+        <v>2064.77</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>180.03</v>
+        <v>138.96</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5085,76 +5085,76 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>112.65</v>
+        <v>111.82</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2064.15</v>
+        <v>2049.49</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>417.58</v>
+        <v>402.92</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="D7" t="n">
-        <v>509.7</v>
+        <v>219.76</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1882.51</v>
+        <v>1774.11</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-16.04</v>
+        <v>521.4299999999999</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10.9260596</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>225.63</v>
+        <v>479.64</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1821.01</v>
+        <v>1771.96</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1252.68</v>
+        <v>1898.55</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>568.33</v>
+        <v>-126.59</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5166,22 +5166,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>235.11</v>
+        <v>213.4</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1667.23</v>
+        <v>1513.68</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-328.83</v>
+        <v>-482.38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5193,22 +5193,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>168.77</v>
+        <v>160.11</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1568.58</v>
+        <v>1488.48</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-303.26</v>
+        <v>-383.36</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5220,22 +5220,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.06</v>
+        <v>119.08</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1398.53</v>
+        <v>1399.14</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>54.74</v>
+        <v>55.35</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5247,22 +5247,22 @@
         <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>43.55</v>
+        <v>43.07</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1387.27</v>
+        <v>1370.65</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>158.93</v>
+        <v>142.31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5274,22 +5274,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>438.6</v>
+        <v>442</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1208.14</v>
+        <v>1217.98</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>293.65</v>
+        <v>303.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5301,22 +5301,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>114.7</v>
+        <v>112.75</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1163.47</v>
+        <v>1143.69</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>556.28</v>
+        <v>536.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5328,22 +5328,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>709</v>
+        <v>693.2</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1134.4</v>
+        <v>1109.12</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>380.94</v>
+        <v>355.66</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5355,22 +5355,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>333.88</v>
+        <v>324.62</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1080.58</v>
+        <v>1050.89</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>438.59</v>
+        <v>408.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5382,22 +5382,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D17" t="n">
-        <v>305.68</v>
+        <v>310.17</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>690.92</v>
+        <v>701.25</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>199.87</v>
+        <v>210.2</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5409,22 +5409,22 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>44.8</v>
+        <v>45.77</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>661.85</v>
+        <v>676.36</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-205.73</v>
+        <v>-191.22</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5436,22 +5436,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D19" t="n">
-        <v>480.36</v>
+        <v>482.7</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>661.77</v>
+        <v>665.17</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>127.39</v>
+        <v>130.79</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5463,22 +5463,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>96.62</v>
+        <v>97.66</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>656.3200000000001</v>
+        <v>663.5599999999999</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>107.14</v>
+        <v>114.38</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5490,22 +5490,22 @@
         <v>65</v>
       </c>
       <c r="D21" t="n">
-        <v>997.75</v>
+        <v>1011</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>648.54</v>
+        <v>657.15</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-14.14</v>
+        <v>-5.53</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5517,22 +5517,22 @@
         <v>2.330043</v>
       </c>
       <c r="D22" t="n">
-        <v>337.55</v>
+        <v>338.07</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>580.97</v>
+        <v>582.02</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>91.7</v>
+        <v>92.75</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5544,22 +5544,22 @@
         <v>140</v>
       </c>
       <c r="D23" t="n">
-        <v>3.82</v>
+        <v>3.811</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>534.8</v>
+        <v>533.54</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-3.57</v>
+        <v>-4.83</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5571,22 +5571,22 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>343.85</v>
+        <v>342.81</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>507.99</v>
+        <v>506.58</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>100.07</v>
+        <v>98.66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5598,22 +5598,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D25" t="n">
-        <v>228.15</v>
+        <v>233.96</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>187.1</v>
+        <v>191.92</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-9.42</v>
+        <v>-4.6</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5625,76 +5625,76 @@
         <v>1.55804584</v>
       </c>
       <c r="D26" t="n">
-        <v>110.03</v>
+        <v>113.23</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>126.63</v>
+        <v>130.35</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>21.35</v>
+        <v>25.07</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ADP_US_EQ</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>0.7</v>
+        <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>242.43</v>
+        <v>271.43</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>125.35</v>
+        <v>127.19</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>118.76</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>6.59</v>
+        <v>27.34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ADP_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.63422137</v>
+        <v>0.7</v>
       </c>
       <c r="D28" t="n">
-        <v>266.36</v>
+        <v>244.18</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>124.78</v>
+        <v>126.29</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>118.76</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>24.93</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5706,76 +5706,76 @@
         <v>0.42010405</v>
       </c>
       <c r="D29" t="n">
-        <v>391.08</v>
+        <v>399.48</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>121.36</v>
+        <v>124</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>12.2</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>2.50421091</v>
       </c>
       <c r="D30" t="n">
-        <v>49.23</v>
+        <v>66.27</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>120.32</v>
+        <v>122.62</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>112.71</v>
+        <v>106.81</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>7.61</v>
+        <v>15.81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.30858696</v>
       </c>
       <c r="D31" t="n">
-        <v>64.43000000000001</v>
+        <v>49.5</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>119.18</v>
+        <v>121.01</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>106.81</v>
+        <v>112.71</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>12.37</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5787,76 +5787,76 @@
         <v>0.7905852</v>
       </c>
       <c r="D32" t="n">
-        <v>203.3</v>
+        <v>205.42</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>118.72</v>
+        <v>119.99</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>8.31</v>
+        <v>9.58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.28038062</v>
       </c>
       <c r="D33" t="n">
-        <v>58.48</v>
+        <v>576.51</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>116.95</v>
+        <v>119.43</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>107.64</v>
+        <v>105.75</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>9.31</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.59183053</v>
       </c>
       <c r="D34" t="n">
-        <v>563.8</v>
+        <v>270.62</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>116.77</v>
+        <v>118.34</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>105.75</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>11.02</v>
+        <v>18.49</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5868,427 +5868,427 @@
         <v>1.32559468</v>
       </c>
       <c r="D35" t="n">
-        <v>118.06</v>
+        <v>120.43</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>115.6</v>
+        <v>117.95</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-4.13</v>
+        <v>-1.78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>2.70722512</v>
       </c>
       <c r="D36" t="n">
-        <v>261.68</v>
+        <v>58.13</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>114.4</v>
+        <v>116.28</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>107.64</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>14.55</v>
+        <v>8.640000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>3.81488812</v>
+        <v>1.73400968</v>
       </c>
       <c r="D37" t="n">
-        <v>40.16</v>
+        <v>88.91</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>113.17</v>
+        <v>113.91</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>108.23</v>
+        <v>101.53</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>4.94</v>
+        <v>12.38</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.43583007</v>
+        <v>3.81488812</v>
       </c>
       <c r="D38" t="n">
-        <v>349.28</v>
+        <v>39.9</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>112.45</v>
+        <v>112.47</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>104.04</v>
+        <v>108.23</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>8.41</v>
+        <v>4.24</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.43583007</v>
       </c>
       <c r="D39" t="n">
-        <v>271.76</v>
+        <v>347.89</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>111.42</v>
+        <v>112.03</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>20.24</v>
+        <v>7.99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>1.73400968</v>
+        <v>5.691347</v>
       </c>
       <c r="D40" t="n">
-        <v>86.86</v>
+        <v>26.25</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>111.26</v>
+        <v>110.39</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>101.53</v>
+        <v>452.96</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>9.73</v>
+        <v>-342.57</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="D41" t="n">
-        <v>288.5</v>
+        <v>1159.99</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>110.56</v>
+        <v>110.19</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>95.94</v>
+        <v>98.89</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>14.62</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.37810738</v>
       </c>
       <c r="D42" t="n">
-        <v>185.27</v>
+        <v>394.05</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>110.04</v>
+        <v>110.09</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>88.44</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>21.6</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0.40867246</v>
       </c>
       <c r="D43" t="n">
-        <v>1154.58</v>
+        <v>362.04</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>109.65</v>
+        <v>109.32</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>98.89</v>
+        <v>92.83</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>10.76</v>
+        <v>16.49</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.51881442</v>
       </c>
       <c r="D44" t="n">
-        <v>216.43</v>
+        <v>285.17</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>109.5</v>
+        <v>109.32</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>95.94</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>20.04</v>
+        <v>13.38</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.76637723</v>
       </c>
       <c r="D45" t="n">
-        <v>362.7</v>
+        <v>53.34</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>109.49</v>
+        <v>109.03</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>92.83</v>
+        <v>112.48</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>16.66</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.5550481</v>
       </c>
       <c r="D46" t="n">
-        <v>53.57</v>
+        <v>264.46</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>109.47</v>
+        <v>108.46</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>112.48</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>-3.01</v>
+        <v>17.28</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.80409618</v>
       </c>
       <c r="D47" t="n">
-        <v>390.44</v>
+        <v>182.12</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>109.05</v>
+        <v>108.2</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>88.44</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>13.54</v>
+        <v>19.76</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.62445608</v>
+        <v>11.40066159</v>
       </c>
       <c r="D48" t="n">
-        <v>235.02</v>
+        <v>12.84</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>108.41</v>
+        <v>108.16</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>108.77</v>
+        <v>106.15</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>-0.36</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.90543241</v>
+        <v>1.35094641</v>
       </c>
       <c r="D49" t="n">
-        <v>161.85</v>
+        <v>108.26</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>108.25</v>
+        <v>108.06</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>92.27</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>15.98</v>
+        <v>11.38</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.42255419</v>
       </c>
       <c r="D50" t="n">
-        <v>12.81</v>
+        <v>345.2</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>107.88</v>
+        <v>107.78</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>106.15</v>
+        <v>101.39</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>1.73</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6300,238 +6300,238 @@
         <v>13.30225117</v>
       </c>
       <c r="D51" t="n">
-        <v>10.94</v>
+        <v>10.95</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>107.5</v>
+        <v>107.62</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.54</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.68495686</v>
       </c>
       <c r="D52" t="n">
-        <v>107.61</v>
+        <v>211.66</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>107.38</v>
+        <v>107.12</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>10.7</v>
+        <v>17.66</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.62445608</v>
       </c>
       <c r="D53" t="n">
-        <v>91.40000000000001</v>
+        <v>231.6</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>107.36</v>
+        <v>106.86</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>89.66</v>
+        <v>108.77</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>17.7</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.61215748</v>
       </c>
       <c r="D54" t="n">
-        <v>341.98</v>
+        <v>235.41</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>106.74</v>
+        <v>106.48</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>101.39</v>
+        <v>88.09</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>5.35</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.74206342</v>
       </c>
       <c r="D55" t="n">
-        <v>124.57</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>106.13</v>
+        <v>106.24</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>89.53</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>16.6</v>
+        <v>9.56</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.61215748</v>
+        <v>1.17949395</v>
       </c>
       <c r="D56" t="n">
-        <v>234.5</v>
+        <v>121.89</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>106.04</v>
+        <v>106.23</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>88.09</v>
+        <v>98.72</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>17.95</v>
+        <v>7.51</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.90543241</v>
       </c>
       <c r="D57" t="n">
-        <v>121.39</v>
+        <v>158.51</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>105.76</v>
+        <v>106.04</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>98.72</v>
+        <v>92.27</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>7.04</v>
+        <v>13.77</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>5.691347</v>
+        <v>1.59010207</v>
       </c>
       <c r="D58" t="n">
-        <v>25.13</v>
+        <v>89.78</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105.65</v>
+        <v>105.48</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>452.96</v>
+        <v>89.66</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-347.31</v>
+        <v>15.82</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.50675322</v>
       </c>
       <c r="D59" t="n">
-        <v>81.79000000000001</v>
+        <v>280.76</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>105.25</v>
+        <v>105.12</v>
       </c>
       <c r="F59" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>8.57</v>
+        <v>8.44</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6543,49 +6543,49 @@
         <v>2.27580753</v>
       </c>
       <c r="D60" t="n">
-        <v>62.27</v>
+        <v>62.33</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>104.68</v>
+        <v>104.81</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-1.47</v>
+        <v>-1.34</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.50675322</v>
+        <v>1.1533463</v>
       </c>
       <c r="D61" t="n">
-        <v>276.52</v>
+        <v>121.45</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.51</v>
+        <v>103.5</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>89.53</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>6.83</v>
+        <v>13.97</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6597,22 +6597,22 @@
         <v>1.11796351</v>
       </c>
       <c r="D62" t="n">
-        <v>123.67</v>
+        <v>124.37</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>102.13</v>
+        <v>102.73</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-3.23</v>
+        <v>-2.63</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6624,22 +6624,22 @@
         <v>1.85908491</v>
       </c>
       <c r="D63" t="n">
-        <v>74.11</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>101.77</v>
+        <v>102.2</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-3.21</v>
+        <v>-2.78</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6651,22 +6651,22 @@
         <v>0.10445851</v>
       </c>
       <c r="D64" t="n">
-        <v>1318.17</v>
+        <v>1313.82</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101.71</v>
+        <v>101.4</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>88.89</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>12.82</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6678,22 +6678,22 @@
         <v>0.97307689</v>
       </c>
       <c r="D65" t="n">
-        <v>137.98</v>
+        <v>140.58</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>99.18000000000001</v>
+        <v>101.07</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>111.44</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-12.26</v>
+        <v>-10.37</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6705,22 +6705,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D66" t="n">
-        <v>113.94</v>
+        <v>115.73</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>98.73</v>
+        <v>100.31</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-11.72</v>
+        <v>-10.14</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6732,76 +6732,76 @@
         <v>0.6214908</v>
       </c>
       <c r="D67" t="n">
-        <v>215.02</v>
+        <v>217.38</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>98.70999999999999</v>
+        <v>99.81999999999999</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-9.109999999999999</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D68" t="n">
-        <v>112.94</v>
+        <v>143.67</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>97.23999999999999</v>
+        <v>97.28</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>92.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>4.47</v>
+        <v>-2.57</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.16558147</v>
       </c>
       <c r="D69" t="n">
-        <v>142.82</v>
+        <v>112.95</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>96.67</v>
+        <v>97.27</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>92.77</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>-3.18</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6813,22 +6813,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D70" t="n">
-        <v>138.9</v>
+        <v>137.21</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>95.89</v>
+        <v>94.75</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>7.51</v>
+        <v>6.37</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6840,22 +6840,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D71" t="n">
-        <v>64.06999999999999</v>
+        <v>63.99</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>87.41</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-23.12</v>
+        <v>-23.21</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6867,22 +6867,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D72" t="n">
-        <v>110.81</v>
+        <v>111.13</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>51.75</v>
+        <v>51.91</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>3.88</v>
+        <v>4.04</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6894,16 +6894,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D73" t="n">
-        <v>265.46</v>
+        <v>268.94</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>47.52</v>
+        <v>48.16</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-4.59</v>
+        <v>-3.95</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43500.7</v>
+        <v>43319.97</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>42208.5</v>
+        <v>42027.63</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5568.58</v>
+        <v>5387.71</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1519812270332468</v>
+        <v>0.147044807958096</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1292.2</v>
+        <v>1292.34</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-18 19:05:52</t>
+          <t>2026-08-19 19:01:17</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>109.88</v>
+        <v>109.74</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7032.32</v>
+        <v>7023.36</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1667065713821081</v>
+        <v>0.1672109135061781</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>986.55</v>
+        <v>977.59</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1631802069876955</v>
+        <v>0.1616981790574236</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.544</v>
+        <v>14.33</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4217.76</v>
+        <v>4155.7</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09998525501009629</v>
+        <v>0.09893817108301788</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>787.05</v>
+        <v>724.99</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.229413153545476</v>
+        <v>0.2113236035689405</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1514.6</v>
+        <v>1497.2</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2671.65</v>
+        <v>2640.96</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.0633335245598905</v>
+        <v>0.06287550889222199</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1475.69</v>
+        <v>1445</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.233895782467641</v>
+        <v>1.208234389110004</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>22.51</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.3</v>
+        <v>24.29</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2064.77</v>
+        <v>2052.71</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04894696592200517</v>
+        <v>0.04887055686498584</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>138.96</v>
+        <v>126.9</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.07215665096764479</v>
+        <v>0.06589435094843209</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-13.14</v>
+        <v>-23.53</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>0</v>
@@ -940,25 +940,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>111.82</v>
+        <v>111.69</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2049.49</v>
+        <v>2035.99</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.0485847417327307</v>
+        <v>0.04847249006023379</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>402.92</v>
+        <v>389.42</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2447026242431236</v>
+        <v>0.2365037623666167</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-14.25</v>
+        <v>-23.12</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>1.15856288</v>
@@ -997,25 +997,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>219.76</v>
+        <v>219.53</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1774.11</v>
+        <v>1762.63</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04205664636346353</v>
+        <v>0.04196438349641692</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>521.4299999999999</v>
+        <v>509.95</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.4162515566625155</v>
+        <v>0.4070872050324105</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-40.98</v>
+        <v>-47.55</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>509.97</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>479.64</v>
+        <v>466.41</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1771.96</v>
+        <v>1713.72</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04200567895463237</v>
+        <v>0.0407999428612242</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-126.59</v>
+        <v>-184.83</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0.06667720102183246</v>
+        <v>-0.09735324326459667</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-14.54</v>
+        <v>-24.78</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>213.4</v>
+        <v>233.69</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1513.68</v>
+        <v>1648.59</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03588295227885953</v>
+        <v>0.03924933933290479</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-482.38</v>
+        <v>-347.47</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.2416660821818983</v>
+        <v>-0.1740779335290523</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-20.25</v>
+        <v>-30.98</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>160.11</v>
+        <v>153.07</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1488.48</v>
+        <v>1415.31</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03528556683581525</v>
+        <v>0.03369545032497678</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-383.36</v>
+        <v>-456.53</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2048038293871271</v>
+        <v>-0.2438937088640055</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-91.3</v>
+        <v>-100.97</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.08</v>
+        <v>119.14</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1399.14</v>
+        <v>1392.24</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.033167693205594</v>
+        <v>0.03314620384258268</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>55.35</v>
+        <v>48.45</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.04118947156921841</v>
+        <v>0.03605474069609091</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-15.62</v>
+        <v>-22.83</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>43.07</v>
+        <v>42.88</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1370.65</v>
+        <v>1382.07</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03249231577415227</v>
+        <v>0.03290407828012284</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>142.31</v>
+        <v>153.73</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1158555448817103</v>
+        <v>0.1251526450331341</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-49.27</v>
+        <v>-34.18</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1217.98</v>
+        <v>1210.61</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02887315563170903</v>
+        <v>0.02882198890555436</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>303.49</v>
+        <v>296.12</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3318680357357653</v>
+        <v>0.3238088989491411</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-3.19</v>
+        <v>-0.43</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>112.75</v>
+        <v>110.35</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1143.69</v>
+        <v>1119.35</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02711205386330589</v>
+        <v>0.02664928695569364</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>536.5</v>
+        <v>512.16</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8835784515555262</v>
+        <v>0.8434921523740508</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>693.2</v>
+        <v>682</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1109.12</v>
+        <v>1091.2</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02629254534084395</v>
+        <v>0.02597909673118587</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>355.66</v>
+        <v>337.74</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4720356754174077</v>
+        <v>0.4482520638122793</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>324.62</v>
+        <v>322.51</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1050.89</v>
+        <v>1038.39</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02491215826352379</v>
+        <v>0.02472180558531534</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>408.9</v>
+        <v>396.4</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6369258088132214</v>
+        <v>0.6174551005467375</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-33.8</v>
+        <v>-37.1</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>310.17</v>
+        <v>314.87</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>701.25</v>
+        <v>708.01</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.01662367229899995</v>
+        <v>0.0168561769397424</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>210.2</v>
+        <v>216.96</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4280623154464922</v>
+        <v>0.4418287343447714</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-21.08</v>
+        <v>-23.63</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.46065664</v>
@@ -1624,25 +1624,25 @@
         <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>45.77</v>
+        <v>46.69</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>676.36</v>
+        <v>686.21</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01603363564513598</v>
+        <v>0.0163371663928767</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-191.22</v>
+        <v>-181.37</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.2204061873256645</v>
+        <v>-0.2090527674681297</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-12.86</v>
+        <v>-17.5</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -1656,74 +1656,74 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>IE00B43HR379</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>GBX</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>1.8650317</v>
+        <v>65</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>369.46288902</v>
+        <v>1019.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>482.7</v>
+        <v>1035</v>
       </c>
       <c r="H19" s="2" t="n">
-        <v>534.38</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>665.17</v>
+        <v>672.75</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01576836806149846</v>
+        <v>0.01601671309192201</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>130.79</v>
+        <v>10.07</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.2447509263071223</v>
+        <v>0.01519587131043641</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>-25.25</v>
+        <v>0</v>
       </c>
       <c r="N19" s="4" t="n">
-        <v>0.3650317</v>
+        <v>0</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2026-07-29</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US6311031081</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1732,95 +1732,95 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>1.8650317</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>77.20222067</v>
+        <v>369.46288902</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>97.66</v>
+        <v>483.91</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>534.38</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>663.5599999999999</v>
+        <v>663.21</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01573020176930396</v>
+        <v>0.01578958645811013</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>114.38</v>
+        <v>128.83</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.2082741541935249</v>
+        <v>0.241083124368427</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-24.62</v>
+        <v>-28.02</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0</v>
+        <v>0.3650317</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>iShares S&amp;P 500 Health Care Sector (Acc)</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>IE00B43HR379</t>
+          <t>US6311031081</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>GBX</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>65</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>1019.5</v>
+        <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>1011</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>657.15</v>
+        <v>662.53</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01557824777367246</v>
+        <v>0.01577339713829964</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>-5.53</v>
+        <v>113.35</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>-0.008344902517051972</v>
+        <v>0.2063986306857497</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>0</v>
+        <v>-27.47</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2024-09-26</t>
         </is>
       </c>
     </row>
@@ -1852,25 +1852,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>338.07</v>
+        <v>340.21</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>582.02</v>
+        <v>582.52</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01379723315716784</v>
+        <v>0.01386853320000952</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>92.75</v>
+        <v>93.25</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.189568132115192</v>
+        <v>0.1905900627465408</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-31.98</v>
+        <v>-34.46</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,22 +1909,22 @@
         <v>3.8455</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3.811</v>
+        <v>3.8285</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>533.54</v>
+        <v>535.99</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01264797735245409</v>
+        <v>0.01276075518415351</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-4.83</v>
+        <v>-2.38</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.008971525159277077</v>
+        <v>-0.004420751527759719</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -1966,25 +1966,25 @@
         <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>342.81</v>
+        <v>344.35</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>506.58</v>
+        <v>506.1</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01200886975148291</v>
+        <v>0.01204913934718949</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>98.66</v>
+        <v>98.18000000000001</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.24186114924495</v>
+        <v>0.2406844479309669</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-9.779999999999999</v>
+        <v>-11.93</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>233.96</v>
+        <v>236.65</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>191.92</v>
+        <v>193.07</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.004549611675756249</v>
+        <v>0.004596576435016546</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-4.6</v>
+        <v>-3.45</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.02340728679014858</v>
+        <v>-0.01755546509261144</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-2.21</v>
+        <v>-3.27</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>1.11022215</v>
@@ -2080,25 +2080,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>113.23</v>
+        <v>114.76</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>130.35</v>
+        <v>131.39</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.003090047321461167</v>
+        <v>0.003128109896912125</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>25.07</v>
+        <v>26.11</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.2381268996960486</v>
+        <v>0.2480053191489362</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.86</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.55804584</v>
@@ -2137,25 +2137,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>271.43</v>
+        <v>277.96</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>127.19</v>
+        <v>129.55</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003015137083365138</v>
+        <v>0.003084303502130801</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>27.34</v>
+        <v>29.7</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.2738107160741112</v>
+        <v>0.2974461692538808</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.68</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0.63422137</v>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,55 +2188,55 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.7</v>
+        <v>0.42010405</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>225.62857143</v>
+        <v>350.55601106</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>244.18</v>
+        <v>408.2</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>118.76</v>
+        <v>109.16</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>126.29</v>
+        <v>126.02</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.0029938018889707</v>
+        <v>0.003000261886055758</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>7.53</v>
+        <v>16.86</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.06340518693162681</v>
+        <v>0.154452180285819</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-2.06</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0</v>
+        <v>0.42010405</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>350.55601106</v>
+        <v>57.56703616</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>399.48</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>109.16</v>
+        <v>106.81</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>124</v>
+        <v>125.01</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002939515672122629</v>
+        <v>0.002976215984572531</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>14.84</v>
+        <v>18.2</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1359472334188347</v>
+        <v>0.1703960303342384</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.35</v>
+        <v>-0.87</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,38 +2302,38 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.7</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>57.56703616</v>
+        <v>225.62857143</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>66.27</v>
+        <v>238.54</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>106.81</v>
+        <v>118.76</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>122.62</v>
+        <v>122.7</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.00290680170738449</v>
+        <v>0.002921219912863367</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>15.81</v>
+        <v>3.94</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1480198483288082</v>
+        <v>0.03317615358706635</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-0.29</v>
+        <v>-2.7</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
@@ -2365,25 +2365,25 @@
         <v>45.93199509</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>49.5</v>
+        <v>49.57</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>121.01</v>
+        <v>120.52</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002868635415189995</v>
+        <v>0.002869318858176797</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>7.81</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.07364031585484873</v>
+        <v>0.06929287552124923</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-0.42</v>
+        <v>-1.04</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>3.30858696</v>
@@ -2422,25 +2422,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>205.42</v>
+        <v>206.62</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>119.99</v>
+        <v>120.04</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002844455528209631</v>
+        <v>0.002857891103016451</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>9.58</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.08676750294357395</v>
+        <v>0.08722036047459471</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>0.7905852</v>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.59183053</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>509.16500577</v>
+        <v>228.00445932</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>576.51</v>
+        <v>274.55</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>105.75</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.43</v>
+        <v>119.4</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002831180296141981</v>
+        <v>0.00284265409613599</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.68</v>
+        <v>19.55</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1293617021276596</v>
+        <v>0.1957936905358037</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.59183053</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.28038062</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>228.00445932</v>
+        <v>509.16500577</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>270.62</v>
+        <v>575.6900000000001</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.75</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118.34</v>
+        <v>118.61</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002805341005153161</v>
+        <v>0.002823845915767921</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>18.49</v>
+        <v>12.86</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.185177766649975</v>
+        <v>0.1216075650118203</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.85</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.28038062</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2593,25 +2593,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>120.43</v>
+        <v>120.14</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>117.95</v>
+        <v>117.03</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002796095754248904</v>
+        <v>0.002786229555031783</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>-1.78</v>
+        <v>-2.7</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-0.01486678359642529</v>
+        <v>-0.02255073916311701</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.57</v>
+        <v>-1.21</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>1.32559468</v>
@@ -2650,25 +2650,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>58.13</v>
+        <v>58.22</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>116.28</v>
+        <v>115.82</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002756507115761446</v>
+        <v>0.002757422088898412</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.0802675585284281</v>
+        <v>0.07599405425492382</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.31</v>
+        <v>-0.9</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>2.70722512</v>
@@ -2707,25 +2707,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>88.91</v>
+        <v>90.73</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>113.91</v>
+        <v>115.61</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002700324437189425</v>
+        <v>0.002752422446015761</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>12.38</v>
+        <v>14.08</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.1219344036245445</v>
+        <v>0.1386782231852654</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.73</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>1.73400968</v>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.43583007</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>38.28159448</v>
+        <v>322.35040597</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>39.9</v>
+        <v>353.53</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>108.23</v>
+        <v>104.04</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>112.47</v>
+        <v>113.23</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002666188126158323</v>
+        <v>0.002695759826679047</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>4.24</v>
+        <v>9.19</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.03917582925251779</v>
+        <v>0.08833141099577085</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.8</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.43583007</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.62445608</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>322.35040597</v>
+        <v>235.02053179</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>347.89</v>
+        <v>245.91</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>104.04</v>
+        <v>108.77</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.03</v>
+        <v>112.84</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002655757586676598</v>
+        <v>0.002686474775611266</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>7.99</v>
+        <v>4.07</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.07679738562091502</v>
+        <v>0.03741840581042567</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.93</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.62445608</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,55 +2872,55 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>5.691347</v>
+        <v>3.81488812</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>105.04894536</v>
+        <v>38.28159448</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>26.25</v>
+        <v>40.23</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>452.96</v>
+        <v>108.23</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>110.39</v>
+        <v>112.78</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002616880121335621</v>
+        <v>0.002685046306216222</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-342.57</v>
+        <v>4.55</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.7562919463087249</v>
+        <v>0.04204009978748961</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-11.21</v>
+        <v>-0.91</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0</v>
+        <v>3.81488812</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,55 +2929,55 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>0.1285649</v>
+        <v>5.691347</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>105.04894536</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>1159.99</v>
+        <v>26.56</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>98.89</v>
+        <v>452.96</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>110.19</v>
+        <v>111.08</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002612138967025746</v>
+        <v>0.002644573006689998</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>11.3</v>
+        <v>-341.88</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.1142683790069774</v>
+        <v>-0.7547686329918757</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.15</v>
+        <v>-13.61</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0.1285649</v>
+        <v>0</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.1285649</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>341.38450299</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>394.05</v>
+        <v>1160.96</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>110.09</v>
+        <v>109.68</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002609768389870809</v>
+        <v>0.00261124205413899</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>14.58</v>
+        <v>10.79</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.1526541723379751</v>
+        <v>0.1091111335827687</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.1285649</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.37810738</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>306.99401668</v>
+        <v>341.38450299</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>362.04</v>
+        <v>393.41</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>92.83</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>109.32</v>
+        <v>109.31</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002591514945777789</v>
+        <v>0.002602433159536224</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>16.49</v>
+        <v>13.8</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.1776365399116665</v>
+        <v>0.1444874882211287</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.66</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.37810738</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.35094641</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>249.91595261</v>
+        <v>96.717382</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>285.17</v>
+        <v>109.5</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>95.94</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>109.32</v>
+        <v>108.71</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002591514945777789</v>
+        <v>0.002588148465585791</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>13.38</v>
+        <v>12.03</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1394621638524078</v>
+        <v>0.1244311129499379</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.66</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.35094641</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.51881442</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>54.82621761</v>
+        <v>249.91595261</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>53.34</v>
+        <v>285</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>112.48</v>
+        <v>95.94</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>109.03</v>
+        <v>108.66</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.00258464027202847</v>
+        <v>0.002586958074423255</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>-3.45</v>
+        <v>12.72</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>-0.03067211948790896</v>
+        <v>0.1325828642901814</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.41</v>
+        <v>-0.66</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.51881442</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>221.99877812</v>
+        <v>12.56856884</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>264.46</v>
+        <v>12.96</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>108.46</v>
+        <v>108.58</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002571127982245325</v>
+        <v>0.002585053448563198</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>17.28</v>
+        <v>2.43</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1895152445711779</v>
+        <v>0.02289213377296279</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.85</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>148.63893521</v>
+        <v>54.82621761</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>182.12</v>
+        <v>53.32</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>88.44</v>
+        <v>112.48</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>108.2</v>
+        <v>108.39</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002564964481642487</v>
+        <v>0.002580529962145561</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>19.76</v>
+        <v>-4.09</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.2234283129805518</v>
+        <v>-0.03636201991465149</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.13</v>
+        <v>-1.03</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>11.40066159</v>
+        <v>13.30225117</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>12.56856884</v>
+        <v>10.85229847</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>12.84</v>
+        <v>11.03</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>106.15</v>
+        <v>106.96</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>108.16</v>
+        <v>107.82</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002564016250780512</v>
+        <v>0.00256695950289265</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>2.01</v>
+        <v>0.86</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.01893546867640132</v>
+        <v>0.008040388930441287</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.88</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>11.40066159</v>
+        <v>13.30225117</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.40867246</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>96.717382</v>
+        <v>306.99401668</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>108.26</v>
+        <v>356.57</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>108.06</v>
+        <v>107.08</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002561645673625575</v>
+        <v>0.002549341713687118</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>11.38</v>
+        <v>14.25</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1177079023582954</v>
+        <v>0.1535064095658731</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.64</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.40867246</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3448,25 +3448,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>345.2</v>
+        <v>343.1</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>107.78</v>
+        <v>106.54</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.00255500805759175</v>
+        <v>0.002536485489131729</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>6.39</v>
+        <v>5.15</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.06302396686063715</v>
+        <v>0.05079396390176547</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.76</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>0.42255419</v>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.61215748</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>10.85229847</v>
+        <v>194.45976548</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>10.95</v>
+        <v>236.71</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>106.96</v>
+        <v>88.09</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>107.62</v>
+        <v>106.48</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.00255121513414385</v>
+        <v>0.002535057019736686</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>0.66</v>
+        <v>18.39</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.006170531039640988</v>
+        <v>0.2087637643319332</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.62</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.61215748</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.50675322</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>176.50746647</v>
+        <v>257.81779936</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>211.66</v>
+        <v>284.24</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>107.12</v>
+        <v>105.85</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002539362248369161</v>
+        <v>0.002520058091088732</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>17.66</v>
+        <v>9.17</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1974066621953946</v>
+        <v>0.0948489863467108</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.67</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.50675322</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.74206342</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>235.02053179</v>
+        <v>74.99726962</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>231.6</v>
+        <v>82.61</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>108.77</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>106.86</v>
+        <v>105.75</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002533198747766324</v>
+        <v>0.00251767730876366</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>-1.91</v>
+        <v>9.07</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>-0.0175599889675462</v>
+        <v>0.09381464625568886</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.68</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.74206342</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>194.45976548</v>
+        <v>62.95787236</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>235.41</v>
+        <v>62.91</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>88.09</v>
+        <v>106.15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>106.48</v>
+        <v>105.21</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002524190554577561</v>
+        <v>0.002504821084208271</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>18.39</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.2087637643319332</v>
+        <v>-0.008855393311351859</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.86</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.90543241</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>74.99726962</v>
+        <v>137.713206</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>82.54000000000001</v>
+        <v>157.59</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>106.24</v>
+        <v>104.85</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002518501169405711</v>
+        <v>0.002496250267838012</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>9.56</v>
+        <v>12.58</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.09888291270169632</v>
+        <v>0.1363390050937466</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.65</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.90543241</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.68495686</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>113.12478542</v>
+        <v>176.50746647</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>121.89</v>
+        <v>207.72</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>98.72</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>106.23</v>
+        <v>104.55</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002518264111690217</v>
+        <v>0.002489107920862795</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>7.51</v>
+        <v>15.09</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.07607374392220421</v>
+        <v>0.1686787391012743</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.62</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.68495686</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.80409618</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>137.713206</v>
+        <v>148.63893521</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>158.51</v>
+        <v>176.23</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>92.27</v>
+        <v>88.44</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>106.04</v>
+        <v>104.13</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002513760015095835</v>
+        <v>0.002479108635097493</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>13.77</v>
+        <v>15.69</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.1492359380080199</v>
+        <v>0.1774084124830393</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.61</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.80409618</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3904,25 +3904,25 @@
         <v>76.19636644000001</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>89.78</v>
+        <v>87.83</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>105.48</v>
+        <v>102.63</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002500484783028185</v>
+        <v>0.002443396900221413</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>15.82</v>
+        <v>12.97</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.1764443453044836</v>
+        <v>0.1446575953602499</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.62</v>
       </c>
       <c r="N58" s="4" t="n">
         <v>1.59010207</v>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.97307689</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>257.81779936</v>
+        <v>154.44822659</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>280.76</v>
+        <v>143.45</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>111.44</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>105.12</v>
+        <v>102.58</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.00249195070527041</v>
+        <v>0.002442206509058877</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>8.44</v>
+        <v>-8.859999999999999</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.08729830368225071</v>
+        <v>-0.07950466618808327</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.15</v>
+        <v>-1</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.97307689</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.11796351</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>62.95787236</v>
+        <v>127.23134407</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>62.33</v>
+        <v>123.92</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>106.15</v>
+        <v>105.36</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>104.81</v>
+        <v>101.81</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002484601916090103</v>
+        <v>0.002423874485155822</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>-1.34</v>
+        <v>-3.55</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>-0.01262364578426755</v>
+        <v>-0.03369400151860288</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.28</v>
+        <v>-0.83</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.11796351</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.85908491</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>104.90344487</v>
+        <v>76.24181082</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>121.45</v>
+        <v>74.47</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>89.53</v>
+        <v>104.98</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>103.5</v>
+        <v>101.74</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.00245354735536042</v>
+        <v>0.002422207937528272</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>13.97</v>
+        <v>-3.24</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.1560370825421646</v>
+        <v>-0.03086302152791008</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.82</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.85908491</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.17949395</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>127.23134407</v>
+        <v>113.12478542</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>124.37</v>
+        <v>116.93</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>105.36</v>
+        <v>98.72</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>102.73</v>
+        <v>101.35</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002435293911267401</v>
+        <v>0.002412922886460491</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>-2.63</v>
+        <v>2.63</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>-0.02496203492786636</v>
+        <v>0.02664100486223663</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.27</v>
+        <v>-0.67</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.17949395</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.6214908</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>76.24181082</v>
+        <v>234.11448729</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>74.40000000000001</v>
+        <v>221.6</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>104.98</v>
+        <v>107.82</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>102.2</v>
+        <v>101.21</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002422729852346232</v>
+        <v>0.00240958979120539</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-2.78</v>
+        <v>-6.61</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.02648123452086111</v>
+        <v>-0.0613058801706548</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.25</v>
+        <v>-0.89</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.6214908</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.5550481</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>221.99877812</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>1313.82</v>
+        <v>247.1</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>88.89</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>101.4</v>
+        <v>100.79</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002403765235106731</v>
+        <v>0.002399590505440088</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>12.51</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1407357408032399</v>
+        <v>0.1053959201579294</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.63</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.5550481</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.1533463</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>154.44822659</v>
+        <v>104.90344487</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>140.58</v>
+        <v>118.69</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>111.44</v>
+        <v>89.53</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>101.07</v>
+        <v>100.59</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002395942330495436</v>
+        <v>0.002394828940789944</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-10.37</v>
+        <v>11.06</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.0930545585068198</v>
+        <v>0.1235340109460516</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.62</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.1533463</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.10445851</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>126.99866255</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>115.73</v>
+        <v>1303.8</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>110.45</v>
+        <v>88.89</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>100.31</v>
+        <v>100.08</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002377925944117911</v>
+        <v>0.002382686950932076</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-10.14</v>
+        <v>11.19</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.09180624717066546</v>
+        <v>0.1258859264259197</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.61</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.10445851</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>234.11448729</v>
+        <v>126.99866255</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>217.38</v>
+        <v>115.02</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>107.82</v>
+        <v>110.45</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>99.81999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002366310116058716</v>
+        <v>0.002360545675308907</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-8</v>
+        <v>-11.3</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.07419773696902245</v>
+        <v>-0.1023087369850611</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.32</v>
+        <v>-0.97</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4474,25 +4474,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>143.67</v>
+        <v>144.76</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>97.28</v>
+        <v>97.48</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002306097456323301</v>
+        <v>0.002320786610480204</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-2.57</v>
+        <v>-2.37</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.0257386079118678</v>
+        <v>-0.02373560340510766</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.72</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4531,25 +4531,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>112.95</v>
+        <v>113.6</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>97.27</v>
+        <v>97.3</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002305860398607807</v>
+        <v>0.002316501202295074</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.04850706047213539</v>
+        <v>0.04883044087528296</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.64</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>1.16558147</v>
@@ -4588,25 +4588,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>137.21</v>
+        <v>132.83</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>94.75</v>
+        <v>91.22</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.00224612185430338</v>
+        <v>0.002171749636930695</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>6.37</v>
+        <v>2.84</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.07207513011993665</v>
+        <v>0.03213396696085087</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.13</v>
+        <v>-0.62</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>0.93456659</v>
@@ -4645,25 +4645,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>63.99</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>87.31999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002069987971691516</v>
+        <v>0.002117705878151561</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-23.21</v>
+        <v>-21.58</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.2099882384872885</v>
+        <v>-0.1952411110105853</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.38</v>
+        <v>-0.97</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.84694851</v>
@@ -4702,25 +4702,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>111.13</v>
+        <v>112.06</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>51.91</v>
+        <v>52.06</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.00123056660112811</v>
+        <v>0.001239435278432493</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4.04</v>
+        <v>4.19</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.08439523710048047</v>
+        <v>0.08752872362648842</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.33</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.63221571</v>
@@ -4759,25 +4759,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>268.94</v>
+        <v>267.36</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>48.16</v>
+        <v>47.62</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.00114166995781795</v>
+        <v>0.001133728543199295</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-3.95</v>
+        <v>-4.49</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.0758011897908271</v>
+        <v>-0.08616388409134523</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.36</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.24236298</v>
@@ -4808,9 +4808,9 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4869,34 +4869,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-18 19:05:52</t>
+          <t>2026-08-19 19:01:17</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43500.7</v>
+        <v>43319.97</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>42208.5</v>
+        <v>42027.63</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>36639.92</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5568.58</v>
+        <v>5387.71</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1519812270332468</v>
+        <v>0.147044807958096</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1316.34</v>
+        <v>1316.48</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4977,22 +4977,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>109.88</v>
+        <v>109.74</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7032.32</v>
+        <v>7023.36</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>986.55</v>
+        <v>977.59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5004,22 +5004,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.544</v>
+        <v>14.33</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4217.76</v>
+        <v>4155.7</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>787.05</v>
+        <v>724.99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5031,22 +5031,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1514.6</v>
+        <v>1497.2</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2671.65</v>
+        <v>2640.96</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1475.69</v>
+        <v>1445</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5058,22 +5058,22 @@
         <v>115</v>
       </c>
       <c r="D5" t="n">
-        <v>24.3</v>
+        <v>24.29</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2064.77</v>
+        <v>2052.71</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>138.96</v>
+        <v>126.9</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5085,22 +5085,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D6" t="n">
-        <v>111.82</v>
+        <v>111.69</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2049.49</v>
+        <v>2035.99</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>402.92</v>
+        <v>389.42</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5112,22 +5112,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D7" t="n">
-        <v>219.76</v>
+        <v>219.53</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1774.11</v>
+        <v>1762.63</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>521.4299999999999</v>
+        <v>509.95</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5139,22 +5139,22 @@
         <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>479.64</v>
+        <v>466.41</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1771.96</v>
+        <v>1713.72</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-126.59</v>
+        <v>-184.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5166,22 +5166,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>213.4</v>
+        <v>233.69</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1513.68</v>
+        <v>1648.59</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-482.38</v>
+        <v>-347.47</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5193,22 +5193,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>160.11</v>
+        <v>153.07</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1488.48</v>
+        <v>1415.31</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-383.36</v>
+        <v>-456.53</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5220,22 +5220,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.08</v>
+        <v>119.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1399.14</v>
+        <v>1392.24</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>55.35</v>
+        <v>48.45</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5247,22 +5247,22 @@
         <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>43.07</v>
+        <v>42.88</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1370.65</v>
+        <v>1382.07</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>142.31</v>
+        <v>153.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5274,22 +5274,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1217.98</v>
+        <v>1210.61</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>303.49</v>
+        <v>296.12</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5301,22 +5301,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>112.75</v>
+        <v>110.35</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1143.69</v>
+        <v>1119.35</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>536.5</v>
+        <v>512.16</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5328,22 +5328,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>693.2</v>
+        <v>682</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1109.12</v>
+        <v>1091.2</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>355.66</v>
+        <v>337.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5355,22 +5355,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>324.62</v>
+        <v>322.51</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1050.89</v>
+        <v>1038.39</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>408.9</v>
+        <v>396.4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5382,22 +5382,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D17" t="n">
-        <v>310.17</v>
+        <v>314.87</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>701.25</v>
+        <v>708.01</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>210.2</v>
+        <v>216.96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5409,103 +5409,103 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>45.77</v>
+        <v>46.69</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>676.36</v>
+        <v>686.21</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-191.22</v>
+        <v>-181.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>IHCUl_EQ</t>
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>1.8650317</v>
+        <v>65</v>
       </c>
       <c r="D19" t="n">
-        <v>482.7</v>
+        <v>1035</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>665.17</v>
+        <v>672.75</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>534.38</v>
+        <v>662.6799999999999</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>130.79</v>
+        <v>10.07</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>1.8650317</v>
       </c>
       <c r="D20" t="n">
-        <v>97.66</v>
+        <v>483.91</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>663.5599999999999</v>
+        <v>663.21</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>534.38</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>114.38</v>
+        <v>128.83</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IHCUl_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>65</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>1011</v>
+        <v>98.04000000000001</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>657.15</v>
+        <v>662.53</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>662.6799999999999</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>-5.53</v>
+        <v>113.35</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5517,22 +5517,22 @@
         <v>2.330043</v>
       </c>
       <c r="D22" t="n">
-        <v>338.07</v>
+        <v>340.21</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>582.02</v>
+        <v>582.52</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>92.75</v>
+        <v>93.25</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5544,22 +5544,22 @@
         <v>140</v>
       </c>
       <c r="D23" t="n">
-        <v>3.811</v>
+        <v>3.8285</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>533.54</v>
+        <v>535.99</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-4.83</v>
+        <v>-2.38</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5571,22 +5571,22 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>342.81</v>
+        <v>344.35</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>506.58</v>
+        <v>506.1</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>98.66</v>
+        <v>98.18000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5598,22 +5598,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D25" t="n">
-        <v>233.96</v>
+        <v>236.65</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>191.92</v>
+        <v>193.07</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-4.6</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5625,22 +5625,22 @@
         <v>1.55804584</v>
       </c>
       <c r="D26" t="n">
-        <v>113.23</v>
+        <v>114.76</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>130.35</v>
+        <v>131.39</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>25.07</v>
+        <v>26.11</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5652,103 +5652,103 @@
         <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>271.43</v>
+        <v>277.96</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>127.19</v>
+        <v>129.55</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>27.34</v>
+        <v>29.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.7</v>
+        <v>0.42010405</v>
       </c>
       <c r="D28" t="n">
-        <v>244.18</v>
+        <v>408.2</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>126.29</v>
+        <v>126.02</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>118.76</v>
+        <v>109.16</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>7.53</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>2.50421091</v>
       </c>
       <c r="D29" t="n">
-        <v>399.48</v>
+        <v>67.93000000000001</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>124</v>
+        <v>125.01</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>109.16</v>
+        <v>106.81</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>14.84</v>
+        <v>18.2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.7</v>
       </c>
       <c r="D30" t="n">
-        <v>66.27</v>
+        <v>238.54</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>122.62</v>
+        <v>122.7</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>106.81</v>
+        <v>118.76</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>15.81</v>
+        <v>3.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5760,22 +5760,22 @@
         <v>3.30858696</v>
       </c>
       <c r="D31" t="n">
-        <v>49.5</v>
+        <v>49.57</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>121.01</v>
+        <v>120.52</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>8.300000000000001</v>
+        <v>7.81</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5787,76 +5787,76 @@
         <v>0.7905852</v>
       </c>
       <c r="D32" t="n">
-        <v>205.42</v>
+        <v>206.62</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>119.99</v>
+        <v>120.04</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>9.58</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.59183053</v>
       </c>
       <c r="D33" t="n">
-        <v>576.51</v>
+        <v>274.55</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.43</v>
+        <v>119.4</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>105.75</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.68</v>
+        <v>19.55</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.28038062</v>
       </c>
       <c r="D34" t="n">
-        <v>270.62</v>
+        <v>575.6900000000001</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>118.34</v>
+        <v>118.61</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>105.75</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>18.49</v>
+        <v>12.86</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5868,22 +5868,22 @@
         <v>1.32559468</v>
       </c>
       <c r="D35" t="n">
-        <v>120.43</v>
+        <v>120.14</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>117.95</v>
+        <v>117.03</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-1.78</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5895,22 +5895,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D36" t="n">
-        <v>58.13</v>
+        <v>58.22</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>116.28</v>
+        <v>115.82</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.640000000000001</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5922,346 +5922,346 @@
         <v>1.73400968</v>
       </c>
       <c r="D37" t="n">
-        <v>88.91</v>
+        <v>90.73</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>113.91</v>
+        <v>115.61</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>12.38</v>
+        <v>14.08</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0.43583007</v>
       </c>
       <c r="D38" t="n">
-        <v>39.9</v>
+        <v>353.53</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>112.47</v>
+        <v>113.23</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>108.23</v>
+        <v>104.04</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>4.24</v>
+        <v>9.19</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.62445608</v>
       </c>
       <c r="D39" t="n">
-        <v>347.89</v>
+        <v>245.91</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.03</v>
+        <v>112.84</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>104.04</v>
+        <v>108.77</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>7.99</v>
+        <v>4.07</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>5.691347</v>
+        <v>3.81488812</v>
       </c>
       <c r="D40" t="n">
-        <v>26.25</v>
+        <v>40.23</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>110.39</v>
+        <v>112.78</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>452.96</v>
+        <v>108.23</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-342.57</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>0.1285649</v>
+        <v>5.691347</v>
       </c>
       <c r="D41" t="n">
-        <v>1159.99</v>
+        <v>26.56</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>110.19</v>
+        <v>111.08</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>98.89</v>
+        <v>452.96</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>11.3</v>
+        <v>-341.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.1285649</v>
       </c>
       <c r="D42" t="n">
-        <v>394.05</v>
+        <v>1160.96</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>110.09</v>
+        <v>109.68</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>98.89</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>14.58</v>
+        <v>10.79</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.37810738</v>
       </c>
       <c r="D43" t="n">
-        <v>362.04</v>
+        <v>393.41</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>109.32</v>
+        <v>109.31</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>92.83</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>16.49</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>0.51881442</v>
+        <v>1.35094641</v>
       </c>
       <c r="D44" t="n">
-        <v>285.17</v>
+        <v>109.5</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>109.32</v>
+        <v>108.71</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>95.94</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>13.38</v>
+        <v>12.03</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.51881442</v>
       </c>
       <c r="D45" t="n">
-        <v>53.34</v>
+        <v>285</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>109.03</v>
+        <v>108.66</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>112.48</v>
+        <v>95.94</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>-3.45</v>
+        <v>12.72</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>0.5550481</v>
+        <v>11.40066159</v>
       </c>
       <c r="D46" t="n">
-        <v>264.46</v>
+        <v>12.96</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>108.46</v>
+        <v>108.58</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>17.28</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.80409618</v>
+        <v>2.76637723</v>
       </c>
       <c r="D47" t="n">
-        <v>182.12</v>
+        <v>53.32</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>108.2</v>
+        <v>108.39</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>88.44</v>
+        <v>112.48</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>19.76</v>
+        <v>-4.09</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>11.40066159</v>
+        <v>13.30225117</v>
       </c>
       <c r="D48" t="n">
-        <v>12.84</v>
+        <v>11.03</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>108.16</v>
+        <v>107.82</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>106.15</v>
+        <v>106.96</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>2.01</v>
+        <v>0.86</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1.35094641</v>
+        <v>0.40867246</v>
       </c>
       <c r="D49" t="n">
-        <v>108.26</v>
+        <v>356.57</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>108.06</v>
+        <v>107.08</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>11.38</v>
+        <v>14.25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6273,211 +6273,211 @@
         <v>0.42255419</v>
       </c>
       <c r="D50" t="n">
-        <v>345.2</v>
+        <v>343.1</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>107.78</v>
+        <v>106.54</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>6.39</v>
+        <v>5.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>13.30225117</v>
+        <v>0.61215748</v>
       </c>
       <c r="D51" t="n">
-        <v>10.95</v>
+        <v>236.71</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>107.62</v>
+        <v>106.48</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>106.96</v>
+        <v>88.09</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>0.66</v>
+        <v>18.39</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.50675322</v>
       </c>
       <c r="D52" t="n">
-        <v>211.66</v>
+        <v>284.24</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>107.12</v>
+        <v>105.85</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>17.66</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.74206342</v>
       </c>
       <c r="D53" t="n">
-        <v>231.6</v>
+        <v>82.61</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>106.86</v>
+        <v>105.75</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>108.77</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>-1.91</v>
+        <v>9.07</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="D54" t="n">
-        <v>235.41</v>
+        <v>62.91</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>106.48</v>
+        <v>105.21</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>88.09</v>
+        <v>106.15</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>18.39</v>
+        <v>-0.9399999999999999</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.90543241</v>
       </c>
       <c r="D55" t="n">
-        <v>82.54000000000001</v>
+        <v>157.59</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>106.24</v>
+        <v>104.85</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.27</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>9.56</v>
+        <v>12.58</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.68495686</v>
       </c>
       <c r="D56" t="n">
-        <v>121.89</v>
+        <v>207.72</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>106.23</v>
+        <v>104.55</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>98.72</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>7.51</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.80409618</v>
       </c>
       <c r="D57" t="n">
-        <v>158.51</v>
+        <v>176.23</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>106.04</v>
+        <v>104.13</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>92.27</v>
+        <v>88.44</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>13.77</v>
+        <v>15.69</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6489,265 +6489,265 @@
         <v>1.59010207</v>
       </c>
       <c r="D58" t="n">
-        <v>89.78</v>
+        <v>87.83</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>105.48</v>
+        <v>102.63</v>
       </c>
       <c r="F58" s="2" t="n">
         <v>89.66</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>15.82</v>
+        <v>12.97</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.97307689</v>
       </c>
       <c r="D59" t="n">
-        <v>280.76</v>
+        <v>143.45</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>105.12</v>
+        <v>102.58</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>111.44</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>8.44</v>
+        <v>-8.859999999999999</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>2.27580753</v>
+        <v>1.11796351</v>
       </c>
       <c r="D60" t="n">
-        <v>62.33</v>
+        <v>123.92</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>104.81</v>
+        <v>101.81</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>106.15</v>
+        <v>105.36</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-1.34</v>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.85908491</v>
       </c>
       <c r="D61" t="n">
-        <v>121.45</v>
+        <v>74.47</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>103.5</v>
+        <v>101.74</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>89.53</v>
+        <v>104.98</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>13.97</v>
+        <v>-3.24</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1.11796351</v>
+        <v>1.17949395</v>
       </c>
       <c r="D62" t="n">
-        <v>124.37</v>
+        <v>116.93</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>102.73</v>
+        <v>101.35</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>105.36</v>
+        <v>98.72</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>-2.63</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.6214908</v>
       </c>
       <c r="D63" t="n">
-        <v>74.40000000000001</v>
+        <v>221.6</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>102.2</v>
+        <v>101.21</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>104.98</v>
+        <v>107.82</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-2.78</v>
+        <v>-6.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.5550481</v>
       </c>
       <c r="D64" t="n">
-        <v>1313.82</v>
+        <v>247.1</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>101.4</v>
+        <v>100.79</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>88.89</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>12.51</v>
+        <v>9.609999999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.1533463</v>
       </c>
       <c r="D65" t="n">
-        <v>140.58</v>
+        <v>118.69</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>101.07</v>
+        <v>100.59</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>111.44</v>
+        <v>89.53</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-10.37</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.10445851</v>
       </c>
       <c r="D66" t="n">
-        <v>115.73</v>
+        <v>1303.8</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>100.31</v>
+        <v>100.08</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>110.45</v>
+        <v>88.89</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-10.14</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.17308322</v>
       </c>
       <c r="D67" t="n">
-        <v>217.38</v>
+        <v>115.02</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>99.81999999999999</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>107.82</v>
+        <v>110.45</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-8</v>
+        <v>-11.3</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6759,22 +6759,22 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D68" t="n">
-        <v>143.67</v>
+        <v>144.76</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>97.28</v>
+        <v>97.48</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-2.57</v>
+        <v>-2.37</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6786,22 +6786,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D69" t="n">
-        <v>112.95</v>
+        <v>113.6</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>97.27</v>
+        <v>97.3</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6813,22 +6813,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D70" t="n">
-        <v>137.21</v>
+        <v>132.83</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>94.75</v>
+        <v>91.22</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>6.37</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6840,22 +6840,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D71" t="n">
-        <v>63.99</v>
+        <v>65.54000000000001</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>87.31999999999999</v>
+        <v>88.95</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-23.21</v>
+        <v>-21.58</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6867,22 +6867,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D72" t="n">
-        <v>111.13</v>
+        <v>112.06</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>51.91</v>
+        <v>52.06</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>4.04</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6894,16 +6894,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D73" t="n">
-        <v>268.94</v>
+        <v>267.36</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>48.16</v>
+        <v>47.62</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-3.95</v>
+        <v>-4.49</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43319.97</v>
+        <v>43030.56</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>42027.63</v>
+        <v>41738.09</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5387.71</v>
+        <v>5098.17</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.147044807958096</v>
+        <v>0.1391424981277252</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1292.34</v>
+        <v>1292.47</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-19 19:01:17</t>
+          <t>2026-08-20 19:09:36</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="23" customWidth="1" min="12" max="12"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>109.74</v>
+        <v>108.84</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>7023.36</v>
+        <v>6965.76</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1672109135061781</v>
+        <v>0.1669847380855065</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>977.59</v>
+        <v>919.99</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1616981790574236</v>
+        <v>0.1521708566485328</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.33</v>
+        <v>14.276</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4155.7</v>
+        <v>4140.04</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09893817108301788</v>
+        <v>0.09924595378874959</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>724.99</v>
+        <v>709.33</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2113236035689405</v>
+        <v>0.2067589507711232</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1497.2</v>
+        <v>1502.6</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2640.96</v>
+        <v>2650.48</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06287550889222199</v>
+        <v>0.06353789229041386</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1445</v>
+        <v>1454.52</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.208234389110004</v>
+        <v>1.216194521555905</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -858,17 +858,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>LCLN_US_EQ</t>
+          <t>CSCO_US_EQ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Lincoln International</t>
+          <t>Cisco Systems</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US5337141015</t>
+          <t>US17275R1023</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -877,55 +877,55 @@
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>115</v>
+        <v>24.80610988</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>22.51</v>
+        <v>89.05910724</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>24.29</v>
+        <v>109.61</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1925.81</v>
+        <v>1646.57</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2052.71</v>
+        <v>1995.23</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04887055686498584</v>
+        <v>0.04783009448650903</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>126.9</v>
+        <v>348.66</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.06589435094843209</v>
+        <v>0.2117492727305854</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-23.53</v>
+        <v>-25.43</v>
       </c>
       <c r="N5" s="4" t="n">
-        <v>0</v>
+        <v>1.15856288</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2024-10-15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CSCO_US_EQ</t>
+          <t>LCLN_US_EQ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cisco Systems</t>
+          <t>Lincoln International</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US17275R1023</t>
+          <t>US5337141015</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -934,55 +934,55 @@
         </is>
       </c>
       <c r="E6" s="4" t="n">
-        <v>24.80610988</v>
+        <v>115</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>89.05910724</v>
+        <v>22.51</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>111.69</v>
+        <v>23.31</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1646.57</v>
+        <v>1925.81</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2035.99</v>
+        <v>1967.09</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04847249006023379</v>
+        <v>0.04715551618784152</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>389.42</v>
+        <v>41.28</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.2365037623666167</v>
+        <v>0.02143513638417082</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-23.12</v>
+        <v>-26.23</v>
       </c>
       <c r="N6" s="4" t="n">
-        <v>1.15856288</v>
+        <v>0</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2024-10-15</t>
+          <t>2026-05-20</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US67066G1040</t>
+          <t>US5738741041</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -991,55 +991,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.9260596</v>
+        <v>9.6</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>150.09436705</v>
+        <v>278.55208333</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>219.53</v>
+        <v>247.02</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1252.68</v>
+        <v>1996.06</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1762.63</v>
+        <v>1740.15</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04196438349641692</v>
+        <v>0.04171526035629912</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>509.95</v>
+        <v>-255.91</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.4070872050324105</v>
+        <v>-0.1282075689107542</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-47.55</v>
+        <v>-33.78</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US0079031078</t>
+          <t>US67066G1040</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,55 +1048,55 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>509.97</v>
+        <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>466.41</v>
+        <v>216.97</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1713.72</v>
+        <v>1739.59</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.0407999428612242</v>
+        <v>0.04170183591254454</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-184.83</v>
+        <v>486.91</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0.09735324326459667</v>
+        <v>0.3886946386946387</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-24.78</v>
+        <v>-49.28</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US5738741041</t>
+          <t>US0079031078</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1105,55 +1105,55 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>278.55208333</v>
+        <v>509.97</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>233.69</v>
+        <v>465.19</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1996.06</v>
+        <v>1898.55</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1648.59</v>
+        <v>1706.81</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03924933933290479</v>
+        <v>0.04091602650848197</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-347.47</v>
+        <v>-191.74</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1740779335290523</v>
+        <v>-0.1009928629743752</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-30.98</v>
+        <v>-27.44</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US75734B1008</t>
+          <t>IE00BMD8KM66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1162,152 +1162,152 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>12.5822526</v>
+        <v>15.9020618</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>191.52532353</v>
+        <v>113.04005874</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>153.07</v>
+        <v>119.14</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1871.84</v>
+        <v>1343.79</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1415.31</v>
+        <v>1390.26</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03369545032497678</v>
+        <v>0.03332761995399731</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-456.53</v>
+        <v>46.47</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2438937088640055</v>
+        <v>0.03458129618467171</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-100.97</v>
+        <v>-24.71</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2024-07-16</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
+          <t>UBS Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>IE00BMD8KM66</t>
+          <t>CH0244767585</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>113.04005874</v>
+        <v>37.05</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.14</v>
+        <v>42.72</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1392.24</v>
+        <v>1369.83</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03314620384258268</v>
+        <v>0.03283786747916514</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>48.45</v>
+        <v>141.49</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.03605474069609091</v>
+        <v>0.115187977270137</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-22.83</v>
+        <v>-40.32</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UBS Group</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CH0244767585</t>
+          <t>US75734B1008</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>35</v>
+        <v>12.5822526</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>37.05</v>
+        <v>191.52532353</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>42.88</v>
+        <v>147.74</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1228.34</v>
+        <v>1871.84</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1382.07</v>
+        <v>1364.08</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03290407828012284</v>
+        <v>0.03270002720847082</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>153.73</v>
+        <v>-507.76</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1251526450331341</v>
+        <v>-0.2712625010684674</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-34.18</v>
+        <v>-103.49</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-03-22</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>438</v>
+        <v>438.3</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1210.61</v>
+        <v>1209.76</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02882198890555436</v>
+        <v>0.02900063406524519</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>296.12</v>
+        <v>295.27</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3238088989491411</v>
+        <v>0.3228794191297882</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-0.43</v>
+        <v>-1.7</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>110.35</v>
+        <v>109.75</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1119.35</v>
+        <v>1113.26</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02664928695569364</v>
+        <v>0.02668731473967965</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>512.16</v>
+        <v>506.07</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8434921523740508</v>
+        <v>0.8334623429239612</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>682</v>
+        <v>677.6</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1091.2</v>
+        <v>1084.16</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02597909673118587</v>
+        <v>0.02598972310886145</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>337.74</v>
+        <v>330.7</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4482520638122793</v>
+        <v>0.4389085021102646</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>322.51</v>
+        <v>320.62</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1038.39</v>
+        <v>1030.84</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02472180558531534</v>
+        <v>0.02471152428565777</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>396.4</v>
+        <v>388.85</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6174551005467375</v>
+        <v>0.6056947927537812</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-37.1</v>
+        <v>-37.96</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>314.87</v>
+        <v>314.95</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>708.01</v>
+        <v>707.1900000000001</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.0168561769397424</v>
+        <v>0.01695291496214187</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>216.96</v>
+        <v>216.14</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4418287343447714</v>
+        <v>0.4401588432949801</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-23.63</v>
+        <v>-24.29</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.46065664</v>
@@ -1624,25 +1624,25 @@
         <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46.69</v>
+        <v>46.32</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>686.21</v>
+        <v>679.8</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.0163371663928767</v>
+        <v>0.0162963158292171</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-181.37</v>
+        <v>-187.78</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.2090527674681297</v>
+        <v>-0.2164411351114595</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-17.5</v>
+        <v>-18.71</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -1681,22 +1681,22 @@
         <v>1019.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1035</v>
+        <v>1035.5</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>672.75</v>
+        <v>673.08</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01601671309192201</v>
+        <v>0.01613522250416217</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>10.07</v>
+        <v>10.4</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.01519587131043641</v>
+        <v>0.01569384921832559</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -1713,17 +1713,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>US6311031081</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1732,55 +1732,55 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>1.8650317</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>369.46288902</v>
+        <v>77.20222067</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>483.91</v>
+        <v>98.08</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>534.38</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>663.21</v>
+        <v>661.85</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01578958645811013</v>
+        <v>0.01586601446244092</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>128.83</v>
+        <v>112.67</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.241083124368427</v>
+        <v>0.2051604209912961</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-28.02</v>
+        <v>-28.22</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0.3650317</v>
+        <v>0</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-09-26</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US6311031081</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1789,38 +1789,38 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>1.8650317</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>77.20222067</v>
+        <v>369.46288902</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>98.04000000000001</v>
+        <v>482.16</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>534.38</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>662.53</v>
+        <v>659.87</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01577339713829964</v>
+        <v>0.01581854946488009</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>113.35</v>
+        <v>125.49</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.2063986306857497</v>
+        <v>0.234832890452487</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-27.47</v>
+        <v>-28.74</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0</v>
+        <v>0.3650317</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
@@ -1852,25 +1852,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>340.21</v>
+        <v>331.59</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>582.52</v>
+        <v>566.96</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01386853320000952</v>
+        <v>0.0135912904126698</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>93.25</v>
+        <v>77.69</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1905900627465408</v>
+        <v>0.1587875814989679</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-34.46</v>
+        <v>-35.1</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,22 +1909,22 @@
         <v>3.8455</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3.8285</v>
+        <v>3.7935</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>535.99</v>
+        <v>531.09</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01276075518415351</v>
+        <v>0.01273140684574715</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-2.38</v>
+        <v>-7.28</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.004420751527759719</v>
+        <v>-0.01352229879079444</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -1966,25 +1966,25 @@
         <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>344.35</v>
+        <v>340.29</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>506.1</v>
+        <v>499.42</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01204913934718949</v>
+        <v>0.01197220660698383</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>98.18000000000001</v>
+        <v>91.5</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.2406844479309669</v>
+        <v>0.2243086879780349</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-11.93</v>
+        <v>-12.5</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>236.65</v>
+        <v>234.74</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>193.07</v>
+        <v>191.24</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.004596576435016546</v>
+        <v>0.004584447542188112</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-3.45</v>
+        <v>-5.28</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.01755546509261144</v>
+        <v>-0.02686749440260533</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-3.27</v>
+        <v>-3.54</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>1.11022215</v>
@@ -2080,25 +2080,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>114.76</v>
+        <v>114.71</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>131.39</v>
+        <v>131.15</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.003128109896912125</v>
+        <v>0.003143956782879999</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>26.11</v>
+        <v>25.87</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.2480053191489362</v>
+        <v>0.2457256838905775</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-0.86</v>
+        <v>-1</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.55804584</v>
@@ -2137,25 +2137,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>277.96</v>
+        <v>280.14</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>129.55</v>
+        <v>130.38</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003084303502130801</v>
+        <v>0.003125498172717454</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>29.7</v>
+        <v>30.53</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.2974461692538808</v>
+        <v>0.3057586379569354</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.68</v>
+        <v>-0.83</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0.63422137</v>
@@ -2194,25 +2194,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>408.2</v>
+        <v>410.97</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>126.02</v>
+        <v>126.69</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.003000261886055758</v>
+        <v>0.003037040677263187</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>16.86</v>
+        <v>17.53</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.154452180285819</v>
+        <v>0.160589959692195</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.09</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>0.42010405</v>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.30858696</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>57.56703616</v>
+        <v>45.93199509</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>67.93000000000001</v>
+        <v>50.73</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>106.81</v>
+        <v>112.71</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>125.01</v>
+        <v>123.17</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002976215984572531</v>
+        <v>0.002952658459377273</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>18.2</v>
+        <v>10.46</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1703960303342384</v>
+        <v>0.09280454263153226</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-0.87</v>
+        <v>-1.19</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.30858696</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2308,25 +2308,25 @@
         <v>225.62857143</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>238.54</v>
+        <v>239.69</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>122.7</v>
+        <v>123.12</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002921219912863367</v>
+        <v>0.002951459848327757</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>3.94</v>
+        <v>4.36</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.03317615358706635</v>
+        <v>0.03671269787807343</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-2.7</v>
+        <v>-2.86</v>
       </c>
       <c r="N30" s="4" t="n">
         <v>0</v>
@@ -2340,17 +2340,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,34 +2359,34 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>3.30858696</v>
+        <v>1.32559468</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>45.93199509</v>
+        <v>121.66614911</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>49.57</v>
+        <v>125.12</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>112.71</v>
+        <v>119.73</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>120.52</v>
+        <v>121.71</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002869318858176797</v>
+        <v>0.002917659016731411</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>7.81</v>
+        <v>1.98</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.06929287552124923</v>
+        <v>0.01653720871961914</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-1.04</v>
+        <v>-1.38</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>3.30858696</v>
+        <v>1.32559468</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>0.7905852</v>
+        <v>2.50421091</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>188.32884805</v>
+        <v>57.56703616</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>206.62</v>
+        <v>66.2</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>110.41</v>
+        <v>106.81</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>120.04</v>
+        <v>121.65</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002857891103016451</v>
+        <v>0.002916220683471992</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>14.84</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.08722036047459471</v>
+        <v>0.1389383016571482</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-1</v>
+        <v>-1.02</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>0.7905852</v>
+        <v>2.50421091</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>228.00445932</v>
+        <v>188.32884805</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>274.55</v>
+        <v>206.46</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>110.41</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.4</v>
+        <v>119.78</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.00284265409613599</v>
+        <v>0.002871392630220101</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>19.55</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1957936905358037</v>
+        <v>0.08486550131328684</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.15</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2536,25 +2536,25 @@
         <v>509.16500577</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>575.6900000000001</v>
+        <v>576.11</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118.61</v>
+        <v>118.53</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002823845915767921</v>
+        <v>0.002841427353982205</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>12.86</v>
+        <v>12.78</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1216075650118203</v>
+        <v>0.1208510638297872</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.85</v>
+        <v>-0.99</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>0.28038062</v>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.59183053</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>121.66614911</v>
+        <v>228.00445932</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>120.14</v>
+        <v>269.13</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>117.03</v>
+        <v>116.88</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002786229555031783</v>
+        <v>0.002801873189348183</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>-2.7</v>
+        <v>17.03</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>-0.02255073916311701</v>
+        <v>0.170555833750626</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-1.21</v>
+        <v>-0.83</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.59183053</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2650,25 +2650,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>58.22</v>
+        <v>58.55</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>115.82</v>
+        <v>116.31</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002757422088898412</v>
+        <v>0.002788209023383703</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>8.18</v>
+        <v>8.67</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.07599405425492382</v>
+        <v>0.08054626532887402</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.9</v>
+        <v>-1.05</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>2.70722512</v>
@@ -2707,25 +2707,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>90.73</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>115.61</v>
+        <v>116.06</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002752422446015761</v>
+        <v>0.002782215968136124</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>14.08</v>
+        <v>14.53</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.1386782231852654</v>
+        <v>0.1431104107160445</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.73</v>
+        <v>-0.87</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>1.73400968</v>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sherwin-Williams</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US8243481061</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.62445608</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>322.35040597</v>
+        <v>235.02053179</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>353.53</v>
+        <v>252.79</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>104.04</v>
+        <v>108.77</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>113.23</v>
+        <v>115.84</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002695759826679047</v>
+        <v>0.002776942079518254</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>9.19</v>
+        <v>7.07</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.08833141099577085</v>
+        <v>0.06499954031442494</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-0.8</v>
+        <v>-1.07</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.62445608</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>0.62445608</v>
+        <v>3.81488812</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>235.02053179</v>
+        <v>38.28159448</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>245.91</v>
+        <v>40.89</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>108.77</v>
+        <v>108.23</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.84</v>
+        <v>114.47</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002686474775611266</v>
+        <v>0.00274410013676152</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>4.07</v>
+        <v>6.24</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.03741840581042567</v>
+        <v>0.05765499399427146</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-0.93</v>
+        <v>-1.06</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>0.62445608</v>
+        <v>3.81488812</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
@@ -2853,17 +2853,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,55 +2872,55 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>3.81488812</v>
+        <v>5.691347</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>38.28159448</v>
+        <v>105.04894536</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>40.23</v>
+        <v>27.23</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>108.23</v>
+        <v>452.96</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112.78</v>
+        <v>113.72</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002685046306216222</v>
+        <v>0.002726120971018783</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4.55</v>
+        <v>-339.24</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.04204009978748961</v>
+        <v>-0.7489403037795832</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-0.91</v>
+        <v>-14.24</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>Sherwin-Williams</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US8243481061</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2929,55 +2929,55 @@
         </is>
       </c>
       <c r="E41" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.43583007</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>105.04894536</v>
+        <v>322.35040597</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>26.56</v>
+        <v>346.94</v>
       </c>
       <c r="H41" s="2" t="n">
-        <v>452.96</v>
+        <v>104.04</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>111.08</v>
+        <v>110.96</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002644573006689998</v>
+        <v>0.00265995764108551</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>-341.88</v>
+        <v>6.92</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>-0.7547686329918757</v>
+        <v>0.06651287966166858</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-13.61</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="N41" s="4" t="n">
-        <v>0</v>
+        <v>0.43583007</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>0.1285649</v>
+        <v>2.76637723</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>54.82621761</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>1160.96</v>
+        <v>53.76</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>98.89</v>
+        <v>112.48</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>109.68</v>
+        <v>109.13</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.00261124205413899</v>
+        <v>0.002616088476673231</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>10.79</v>
+        <v>-3.35</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.1091111335827687</v>
+        <v>-0.02978307254623044</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-1.19</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>0.1285649</v>
+        <v>2.76637723</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.37810738</v>
+        <v>11.40066159</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>341.38450299</v>
+        <v>12.56856884</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>393.41</v>
+        <v>13.01</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>109.31</v>
+        <v>108.84</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002602433159536224</v>
+        <v>0.002609136532586039</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>13.8</v>
+        <v>2.69</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.1444874882211287</v>
+        <v>0.02534149788035798</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.66</v>
+        <v>-1</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.37810738</v>
+        <v>11.40066159</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3106,25 +3106,25 @@
         <v>96.717382</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>109.5</v>
+        <v>109.01</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>108.71</v>
+        <v>108.07</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002588148465585791</v>
+        <v>0.002590677922423495</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>12.03</v>
+        <v>11.39</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1244311129499379</v>
+        <v>0.1178113363673976</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.8</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>1.35094641</v>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Illinois Tool Works</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US4523081093</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>249.91595261</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>285</v>
+        <v>1144.93</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>95.94</v>
+        <v>98.89</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>108.66</v>
+        <v>108.02</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002586958074423255</v>
+        <v>0.00258947931137398</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>12.72</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.1325828642901814</v>
+        <v>0.09232480533926586</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.66</v>
+        <v>-0.82</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3195,17 +3195,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>Illinois Tool Works</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US4523081093</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -3214,34 +3214,34 @@
         </is>
       </c>
       <c r="E46" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.51881442</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>12.56856884</v>
+        <v>249.91595261</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>12.96</v>
+        <v>283.19</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>106.15</v>
+        <v>95.94</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>108.58</v>
+        <v>107.81</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002585053448563198</v>
+        <v>0.002584445144966013</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>2.43</v>
+        <v>11.87</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.02289213377296279</v>
+        <v>0.1237231603085262</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.85</v>
+        <v>-0.8</v>
       </c>
       <c r="N46" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.51881442</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.37810738</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>54.82621761</v>
+        <v>341.38450299</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>53.32</v>
+        <v>387.13</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>112.48</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>108.39</v>
+        <v>107.41</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002580529962145561</v>
+        <v>0.002574856256569886</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>-4.09</v>
+        <v>11.9</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>-0.03636201991465149</v>
+        <v>0.1245942833211182</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-1.03</v>
+        <v>-0.79</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.37810738</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AGNC Investment</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US00123Q1040</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.74206342</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>10.85229847</v>
+        <v>74.99726962</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>11.03</v>
+        <v>83.47</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>106.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>107.82</v>
+        <v>106.7</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.00256695950289265</v>
+        <v>0.002557835979666762</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>0.86</v>
+        <v>10.02</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.008040388930441287</v>
+        <v>0.1036408771203972</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.88</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.74206342</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3366,17 +3366,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>AGNC Investment</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US00123Q1040</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -3385,34 +3385,34 @@
         </is>
       </c>
       <c r="E49" s="4" t="n">
-        <v>0.40867246</v>
+        <v>13.30225117</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>306.99401668</v>
+        <v>10.85229847</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>356.57</v>
+        <v>10.92</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>92.83</v>
+        <v>106.96</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>107.08</v>
+        <v>106.59</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002549341713687118</v>
+        <v>0.002555199035357827</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>14.25</v>
+        <v>-0.37</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.1535064095658731</v>
+        <v>-0.003459237097980554</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-0.64</v>
+        <v>-1.03</v>
       </c>
       <c r="N49" s="4" t="n">
-        <v>0.40867246</v>
+        <v>13.30225117</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
@@ -3448,25 +3448,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>343.1</v>
+        <v>343.3</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>106.54</v>
+        <v>106.45</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002536485489131729</v>
+        <v>0.002551842924419183</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>5.15</v>
+        <v>5.06</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.05079396390176547</v>
+        <v>0.04990630239668606</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.76</v>
+        <v>-0.9</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>0.42255419</v>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>194.45976548</v>
+        <v>62.95787236</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>236.71</v>
+        <v>63.46</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>88.09</v>
+        <v>106.15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>106.48</v>
+        <v>105.98</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002535057019736686</v>
+        <v>0.002540575980553734</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>18.39</v>
+        <v>-0.17</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.2087637643319332</v>
+        <v>-0.001601507300989166</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.62</v>
+        <v>-1.01</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.40867246</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>257.81779936</v>
+        <v>306.99401668</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>284.24</v>
+        <v>352.64</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>105.85</v>
+        <v>105.75</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002520058091088732</v>
+        <v>0.002535062369725961</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>9.17</v>
+        <v>12.92</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.0948489863467108</v>
+        <v>0.1391791446730583</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.77</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.40867246</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.50675322</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>74.99726962</v>
+        <v>257.81779936</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>82.61</v>
+        <v>281.34</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>105.75</v>
+        <v>104.62</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.00251767730876366</v>
+        <v>0.002507973760006904</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>9.07</v>
+        <v>7.94</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.09381464625568886</v>
+        <v>0.08212660322714108</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.68</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.50675322</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.61215748</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>62.95787236</v>
+        <v>194.45976548</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>62.91</v>
+        <v>230.41</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>106.15</v>
+        <v>88.09</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>105.21</v>
+        <v>103.5</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002504821084208271</v>
+        <v>0.002481124872497749</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>-0.9399999999999999</v>
+        <v>15.41</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>-0.008855393311351859</v>
+        <v>0.174934725848564</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.86</v>
+        <v>-0.74</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.61215748</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.68495686</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>137.713206</v>
+        <v>176.50746647</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>157.59</v>
+        <v>205.07</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>92.27</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>104.85</v>
+        <v>103.07</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002496250267838012</v>
+        <v>0.002470816817471913</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>12.58</v>
+        <v>13.61</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1363390050937466</v>
+        <v>0.1521350324167225</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.65</v>
+        <v>-0.75</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.68495686</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.90543241</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>176.50746647</v>
+        <v>137.713206</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>207.72</v>
+        <v>154.72</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>104.55</v>
+        <v>102.8</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002489107920862795</v>
+        <v>0.002464344317804528</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>15.09</v>
+        <v>10.53</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.1686787391012743</v>
+        <v>0.1141215996531917</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.77</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.90543241</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3847,25 +3847,25 @@
         <v>148.63893521</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>176.23</v>
+        <v>172.65</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>104.13</v>
+        <v>101.87</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002479108635097493</v>
+        <v>0.002442050152283534</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>15.69</v>
+        <v>13.43</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.1774084124830393</v>
+        <v>0.1518543645409317</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.74</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>0.80409618</v>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.97307689</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>154.44822659</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>87.83</v>
+        <v>142.63</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>89.66</v>
+        <v>111.44</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>102.63</v>
+        <v>101.85</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002443396900221413</v>
+        <v>0.002441570707863727</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>12.97</v>
+        <v>-9.59</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.1446575953602499</v>
+        <v>-0.08605527638190955</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.62</v>
+        <v>-1.15</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.97307689</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.85908491</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>154.44822659</v>
+        <v>76.24181082</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>143.45</v>
+        <v>74.62</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>111.44</v>
+        <v>104.98</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>102.58</v>
+        <v>101.8</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002442206509058877</v>
+        <v>0.002440372096814211</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-8.859999999999999</v>
+        <v>-3.18</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.07950466618808327</v>
+        <v>-0.03029148409220804</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-1</v>
+        <v>-0.97</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.85908491</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4018,25 +4018,25 @@
         <v>127.23134407</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>123.92</v>
+        <v>123.31</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>101.81</v>
+        <v>101.16</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002423874485155822</v>
+        <v>0.002425029875380409</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>-3.55</v>
+        <v>-4.2</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>-0.03369400151860288</v>
+        <v>-0.03986332574031891</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.83</v>
+        <v>-0.98</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>1.11796351</v>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.17949395</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>76.24181082</v>
+        <v>113.12478542</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>74.47</v>
+        <v>116.78</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>104.98</v>
+        <v>98.72</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>101.74</v>
+        <v>101.08</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002422207937528272</v>
+        <v>0.002423112097701184</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-3.24</v>
+        <v>2.36</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.03086302152791008</v>
+        <v>0.02390599675850891</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.82</v>
+        <v>-0.8</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.17949395</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.59010207</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>113.12478542</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>116.93</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>98.72</v>
+        <v>89.66</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>101.35</v>
+        <v>100.85</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002412922886460491</v>
+        <v>0.002417598486873411</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>2.63</v>
+        <v>11.19</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.02664100486223663</v>
+        <v>0.1248048182020968</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.67</v>
+        <v>-0.75</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.59010207</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.6214908</v>
+        <v>0.10445851</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>234.11448729</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>221.6</v>
+        <v>1298.12</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>107.82</v>
+        <v>88.89</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>101.21</v>
+        <v>99.5</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.00240958979120539</v>
+        <v>0.002385235988536484</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>-6.61</v>
+        <v>10.61</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>-0.0613058801706548</v>
+        <v>0.1193610079874002</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.89</v>
+        <v>-0.74</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.6214908</v>
+        <v>0.10445851</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.6214908</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>221.99877812</v>
+        <v>234.11448729</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>247.1</v>
+        <v>216.66</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>107.82</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>100.79</v>
+        <v>98.81</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002399590505440088</v>
+        <v>0.002368695156053165</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>9.609999999999999</v>
+        <v>-9.01</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.1053959201579294</v>
+        <v>-0.08356520126136154</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.63</v>
+        <v>-1.05</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.6214908</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4303,25 +4303,25 @@
         <v>104.90344487</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>118.69</v>
+        <v>116.62</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>100.59</v>
+        <v>98.7</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002394828940789944</v>
+        <v>0.002366058211744231</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>11.06</v>
+        <v>9.17</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>0.1235340109460516</v>
+        <v>0.1024237685691947</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.75</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>1.1533463</v>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.5550481</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>221.99877812</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>1303.8</v>
+        <v>241.83</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>88.89</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>100.08</v>
+        <v>98.5</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002382686950932076</v>
+        <v>0.002361263767546167</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>11.19</v>
+        <v>7.32</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.1258859264259197</v>
+        <v>0.08028076332529063</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.61</v>
+        <v>-0.76</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.5550481</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1.17308322</v>
+        <v>1.16558147</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>126.99866255</v>
+        <v>107.56862839</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>115.02</v>
+        <v>112.79</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>110.45</v>
+        <v>92.77</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>96.47</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002360545675308907</v>
+        <v>0.002312600158935825</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-11.3</v>
+        <v>3.7</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.1023087369850611</v>
+        <v>0.03988358305486688</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.97</v>
+        <v>-0.77</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>1.17308322</v>
+        <v>1.16558147</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4474,25 +4474,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>144.76</v>
+        <v>143</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>97.48</v>
+        <v>96.16</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002320786610480204</v>
+        <v>0.002305168770428827</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-2.37</v>
+        <v>-3.69</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.02373560340510766</v>
+        <v>-0.03695543314972459</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.72</v>
+        <v>-0.86</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.93456659</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>107.56862839</v>
+        <v>127.79185697</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>113.6</v>
+        <v>130.64</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>92.77</v>
+        <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>97.3</v>
+        <v>89.59</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002316501202295074</v>
+        <v>0.002147671278522448</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>4.53</v>
+        <v>1.21</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.04883044087528296</v>
+        <v>0.01369088028965829</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.64</v>
+        <v>-0.74</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.93456659</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,34 +4582,34 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>127.79185697</v>
+        <v>126.99866255</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>132.83</v>
+        <v>103.18</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>88.38</v>
+        <v>110.45</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>91.22</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002171749636930695</v>
+        <v>0.002129212668359904</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>2.84</v>
+        <v>-21.63</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.03213396696085087</v>
+        <v>-0.1958352195563603</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-0.62</v>
+        <v>-1.13</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4645,25 +4645,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>65.54000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>88.95</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002117705878151561</v>
+        <v>0.002075994337761402</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-21.58</v>
+        <v>-23.93</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.1952411110105853</v>
+        <v>-0.2165023070659549</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-0.97</v>
+        <v>-1.13</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.84694851</v>
@@ -4702,25 +4702,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>112.06</v>
+        <v>112.57</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>52.06</v>
+        <v>52.22</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001239435278432493</v>
+        <v>0.001251829380114323</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4.19</v>
+        <v>4.35</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.08752872362648842</v>
+        <v>0.0908711092542302</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.4</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.63221571</v>
@@ -4759,25 +4759,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>267.36</v>
+        <v>269.71</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>47.62</v>
+        <v>47.97</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001133728543199295</v>
+        <v>0.001149947440905478</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-4.49</v>
+        <v>-4.14</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.08616388409134523</v>
+        <v>-0.07944732297063903</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.43</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.24236298</v>
@@ -4808,9 +4808,9 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4869,34 +4869,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-19 19:01:17</t>
+          <t>2026-08-20 19:09:36</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43319.97</v>
+        <v>43030.56</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>42027.63</v>
+        <v>41738.09</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>36639.92</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5387.71</v>
+        <v>5098.17</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.147044807958096</v>
+        <v>0.1391424981277252</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1316.48</v>
+        <v>1316.61</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4977,22 +4977,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>109.74</v>
+        <v>108.84</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7023.36</v>
+        <v>6965.76</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>977.59</v>
+        <v>919.99</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5004,22 +5004,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.33</v>
+        <v>14.276</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4155.7</v>
+        <v>4140.04</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>724.99</v>
+        <v>709.33</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5031,238 +5031,238 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1497.2</v>
+        <v>1502.6</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2640.96</v>
+        <v>2650.48</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1445</v>
+        <v>1454.52</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>LCLN_US_EQ</t>
+          <t>CSCO_US_EQ</t>
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>115</v>
+        <v>24.80610988</v>
       </c>
       <c r="D5" t="n">
-        <v>24.29</v>
+        <v>109.61</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2052.71</v>
+        <v>1995.23</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>1925.81</v>
+        <v>1646.57</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>126.9</v>
+        <v>348.66</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CSCO_US_EQ</t>
+          <t>LCLN_US_EQ</t>
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>24.80610988</v>
+        <v>115</v>
       </c>
       <c r="D6" t="n">
-        <v>111.69</v>
+        <v>23.31</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2035.99</v>
+        <v>1967.09</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>1646.57</v>
+        <v>1925.81</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>389.42</v>
+        <v>41.28</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>10.9260596</v>
+        <v>9.6</v>
       </c>
       <c r="D7" t="n">
-        <v>219.53</v>
+        <v>247.02</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1762.63</v>
+        <v>1740.15</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1252.68</v>
+        <v>1996.06</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>509.95</v>
+        <v>-255.91</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>466.41</v>
+        <v>216.97</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1713.72</v>
+        <v>1739.59</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>-184.83</v>
+        <v>486.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="D9" t="n">
-        <v>233.69</v>
+        <v>465.19</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1648.59</v>
+        <v>1706.81</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1996.06</v>
+        <v>1898.55</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-347.47</v>
+        <v>-191.74</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>12.5822526</v>
+        <v>15.9020618</v>
       </c>
       <c r="D10" t="n">
-        <v>153.07</v>
+        <v>119.14</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1415.31</v>
+        <v>1390.26</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1871.84</v>
+        <v>1343.79</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-456.53</v>
+        <v>46.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>15.9020618</v>
+        <v>35</v>
       </c>
       <c r="D11" t="n">
-        <v>119.14</v>
+        <v>42.72</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1392.24</v>
+        <v>1369.83</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1343.79</v>
+        <v>1228.34</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>48.45</v>
+        <v>141.49</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>35</v>
+        <v>12.5822526</v>
       </c>
       <c r="D12" t="n">
-        <v>42.88</v>
+        <v>147.74</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1382.07</v>
+        <v>1364.08</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1228.34</v>
+        <v>1871.84</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>153.73</v>
+        <v>-507.76</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5274,22 +5274,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>438</v>
+        <v>438.3</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1210.61</v>
+        <v>1209.76</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>296.12</v>
+        <v>295.27</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5301,22 +5301,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>110.35</v>
+        <v>109.75</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1119.35</v>
+        <v>1113.26</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>512.16</v>
+        <v>506.07</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5328,22 +5328,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>682</v>
+        <v>677.6</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1091.2</v>
+        <v>1084.16</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>337.74</v>
+        <v>330.7</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5355,22 +5355,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>322.51</v>
+        <v>320.62</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1038.39</v>
+        <v>1030.84</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>396.4</v>
+        <v>388.85</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5382,22 +5382,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D17" t="n">
-        <v>314.87</v>
+        <v>314.95</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>708.01</v>
+        <v>707.1900000000001</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>216.96</v>
+        <v>216.14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5409,22 +5409,22 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>46.69</v>
+        <v>46.32</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>686.21</v>
+        <v>679.8</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-181.37</v>
+        <v>-187.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5436,76 +5436,76 @@
         <v>65</v>
       </c>
       <c r="D19" t="n">
-        <v>1035</v>
+        <v>1035.5</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>672.75</v>
+        <v>673.08</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>10.07</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1.8650317</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>483.91</v>
+        <v>98.08</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>663.21</v>
+        <v>661.85</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>534.38</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>128.83</v>
+        <v>112.67</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>1.8650317</v>
       </c>
       <c r="D21" t="n">
-        <v>98.04000000000001</v>
+        <v>482.16</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>662.53</v>
+        <v>659.87</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>534.38</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>113.35</v>
+        <v>125.49</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5517,22 +5517,22 @@
         <v>2.330043</v>
       </c>
       <c r="D22" t="n">
-        <v>340.21</v>
+        <v>331.59</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>582.52</v>
+        <v>566.96</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>93.25</v>
+        <v>77.69</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5544,22 +5544,22 @@
         <v>140</v>
       </c>
       <c r="D23" t="n">
-        <v>3.8285</v>
+        <v>3.7935</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>535.99</v>
+        <v>531.09</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-2.38</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5571,22 +5571,22 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>344.35</v>
+        <v>340.29</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>506.1</v>
+        <v>499.42</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>98.18000000000001</v>
+        <v>91.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5598,22 +5598,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D25" t="n">
-        <v>236.65</v>
+        <v>234.74</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>193.07</v>
+        <v>191.24</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-3.45</v>
+        <v>-5.28</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5625,22 +5625,22 @@
         <v>1.55804584</v>
       </c>
       <c r="D26" t="n">
-        <v>114.76</v>
+        <v>114.71</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>131.39</v>
+        <v>131.15</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>26.11</v>
+        <v>25.87</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5652,22 +5652,22 @@
         <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>277.96</v>
+        <v>280.14</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>129.55</v>
+        <v>130.38</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>29.7</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5679,49 +5679,49 @@
         <v>0.42010405</v>
       </c>
       <c r="D28" t="n">
-        <v>408.2</v>
+        <v>410.97</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>126.02</v>
+        <v>126.69</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>16.86</v>
+        <v>17.53</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2.50421091</v>
+        <v>3.30858696</v>
       </c>
       <c r="D29" t="n">
-        <v>67.93000000000001</v>
+        <v>50.73</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>125.01</v>
+        <v>123.17</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>106.81</v>
+        <v>112.71</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>18.2</v>
+        <v>10.46</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5733,103 +5733,103 @@
         <v>0.7</v>
       </c>
       <c r="D30" t="n">
-        <v>238.54</v>
+        <v>239.69</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>122.7</v>
+        <v>123.12</v>
       </c>
       <c r="F30" s="2" t="n">
         <v>118.76</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>3.94</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>3.30858696</v>
+        <v>1.32559468</v>
       </c>
       <c r="D31" t="n">
-        <v>49.57</v>
+        <v>125.12</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>120.52</v>
+        <v>121.71</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>112.71</v>
+        <v>119.73</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>7.81</v>
+        <v>1.98</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>0.7905852</v>
+        <v>2.50421091</v>
       </c>
       <c r="D32" t="n">
-        <v>206.62</v>
+        <v>66.2</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>120.04</v>
+        <v>121.65</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>110.41</v>
+        <v>106.81</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>14.84</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="D33" t="n">
-        <v>274.55</v>
+        <v>206.46</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.4</v>
+        <v>119.78</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>110.41</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>19.55</v>
+        <v>9.369999999999999</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5841,49 +5841,49 @@
         <v>0.28038062</v>
       </c>
       <c r="D34" t="n">
-        <v>575.6900000000001</v>
+        <v>576.11</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>118.61</v>
+        <v>118.53</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12.86</v>
+        <v>12.78</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.59183053</v>
       </c>
       <c r="D35" t="n">
-        <v>120.14</v>
+        <v>269.13</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>117.03</v>
+        <v>116.88</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>119.73</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>-2.7</v>
+        <v>17.03</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5895,22 +5895,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D36" t="n">
-        <v>58.22</v>
+        <v>58.55</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>115.82</v>
+        <v>116.31</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.18</v>
+        <v>8.67</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5922,184 +5922,184 @@
         <v>1.73400968</v>
       </c>
       <c r="D37" t="n">
-        <v>90.73</v>
+        <v>91.20999999999999</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>115.61</v>
+        <v>116.06</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>14.08</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SHW_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.43583007</v>
+        <v>0.62445608</v>
       </c>
       <c r="D38" t="n">
-        <v>353.53</v>
+        <v>252.79</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>113.23</v>
+        <v>115.84</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>104.04</v>
+        <v>108.77</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>9.19</v>
+        <v>7.07</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>0.62445608</v>
+        <v>3.81488812</v>
       </c>
       <c r="D39" t="n">
-        <v>245.91</v>
+        <v>40.89</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.84</v>
+        <v>114.47</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>108.77</v>
+        <v>108.23</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>4.07</v>
+        <v>6.24</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>3.81488812</v>
+        <v>5.691347</v>
       </c>
       <c r="D40" t="n">
-        <v>40.23</v>
+        <v>27.23</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>112.78</v>
+        <v>113.72</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>108.23</v>
+        <v>452.96</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>4.55</v>
+        <v>-339.24</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>SHW_US_EQ</t>
         </is>
       </c>
       <c r="C41" s="4" t="n">
-        <v>5.691347</v>
+        <v>0.43583007</v>
       </c>
       <c r="D41" t="n">
-        <v>26.56</v>
+        <v>346.94</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>111.08</v>
+        <v>110.96</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>452.96</v>
+        <v>104.04</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>-341.88</v>
+        <v>6.92</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>0.1285649</v>
+        <v>2.76637723</v>
       </c>
       <c r="D42" t="n">
-        <v>1160.96</v>
+        <v>53.76</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>109.68</v>
+        <v>109.13</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>98.89</v>
+        <v>112.48</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>10.79</v>
+        <v>-3.35</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.37810738</v>
+        <v>11.40066159</v>
       </c>
       <c r="D43" t="n">
-        <v>393.41</v>
+        <v>13.01</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>109.31</v>
+        <v>108.84</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>13.8</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6111,157 +6111,157 @@
         <v>1.35094641</v>
       </c>
       <c r="D44" t="n">
-        <v>109.5</v>
+        <v>109.01</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>108.71</v>
+        <v>108.07</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>12.03</v>
+        <v>11.39</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ITW_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.51881442</v>
+        <v>0.1285649</v>
       </c>
       <c r="D45" t="n">
-        <v>285</v>
+        <v>1144.93</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>108.66</v>
+        <v>108.02</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>95.94</v>
+        <v>98.89</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>12.72</v>
+        <v>9.130000000000001</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>ITW_US_EQ</t>
         </is>
       </c>
       <c r="C46" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.51881442</v>
       </c>
       <c r="D46" t="n">
-        <v>12.96</v>
+        <v>283.19</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>108.58</v>
+        <v>107.81</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>106.15</v>
+        <v>95.94</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>2.43</v>
+        <v>11.87</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.37810738</v>
       </c>
       <c r="D47" t="n">
-        <v>53.32</v>
+        <v>387.13</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>108.39</v>
+        <v>107.41</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>112.48</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>-4.09</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>AGNC_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>13.30225117</v>
+        <v>1.74206342</v>
       </c>
       <c r="D48" t="n">
-        <v>11.03</v>
+        <v>83.47</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>107.82</v>
+        <v>106.7</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>106.96</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>0.86</v>
+        <v>10.02</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>AGNC_US_EQ</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>0.40867246</v>
+        <v>13.30225117</v>
       </c>
       <c r="D49" t="n">
-        <v>356.57</v>
+        <v>10.92</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>107.08</v>
+        <v>106.59</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>92.83</v>
+        <v>106.96</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>14.25</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6273,184 +6273,184 @@
         <v>0.42255419</v>
       </c>
       <c r="D50" t="n">
-        <v>343.1</v>
+        <v>343.3</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>106.54</v>
+        <v>106.45</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>5.15</v>
+        <v>5.06</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.61215748</v>
+        <v>2.27580753</v>
       </c>
       <c r="D51" t="n">
-        <v>236.71</v>
+        <v>63.46</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>106.48</v>
+        <v>105.98</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>88.09</v>
+        <v>106.15</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>18.39</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.50675322</v>
+        <v>0.40867246</v>
       </c>
       <c r="D52" t="n">
-        <v>284.24</v>
+        <v>352.64</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>105.85</v>
+        <v>105.75</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>92.83</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>9.17</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.50675322</v>
       </c>
       <c r="D53" t="n">
-        <v>82.61</v>
+        <v>281.34</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>105.75</v>
+        <v>104.62</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>9.07</v>
+        <v>7.94</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.61215748</v>
       </c>
       <c r="D54" t="n">
-        <v>62.91</v>
+        <v>230.41</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>105.21</v>
+        <v>103.5</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>106.15</v>
+        <v>88.09</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>-0.9399999999999999</v>
+        <v>15.41</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.68495686</v>
       </c>
       <c r="D55" t="n">
-        <v>157.59</v>
+        <v>205.07</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>104.85</v>
+        <v>103.07</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>92.27</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>12.58</v>
+        <v>13.61</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.90543241</v>
       </c>
       <c r="D56" t="n">
-        <v>207.72</v>
+        <v>154.72</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>104.55</v>
+        <v>102.8</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>92.27</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>15.09</v>
+        <v>10.53</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6462,76 +6462,76 @@
         <v>0.80409618</v>
       </c>
       <c r="D57" t="n">
-        <v>176.23</v>
+        <v>172.65</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>104.13</v>
+        <v>101.87</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>15.69</v>
+        <v>13.43</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.97307689</v>
       </c>
       <c r="D58" t="n">
-        <v>87.83</v>
+        <v>142.63</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>102.63</v>
+        <v>101.85</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>89.66</v>
+        <v>111.44</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>12.97</v>
+        <v>-9.59</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.85908491</v>
       </c>
       <c r="D59" t="n">
-        <v>143.45</v>
+        <v>74.62</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>102.58</v>
+        <v>101.8</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>111.44</v>
+        <v>104.98</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-8.859999999999999</v>
+        <v>-3.18</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6543,130 +6543,130 @@
         <v>1.11796351</v>
       </c>
       <c r="D60" t="n">
-        <v>123.92</v>
+        <v>123.31</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>101.81</v>
+        <v>101.16</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-3.55</v>
+        <v>-4.2</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>1.17949395</v>
       </c>
       <c r="D61" t="n">
-        <v>74.47</v>
+        <v>116.78</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>101.74</v>
+        <v>101.08</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>104.98</v>
+        <v>98.72</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-3.24</v>
+        <v>2.36</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.59010207</v>
       </c>
       <c r="D62" t="n">
-        <v>116.93</v>
+        <v>86.43000000000001</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>101.35</v>
+        <v>100.85</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>98.72</v>
+        <v>89.66</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>2.63</v>
+        <v>11.19</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.6214908</v>
+        <v>0.10445851</v>
       </c>
       <c r="D63" t="n">
-        <v>221.6</v>
+        <v>1298.12</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>101.21</v>
+        <v>99.5</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>107.82</v>
+        <v>88.89</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>-6.61</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.6214908</v>
       </c>
       <c r="D64" t="n">
-        <v>247.1</v>
+        <v>216.66</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>100.79</v>
+        <v>98.81</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>107.82</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>9.609999999999999</v>
+        <v>-9.01</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6678,76 +6678,76 @@
         <v>1.1533463</v>
       </c>
       <c r="D65" t="n">
-        <v>118.69</v>
+        <v>116.62</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>100.59</v>
+        <v>98.7</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>11.06</v>
+        <v>9.17</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.10445851</v>
+        <v>0.5550481</v>
       </c>
       <c r="D66" t="n">
-        <v>1303.8</v>
+        <v>241.83</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>100.08</v>
+        <v>98.5</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>88.89</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>11.19</v>
+        <v>7.32</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1.17308322</v>
+        <v>1.16558147</v>
       </c>
       <c r="D67" t="n">
-        <v>115.02</v>
+        <v>112.79</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>99.15000000000001</v>
+        <v>96.47</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>110.45</v>
+        <v>92.77</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-11.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6759,76 +6759,76 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D68" t="n">
-        <v>144.76</v>
+        <v>143</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>97.48</v>
+        <v>96.16</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-2.37</v>
+        <v>-3.69</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.93456659</v>
       </c>
       <c r="D69" t="n">
-        <v>113.6</v>
+        <v>130.64</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>97.3</v>
+        <v>89.59</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>92.77</v>
+        <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>4.53</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="D70" t="n">
-        <v>132.83</v>
+        <v>103.18</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>91.22</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>88.38</v>
+        <v>110.45</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>2.84</v>
+        <v>-21.63</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6840,22 +6840,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D71" t="n">
-        <v>65.54000000000001</v>
+        <v>63.9</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>88.95</v>
+        <v>86.59999999999999</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-21.58</v>
+        <v>-23.93</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6867,22 +6867,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D72" t="n">
-        <v>112.06</v>
+        <v>112.57</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>52.06</v>
+        <v>52.22</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>4.19</v>
+        <v>4.35</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6894,16 +6894,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D73" t="n">
-        <v>267.36</v>
+        <v>269.71</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>47.62</v>
+        <v>47.97</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-4.49</v>
+        <v>-4.14</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43030.56</v>
+        <v>43180.3</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>41738.09</v>
+        <v>41887.69</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5098.17</v>
+        <v>5247.77</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1391424981277252</v>
+        <v>0.1432254764748395</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1292.47</v>
+        <v>1292.61</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-20 19:09:36</t>
+          <t>2026-08-21 19:05:59</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>108.84</v>
+        <v>108.88</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6965.76</v>
+        <v>6968.32</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1669847380855065</v>
+        <v>0.1664476687289337</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>919.99</v>
+        <v>922.55</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1521708566485328</v>
+        <v>0.152594293200039</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.276</v>
+        <v>14.364</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4140.04</v>
+        <v>4165.56</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09924595378874959</v>
+        <v>0.0994999872208075</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>709.33</v>
+        <v>734.85</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2067589507711232</v>
+        <v>0.2141976442194181</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1502.6</v>
+        <v>1518.4</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2650.48</v>
+        <v>2678.35</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06353789229041386</v>
+        <v>0.06397598180625168</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1454.52</v>
+        <v>1482.39</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.216194521555905</v>
+        <v>1.239497976520954</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>109.61</v>
+        <v>111.59</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>1995.23</v>
+        <v>2028.01</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04783009448650903</v>
+        <v>0.04844173870588103</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>348.66</v>
+        <v>381.44</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2117492727305854</v>
+        <v>0.2316573240129481</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-25.43</v>
+        <v>-28.03</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>1.15856288</v>
@@ -940,25 +940,25 @@
         <v>22.51</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>23.31</v>
+        <v>23.73</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1967.09</v>
+        <v>1999.32</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04715551618784152</v>
+        <v>0.04775643957842519</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>41.28</v>
+        <v>73.51000000000001</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.02143513638417082</v>
+        <v>0.03817095144380806</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-26.23</v>
+        <v>-29.28</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -972,17 +972,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Marvell Technology</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US5738741041</t>
+          <t>US0079031078</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -991,38 +991,38 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>278.55208333</v>
+        <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>247.02</v>
+        <v>472.4</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1996.06</v>
+        <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1740.15</v>
+        <v>1730.48</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04171526035629912</v>
+        <v>0.04133483562494909</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-255.91</v>
+        <v>-168.07</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.1282075689107542</v>
+        <v>-0.08852545363566933</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-33.78</v>
+        <v>-30.44</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>216.97</v>
+        <v>215.31</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1739.59</v>
+        <v>1723.51</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04170183591254454</v>
+        <v>0.04116834782716704</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>486.91</v>
+        <v>470.83</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.3886946386946387</v>
+        <v>0.3758581601047354</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-49.28</v>
+        <v>-51.21</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1086,17 +1086,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Marvell Technology</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US0079031078</t>
+          <t>US5738741041</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1105,55 +1105,55 @@
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>509.97</v>
+        <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>465.19</v>
+        <v>237.15</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1898.55</v>
+        <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1706.81</v>
+        <v>1667.94</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.04091602650848197</v>
+        <v>0.03984098384972816</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-191.74</v>
+        <v>-328.12</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1009928629743752</v>
+        <v>-0.1643838361572298</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-27.44</v>
+        <v>-36.93</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
+          <t>Reddit</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IE00BMD8KM66</t>
+          <t>US75734B1008</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1162,152 +1162,152 @@
         </is>
       </c>
       <c r="E10" s="4" t="n">
-        <v>15.9020618</v>
+        <v>12.5822526</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>113.04005874</v>
+        <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>119.14</v>
+        <v>152.79</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1343.79</v>
+        <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1390.26</v>
+        <v>1408.44</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03332761995399731</v>
+        <v>0.03364247832254826</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>46.47</v>
+        <v>-463.4</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.03458129618467171</v>
+        <v>-0.2475638943499444</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-24.71</v>
+        <v>-106.33</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-03-22</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UBS Group</t>
+          <t>JPMorgan Betabuilders US Treasury Bond 0-3 Months (Acc)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CH0244767585</t>
+          <t>IE00BMD8KM66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>CHF</t>
+          <t>USD</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>37.05</v>
+        <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>42.72</v>
+        <v>119.16</v>
       </c>
       <c r="H11" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1369.83</v>
+        <v>1388.26</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03283786747916514</v>
+        <v>0.03316045195823807</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>141.49</v>
+        <v>44.47</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.115187977270137</v>
+        <v>0.03309296839535939</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-40.32</v>
+        <v>-26.83</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-22</t>
+          <t>2024-07-16</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Reddit</t>
+          <t>UBS Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>US75734B1008</t>
+          <t>CH0244767585</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>USD</t>
+          <t>CHF</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>12.5822526</v>
+        <v>35</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>191.52532353</v>
+        <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>147.74</v>
+        <v>42.5</v>
       </c>
       <c r="H12" s="2" t="n">
-        <v>1871.84</v>
+        <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1364.08</v>
+        <v>1360.47</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03270002720847082</v>
+        <v>0.03249665053781291</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>-507.76</v>
+        <v>132.13</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>-0.2712625010684674</v>
+        <v>0.1075679372160802</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-103.49</v>
+        <v>-42.33</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2024-03-22</t>
+          <t>2026-05-22</t>
         </is>
       </c>
     </row>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>438.3</v>
+        <v>440.8</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1209.76</v>
+        <v>1215.38</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02900063406524519</v>
+        <v>0.02903098130105556</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>295.27</v>
+        <v>300.89</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3228794191297882</v>
+        <v>0.3290249209942153</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-1.7</v>
+        <v>-2.66</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>109.75</v>
+        <v>111.25</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1113.26</v>
+        <v>1128.48</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02668731473967965</v>
+        <v>0.02695525825553751</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>506.07</v>
+        <v>521.29</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8334623429239612</v>
+        <v>0.8585286318944645</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>677.6</v>
+        <v>683.8</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1084.16</v>
+        <v>1094.08</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02598972310886145</v>
+        <v>0.02613356812014256</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>330.7</v>
+        <v>340.62</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4389085021102646</v>
+        <v>0.4520744299631035</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>320.62</v>
+        <v>328.07</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1030.84</v>
+        <v>1053.1</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02471152428565777</v>
+        <v>0.02515470586001219</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>388.85</v>
+        <v>411.11</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6056947927537812</v>
+        <v>0.6403682300347358</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-37.96</v>
+        <v>-38.93</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>314.95</v>
+        <v>308.52</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>707.1900000000001</v>
+        <v>691.64</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.01695291496214187</v>
+        <v>0.01652074898966749</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>216.14</v>
+        <v>200.59</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4401588432949801</v>
+        <v>0.4084920069239385</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-24.29</v>
+        <v>-25.04</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.46065664</v>
@@ -1624,25 +1624,25 @@
         <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46.32</v>
+        <v>46.83</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>679.8</v>
+        <v>686.1799999999999</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.0162963158292171</v>
+        <v>0.01639032956701468</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-187.78</v>
+        <v>-181.4</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.2164411351114595</v>
+        <v>-0.2090873464118583</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-18.71</v>
+        <v>-20.07</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -1681,22 +1681,22 @@
         <v>1019.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1035.5</v>
+        <v>1036</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>673.08</v>
+        <v>673.4</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01613522250416217</v>
+        <v>0.016085062127179</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>10.4</v>
+        <v>10.72</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.01569384921832559</v>
+        <v>0.01617673688658176</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -1738,25 +1738,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>98.08</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>661.85</v>
+        <v>659.78</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01586601446244092</v>
+        <v>0.01575973016078135</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>112.67</v>
+        <v>110.6</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.2051604209912961</v>
+        <v>0.2013911650096508</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-28.22</v>
+        <v>-29.05</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>482.16</v>
+        <v>482.77</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>659.87</v>
+        <v>659.65</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01581854946488009</v>
+        <v>0.01575662493643247</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>125.49</v>
+        <v>125.27</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.234832890452487</v>
+        <v>0.2344211983981436</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-28.74</v>
+        <v>-29.55</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0.3650317</v>
@@ -1852,25 +1852,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>331.59</v>
+        <v>334.93</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>566.96</v>
+        <v>571.75</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.0135912904126698</v>
+        <v>0.01365701554976922</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>77.69</v>
+        <v>82.48</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1587875814989679</v>
+        <v>0.1685776769472888</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-35.1</v>
+        <v>-35.83</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,22 +1909,22 @@
         <v>3.8455</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3.7935</v>
+        <v>3.798</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>531.09</v>
+        <v>531.72</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01273140684574715</v>
+        <v>0.01270084531372679</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-7.28</v>
+        <v>-6.65</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.01352229879079444</v>
+        <v>-0.01235209985697569</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -1966,25 +1966,25 @@
         <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>340.29</v>
+        <v>345.26</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>499.42</v>
+        <v>505.9</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01197220660698383</v>
+        <v>0.01208409998535767</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>91.5</v>
+        <v>97.98</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.2243086879780349</v>
+        <v>0.2401941557168072</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-12.5</v>
+        <v>-13.13</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>234.74</v>
+        <v>235.8</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>191.24</v>
+        <v>191.8</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.004584447542188112</v>
+        <v>0.004581400231649737</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-5.28</v>
+        <v>-4.72</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.02686749440260533</v>
+        <v>-0.02401791166293507</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-3.54</v>
+        <v>-3.85</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>1.11022215</v>
@@ -2080,25 +2080,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>114.71</v>
+        <v>116.33</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>131.15</v>
+        <v>132.79</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.003143956782879999</v>
+        <v>0.003171867240671368</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>25.87</v>
+        <v>27.51</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.2457256838905775</v>
+        <v>0.2613031914893617</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1</v>
+        <v>-1.17</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.55804584</v>
@@ -2137,25 +2137,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>280.14</v>
+        <v>280.25</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>130.38</v>
+        <v>130.22</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003125498172717454</v>
+        <v>0.003110479343928199</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>30.53</v>
+        <v>30.37</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.3057586379569354</v>
+        <v>0.3041562343515273</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.83</v>
+        <v>-0.99</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0.63422137</v>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.32559468</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>350.55601106</v>
+        <v>121.66614911</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>410.97</v>
+        <v>130.1</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>109.16</v>
+        <v>119.73</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>126.69</v>
+        <v>126.35</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.003037040677263187</v>
+        <v>0.003018039203696268</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>17.53</v>
+        <v>6.62</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.160589959692195</v>
+        <v>0.05529107157771652</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-1.09</v>
+        <v>-1.57</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.32559468</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.42010405</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>45.93199509</v>
+        <v>350.55601106</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>50.73</v>
+        <v>410.18</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>112.71</v>
+        <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>123.17</v>
+        <v>126.25</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.002952658459377273</v>
+        <v>0.003015650569581748</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>10.46</v>
+        <v>17.09</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.09280454263153226</v>
+        <v>0.1565591791865152</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-1.19</v>
+        <v>-1.26</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.42010405</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,55 +2302,55 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7</v>
+        <v>3.30858696</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>225.62857143</v>
+        <v>45.93199509</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>239.69</v>
+        <v>51.23</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>118.76</v>
+        <v>112.71</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>123.12</v>
+        <v>124.18</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002951459848327757</v>
+        <v>0.00296620584341118</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>4.36</v>
+        <v>11.47</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.03671269787807343</v>
+        <v>0.1017655931150741</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-2.86</v>
+        <v>-1.37</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0</v>
+        <v>3.30858696</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,38 +2359,38 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.7</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>121.66614911</v>
+        <v>225.62857143</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>125.12</v>
+        <v>241.67</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>119.73</v>
+        <v>118.76</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>121.71</v>
+        <v>123.94</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002917659016731411</v>
+        <v>0.002960473121536331</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>1.98</v>
+        <v>5.18</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.01653720871961914</v>
+        <v>0.04361737958908723</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-1.38</v>
+        <v>-3.05</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
@@ -2422,25 +2422,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>66.2</v>
+        <v>67.27</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>121.65</v>
+        <v>123.42</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002916220683471992</v>
+        <v>0.002948052224140826</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>14.84</v>
+        <v>16.61</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1389383016571482</v>
+        <v>0.1555097837281153</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-1.02</v>
+        <v>-1.19</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>2.50421091</v>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,34 +2473,34 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.28038062</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>188.32884805</v>
+        <v>509.16500577</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>206.46</v>
+        <v>580.1</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>110.41</v>
+        <v>105.75</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.78</v>
+        <v>119.16</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002871392630220101</v>
+        <v>0.002846296410862266</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>13.41</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.08486550131328684</v>
+        <v>0.1268085106382979</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-1.15</v>
+        <v>-1.16</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.28038062</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
@@ -2511,17 +2511,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.7905852</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>509.16500577</v>
+        <v>188.32884805</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>576.11</v>
+        <v>205.6</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>105.75</v>
+        <v>110.41</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118.53</v>
+        <v>119.09</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002841427353982205</v>
+        <v>0.002844624366982102</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>12.78</v>
+        <v>8.68</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.1208510638297872</v>
+        <v>0.07861606738520062</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-0.99</v>
+        <v>-1.32</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.7905852</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.62445608</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>228.00445932</v>
+        <v>235.02053179</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>269.13</v>
+        <v>258.79</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>108.77</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>116.88</v>
+        <v>118.4</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002801873189348183</v>
+        <v>0.002828142791591912</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>17.03</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.170555833750626</v>
+        <v>0.08853544175783765</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-0.83</v>
+        <v>-1.24</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.62445608</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Main Street Capital</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US56035L1044</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.59183053</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>53.65641702</v>
+        <v>228.00445932</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>58.55</v>
+        <v>271.57</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>107.64</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>116.31</v>
+        <v>117.75</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002788209023383703</v>
+        <v>0.002812616669847531</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>8.67</v>
+        <v>17.9</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.08054626532887402</v>
+        <v>0.1792689033550325</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-1.05</v>
+        <v>-0.99</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.59183053</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2682,17 +2682,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Coca-Cola</t>
+          <t>Main Street Capital</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US1912161007</t>
+          <t>US56035L1044</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2701,34 +2701,34 @@
         </is>
       </c>
       <c r="E37" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>79.10567143</v>
+        <v>53.65641702</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>91.20999999999999</v>
+        <v>58.37</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>116.06</v>
+        <v>115.77</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002782215968136124</v>
+        <v>0.002765321714380031</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>14.53</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.1431104107160445</v>
+        <v>0.07552954292084728</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-0.87</v>
+        <v>-1.22</v>
       </c>
       <c r="N37" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -2739,17 +2739,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US1912161007</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2758,34 +2758,34 @@
         </is>
       </c>
       <c r="E38" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.73400968</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>235.02053179</v>
+        <v>79.10567143</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>252.79</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="H38" s="2" t="n">
-        <v>108.77</v>
+        <v>101.53</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>115.84</v>
+        <v>115.38</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002776942079518254</v>
+        <v>0.002756006041333402</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>7.07</v>
+        <v>13.85</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.06499954031442494</v>
+        <v>0.1364128828917561</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-1.07</v>
+        <v>-1.03</v>
       </c>
       <c r="N38" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.73400968</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -2821,25 +2821,25 @@
         <v>38.28159448</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>40.89</v>
+        <v>40.5</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>114.47</v>
+        <v>113.19</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.00274410013676152</v>
+        <v>0.00270369495422541</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>6.24</v>
+        <v>4.96</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.05765499399427146</v>
+        <v>0.0458283285595491</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-1.06</v>
+        <v>-1.24</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>3.81488812</v>
@@ -2878,25 +2878,25 @@
         <v>105.04894536</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>27.23</v>
+        <v>26.99</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>113.72</v>
+        <v>112.54</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002726120971018783</v>
+        <v>0.002688168832481029</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-339.24</v>
+        <v>-340.42</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.7489403037795832</v>
+        <v>-0.7515453903214413</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-14.24</v>
+        <v>-14.94</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>0</v>
@@ -2935,25 +2935,25 @@
         <v>322.35040597</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>346.94</v>
+        <v>347.56</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>110.96</v>
+        <v>110.98</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.00265995764108551</v>
+        <v>0.002650906140294514</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>6.92</v>
+        <v>6.94</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.06651287966166858</v>
+        <v>0.06670511341791618</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.11</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0.43583007</v>
@@ -2992,25 +2992,25 @@
         <v>54.82621761</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>53.76</v>
+        <v>53.79</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>109.13</v>
+        <v>109.02</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002616088476673231</v>
+        <v>0.002604088911649918</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>-3.35</v>
+        <v>-3.46</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.02978307254623044</v>
+        <v>-0.03076102418207681</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-1.19</v>
+        <v>-1.36</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>2.76637723</v>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.1285649</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>12.56856884</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>13.01</v>
+        <v>1155.21</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>106.15</v>
+        <v>98.89</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>108.84</v>
+        <v>108.81</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002609136532586039</v>
+        <v>0.002599072780009426</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>2.69</v>
+        <v>9.92</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.02534149788035798</v>
+        <v>0.1003134796238244</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-1</v>
+        <v>-0.98</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.1285649</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3106,25 +3106,25 @@
         <v>96.717382</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>109.01</v>
+        <v>109.52</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>108.07</v>
+        <v>108.4</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002590677922423495</v>
+        <v>0.002589279380139893</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>11.39</v>
+        <v>11.72</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1178113363673976</v>
+        <v>0.12122465866777</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.8</v>
+        <v>-0.95</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>1.35094641</v>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>0.1285649</v>
+        <v>11.40066159</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>12.56856884</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>1144.93</v>
+        <v>12.96</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>98.89</v>
+        <v>106.15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>108.02</v>
+        <v>108.25</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.00258947931137398</v>
+        <v>0.002585696428968113</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>2.1</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.09232480533926586</v>
+        <v>0.01978332548280735</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-0.82</v>
+        <v>-1.17</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>0.1285649</v>
+        <v>11.40066159</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3220,25 +3220,25 @@
         <v>249.91595261</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>283.19</v>
+        <v>282.88</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>107.81</v>
+        <v>107.52</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002584445144966013</v>
+        <v>0.002568259399932115</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>11.87</v>
+        <v>11.58</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1237231603085262</v>
+        <v>0.1207004377736085</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.8</v>
+        <v>-0.95</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>0.51881442</v>
@@ -3252,17 +3252,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Sysco</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>US8718291078</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3271,34 +3271,34 @@
         </is>
       </c>
       <c r="E47" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.74206342</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>341.38450299</v>
+        <v>74.99726962</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>387.13</v>
+        <v>83.61</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>107.41</v>
+        <v>106.71</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002574856256569886</v>
+        <v>0.002548911463604501</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>11.9</v>
+        <v>10.03</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1245942833211182</v>
+        <v>0.1037443111294994</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.79</v>
+        <v>-0.96</v>
       </c>
       <c r="N47" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.74206342</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Sysco</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US8718291078</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.37810738</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>74.99726962</v>
+        <v>341.38450299</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>83.47</v>
+        <v>383.62</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>106.7</v>
+        <v>106.27</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002557835979666762</v>
+        <v>0.002538401473500612</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>10.02</v>
+        <v>10.76</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1036408771203972</v>
+        <v>0.1126583603811119</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.37810738</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3391,25 +3391,25 @@
         <v>10.85229847</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>106.59</v>
+        <v>106.13</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002555199035357827</v>
+        <v>0.002535057385740284</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.83</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>-0.003459237097980554</v>
+        <v>-0.007759910246821241</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-1.03</v>
+        <v>-1.2</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>13.30225117</v>
@@ -3448,25 +3448,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>343.3</v>
+        <v>341.28</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>106.45</v>
+        <v>105.65</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002551842924419183</v>
+        <v>0.002523591941990587</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>5.06</v>
+        <v>4.26</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.04990630239668606</v>
+        <v>0.04201597790709143</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-0.9</v>
+        <v>-1.07</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>0.42255419</v>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.40867246</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>62.95787236</v>
+        <v>306.99401668</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>63.46</v>
+        <v>352.11</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>106.15</v>
+        <v>92.83</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>105.98</v>
+        <v>105.42</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002540575980553734</v>
+        <v>0.002518098083527191</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>-0.17</v>
+        <v>12.59</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>-0.001601507300989166</v>
+        <v>0.1356242593989012</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-1.01</v>
+        <v>-0.92</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.40867246</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.27580753</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>306.99401668</v>
+        <v>62.95787236</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>352.64</v>
+        <v>62.66</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>92.83</v>
+        <v>106.15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>105.75</v>
+        <v>104.47</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002535062369725961</v>
+        <v>0.002495406059439249</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>12.92</v>
+        <v>-1.68</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.1391791446730583</v>
+        <v>-0.01582666038624588</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-0.77</v>
+        <v>-1.18</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.27580753</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3619,25 +3619,25 @@
         <v>257.81779936</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>281.34</v>
+        <v>280.21</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>104.62</v>
+        <v>104.03</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002507973760006904</v>
+        <v>0.00248489606933536</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>7.94</v>
+        <v>7.35</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.08212660322714108</v>
+        <v>0.0760239966901117</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.96</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>0.50675322</v>
@@ -3651,17 +3651,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Emerson Electric</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>US2910111044</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3670,34 +3670,34 @@
         </is>
       </c>
       <c r="E54" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.90543241</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>194.45976548</v>
+        <v>137.713206</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>230.41</v>
+        <v>156.75</v>
       </c>
       <c r="H54" s="2" t="n">
-        <v>88.09</v>
+        <v>92.27</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>103.5</v>
+        <v>103.98</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002481124872497749</v>
+        <v>0.0024837017522781</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>15.41</v>
+        <v>11.71</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.174934725848564</v>
+        <v>0.1269101549799502</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.92</v>
       </c>
       <c r="N54" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.90543241</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
@@ -3733,25 +3733,25 @@
         <v>176.50746647</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>205.07</v>
+        <v>205.52</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>103.07</v>
+        <v>103.13</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002470816817471913</v>
+        <v>0.002463398362304678</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>13.61</v>
+        <v>13.67</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1521350324167225</v>
+        <v>0.1528057232282584</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.75</v>
+        <v>-0.89</v>
       </c>
       <c r="N55" s="4" t="n">
         <v>0.68495686</v>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Emerson Electric</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US2910111044</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.61215748</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>137.713206</v>
+        <v>194.45976548</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>154.72</v>
+        <v>229.28</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>92.27</v>
+        <v>88.09</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>102.8</v>
+        <v>102.83</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002464344317804528</v>
+        <v>0.002456232459961118</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>10.53</v>
+        <v>14.74</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.1141215996531917</v>
+        <v>0.1673288682029742</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.77</v>
+        <v>-0.88</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.61215748</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3847,25 +3847,25 @@
         <v>148.63893521</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>172.65</v>
+        <v>174.51</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>101.87</v>
+        <v>102.81</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002442050152283534</v>
+        <v>0.002455754733138214</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>13.43</v>
+        <v>14.37</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.1518543645409317</v>
+        <v>0.162483039348711</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.87</v>
       </c>
       <c r="N57" s="4" t="n">
         <v>0.80409618</v>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.59010207</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>154.44822659</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>142.63</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>111.44</v>
+        <v>89.66</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>101.85</v>
+        <v>102.14</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002441570707863727</v>
+        <v>0.002439750884570928</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-9.59</v>
+        <v>12.48</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.08605527638190955</v>
+        <v>0.1391925050189605</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-1.15</v>
+        <v>-0.9</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.59010207</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.97307689</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>76.24181082</v>
+        <v>154.44822659</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>74.62</v>
+        <v>143.05</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>104.98</v>
+        <v>111.44</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>101.8</v>
+        <v>101.98</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002440372096814211</v>
+        <v>0.002435929069987696</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-3.18</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.03029148409220804</v>
+        <v>-0.08488872936109118</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.97</v>
+        <v>-1.33</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.97307689</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>127.23134407</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>123.31</v>
+        <v>1314.99</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>105.36</v>
+        <v>88.89</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>101.16</v>
+        <v>100.64</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002425029875380409</v>
+        <v>0.002403921372853125</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>-4.2</v>
+        <v>11.75</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>-0.03986332574031891</v>
+        <v>0.132185847676904</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.98</v>
+        <v>-0.87</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.85908491</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>113.12478542</v>
+        <v>76.24181082</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>116.78</v>
+        <v>73.84</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>98.72</v>
+        <v>104.98</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>101.08</v>
+        <v>100.57</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002423112097701184</v>
+        <v>0.002402249328972961</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>2.36</v>
+        <v>-4.41</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.02390599675850891</v>
+        <v>-0.04200800152409983</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.8</v>
+        <v>-1.14</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.85908491</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.59010207</v>
+        <v>1.17949395</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>113.12478542</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>86.43000000000001</v>
+        <v>116.34</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>89.66</v>
+        <v>98.72</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>100.85</v>
+        <v>100.53</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002417598486873411</v>
+        <v>0.002401293875327153</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>11.19</v>
+        <v>1.81</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.1248048182020968</v>
+        <v>0.01833468395461912</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.75</v>
+        <v>-0.97</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.59010207</v>
+        <v>1.17949395</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.1533463</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>104.90344487</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>1298.12</v>
+        <v>117.39</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>88.89</v>
+        <v>89.53</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>99.5</v>
+        <v>99.19</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002385235988536484</v>
+        <v>0.002369286178192583</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>10.61</v>
+        <v>9.66</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.1193610079874002</v>
+        <v>0.107896794370602</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.89</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.1533463</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4221,17 +4221,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Nucor</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>US6703461052</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4240,34 +4240,34 @@
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>0.6214908</v>
+        <v>0.5550481</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>234.11448729</v>
+        <v>221.99877812</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>216.66</v>
+        <v>242.78</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>107.82</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98.81</v>
+        <v>98.73</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002368695156053165</v>
+        <v>0.00235829846126579</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>-9.01</v>
+        <v>7.55</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>-0.08356520126136154</v>
+        <v>0.08280324632594867</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-1.05</v>
+        <v>-0.9</v>
       </c>
       <c r="N64" s="4" t="n">
-        <v>0.6214908</v>
+        <v>0.5550481</v>
       </c>
       <c r="O64" t="inlineStr">
         <is>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.11796351</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>104.90344487</v>
+        <v>127.23134407</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>116.62</v>
+        <v>120.19</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>89.53</v>
+        <v>105.36</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>98.7</v>
+        <v>98.44</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002366058211744231</v>
+        <v>0.002351371422333681</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>9.17</v>
+        <v>-6.92</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>0.1024237685691947</v>
+        <v>-0.0656795747911921</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-0.75</v>
+        <v>-1.15</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.11796351</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Nucor</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US6703461052</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.6214908</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>221.99877812</v>
+        <v>234.11448729</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>241.83</v>
+        <v>216.11</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>107.82</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002361263767546167</v>
+        <v>0.002350415968687873</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>7.32</v>
+        <v>-9.42</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.08028076332529063</v>
+        <v>-0.08736783528102393</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-0.76</v>
+        <v>-1.22</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.6214908</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4392,17 +4392,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PPG Industries</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US6935061076</t>
+          <t>US7427181091</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4411,34 +4411,34 @@
         </is>
       </c>
       <c r="E67" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>107.56862839</v>
+        <v>147.21071381</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>112.79</v>
+        <v>144.93</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>92.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>96.47</v>
+        <v>97.3</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002312600158935825</v>
+        <v>0.002324140993428151</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>3.7</v>
+        <v>-2.55</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.03988358305486688</v>
+        <v>-0.02553830746119179</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-0.77</v>
+        <v>-1.02</v>
       </c>
       <c r="N67" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
@@ -4449,17 +4449,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>PPG Industries</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US7427181091</t>
+          <t>US6935061076</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -4468,34 +4468,34 @@
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.16558147</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>147.21071381</v>
+        <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>143</v>
+        <v>113.54</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>96.16</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002305168770428827</v>
+        <v>0.002316019637438782</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>-3.69</v>
+        <v>4.19</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>-0.03695543314972459</v>
+        <v>0.04516546297294385</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.86</v>
+        <v>-0.91</v>
       </c>
       <c r="N68" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.16558147</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
@@ -4531,25 +4531,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>130.64</v>
+        <v>131.52</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>89.59</v>
+        <v>90.05</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002147671278522448</v>
+        <v>0.002150965020125437</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.01369088028965829</v>
+        <v>0.01889567775514822</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.74</v>
+        <v>-0.88</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>0.93456659</v>
@@ -4588,25 +4588,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>103.18</v>
+        <v>102.82</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>88.81999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002129212668359904</v>
+        <v>0.002110835967001498</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-21.63</v>
+        <v>-22.08</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.1958352195563603</v>
+        <v>-0.1999094612947035</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-1.13</v>
+        <v>-1.3</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>1.17308322</v>
@@ -4645,25 +4645,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>63.9</v>
+        <v>64.64</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>86.59999999999999</v>
+        <v>87.47</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002075994337761402</v>
+        <v>0.002089338259970816</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-23.93</v>
+        <v>-23.06</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.2165023070659549</v>
+        <v>-0.208631140866733</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-1.13</v>
+        <v>-1.3</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.84694851</v>
@@ -4702,25 +4702,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>112.57</v>
+        <v>111.74</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>52.22</v>
+        <v>51.76</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001251829380114323</v>
+        <v>0.001236357017675653</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>4.35</v>
+        <v>3.89</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.0908711092542302</v>
+        <v>0.08126175057447253</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.4</v>
+        <v>-0.47</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.63221571</v>
@@ -4759,25 +4759,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>269.71</v>
+        <v>270.54</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>47.97</v>
+        <v>48.04</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001149947440905478</v>
+        <v>0.001147499828615502</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-4.14</v>
+        <v>-4.07</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.07944732297063903</v>
+        <v>-0.0781040107464978</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.43</v>
+        <v>-0.52</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.24236298</v>
@@ -4808,9 +4808,9 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -4869,34 +4869,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-20 19:09:36</t>
+          <t>2026-08-21 19:05:59</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43030.56</v>
+        <v>43180.3</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>41738.09</v>
+        <v>41887.69</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>36639.92</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5098.17</v>
+        <v>5247.77</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1391424981277252</v>
+        <v>0.1432254764748395</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1316.61</v>
+        <v>1316.75</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4977,22 +4977,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>108.84</v>
+        <v>108.88</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6965.76</v>
+        <v>6968.32</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>919.99</v>
+        <v>922.55</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5004,22 +5004,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.276</v>
+        <v>14.364</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4140.04</v>
+        <v>4165.56</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>709.33</v>
+        <v>734.85</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5031,22 +5031,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1502.6</v>
+        <v>1518.4</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2650.48</v>
+        <v>2678.35</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1454.52</v>
+        <v>1482.39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5058,22 +5058,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D5" t="n">
-        <v>109.61</v>
+        <v>111.59</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>1995.23</v>
+        <v>2028.01</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>348.66</v>
+        <v>381.44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5085,49 +5085,49 @@
         <v>115</v>
       </c>
       <c r="D6" t="n">
-        <v>23.31</v>
+        <v>23.73</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1967.09</v>
+        <v>1999.32</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>41.28</v>
+        <v>73.51000000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MRVL_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>9.6</v>
+        <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>247.02</v>
+        <v>472.4</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1740.15</v>
+        <v>1730.48</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1996.06</v>
+        <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-255.91</v>
+        <v>-168.07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5139,130 +5139,130 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>216.97</v>
+        <v>215.31</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1739.59</v>
+        <v>1723.51</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>486.91</v>
+        <v>470.83</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>MRVL_US_EQ</t>
         </is>
       </c>
       <c r="C9" s="4" t="n">
-        <v>5</v>
+        <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>465.19</v>
+        <v>237.15</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1706.81</v>
+        <v>1667.94</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>1898.55</v>
+        <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-191.74</v>
+        <v>-328.12</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BB3Ml_EQ</t>
+          <t>RDDT_US_EQ</t>
         </is>
       </c>
       <c r="C10" s="4" t="n">
-        <v>15.9020618</v>
+        <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>119.14</v>
+        <v>152.79</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1390.26</v>
+        <v>1408.44</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>1343.79</v>
+        <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46.47</v>
+        <v>-463.4</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>UBSGs_EQ</t>
+          <t>BB3Ml_EQ</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>35</v>
+        <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>42.72</v>
+        <v>119.16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1369.83</v>
+        <v>1388.26</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>1228.34</v>
+        <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>141.49</v>
+        <v>44.47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>RDDT_US_EQ</t>
+          <t>UBSGs_EQ</t>
         </is>
       </c>
       <c r="C12" s="4" t="n">
-        <v>12.5822526</v>
+        <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>147.74</v>
+        <v>42.5</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1364.08</v>
+        <v>1360.47</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>1871.84</v>
+        <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-507.76</v>
+        <v>132.13</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5274,22 +5274,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>438.3</v>
+        <v>440.8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1209.76</v>
+        <v>1215.38</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>295.27</v>
+        <v>300.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5301,22 +5301,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>109.75</v>
+        <v>111.25</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1113.26</v>
+        <v>1128.48</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>506.07</v>
+        <v>521.29</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5328,22 +5328,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>677.6</v>
+        <v>683.8</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1084.16</v>
+        <v>1094.08</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>330.7</v>
+        <v>340.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5355,22 +5355,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>320.62</v>
+        <v>328.07</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1030.84</v>
+        <v>1053.1</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>388.85</v>
+        <v>411.11</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5382,22 +5382,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D17" t="n">
-        <v>314.95</v>
+        <v>308.52</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>707.1900000000001</v>
+        <v>691.64</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>216.14</v>
+        <v>200.59</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5409,22 +5409,22 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>46.32</v>
+        <v>46.83</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>679.8</v>
+        <v>686.1799999999999</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-187.78</v>
+        <v>-181.4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5436,22 +5436,22 @@
         <v>65</v>
       </c>
       <c r="D19" t="n">
-        <v>1035.5</v>
+        <v>1036</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>673.08</v>
+        <v>673.4</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>10.4</v>
+        <v>10.72</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5463,22 +5463,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>98.08</v>
+        <v>97.93000000000001</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>661.85</v>
+        <v>659.78</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>112.67</v>
+        <v>110.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5490,22 +5490,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D21" t="n">
-        <v>482.16</v>
+        <v>482.77</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>659.87</v>
+        <v>659.65</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>125.49</v>
+        <v>125.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5517,22 +5517,22 @@
         <v>2.330043</v>
       </c>
       <c r="D22" t="n">
-        <v>331.59</v>
+        <v>334.93</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>566.96</v>
+        <v>571.75</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>77.69</v>
+        <v>82.48</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5544,22 +5544,22 @@
         <v>140</v>
       </c>
       <c r="D23" t="n">
-        <v>3.7935</v>
+        <v>3.798</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>531.09</v>
+        <v>531.72</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-7.28</v>
+        <v>-6.65</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5571,22 +5571,22 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>340.29</v>
+        <v>345.26</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>499.42</v>
+        <v>505.9</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>91.5</v>
+        <v>97.98</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5598,22 +5598,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D25" t="n">
-        <v>234.74</v>
+        <v>235.8</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>191.24</v>
+        <v>191.8</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-5.28</v>
+        <v>-4.72</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5625,22 +5625,22 @@
         <v>1.55804584</v>
       </c>
       <c r="D26" t="n">
-        <v>114.71</v>
+        <v>116.33</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>131.15</v>
+        <v>132.79</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>25.87</v>
+        <v>27.51</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5652,130 +5652,130 @@
         <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>280.14</v>
+        <v>280.25</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>130.38</v>
+        <v>130.22</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30.53</v>
+        <v>30.37</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.32559468</v>
       </c>
       <c r="D28" t="n">
-        <v>410.97</v>
+        <v>130.1</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>126.69</v>
+        <v>126.35</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>109.16</v>
+        <v>119.73</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>17.53</v>
+        <v>6.62</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.42010405</v>
       </c>
       <c r="D29" t="n">
-        <v>50.73</v>
+        <v>410.18</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>123.17</v>
+        <v>126.25</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>112.71</v>
+        <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>10.46</v>
+        <v>17.09</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.7</v>
+        <v>3.30858696</v>
       </c>
       <c r="D30" t="n">
-        <v>239.69</v>
+        <v>51.23</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>123.12</v>
+        <v>124.18</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>118.76</v>
+        <v>112.71</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>4.36</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.7</v>
       </c>
       <c r="D31" t="n">
-        <v>125.12</v>
+        <v>241.67</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>121.71</v>
+        <v>123.94</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>119.73</v>
+        <v>118.76</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>1.98</v>
+        <v>5.18</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5787,184 +5787,184 @@
         <v>2.50421091</v>
       </c>
       <c r="D32" t="n">
-        <v>66.2</v>
+        <v>67.27</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>121.65</v>
+        <v>123.42</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>14.84</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.28038062</v>
       </c>
       <c r="D33" t="n">
-        <v>206.46</v>
+        <v>580.1</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.78</v>
+        <v>119.16</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>110.41</v>
+        <v>105.75</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>9.369999999999999</v>
+        <v>13.41</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.7905852</v>
       </c>
       <c r="D34" t="n">
-        <v>576.11</v>
+        <v>205.6</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>118.53</v>
+        <v>119.09</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>105.75</v>
+        <v>110.41</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>12.78</v>
+        <v>8.68</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.62445608</v>
       </c>
       <c r="D35" t="n">
-        <v>269.13</v>
+        <v>258.79</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>116.88</v>
+        <v>118.4</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>108.77</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>17.03</v>
+        <v>9.630000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MAIN_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>2.70722512</v>
+        <v>0.59183053</v>
       </c>
       <c r="D36" t="n">
-        <v>58.55</v>
+        <v>271.57</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>116.31</v>
+        <v>117.75</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>107.64</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>8.67</v>
+        <v>17.9</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>KO_US_EQ</t>
+          <t>MAIN_US_EQ</t>
         </is>
       </c>
       <c r="C37" s="4" t="n">
-        <v>1.73400968</v>
+        <v>2.70722512</v>
       </c>
       <c r="D37" t="n">
-        <v>91.20999999999999</v>
+        <v>58.37</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>116.06</v>
+        <v>115.77</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>101.53</v>
+        <v>107.64</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>14.53</v>
+        <v>8.130000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>KO_US_EQ</t>
         </is>
       </c>
       <c r="C38" s="4" t="n">
-        <v>0.62445608</v>
+        <v>1.73400968</v>
       </c>
       <c r="D38" t="n">
-        <v>252.79</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>115.84</v>
+        <v>115.38</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>108.77</v>
+        <v>101.53</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>7.07</v>
+        <v>13.85</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5976,22 +5976,22 @@
         <v>3.81488812</v>
       </c>
       <c r="D39" t="n">
-        <v>40.89</v>
+        <v>40.5</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>114.47</v>
+        <v>113.19</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>6.24</v>
+        <v>4.96</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6003,22 +6003,22 @@
         <v>5.691347</v>
       </c>
       <c r="D40" t="n">
-        <v>27.23</v>
+        <v>26.99</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>113.72</v>
+        <v>112.54</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-339.24</v>
+        <v>-340.42</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6030,22 +6030,22 @@
         <v>0.43583007</v>
       </c>
       <c r="D41" t="n">
-        <v>346.94</v>
+        <v>347.56</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>110.96</v>
+        <v>110.98</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>6.92</v>
+        <v>6.94</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6057,49 +6057,49 @@
         <v>2.76637723</v>
       </c>
       <c r="D42" t="n">
-        <v>53.76</v>
+        <v>53.79</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>109.13</v>
+        <v>109.02</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>-3.35</v>
+        <v>-3.46</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>11.40066159</v>
+        <v>0.1285649</v>
       </c>
       <c r="D43" t="n">
-        <v>13.01</v>
+        <v>1155.21</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>108.84</v>
+        <v>108.81</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>106.15</v>
+        <v>98.89</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>2.69</v>
+        <v>9.92</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6111,49 +6111,49 @@
         <v>1.35094641</v>
       </c>
       <c r="D44" t="n">
-        <v>109.01</v>
+        <v>109.52</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>108.07</v>
+        <v>108.4</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>11.39</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>0.1285649</v>
+        <v>11.40066159</v>
       </c>
       <c r="D45" t="n">
-        <v>1144.93</v>
+        <v>12.96</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>108.02</v>
+        <v>108.25</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>98.89</v>
+        <v>106.15</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>9.130000000000001</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6165,76 +6165,76 @@
         <v>0.51881442</v>
       </c>
       <c r="D46" t="n">
-        <v>283.19</v>
+        <v>282.88</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>107.81</v>
+        <v>107.52</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>11.87</v>
+        <v>11.58</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>SYY_US_EQ</t>
         </is>
       </c>
       <c r="C47" s="4" t="n">
-        <v>0.37810738</v>
+        <v>1.74206342</v>
       </c>
       <c r="D47" t="n">
-        <v>387.13</v>
+        <v>83.61</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>107.41</v>
+        <v>106.71</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>11.9</v>
+        <v>10.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SYY_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>1.74206342</v>
+        <v>0.37810738</v>
       </c>
       <c r="D48" t="n">
-        <v>83.47</v>
+        <v>383.62</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>106.7</v>
+        <v>106.27</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>10.02</v>
+        <v>10.76</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6246,22 +6246,22 @@
         <v>13.30225117</v>
       </c>
       <c r="D49" t="n">
-        <v>10.92</v>
+        <v>10.89</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>106.59</v>
+        <v>106.13</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-0.37</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6273,76 +6273,76 @@
         <v>0.42255419</v>
       </c>
       <c r="D50" t="n">
-        <v>343.3</v>
+        <v>341.28</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>106.45</v>
+        <v>105.65</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>5.06</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.40867246</v>
       </c>
       <c r="D51" t="n">
-        <v>63.46</v>
+        <v>352.11</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>105.98</v>
+        <v>105.42</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>106.15</v>
+        <v>92.83</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>-0.17</v>
+        <v>12.59</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>0.40867246</v>
+        <v>2.27580753</v>
       </c>
       <c r="D52" t="n">
-        <v>352.64</v>
+        <v>62.66</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>105.75</v>
+        <v>104.47</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>92.83</v>
+        <v>106.15</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>12.92</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6354,49 +6354,49 @@
         <v>0.50675322</v>
       </c>
       <c r="D53" t="n">
-        <v>281.34</v>
+        <v>280.21</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>104.62</v>
+        <v>104.03</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>7.94</v>
+        <v>7.35</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>EMR_US_EQ</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.90543241</v>
       </c>
       <c r="D54" t="n">
-        <v>230.41</v>
+        <v>156.75</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>103.5</v>
+        <v>103.98</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>88.09</v>
+        <v>92.27</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>15.41</v>
+        <v>11.71</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6408,49 +6408,49 @@
         <v>0.68495686</v>
       </c>
       <c r="D55" t="n">
-        <v>205.07</v>
+        <v>205.52</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>103.07</v>
+        <v>103.13</v>
       </c>
       <c r="F55" s="2" t="n">
         <v>89.45999999999999</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>13.61</v>
+        <v>13.67</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>EMR_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.90543241</v>
+        <v>0.61215748</v>
       </c>
       <c r="D56" t="n">
-        <v>154.72</v>
+        <v>229.28</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>102.8</v>
+        <v>102.83</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>92.27</v>
+        <v>88.09</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>10.53</v>
+        <v>14.74</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6462,319 +6462,319 @@
         <v>0.80409618</v>
       </c>
       <c r="D57" t="n">
-        <v>172.65</v>
+        <v>174.51</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>101.87</v>
+        <v>102.81</v>
       </c>
       <c r="F57" s="2" t="n">
         <v>88.44</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>13.43</v>
+        <v>14.37</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.59010207</v>
       </c>
       <c r="D58" t="n">
-        <v>142.63</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>101.85</v>
+        <v>102.14</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>111.44</v>
+        <v>89.66</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-9.59</v>
+        <v>12.48</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.97307689</v>
       </c>
       <c r="D59" t="n">
-        <v>74.62</v>
+        <v>143.05</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>101.8</v>
+        <v>101.98</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>104.98</v>
+        <v>111.44</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-3.18</v>
+        <v>-9.460000000000001</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.10445851</v>
       </c>
       <c r="D60" t="n">
-        <v>123.31</v>
+        <v>1314.99</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>101.16</v>
+        <v>100.64</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>105.36</v>
+        <v>88.89</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-4.2</v>
+        <v>11.75</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.17949395</v>
+        <v>1.85908491</v>
       </c>
       <c r="D61" t="n">
-        <v>116.78</v>
+        <v>73.84</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>101.08</v>
+        <v>100.57</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>98.72</v>
+        <v>104.98</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>2.36</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1.59010207</v>
+        <v>1.17949395</v>
       </c>
       <c r="D62" t="n">
-        <v>86.43000000000001</v>
+        <v>116.34</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>100.85</v>
+        <v>100.53</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>89.66</v>
+        <v>98.72</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>11.19</v>
+        <v>1.81</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.1533463</v>
       </c>
       <c r="D63" t="n">
-        <v>1298.12</v>
+        <v>117.39</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>99.5</v>
+        <v>99.19</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>88.89</v>
+        <v>89.53</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>10.61</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>NUE_US_EQ</t>
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>0.6214908</v>
+        <v>0.5550481</v>
       </c>
       <c r="D64" t="n">
-        <v>216.66</v>
+        <v>242.78</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.81</v>
+        <v>98.73</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>107.82</v>
+        <v>91.18000000000001</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>-9.01</v>
+        <v>7.55</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.11796351</v>
       </c>
       <c r="D65" t="n">
-        <v>116.62</v>
+        <v>120.19</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>98.7</v>
+        <v>98.44</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>89.53</v>
+        <v>105.36</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>9.17</v>
+        <v>-6.92</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NUE_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.5550481</v>
+        <v>0.6214908</v>
       </c>
       <c r="D66" t="n">
-        <v>241.83</v>
+        <v>216.11</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>91.18000000000001</v>
+        <v>107.82</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>7.32</v>
+        <v>-9.42</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>PPG_US_EQ</t>
+          <t>PG_US_EQ</t>
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>1.16558147</v>
+        <v>0.9163735200000001</v>
       </c>
       <c r="D67" t="n">
-        <v>112.79</v>
+        <v>144.93</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>96.47</v>
+        <v>97.3</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>92.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>3.7</v>
+        <v>-2.55</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PG_US_EQ</t>
+          <t>PPG_US_EQ</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>0.9163735200000001</v>
+        <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>143</v>
+        <v>113.54</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>96.16</v>
+        <v>96.95999999999999</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>-3.69</v>
+        <v>4.19</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6786,22 +6786,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D69" t="n">
-        <v>130.64</v>
+        <v>131.52</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>89.59</v>
+        <v>90.05</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6813,22 +6813,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D70" t="n">
-        <v>103.18</v>
+        <v>102.82</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>88.81999999999999</v>
+        <v>88.37</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-21.63</v>
+        <v>-22.08</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6840,22 +6840,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D71" t="n">
-        <v>63.9</v>
+        <v>64.64</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>86.59999999999999</v>
+        <v>87.47</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-23.93</v>
+        <v>-23.06</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6867,22 +6867,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D72" t="n">
-        <v>112.57</v>
+        <v>111.74</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>52.22</v>
+        <v>51.76</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>4.35</v>
+        <v>3.89</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6894,16 +6894,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D73" t="n">
-        <v>269.71</v>
+        <v>270.54</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>47.97</v>
+        <v>48.04</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-4.14</v>
+        <v>-4.07</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43180.3</v>
+        <v>43186.83</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>41887.69</v>
+        <v>41894.09</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5247.77</v>
+        <v>5254.17</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1432254764748395</v>
+        <v>0.1434001493453043</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1292.61</v>
+        <v>1292.74</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-21 19:05:59</t>
+          <t>2026-08-22 18:55:40</t>
         </is>
       </c>
     </row>
@@ -601,7 +601,7 @@
     <col width="15" customWidth="1" min="9" max="9"/>
     <col width="23" customWidth="1" min="10" max="10"/>
     <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="23" customWidth="1" min="12" max="12"/>
     <col width="11" customWidth="1" min="13" max="13"/>
     <col width="13" customWidth="1" min="14" max="14"/>
     <col width="12" customWidth="1" min="15" max="15"/>
@@ -721,7 +721,7 @@
         <v>6968.32</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1664476687289337</v>
+        <v>0.1664277124763703</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>922.55</v>
@@ -778,7 +778,7 @@
         <v>4165.56</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0994999872208075</v>
+        <v>0.09948805766426758</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>734.85</v>
@@ -835,7 +835,7 @@
         <v>2678.35</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06397598180625168</v>
+        <v>0.06396831140233031</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>1482.39</v>
@@ -883,25 +883,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>111.59</v>
+        <v>111.2</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2028.01</v>
+        <v>2019.33</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04844173870588103</v>
+        <v>0.04822862219802029</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>381.44</v>
+        <v>372.76</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2316573240129481</v>
+        <v>0.2263857594879052</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-28.03</v>
+        <v>-29.31</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>1.15856288</v>
@@ -940,25 +940,25 @@
         <v>22.51</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>23.73</v>
+        <v>23.81</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1999.32</v>
+        <v>2004.47</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04775643957842519</v>
+        <v>0.04787371372547614</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>73.51000000000001</v>
+        <v>78.66</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.03817095144380806</v>
+        <v>0.04084515087158131</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-29.28</v>
+        <v>-30.78</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -997,25 +997,25 @@
         <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>472.4</v>
+        <v>472.31</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1730.48</v>
+        <v>1728.78</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04133483562494909</v>
+        <v>0.04128927787112236</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-168.07</v>
+        <v>-169.77</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.08852545363566933</v>
+        <v>-0.08942087382476101</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-30.44</v>
+        <v>-31.92</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
@@ -1054,25 +1054,25 @@
         <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>215.31</v>
+        <v>215.38</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1723.51</v>
+        <v>1722.71</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04116834782716704</v>
+        <v>0.04114430516396604</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>470.83</v>
+        <v>470.03</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.3758581601047354</v>
+        <v>0.3752195293291183</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-51.21</v>
+        <v>-52.15</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>237.15</v>
+        <v>236.1</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1667.94</v>
+        <v>1659.24</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03984098384972816</v>
+        <v>0.03962842086030673</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-328.12</v>
+        <v>-336.82</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1643838361572298</v>
+        <v>-0.1687424225724678</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-36.93</v>
+        <v>-38.48</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>152.79</v>
+        <v>153.75</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1408.44</v>
+        <v>1416.17</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03364247832254826</v>
+        <v>0.03382306403518514</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-463.4</v>
+        <v>-455.67</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2475638943499444</v>
+        <v>-0.2434342678861441</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-106.33</v>
+        <v>-107.73</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1231,19 +1231,19 @@
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1388.26</v>
+        <v>1387.16</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03316045195823807</v>
+        <v>0.03313020435897344</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>44.47</v>
+        <v>43.37</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.03309296839535939</v>
+        <v>0.03227438811123762</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-26.83</v>
+        <v>-27.87</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1288,19 +1288,19 @@
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1360.47</v>
+        <v>1358.86</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03249665053781291</v>
+        <v>0.03245430195163834</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>132.13</v>
+        <v>130.52</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1075679372160802</v>
+        <v>0.106257225198235</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-42.33</v>
+        <v>-43.73</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1345,19 +1345,19 @@
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1215.38</v>
+        <v>1214.81</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02903098130105556</v>
+        <v>0.02901388704787084</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>300.89</v>
+        <v>300.32</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3290249209942153</v>
+        <v>0.328401622762414</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-2.66</v>
+        <v>-3.09</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>1128.48</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02695525825553751</v>
+        <v>0.02695202645333945</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>521.29</v>
@@ -1462,7 +1462,7 @@
         <v>1094.08</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02613356812014256</v>
+        <v>0.02613043483452929</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>340.62</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>328.07</v>
+        <v>333.48</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1053.1</v>
+        <v>1069.62</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02515470586001219</v>
+        <v>0.02554624497999161</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>411.11</v>
+        <v>427.63</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6403682300347358</v>
+        <v>0.6661007180797208</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-38.93</v>
+        <v>-39.4</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>308.52</v>
+        <v>309.69</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>691.64</v>
+        <v>693.71</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.01652074898966749</v>
+        <v>0.01656820703153455</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>200.59</v>
+        <v>202.66</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4084920069239385</v>
+        <v>0.4127074635984115</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-25.04</v>
+        <v>-25.41</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.46065664</v>
@@ -1624,25 +1624,25 @@
         <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46.83</v>
+        <v>46.81</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>686.1799999999999</v>
+        <v>685.35</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01639032956701468</v>
+        <v>0.01636854116138185</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-181.4</v>
+        <v>-182.23</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.2090873464118583</v>
+        <v>-0.210044030521681</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-20.07</v>
+        <v>-20.74</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -1690,7 +1690,7 @@
         <v>673.4</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.016085062127179</v>
+        <v>0.01608313360775449</v>
       </c>
       <c r="K19" s="2" t="n">
         <v>10.72</v>
@@ -1713,17 +1713,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Nasdaq</t>
+          <t>Microsoft</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US6311031081</t>
+          <t>US5949181045</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1732,55 +1732,55 @@
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>1.8650317</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>77.20222067</v>
+        <v>369.46288902</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>97.93000000000001</v>
+        <v>483.61</v>
       </c>
       <c r="H20" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>534.38</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>659.78</v>
+        <v>660.27</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01575973016078135</v>
+        <v>0.01576954355092375</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>110.6</v>
+        <v>125.89</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.2013911650096508</v>
+        <v>0.235581421460384</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-29.05</v>
+        <v>-29.96</v>
       </c>
       <c r="N20" s="4" t="n">
-        <v>0</v>
+        <v>0.3650317</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2024-09-26</t>
+          <t>2025-04-08</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Microsoft</t>
+          <t>Nasdaq</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>US5949181045</t>
+          <t>US6311031081</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1789,38 +1789,38 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>1.8650317</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>369.46288902</v>
+        <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>482.77</v>
+        <v>97.37</v>
       </c>
       <c r="H21" s="2" t="n">
-        <v>534.38</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>659.65</v>
+        <v>655.49</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01575662493643247</v>
+        <v>0.01565538052947281</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>125.27</v>
+        <v>106.31</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.2344211983981436</v>
+        <v>0.1935795185549365</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-29.55</v>
+        <v>-29.46</v>
       </c>
       <c r="N21" s="4" t="n">
-        <v>0.3650317</v>
+        <v>0</v>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2025-04-08</t>
+          <t>2024-09-26</t>
         </is>
       </c>
     </row>
@@ -1852,25 +1852,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>334.93</v>
+        <v>336.05</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>571.75</v>
+        <v>573.21</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01365701554976922</v>
+        <v>0.01369024801796993</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>82.48</v>
+        <v>83.94</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1685776769472888</v>
+        <v>0.1715617143908272</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-35.83</v>
+        <v>-36.19</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1918,7 +1918,7 @@
         <v>531.72</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01270084531372679</v>
+        <v>0.01269932254516664</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>-6.65</v>
@@ -1966,25 +1966,25 @@
         <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>345.26</v>
+        <v>345.1</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>505.9</v>
+        <v>505.26</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01208409998535767</v>
+        <v>0.01206736573604697</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>97.98</v>
+        <v>97.34</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.2401941557168072</v>
+        <v>0.2386252206314964</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-13.13</v>
+        <v>-13.45</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -2029,19 +2029,19 @@
         <v>196.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>191.8</v>
+        <v>191.64</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.004581400231649737</v>
+        <v>0.004577029588045841</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-4.72</v>
+        <v>-4.88</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.02401791166293507</v>
+        <v>-0.02483207815998371</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-3.85</v>
+        <v>-4.01</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>1.11022215</v>
@@ -2080,25 +2080,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>116.33</v>
+        <v>116.55</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>132.79</v>
+        <v>132.93</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.003171867240671368</v>
+        <v>0.00317483063629166</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>27.51</v>
+        <v>27.65</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.2613031914893617</v>
+        <v>0.2626329787234042</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.17</v>
+        <v>-1.26</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.55804584</v>
@@ -2137,25 +2137,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>280.25</v>
+        <v>280.81</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>130.22</v>
+        <v>130.38</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003110479343928199</v>
+        <v>0.003113927769199628</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>30.37</v>
+        <v>30.53</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.3041562343515273</v>
+        <v>0.3057586379569354</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-0.99</v>
+        <v>-1.06</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0.63422137</v>
@@ -2194,25 +2194,25 @@
         <v>121.66614911</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>130.1</v>
+        <v>132</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>126.35</v>
+        <v>128.09</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.003018039203696268</v>
+        <v>0.003059234606203255</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>6.62</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.05529107157771652</v>
+        <v>0.06982377014950304</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-1.57</v>
+        <v>-1.67</v>
       </c>
       <c r="N28" s="4" t="n">
         <v>1.32559468</v>
@@ -2251,25 +2251,25 @@
         <v>350.55601106</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>410.18</v>
+        <v>414.88</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>126.25</v>
+        <v>127.59</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.003015650569581748</v>
+        <v>0.003047292867557759</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>17.09</v>
+        <v>18.43</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1565591791865152</v>
+        <v>0.1688347379992671</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-1.26</v>
+        <v>-1.35</v>
       </c>
       <c r="N29" s="4" t="n">
         <v>0.42010405</v>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Canadian Natural Resources</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CA1363851017</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,55 +2302,55 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>45.93199509</v>
+        <v>225.62857143</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>51.23</v>
+        <v>242.69</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>112.71</v>
+        <v>118.76</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>124.18</v>
+        <v>124.36</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.00296620584341118</v>
+        <v>0.002970149235907852</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>11.47</v>
+        <v>5.6</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.1017655931150741</v>
+        <v>0.0471539238800943</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-1.37</v>
+        <v>-3.14</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Canadian Natural Resources</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>CA1363851017</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2359,38 +2359,38 @@
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>0.7</v>
+        <v>3.30858696</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>225.62857143</v>
+        <v>45.93199509</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>241.67</v>
+        <v>51.31</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>118.76</v>
+        <v>112.71</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>123.94</v>
+        <v>124.28</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002960473121536331</v>
+        <v>0.002968238557724573</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>5.18</v>
+        <v>11.57</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.04361737958908723</v>
+        <v>0.1026528258362168</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-3.05</v>
+        <v>-1.46</v>
       </c>
       <c r="N31" s="4" t="n">
-        <v>0</v>
+        <v>3.30858696</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2422,25 +2422,25 @@
         <v>57.56703616</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>67.27</v>
+        <v>67</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>123.42</v>
+        <v>122.83</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002948052224140826</v>
+        <v>0.002933607515652633</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>16.61</v>
+        <v>16.02</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1555097837281153</v>
+        <v>0.1499859563711263</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-1.19</v>
+        <v>-1.27</v>
       </c>
       <c r="N32" s="4" t="n">
         <v>2.50421091</v>
@@ -2479,25 +2479,25 @@
         <v>509.16500577</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>580.1</v>
+        <v>580.05</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.16</v>
+        <v>119.06</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002846296410862266</v>
+        <v>0.002843566806265591</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.41</v>
+        <v>13.31</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1268085106382979</v>
+        <v>0.1258628841607565</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-1.16</v>
+        <v>-1.24</v>
       </c>
       <c r="N33" s="4" t="n">
         <v>0.28038062</v>
@@ -2536,25 +2536,25 @@
         <v>188.32884805</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>205.6</v>
+        <v>205.28</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>119.09</v>
+        <v>118.81</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002844624366982102</v>
+        <v>0.002837595936942843</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>8.68</v>
+        <v>8.4</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.07861606738520062</v>
+        <v>0.07608006521148447</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-1.32</v>
+        <v>-1.41</v>
       </c>
       <c r="N34" s="4" t="n">
         <v>0.7905852</v>
@@ -2593,25 +2593,25 @@
         <v>235.02053179</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>258.79</v>
+        <v>258.59</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>118.4</v>
+        <v>118.21</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002828142791591912</v>
+        <v>0.002823265850568247</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.08853544175783765</v>
+        <v>0.08678863657258436</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-1.24</v>
+        <v>-1.33</v>
       </c>
       <c r="N35" s="4" t="n">
         <v>0.62445608</v>
@@ -2650,25 +2650,25 @@
         <v>228.00445932</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>271.57</v>
+        <v>271</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>117.75</v>
+        <v>117.41</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002812616669847531</v>
+        <v>0.002804159068735453</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>17.9</v>
+        <v>17.56</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1792689033550325</v>
+        <v>0.1758637956935403</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-0.99</v>
+        <v>-1.07</v>
       </c>
       <c r="N36" s="4" t="n">
         <v>0.59183053</v>
@@ -2707,25 +2707,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>58.37</v>
+        <v>58.44</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>115.77</v>
+        <v>115.82</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002765321714380031</v>
+        <v>0.002766184339842775</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.07552954292084728</v>
+        <v>0.07599405425492382</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-1.22</v>
+        <v>-1.3</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>2.70722512</v>
@@ -2764,25 +2764,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>90.81999999999999</v>
+        <v>91.06</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>115.38</v>
+        <v>115.59</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002756006041333402</v>
+        <v>0.002760691140065847</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>13.85</v>
+        <v>14.06</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.1364128828917561</v>
+        <v>0.1384812370727864</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-1.03</v>
+        <v>-1.11</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>1.73400968</v>
@@ -2796,17 +2796,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LTC Properties</t>
+          <t>Figma</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US5021751020</t>
+          <t>US3168411052</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2815,55 +2815,55 @@
         </is>
       </c>
       <c r="E39" s="4" t="n">
-        <v>3.81488812</v>
+        <v>5.691347</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>38.28159448</v>
+        <v>105.04894536</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>40.5</v>
+        <v>27.11</v>
       </c>
       <c r="H39" s="2" t="n">
-        <v>108.23</v>
+        <v>452.96</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>113.19</v>
+        <v>112.95</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.00270369495422541</v>
+        <v>0.002697638760017626</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>4.96</v>
+        <v>-340.01</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.0458283285595491</v>
+        <v>-0.7506402331331685</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-1.24</v>
+        <v>-15.29</v>
       </c>
       <c r="N39" s="4" t="n">
-        <v>3.81488812</v>
+        <v>0</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-07-31</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Figma</t>
+          <t>LTC Properties</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>US3168411052</t>
+          <t>US5021751020</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2872,38 +2872,38 @@
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>5.691347</v>
+        <v>3.81488812</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>105.04894536</v>
+        <v>38.28159448</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>26.99</v>
+        <v>40.27</v>
       </c>
       <c r="H40" s="2" t="n">
-        <v>452.96</v>
+        <v>108.23</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112.54</v>
+        <v>112.46</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002688168832481029</v>
+        <v>0.002685935856145039</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>-340.42</v>
+        <v>4.23</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>-0.7515453903214413</v>
+        <v>0.03908343342880902</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-14.94</v>
+        <v>-1.32</v>
       </c>
       <c r="N40" s="4" t="n">
-        <v>0</v>
+        <v>3.81488812</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>2025-07-31</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2935,25 +2935,25 @@
         <v>322.35040597</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>347.56</v>
+        <v>347.6</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>110.98</v>
+        <v>110.9</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002650906140294514</v>
+        <v>0.002648677631571091</v>
       </c>
       <c r="K41" s="2" t="n">
-        <v>6.94</v>
+        <v>6.86</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.06670511341791618</v>
+        <v>0.0659361783929258</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-1.11</v>
+        <v>-1.2</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0.43583007</v>
@@ -2998,19 +2998,19 @@
         <v>112.48</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>109.02</v>
+        <v>108.93</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002604088911649918</v>
+        <v>0.002601627181307835</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>-3.46</v>
+        <v>-3.55</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.03076102418207681</v>
+        <v>-0.03156116642958748</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-1.36</v>
+        <v>-1.45</v>
       </c>
       <c r="N42" s="4" t="n">
         <v>2.76637723</v>
@@ -3049,25 +3049,25 @@
         <v>1039.47500445</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1155.21</v>
+        <v>1156.55</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>98.89</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>108.81</v>
+        <v>108.85</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002599072780009426</v>
+        <v>0.002599716503124556</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>9.92</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.1003134796238244</v>
+        <v>0.1007179694610173</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-0.98</v>
+        <v>-1.06</v>
       </c>
       <c r="N43" s="4" t="n">
         <v>0.1285649</v>
@@ -3106,25 +3106,25 @@
         <v>96.717382</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>109.52</v>
+        <v>109.1</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>108.4</v>
+        <v>107.9</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002589279380139893</v>
+        <v>0.002577027199698113</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>11.72</v>
+        <v>11.22</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.12122465866777</v>
+        <v>0.1160529582126603</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-0.95</v>
+        <v>-1.03</v>
       </c>
       <c r="N44" s="4" t="n">
         <v>1.35094641</v>
@@ -3163,25 +3163,25 @@
         <v>12.56856884</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>12.96</v>
+        <v>12.87</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>108.25</v>
+        <v>107.41</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002585696428968113</v>
+        <v>0.002565324295825526</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.01978332548280735</v>
+        <v>0.01186999528968441</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-1.17</v>
+        <v>-1.26</v>
       </c>
       <c r="N45" s="4" t="n">
         <v>11.40066159</v>
@@ -3220,25 +3220,25 @@
         <v>249.91595261</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>282.88</v>
+        <v>281.91</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>107.52</v>
+        <v>107.07</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002568259399932115</v>
+        <v>0.002557203913546588</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>11.58</v>
+        <v>11.13</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1207004377736085</v>
+        <v>0.1160100062539087</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-0.95</v>
+        <v>-1.02</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>0.51881442</v>
@@ -3277,25 +3277,25 @@
         <v>74.99726962</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>83.61</v>
+        <v>83.95</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>106.71</v>
+        <v>107.06</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002548911463604501</v>
+        <v>0.002556965078773679</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>10.03</v>
+        <v>10.38</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1037443111294994</v>
+        <v>0.1073645014480761</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-0.96</v>
+        <v>-1.04</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>1.74206342</v>
@@ -3334,25 +3334,25 @@
         <v>341.38450299</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>383.62</v>
+        <v>384.24</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>106.27</v>
+        <v>106.36</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002538401473500612</v>
+        <v>0.002540246644669984</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>10.76</v>
+        <v>10.85</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1126583603811119</v>
+        <v>0.1136006700869019</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-1.01</v>
       </c>
       <c r="N48" s="4" t="n">
         <v>0.37810738</v>
@@ -3391,25 +3391,25 @@
         <v>10.85229847</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>10.89</v>
+        <v>10.92</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>106.13</v>
+        <v>106.34</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002535057385740284</v>
+        <v>0.002539768975124164</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>-0.83</v>
+        <v>-0.62</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>-0.007759910246821241</v>
+        <v>-0.005796559461480928</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-1.2</v>
+        <v>-1.28</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>13.30225117</v>
@@ -3448,25 +3448,25 @@
         <v>324.07677699</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>341.28</v>
+        <v>341</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>105.65</v>
+        <v>105.48</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.002523591941990587</v>
+        <v>0.00251922918465391</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4.26</v>
+        <v>4.09</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.04201597790709143</v>
+        <v>0.04033928395305257</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-1.07</v>
+        <v>-1.14</v>
       </c>
       <c r="N50" s="4" t="n">
         <v>0.42255419</v>
@@ -3505,25 +3505,25 @@
         <v>306.99401668</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>352.11</v>
+        <v>351.99</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>105.42</v>
+        <v>105.3</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002518098083527191</v>
+        <v>0.002514930158741531</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>12.59</v>
+        <v>12.47</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.1356242593989012</v>
+        <v>0.1343315738446623</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.92</v>
+        <v>-0.99</v>
       </c>
       <c r="N51" s="4" t="n">
         <v>0.40867246</v>
@@ -3562,25 +3562,25 @@
         <v>62.95787236</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>62.66</v>
+        <v>62.76</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>104.47</v>
+        <v>104.56</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002495406059439249</v>
+        <v>0.002497256385546197</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>-1.68</v>
+        <v>-1.59</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>-0.01582666038624588</v>
+        <v>-0.01497880357983985</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-1.18</v>
+        <v>-1.26</v>
       </c>
       <c r="N52" s="4" t="n">
         <v>2.27580753</v>
@@ -3619,25 +3619,25 @@
         <v>257.81779936</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>280.21</v>
+        <v>281.63</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>104.03</v>
+        <v>104.48</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.00248489606933536</v>
+        <v>0.002495345707362918</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>7.35</v>
+        <v>7.8</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.0760239966901117</v>
+        <v>0.08067852709971038</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-0.96</v>
+        <v>-1.03</v>
       </c>
       <c r="N53" s="4" t="n">
         <v>0.50675322</v>
@@ -3676,25 +3676,25 @@
         <v>137.713206</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>156.75</v>
+        <v>157.61</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>92.27</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>103.98</v>
+        <v>104.47</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.0024837017522781</v>
+        <v>0.002495106872590008</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>11.71</v>
+        <v>12.2</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.1269101549799502</v>
+        <v>0.1322206567681803</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.92</v>
+        <v>-0.99</v>
       </c>
       <c r="N54" s="4" t="n">
         <v>0.90543241</v>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.80409618</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>176.50746647</v>
+        <v>148.63893521</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>205.52</v>
+        <v>175</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>88.44</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>103.13</v>
+        <v>103.01</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002463398362304678</v>
+        <v>0.002460236995745158</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>13.67</v>
+        <v>14.57</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1528057232282584</v>
+        <v>0.1647444595205789</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.89</v>
+        <v>-0.95</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.80409618</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.68495686</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>194.45976548</v>
+        <v>176.50746647</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>229.28</v>
+        <v>205.34</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>88.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>102.83</v>
+        <v>102.96</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002456232459961118</v>
+        <v>0.002459042821880609</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>14.74</v>
+        <v>13.5</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.1673288682029742</v>
+        <v>0.1509054325955735</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.88</v>
+        <v>-0.96</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.68495686</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.61215748</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>148.63893521</v>
+        <v>194.45976548</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>174.51</v>
+        <v>229.26</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>88.44</v>
+        <v>88.09</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>102.81</v>
+        <v>102.74</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.002455754733138214</v>
+        <v>0.00245378845687659</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>14.37</v>
+        <v>14.65</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.162483039348711</v>
+        <v>0.1663071858326711</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.87</v>
+        <v>-0.95</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.61215748</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.97307689</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>154.44822659</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>87.68000000000001</v>
+        <v>143.45</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>89.66</v>
+        <v>111.44</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>102.14</v>
+        <v>102.19</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002439750884570928</v>
+        <v>0.002440652544366544</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>12.48</v>
+        <v>-9.25</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.1391925050189605</v>
+        <v>-0.08300430725053841</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-0.9</v>
+        <v>-1.42</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.97307689</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.59010207</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>154.44822659</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>143.05</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>111.44</v>
+        <v>89.66</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>101.98</v>
+        <v>101.93</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002435929069987696</v>
+        <v>0.002434442840270886</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>-9.460000000000001</v>
+        <v>12.27</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>-0.08488872936109118</v>
+        <v>0.1368503234441222</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-1.33</v>
+        <v>-0.97</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.59010207</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -3993,17 +3993,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Agree Realty</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>US0084921008</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -4012,34 +4012,34 @@
         </is>
       </c>
       <c r="E60" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.85908491</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>76.24181082</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>1314.99</v>
+        <v>73.88</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>88.89</v>
+        <v>104.98</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>100.64</v>
+        <v>100.55</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002403921372853125</v>
+        <v>0.002401483641609316</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>11.75</v>
+        <v>-4.43</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.132185847676904</v>
+        <v>-0.04219851400266717</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-0.87</v>
+        <v>-1.22</v>
       </c>
       <c r="N60" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.85908491</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Agree Realty</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US0084921008</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.10445851</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>76.24181082</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>73.84</v>
+        <v>1312.24</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>104.98</v>
+        <v>88.89</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>100.57</v>
+        <v>100.35</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002402249328972961</v>
+        <v>0.002396706946151118</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>-4.41</v>
+        <v>11.46</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>-0.04200800152409983</v>
+        <v>0.1289233884576443</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-1.14</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.10445851</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4132,25 +4132,25 @@
         <v>113.12478542</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>116.34</v>
+        <v>116.07</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>100.53</v>
+        <v>100.22</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002401293875327153</v>
+        <v>0.002393602094103288</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.01833468395461912</v>
+        <v>0.01519448946515397</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-0.97</v>
+        <v>-1.04</v>
       </c>
       <c r="N62" s="4" t="n">
         <v>1.17949395</v>
@@ -4189,25 +4189,25 @@
         <v>104.90344487</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>117.39</v>
+        <v>117.15</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>99.19</v>
+        <v>98.91</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002369286178192583</v>
+        <v>0.002362314738852088</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>9.66</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.107896794370602</v>
+        <v>0.1047693510555121</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.89</v>
+        <v>-0.96</v>
       </c>
       <c r="N63" s="4" t="n">
         <v>1.1533463</v>
@@ -4246,25 +4246,25 @@
         <v>221.99877812</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>242.78</v>
+        <v>243</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98.73</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.00235829846126579</v>
+        <v>0.002358254547712619</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>7.55</v>
+        <v>7.56</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.08280324632594867</v>
+        <v>0.08291291949989031</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.9</v>
+        <v>-0.97</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>0.5550481</v>
@@ -4303,25 +4303,25 @@
         <v>127.23134407</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>120.19</v>
+        <v>120.27</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>98.44</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002351371422333681</v>
+        <v>0.002350850669752412</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-6.92</v>
+        <v>-6.93</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.0656795747911921</v>
+        <v>-0.0657744874715262</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-1.15</v>
+        <v>-1.23</v>
       </c>
       <c r="N65" s="4" t="n">
         <v>1.11796351</v>
@@ -4360,25 +4360,25 @@
         <v>234.11448729</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>216.11</v>
+        <v>216.05</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002350415968687873</v>
+        <v>0.002347745817704582</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-9.42</v>
+        <v>-9.52</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.08736783528102393</v>
+        <v>-0.08829530699313672</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-1.22</v>
+        <v>-1.3</v>
       </c>
       <c r="N66" s="4" t="n">
         <v>0.6214908</v>
@@ -4417,25 +4417,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>144.93</v>
+        <v>144.88</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>97.3</v>
+        <v>97.19</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002324140993428151</v>
+        <v>0.002321235157911581</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-2.55</v>
+        <v>-2.66</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.02553830746119179</v>
+        <v>-0.02663995993990987</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-1.02</v>
+        <v>-1.1</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4474,25 +4474,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>113.54</v>
+        <v>113.55</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>96.95999999999999</v>
+        <v>96.89</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002316019637438782</v>
+        <v>0.002314070114724283</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.04516546297294385</v>
+        <v>0.04441090869893285</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.91</v>
+        <v>-0.98</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.16558147</v>
@@ -4531,25 +4531,25 @@
         <v>127.79185697</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>131.52</v>
+        <v>131.73</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>90.05</v>
+        <v>90.12</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002150965020125437</v>
+        <v>0.002152378973464262</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.01889567775514822</v>
+        <v>0.01968771215207061</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.88</v>
+        <v>-0.95</v>
       </c>
       <c r="N69" s="4" t="n">
         <v>0.93456659</v>
@@ -4588,25 +4588,25 @@
         <v>126.99866255</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>102.82</v>
+        <v>103.66</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>88.37</v>
+        <v>89.02</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.002110835967001498</v>
+        <v>0.00212610714844417</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-22.08</v>
+        <v>-21.43</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.1999094612947035</v>
+        <v>-0.19402444545043</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-1.3</v>
+        <v>-1.39</v>
       </c>
       <c r="N70" s="4" t="n">
         <v>1.17308322</v>
@@ -4645,25 +4645,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>64.64</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>87.47</v>
+        <v>87.34</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002089338259970816</v>
+        <v>0.002085982906595303</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-23.06</v>
+        <v>-23.19</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.208631140866733</v>
+        <v>-0.2098072921378811</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-1.3</v>
+        <v>-1.39</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.84694851</v>
@@ -4702,25 +4702,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>111.74</v>
+        <v>110.5</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>51.76</v>
+        <v>51.14</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001236357017675653</v>
+        <v>0.001221401028661367</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3.89</v>
+        <v>3.27</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.08126175057447253</v>
+        <v>0.06831000626697306</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.47</v>
+        <v>-0.51</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.63221571</v>
@@ -4759,25 +4759,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>270.54</v>
+        <v>270.85</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>48.04</v>
+        <v>48.05</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001147499828615502</v>
+        <v>0.001147601083832199</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-4.07</v>
+        <v>-4.06</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.0781040107464978</v>
+        <v>-0.0779121090001919</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.52</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.24236298</v>
@@ -4808,7 +4808,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
@@ -4869,34 +4869,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-21 19:05:59</t>
+          <t>2026-08-22 18:55:40</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43180.3</v>
+        <v>43186.83</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>41887.69</v>
+        <v>41894.09</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>36639.92</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5247.77</v>
+        <v>5254.17</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1432254764748395</v>
+        <v>0.1434001493453043</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1316.75</v>
+        <v>1316.88</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4992,7 +4992,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5058,22 +5058,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D5" t="n">
-        <v>111.59</v>
+        <v>111.2</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2028.01</v>
+        <v>2019.33</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>381.44</v>
+        <v>372.76</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5085,22 +5085,22 @@
         <v>115</v>
       </c>
       <c r="D6" t="n">
-        <v>23.73</v>
+        <v>23.81</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>1999.32</v>
+        <v>2004.47</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>73.51000000000001</v>
+        <v>78.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5112,22 +5112,22 @@
         <v>5</v>
       </c>
       <c r="D7" t="n">
-        <v>472.4</v>
+        <v>472.31</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1730.48</v>
+        <v>1728.78</v>
       </c>
       <c r="F7" s="2" t="n">
         <v>1898.55</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-168.07</v>
+        <v>-169.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5139,22 +5139,22 @@
         <v>10.9260596</v>
       </c>
       <c r="D8" t="n">
-        <v>215.31</v>
+        <v>215.38</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1723.51</v>
+        <v>1722.71</v>
       </c>
       <c r="F8" s="2" t="n">
         <v>1252.68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>470.83</v>
+        <v>470.03</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5166,22 +5166,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>237.15</v>
+        <v>236.1</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1667.94</v>
+        <v>1659.24</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-328.12</v>
+        <v>-336.82</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5193,22 +5193,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>152.79</v>
+        <v>153.75</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1408.44</v>
+        <v>1416.17</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-463.4</v>
+        <v>-455.67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5223,19 +5223,19 @@
         <v>119.16</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1388.26</v>
+        <v>1387.16</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>44.47</v>
+        <v>43.37</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5250,19 +5250,19 @@
         <v>42.5</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1360.47</v>
+        <v>1358.86</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>132.13</v>
+        <v>130.52</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5277,19 +5277,19 @@
         <v>440.8</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1215.38</v>
+        <v>1214.81</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>300.89</v>
+        <v>300.32</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5316,7 +5316,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5343,7 +5343,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5355,22 +5355,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>328.07</v>
+        <v>333.48</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1053.1</v>
+        <v>1069.62</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>411.11</v>
+        <v>427.63</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5382,22 +5382,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D17" t="n">
-        <v>308.52</v>
+        <v>309.69</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>691.64</v>
+        <v>693.71</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>200.59</v>
+        <v>202.66</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5409,22 +5409,22 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>46.83</v>
+        <v>46.81</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>686.1799999999999</v>
+        <v>685.35</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-181.4</v>
+        <v>-182.23</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5451,61 +5451,61 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>NDAQ_US_EQ</t>
+          <t>MSFT_US_EQ</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9.195978999999999</v>
+        <v>1.8650317</v>
       </c>
       <c r="D20" t="n">
-        <v>97.93000000000001</v>
+        <v>483.61</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>659.78</v>
+        <v>660.27</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>549.1799999999999</v>
+        <v>534.38</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>110.6</v>
+        <v>125.89</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>MSFT_US_EQ</t>
+          <t>NDAQ_US_EQ</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>1.8650317</v>
+        <v>9.195978999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>482.77</v>
+        <v>97.37</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>659.65</v>
+        <v>655.49</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>534.38</v>
+        <v>549.1799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>125.27</v>
+        <v>106.31</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5517,22 +5517,22 @@
         <v>2.330043</v>
       </c>
       <c r="D22" t="n">
-        <v>334.93</v>
+        <v>336.05</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>571.75</v>
+        <v>573.21</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>82.48</v>
+        <v>83.94</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5559,7 +5559,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5571,22 +5571,22 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>345.26</v>
+        <v>345.1</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>505.9</v>
+        <v>505.26</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>97.98</v>
+        <v>97.34</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5601,19 +5601,19 @@
         <v>235.8</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>191.8</v>
+        <v>191.64</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-4.72</v>
+        <v>-4.88</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5625,22 +5625,22 @@
         <v>1.55804584</v>
       </c>
       <c r="D26" t="n">
-        <v>116.33</v>
+        <v>116.55</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>132.79</v>
+        <v>132.93</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>27.51</v>
+        <v>27.65</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5652,22 +5652,22 @@
         <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>280.25</v>
+        <v>280.81</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>130.22</v>
+        <v>130.38</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30.37</v>
+        <v>30.53</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5679,22 +5679,22 @@
         <v>1.32559468</v>
       </c>
       <c r="D28" t="n">
-        <v>130.1</v>
+        <v>132</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>126.35</v>
+        <v>128.09</v>
       </c>
       <c r="F28" s="2" t="n">
         <v>119.73</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>6.62</v>
+        <v>8.359999999999999</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5706,76 +5706,76 @@
         <v>0.42010405</v>
       </c>
       <c r="D29" t="n">
-        <v>410.18</v>
+        <v>414.88</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>126.25</v>
+        <v>127.59</v>
       </c>
       <c r="F29" s="2" t="n">
         <v>109.16</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>17.09</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CNQ_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>3.30858696</v>
+        <v>0.7</v>
       </c>
       <c r="D30" t="n">
-        <v>51.23</v>
+        <v>242.69</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>124.18</v>
+        <v>124.36</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>112.71</v>
+        <v>118.76</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>11.47</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>CNQ_US_EQ</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>0.7</v>
+        <v>3.30858696</v>
       </c>
       <c r="D31" t="n">
-        <v>241.67</v>
+        <v>51.31</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>123.94</v>
+        <v>124.28</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>118.76</v>
+        <v>112.71</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>5.18</v>
+        <v>11.57</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5787,22 +5787,22 @@
         <v>2.50421091</v>
       </c>
       <c r="D32" t="n">
-        <v>67.27</v>
+        <v>67</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>123.42</v>
+        <v>122.83</v>
       </c>
       <c r="F32" s="2" t="n">
         <v>106.81</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>16.61</v>
+        <v>16.02</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5814,22 +5814,22 @@
         <v>0.28038062</v>
       </c>
       <c r="D33" t="n">
-        <v>580.1</v>
+        <v>580.05</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.16</v>
+        <v>119.06</v>
       </c>
       <c r="F33" s="2" t="n">
         <v>105.75</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.41</v>
+        <v>13.31</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5841,22 +5841,22 @@
         <v>0.7905852</v>
       </c>
       <c r="D34" t="n">
-        <v>205.6</v>
+        <v>205.28</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>119.09</v>
+        <v>118.81</v>
       </c>
       <c r="F34" s="2" t="n">
         <v>110.41</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>8.68</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5868,22 +5868,22 @@
         <v>0.62445608</v>
       </c>
       <c r="D35" t="n">
-        <v>258.79</v>
+        <v>258.59</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>118.4</v>
+        <v>118.21</v>
       </c>
       <c r="F35" s="2" t="n">
         <v>108.77</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>9.630000000000001</v>
+        <v>9.44</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5895,22 +5895,22 @@
         <v>0.59183053</v>
       </c>
       <c r="D36" t="n">
-        <v>271.57</v>
+        <v>271</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>117.75</v>
+        <v>117.41</v>
       </c>
       <c r="F36" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>17.9</v>
+        <v>17.56</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5922,22 +5922,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D37" t="n">
-        <v>58.37</v>
+        <v>58.44</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>115.77</v>
+        <v>115.82</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>8.130000000000001</v>
+        <v>8.18</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5949,76 +5949,76 @@
         <v>1.73400968</v>
       </c>
       <c r="D38" t="n">
-        <v>90.81999999999999</v>
+        <v>91.06</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>115.38</v>
+        <v>115.59</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>13.85</v>
+        <v>14.06</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>LTC_US_EQ</t>
+          <t>FIG_US_EQ</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>3.81488812</v>
+        <v>5.691347</v>
       </c>
       <c r="D39" t="n">
-        <v>40.5</v>
+        <v>27.11</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>113.19</v>
+        <v>112.95</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>108.23</v>
+        <v>452.96</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>4.96</v>
+        <v>-340.01</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FIG_US_EQ</t>
+          <t>LTC_US_EQ</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>5.691347</v>
+        <v>3.81488812</v>
       </c>
       <c r="D40" t="n">
-        <v>26.99</v>
+        <v>40.27</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>112.54</v>
+        <v>112.46</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>452.96</v>
+        <v>108.23</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>-340.42</v>
+        <v>4.23</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6030,22 +6030,22 @@
         <v>0.43583007</v>
       </c>
       <c r="D41" t="n">
-        <v>347.56</v>
+        <v>347.6</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>110.98</v>
+        <v>110.9</v>
       </c>
       <c r="F41" s="2" t="n">
         <v>104.04</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>6.94</v>
+        <v>6.86</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6060,19 +6060,19 @@
         <v>53.79</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>109.02</v>
+        <v>108.93</v>
       </c>
       <c r="F42" s="2" t="n">
         <v>112.48</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>-3.46</v>
+        <v>-3.55</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6084,22 +6084,22 @@
         <v>0.1285649</v>
       </c>
       <c r="D43" t="n">
-        <v>1155.21</v>
+        <v>1156.55</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>108.81</v>
+        <v>108.85</v>
       </c>
       <c r="F43" s="2" t="n">
         <v>98.89</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>9.92</v>
+        <v>9.960000000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6111,22 +6111,22 @@
         <v>1.35094641</v>
       </c>
       <c r="D44" t="n">
-        <v>109.52</v>
+        <v>109.1</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>108.4</v>
+        <v>107.9</v>
       </c>
       <c r="F44" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>11.72</v>
+        <v>11.22</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6138,22 +6138,22 @@
         <v>11.40066159</v>
       </c>
       <c r="D45" t="n">
-        <v>12.96</v>
+        <v>12.87</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>108.25</v>
+        <v>107.41</v>
       </c>
       <c r="F45" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>2.1</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6165,22 +6165,22 @@
         <v>0.51881442</v>
       </c>
       <c r="D46" t="n">
-        <v>282.88</v>
+        <v>281.91</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>107.52</v>
+        <v>107.07</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>11.58</v>
+        <v>11.13</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6192,22 +6192,22 @@
         <v>1.74206342</v>
       </c>
       <c r="D47" t="n">
-        <v>83.61</v>
+        <v>83.95</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>106.71</v>
+        <v>107.06</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>10.03</v>
+        <v>10.38</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6219,22 +6219,22 @@
         <v>0.37810738</v>
       </c>
       <c r="D48" t="n">
-        <v>383.62</v>
+        <v>384.24</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>106.27</v>
+        <v>106.36</v>
       </c>
       <c r="F48" s="2" t="n">
         <v>95.51000000000001</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>10.76</v>
+        <v>10.85</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6246,22 +6246,22 @@
         <v>13.30225117</v>
       </c>
       <c r="D49" t="n">
-        <v>10.89</v>
+        <v>10.92</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>106.13</v>
+        <v>106.34</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-0.83</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6273,22 +6273,22 @@
         <v>0.42255419</v>
       </c>
       <c r="D50" t="n">
-        <v>341.28</v>
+        <v>341</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>105.65</v>
+        <v>105.48</v>
       </c>
       <c r="F50" s="2" t="n">
         <v>101.39</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>4.26</v>
+        <v>4.09</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6300,22 +6300,22 @@
         <v>0.40867246</v>
       </c>
       <c r="D51" t="n">
-        <v>352.11</v>
+        <v>351.99</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>105.42</v>
+        <v>105.3</v>
       </c>
       <c r="F51" s="2" t="n">
         <v>92.83</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>12.59</v>
+        <v>12.47</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6327,22 +6327,22 @@
         <v>2.27580753</v>
       </c>
       <c r="D52" t="n">
-        <v>62.66</v>
+        <v>62.76</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>104.47</v>
+        <v>104.56</v>
       </c>
       <c r="F52" s="2" t="n">
         <v>106.15</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>-1.68</v>
+        <v>-1.59</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6354,22 +6354,22 @@
         <v>0.50675322</v>
       </c>
       <c r="D53" t="n">
-        <v>280.21</v>
+        <v>281.63</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>104.03</v>
+        <v>104.48</v>
       </c>
       <c r="F53" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>7.35</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6381,211 +6381,211 @@
         <v>0.90543241</v>
       </c>
       <c r="D54" t="n">
-        <v>156.75</v>
+        <v>157.61</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>103.98</v>
+        <v>104.47</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>92.27</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>11.71</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.80409618</v>
       </c>
       <c r="D55" t="n">
-        <v>205.52</v>
+        <v>175</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>103.13</v>
+        <v>103.01</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>88.44</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>13.67</v>
+        <v>14.57</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.68495686</v>
       </c>
       <c r="D56" t="n">
-        <v>229.28</v>
+        <v>205.34</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>102.83</v>
+        <v>102.96</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>88.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>14.74</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.61215748</v>
       </c>
       <c r="D57" t="n">
-        <v>174.51</v>
+        <v>229.26</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>102.81</v>
+        <v>102.74</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>88.44</v>
+        <v>88.09</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>14.37</v>
+        <v>14.65</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.97307689</v>
       </c>
       <c r="D58" t="n">
-        <v>87.68000000000001</v>
+        <v>143.45</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>102.14</v>
+        <v>102.19</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>89.66</v>
+        <v>111.44</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>12.48</v>
+        <v>-9.25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.59010207</v>
       </c>
       <c r="D59" t="n">
-        <v>143.05</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>101.98</v>
+        <v>101.93</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>111.44</v>
+        <v>89.66</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>-9.460000000000001</v>
+        <v>12.27</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>ADC_US_EQ</t>
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.85908491</v>
       </c>
       <c r="D60" t="n">
-        <v>1314.99</v>
+        <v>73.88</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>100.64</v>
+        <v>100.55</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>88.89</v>
+        <v>104.98</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>11.75</v>
+        <v>-4.43</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>ADC_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>1.85908491</v>
+        <v>0.10445851</v>
       </c>
       <c r="D61" t="n">
-        <v>73.84</v>
+        <v>1312.24</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>100.57</v>
+        <v>100.35</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>104.98</v>
+        <v>88.89</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>-4.41</v>
+        <v>11.46</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6597,22 +6597,22 @@
         <v>1.17949395</v>
       </c>
       <c r="D62" t="n">
-        <v>116.34</v>
+        <v>116.07</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>100.53</v>
+        <v>100.22</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>98.72</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1.81</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6624,22 +6624,22 @@
         <v>1.1533463</v>
       </c>
       <c r="D63" t="n">
-        <v>117.39</v>
+        <v>117.15</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>99.19</v>
+        <v>98.91</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>89.53</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>9.66</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6651,22 +6651,22 @@
         <v>0.5550481</v>
       </c>
       <c r="D64" t="n">
-        <v>242.78</v>
+        <v>243</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.73</v>
+        <v>98.73999999999999</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>7.55</v>
+        <v>7.56</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6678,22 +6678,22 @@
         <v>1.11796351</v>
       </c>
       <c r="D65" t="n">
-        <v>120.19</v>
+        <v>120.27</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>98.44</v>
+        <v>98.43000000000001</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>105.36</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-6.92</v>
+        <v>-6.93</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6705,22 +6705,22 @@
         <v>0.6214908</v>
       </c>
       <c r="D66" t="n">
-        <v>216.11</v>
+        <v>216.05</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>98.40000000000001</v>
+        <v>98.3</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>107.82</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-9.42</v>
+        <v>-9.52</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6732,22 +6732,22 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D67" t="n">
-        <v>144.93</v>
+        <v>144.88</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>97.3</v>
+        <v>97.19</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-2.55</v>
+        <v>-2.66</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6759,22 +6759,22 @@
         <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>113.54</v>
+        <v>113.55</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>96.95999999999999</v>
+        <v>96.89</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6786,22 +6786,22 @@
         <v>0.93456659</v>
       </c>
       <c r="D69" t="n">
-        <v>131.52</v>
+        <v>131.73</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>90.05</v>
+        <v>90.12</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>88.38</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6813,22 +6813,22 @@
         <v>1.17308322</v>
       </c>
       <c r="D70" t="n">
-        <v>102.82</v>
+        <v>103.66</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>88.37</v>
+        <v>89.02</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>110.45</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-22.08</v>
+        <v>-21.43</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6840,22 +6840,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D71" t="n">
-        <v>64.64</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>87.47</v>
+        <v>87.34</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-23.06</v>
+        <v>-23.19</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6867,22 +6867,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D72" t="n">
-        <v>111.74</v>
+        <v>110.5</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>51.76</v>
+        <v>51.14</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>3.89</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6894,16 +6894,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D73" t="n">
-        <v>270.54</v>
+        <v>270.85</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>48.04</v>
+        <v>48.05</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-4.07</v>
+        <v>-4.06</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43186.83</v>
+        <v>43186.96</v>
       </c>
     </row>
     <row r="5">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1292.74</v>
+        <v>1292.87</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-22 18:55:40</t>
+          <t>2026-08-23 18:55:10</t>
         </is>
       </c>
     </row>
@@ -4869,16 +4869,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-22 18:55:40</t>
+          <t>2026-08-23 18:55:10</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43186.83</v>
+        <v>43186.96</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>41894.09</v>
@@ -4896,7 +4896,7 @@
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1316.88</v>
+        <v>1317.01</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4992,7 +4992,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5019,7 +5019,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5046,7 +5046,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5073,7 +5073,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5100,7 +5100,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -5127,7 +5127,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -5154,7 +5154,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5181,7 +5181,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5208,7 +5208,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5235,7 +5235,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5262,7 +5262,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5289,7 +5289,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5316,7 +5316,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5343,7 +5343,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5370,7 +5370,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5397,7 +5397,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5424,7 +5424,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5451,7 +5451,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5478,7 +5478,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5505,7 +5505,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5532,7 +5532,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5559,7 +5559,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5586,7 +5586,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5613,7 +5613,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5640,7 +5640,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5667,7 +5667,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -5694,7 +5694,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -5721,7 +5721,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5748,7 +5748,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5775,7 +5775,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -5802,7 +5802,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -5829,7 +5829,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -5856,7 +5856,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -5883,7 +5883,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -5910,7 +5910,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5937,7 +5937,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5964,7 +5964,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5991,7 +5991,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6018,7 +6018,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6045,7 +6045,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -6072,7 +6072,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -6099,7 +6099,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -6126,7 +6126,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -6153,7 +6153,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6180,7 +6180,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6207,7 +6207,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -6234,7 +6234,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6261,7 +6261,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6288,7 +6288,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6315,7 +6315,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6342,7 +6342,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6369,7 +6369,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6396,7 +6396,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6423,7 +6423,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6450,7 +6450,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6477,7 +6477,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6504,7 +6504,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -6531,7 +6531,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6558,7 +6558,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -6585,7 +6585,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -6612,7 +6612,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -6639,7 +6639,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6666,7 +6666,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -6693,7 +6693,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -6720,7 +6720,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6747,7 +6747,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6774,7 +6774,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -6801,7 +6801,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -6828,7 +6828,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6855,7 +6855,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6882,7 +6882,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>43186.96</v>
+        <v>42898.68</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>41894.09</v>
+        <v>41655.67</v>
       </c>
     </row>
     <row r="6">
@@ -501,7 +501,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>36639.92</v>
+        <v>36640.46</v>
       </c>
     </row>
     <row r="7">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5254.17</v>
+        <v>5015.21</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1434001493453043</v>
+        <v>0.1368762837584463</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1292.87</v>
+        <v>1243.01</v>
       </c>
     </row>
     <row r="11">
@@ -551,7 +551,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>24.14</v>
+        <v>24.68</v>
       </c>
     </row>
     <row r="12">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-23 18:55:10</t>
+          <t>2026-08-24 19:09:11</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>108.88</v>
+        <v>108.5</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6968.32</v>
+        <v>6944</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1664277124763703</v>
+        <v>0.1668002221440747</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>922.55</v>
+        <v>898.23</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.152594293200039</v>
+        <v>0.1485716459607296</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>14.364</v>
+        <v>13.928</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4165.56</v>
+        <v>4039.12</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.09948805766426758</v>
+        <v>0.0970227697676519</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>734.85</v>
+        <v>608.41</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.2141976442194181</v>
+        <v>0.1773422994074113</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1518.4</v>
+        <v>1529</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2678.35</v>
+        <v>2697.05</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06396831140233031</v>
+        <v>0.06478521588906633</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1482.39</v>
+        <v>1501.09</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.239497976520954</v>
+        <v>1.25513395096826</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>111.2</v>
+        <v>110.63</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2019.33</v>
+        <v>2013.69</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04822862219802029</v>
+        <v>0.04837038296792939</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>372.76</v>
+        <v>367.12</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2263857594879052</v>
+        <v>0.2229604571928312</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-29.31</v>
+        <v>-25.51</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>1.15856288</v>
@@ -940,25 +940,25 @@
         <v>22.51</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>23.81</v>
+        <v>23.25</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>2004.47</v>
+        <v>1961.92</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04787371372547614</v>
+        <v>0.04712682774033741</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>78.66</v>
+        <v>36.11</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.04084515087158131</v>
+        <v>0.01875055171590136</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-30.78</v>
+        <v>-26.33</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -972,17 +972,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US0079031078</t>
+          <t>US67066G1040</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -991,55 +991,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>509.97</v>
+        <v>150.09436705</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>472.31</v>
+        <v>209.3</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1728.78</v>
+        <v>1678.01</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04128927787112236</v>
+        <v>0.04030709112326882</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>-169.77</v>
+        <v>425.33</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>-0.08942087382476101</v>
+        <v>0.3395360347415142</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-31.92</v>
+        <v>-49.34</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US67066G1040</t>
+          <t>US0079031078</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,38 +1048,38 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>10.9260596</v>
+        <v>5</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>150.09436705</v>
+        <v>509.97</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>215.38</v>
+        <v>457.32</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1252.68</v>
+        <v>1898.55</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1722.71</v>
+        <v>1677.84</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04114430516396604</v>
+        <v>0.04030300759248476</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>470.03</v>
+        <v>-220.71</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.3752195293291183</v>
+        <v>-0.1162518764320139</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-52.15</v>
+        <v>-27.54</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>236.1</v>
+        <v>230.86</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1659.24</v>
+        <v>1626.23</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03962842086030673</v>
+        <v>0.03906329568798366</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-336.82</v>
+        <v>-369.83</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1687424225724678</v>
+        <v>-0.1852800016031582</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-38.48</v>
+        <v>-33.88</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>153.75</v>
+        <v>151.57</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1416.17</v>
+        <v>1399.37</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03382306403518514</v>
+        <v>0.03361394396050601</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-455.67</v>
+        <v>-472.47</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2434342678861441</v>
+        <v>-0.2524093939652962</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-107.73</v>
+        <v>-103.58</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.16</v>
+        <v>119.14</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1387.16</v>
+        <v>1390.18</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03313020435897344</v>
+        <v>0.03339319309047375</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>43.37</v>
+        <v>46.39</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.03227438811123762</v>
+        <v>0.03452176307309922</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-27.87</v>
+        <v>-24.79</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>42.5</v>
+        <v>43.2</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1358.86</v>
+        <v>1382.07</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.03245430195163834</v>
+        <v>0.0331983846513049</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>130.52</v>
+        <v>153.73</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.106257225198235</v>
+        <v>0.1251526450331341</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-43.73</v>
+        <v>-43.02</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>440.8</v>
+        <v>445.4</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1214.81</v>
+        <v>1227.98</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02901388704787084</v>
+        <v>0.02949702430709689</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>300.32</v>
+        <v>313.49</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.328401622762414</v>
+        <v>0.3428030924340343</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-3.09</v>
+        <v>-2.72</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>111.25</v>
+        <v>111.6</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1128.48</v>
+        <v>1132.03</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02695202645333945</v>
+        <v>0.02719223149103641</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>521.29</v>
+        <v>524.84</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8585286318944645</v>
+        <v>0.8643752367463232</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>683.8</v>
+        <v>688.8</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1094.08</v>
+        <v>1102.08</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02613043483452929</v>
+        <v>0.02647280944996281</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>340.62</v>
+        <v>348.62</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.4520744299631035</v>
+        <v>0.462692113715393</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>333.48</v>
+        <v>325.4</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1069.62</v>
+        <v>1046.15</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02554624497999161</v>
+        <v>0.02512932782200802</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>427.63</v>
+        <v>404.16</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6661007180797208</v>
+        <v>0.6295425162385707</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-39.4</v>
+        <v>-37.99</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1567,25 +1567,25 @@
         <v>207.87234231</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>309.69</v>
+        <v>311.45</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>693.71</v>
+        <v>699.29</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.01656820703153455</v>
+        <v>0.0167974837763724</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>202.66</v>
+        <v>208.24</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4127074635984115</v>
+        <v>0.4240708685469912</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-25.41</v>
+        <v>-24.32</v>
       </c>
       <c r="N17" s="4" t="n">
         <v>0.46065664</v>
@@ -1624,25 +1624,25 @@
         <v>57.84</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46.81</v>
+        <v>46.97</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>685.35</v>
+        <v>689.3099999999999</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.01636854116138185</v>
+        <v>0.01655775649857893</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>-182.23</v>
+        <v>-178.27</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>-0.210044030521681</v>
+        <v>-0.2054796099495148</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>-20.74</v>
+        <v>-18.75</v>
       </c>
       <c r="N18" s="4" t="n">
         <v>0</v>
@@ -1681,22 +1681,22 @@
         <v>1019.5</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>673.4</v>
+        <v>669.5</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01608313360775449</v>
+        <v>0.01608190505838969</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>10.72</v>
+        <v>6.82</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.01617673688658176</v>
+        <v>0.01029154342970967</v>
       </c>
       <c r="M19" s="2" t="n">
         <v>0</v>
@@ -1738,25 +1738,25 @@
         <v>369.46288902</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>483.61</v>
+        <v>487.75</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>660.27</v>
+        <v>667.49</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.01576954355092375</v>
+        <v>0.01603362331206054</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>125.89</v>
+        <v>133.11</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.235581421460384</v>
+        <v>0.2490924061529249</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>-29.96</v>
+        <v>-28.77</v>
       </c>
       <c r="N20" s="4" t="n">
         <v>0.3650317</v>
@@ -1795,25 +1795,25 @@
         <v>77.20222067</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>97.37</v>
+        <v>98.47</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>655.49</v>
+        <v>664.45</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.01565538052947281</v>
+        <v>0.01596060017333387</v>
       </c>
       <c r="K21" s="2" t="n">
-        <v>106.31</v>
+        <v>115.27</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.1935795185549365</v>
+        <v>0.2098947521759714</v>
       </c>
       <c r="M21" s="2" t="n">
-        <v>-29.46</v>
+        <v>-28.24</v>
       </c>
       <c r="N21" s="4" t="n">
         <v>0</v>
@@ -1852,25 +1852,25 @@
         <v>265.62170741</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>336.05</v>
+        <v>337.68</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>573.21</v>
+        <v>577.34</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.01369024801796993</v>
+        <v>0.01386815095804437</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>83.94</v>
+        <v>88.06999999999999</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.1715617143908272</v>
+        <v>0.1800028614057678</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>-36.19</v>
+        <v>-35.13</v>
       </c>
       <c r="N22" s="4" t="n">
         <v>0</v>
@@ -1909,22 +1909,22 @@
         <v>3.8455</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>3.798</v>
+        <v>3.8</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>531.72</v>
+        <v>532</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.01269932254516664</v>
+        <v>0.01277904927716701</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>-6.65</v>
+        <v>-6.37</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>-0.01235209985697569</v>
+        <v>-0.01183201144194513</v>
       </c>
       <c r="M23" s="2" t="n">
         <v>0</v>
@@ -1966,25 +1966,25 @@
         <v>269.43</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>345.1</v>
+        <v>348.93</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>505.26</v>
+        <v>512.0700000000001</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.01206736573604697</v>
+        <v>0.01230031534465961</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>97.34</v>
+        <v>104.15</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.2386252206314964</v>
+        <v>0.2553196705236321</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>-13.45</v>
+        <v>-12.52</v>
       </c>
       <c r="N24" s="4" t="n">
         <v>0</v>
@@ -2023,25 +2023,25 @@
         <v>236.87151261</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>235.8</v>
+        <v>232.71</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>191.64</v>
+        <v>189.58</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.004577029588045841</v>
+        <v>0.004553857447303237</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>-4.88</v>
+        <v>-6.94</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>-0.02483207815998371</v>
+        <v>-0.03531447180948504</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>-4.01</v>
+        <v>-3.55</v>
       </c>
       <c r="N25" s="4" t="n">
         <v>1.11022215</v>
@@ -2080,25 +2080,25 @@
         <v>91.20399179</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>116.55</v>
+        <v>116.79</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>132.93</v>
+        <v>133.52</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.00317483063629166</v>
+        <v>0.003207253119337104</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>27.65</v>
+        <v>28.24</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.2626329787234042</v>
+        <v>0.2682370820668693</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>-1.26</v>
+        <v>-1.01</v>
       </c>
       <c r="N26" s="4" t="n">
         <v>1.55804584</v>
@@ -2137,25 +2137,25 @@
         <v>212.76482689</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>280.81</v>
+        <v>282.48</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>130.38</v>
+        <v>131.46</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.003113927769199628</v>
+        <v>0.003157770334542059</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>30.53</v>
+        <v>31.61</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.3057586379569354</v>
+        <v>0.3165748622934402</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>-1.06</v>
+        <v>-0.83</v>
       </c>
       <c r="N27" s="4" t="n">
         <v>0.63422137</v>
@@ -2169,17 +2169,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF Industries</t>
+          <t>Roper Technologies</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US1252691001</t>
+          <t>US7766961061</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2188,34 +2188,34 @@
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.42010405</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>121.66614911</v>
+        <v>350.55601106</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>132</v>
+        <v>414.15</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>119.73</v>
+        <v>109.16</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>128.09</v>
+        <v>127.67</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.003059234606203255</v>
+        <v>0.003066731618826903</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>18.51</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.06982377014950304</v>
+        <v>0.169567607182118</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>-1.67</v>
+        <v>-1.09</v>
       </c>
       <c r="N28" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.42010405</v>
       </c>
       <c r="O28" t="inlineStr">
         <is>
@@ -2226,17 +2226,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Roper Technologies</t>
+          <t>CF Industries</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US7766961061</t>
+          <t>US1252691001</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2245,34 +2245,34 @@
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.32559468</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>350.55601106</v>
+        <v>121.66614911</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>414.88</v>
+        <v>128.87</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>109.16</v>
+        <v>119.73</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>127.59</v>
+        <v>125.35</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.003047292867557759</v>
+        <v>0.003011003434009181</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>18.43</v>
+        <v>5.62</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.1688347379992671</v>
+        <v>0.04693894596174726</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>-1.35</v>
+        <v>-1.39</v>
       </c>
       <c r="N29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.32559468</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2283,17 +2283,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Take-Two Interactive Software</t>
+          <t>Bristol-Myers Squibb</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>US8740541094</t>
+          <t>US1101221083</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2302,38 +2302,38 @@
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>0.7</v>
+        <v>2.50421091</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>225.62857143</v>
+        <v>57.56703616</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>242.69</v>
+        <v>67.22</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>118.76</v>
+        <v>106.81</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>124.36</v>
+        <v>123.52</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.002970149235907852</v>
+        <v>0.002967045426157272</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>5.6</v>
+        <v>16.71</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.0471539238800943</v>
+        <v>0.1564460256530288</v>
       </c>
       <c r="M30" s="2" t="n">
-        <v>-3.14</v>
+        <v>-1.03</v>
       </c>
       <c r="N30" s="4" t="n">
-        <v>0</v>
+        <v>2.50421091</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>2025-05-13</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
@@ -2365,25 +2365,25 @@
         <v>45.93199509</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>51.31</v>
+        <v>50.64</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>124.28</v>
+        <v>122.94</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.002968238557724573</v>
+        <v>0.002953113379952842</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>11.57</v>
+        <v>10.23</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.1026528258362168</v>
+        <v>0.09076390737290392</v>
       </c>
       <c r="M31" s="2" t="n">
-        <v>-1.46</v>
+        <v>-1.2</v>
       </c>
       <c r="N31" s="4" t="n">
         <v>3.30858696</v>
@@ -2397,17 +2397,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Bristol-Myers Squibb</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US1101221083</t>
+          <t>US57636Q1040</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2416,34 +2416,34 @@
         </is>
       </c>
       <c r="E32" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.28038062</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>57.56703616</v>
+        <v>509.16500577</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>67</v>
+        <v>597.52</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>106.81</v>
+        <v>105.75</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>122.83</v>
+        <v>122.93</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.002933607515652633</v>
+        <v>0.002952873172259663</v>
       </c>
       <c r="K32" s="2" t="n">
-        <v>16.02</v>
+        <v>17.18</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.1499859563711263</v>
+        <v>0.1624586288416076</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>-1.27</v>
+        <v>-1</v>
       </c>
       <c r="N32" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.28038062</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
@@ -2454,17 +2454,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Take-Two Interactive Software</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US57636Q1040</t>
+          <t>US8740541094</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2473,55 +2473,55 @@
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.7</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>509.16500577</v>
+        <v>225.62857143</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>580.05</v>
+        <v>234.95</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>105.75</v>
+        <v>118.76</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>119.06</v>
+        <v>120.68</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.002843566806265591</v>
+        <v>0.002898826441294201</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>13.31</v>
+        <v>1.92</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.1258628841607565</v>
+        <v>0.01616705961603233</v>
       </c>
       <c r="M33" s="2" t="n">
-        <v>-1.24</v>
+        <v>-2.87</v>
       </c>
       <c r="N33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>2026-04-30</t>
+          <t>2025-05-13</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Chevron</t>
+          <t>Royal Gold</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US1667641005</t>
+          <t>US7802871084</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2530,34 +2530,34 @@
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.62445608</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>188.32884805</v>
+        <v>235.02053179</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>205.28</v>
+        <v>261.69</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>110.41</v>
+        <v>108.77</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>118.81</v>
+        <v>119.91</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.002837595936942843</v>
+        <v>0.002880330448919353</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>8.4</v>
+        <v>11.14</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.07608006521148447</v>
+        <v>0.1024179461248506</v>
       </c>
       <c r="M34" s="2" t="n">
-        <v>-1.41</v>
+        <v>-1.08</v>
       </c>
       <c r="N34" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.62445608</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
@@ -2568,17 +2568,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Royal Gold</t>
+          <t>Johnson &amp; Johnson</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US7802871084</t>
+          <t>US4781601046</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2587,34 +2587,34 @@
         </is>
       </c>
       <c r="E35" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.59183053</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>235.02053179</v>
+        <v>228.00445932</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>258.59</v>
+        <v>272.91</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>108.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>118.21</v>
+        <v>118.52</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.002823265850568247</v>
+        <v>0.002846941579567357</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>9.44</v>
+        <v>18.67</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.08678863657258436</v>
+        <v>0.1869804707060591</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>-1.33</v>
+        <v>-0.83</v>
       </c>
       <c r="N35" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.59183053</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -2625,17 +2625,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Johnson &amp; Johnson</t>
+          <t>Chevron</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US4781601046</t>
+          <t>US1667641005</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2644,34 +2644,34 @@
         </is>
       </c>
       <c r="E36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>228.00445932</v>
+        <v>188.32884805</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>271</v>
+        <v>203.46</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>110.41</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>117.41</v>
+        <v>118.03</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.002804159068735453</v>
+        <v>0.002835171402601545</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>17.56</v>
+        <v>7.62</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.1758637956935403</v>
+        <v>0.06901548772756091</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>-1.07</v>
+        <v>-1.16</v>
       </c>
       <c r="N36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
@@ -2707,25 +2707,25 @@
         <v>53.65641702</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>58.44</v>
+        <v>58.91</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>115.82</v>
+        <v>117.02</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002766184339842775</v>
+        <v>0.002810910425590383</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>8.18</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.07599405425492382</v>
+        <v>0.08714232627276106</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>-1.3</v>
+        <v>-1.06</v>
       </c>
       <c r="N37" s="4" t="n">
         <v>2.70722512</v>
@@ -2764,25 +2764,25 @@
         <v>79.10567143</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>91.06</v>
+        <v>91.56</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>115.59</v>
+        <v>116.5</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.002760691140065847</v>
+        <v>0.002798419625545031</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>14.06</v>
+        <v>14.97</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.1384812370727864</v>
+        <v>0.1474441051905841</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>-1.11</v>
+        <v>-0.88</v>
       </c>
       <c r="N38" s="4" t="n">
         <v>1.73400968</v>
@@ -2821,25 +2821,25 @@
         <v>105.04894536</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>27.11</v>
+        <v>27.5</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>112.95</v>
+        <v>114.84</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.002697638760017626</v>
+        <v>0.00275854514847718</v>
       </c>
       <c r="K39" s="2" t="n">
-        <v>-340.01</v>
+        <v>-338.12</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>-0.7506402331331685</v>
+        <v>-0.7464676792652774</v>
       </c>
       <c r="M39" s="2" t="n">
-        <v>-15.29</v>
+        <v>-14.26</v>
       </c>
       <c r="N39" s="4" t="n">
         <v>0</v>
@@ -2878,25 +2878,25 @@
         <v>38.28159448</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>40.27</v>
+        <v>40.35</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>112.46</v>
+        <v>112.95</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.002685935856145039</v>
+        <v>0.002713145894466191</v>
       </c>
       <c r="K40" s="2" t="n">
-        <v>4.23</v>
+        <v>4.72</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.03908343342880902</v>
+        <v>0.04361082879053867</v>
       </c>
       <c r="M40" s="2" t="n">
-        <v>-1.32</v>
+        <v>-1.07</v>
       </c>
       <c r="N40" s="4" t="n">
         <v>3.81488812</v>
@@ -2935,7 +2935,7 @@
         <v>322.35040597</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>347.6</v>
+        <v>346.79</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>104.04</v>
@@ -2944,7 +2944,7 @@
         <v>110.9</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.002648677631571091</v>
+        <v>0.002663903317364326</v>
       </c>
       <c r="K41" s="2" t="n">
         <v>6.86</v>
@@ -2953,7 +2953,7 @@
         <v>0.0659361783929258</v>
       </c>
       <c r="M41" s="2" t="n">
-        <v>-1.2</v>
+        <v>-0.96</v>
       </c>
       <c r="N41" s="4" t="n">
         <v>0.43583007</v>
@@ -2967,17 +2967,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>BlackRock</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>AN8068571086</t>
+          <t>US09290D1019</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2986,34 +2986,34 @@
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.1285649</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>54.82621761</v>
+        <v>1039.47500445</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>53.79</v>
+        <v>1168.5</v>
       </c>
       <c r="H42" s="2" t="n">
-        <v>112.48</v>
+        <v>98.89</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>108.93</v>
+        <v>110.23</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.002601627181307835</v>
+        <v>0.002647809401921277</v>
       </c>
       <c r="K42" s="2" t="n">
-        <v>-3.55</v>
+        <v>11.34</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>-0.03156116642958748</v>
+        <v>0.1146728688441703</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>-1.45</v>
+        <v>-0.83</v>
       </c>
       <c r="N42" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.1285649</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3024,17 +3024,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BlackRock</t>
+          <t>Kimberly-Clark</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US09290D1019</t>
+          <t>US4943681035</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3043,34 +3043,34 @@
         </is>
       </c>
       <c r="E43" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.35094641</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>1039.47500445</v>
+        <v>96.717382</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>1156.55</v>
+        <v>111.11</v>
       </c>
       <c r="H43" s="2" t="n">
-        <v>98.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>108.85</v>
+        <v>110.14</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.002599716503124556</v>
+        <v>0.002645647532682659</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>13.46</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.1007179694610173</v>
+        <v>0.1392221762515515</v>
       </c>
       <c r="M43" s="2" t="n">
-        <v>-1.06</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N43" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.35094641</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3081,17 +3081,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Kimberly-Clark</t>
+          <t>Gladstone Commercial</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>US4943681035</t>
+          <t>US3765361080</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3100,34 +3100,34 @@
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>11.40066159</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>96.717382</v>
+        <v>12.56856884</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>109.1</v>
+        <v>13.14</v>
       </c>
       <c r="H44" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>107.9</v>
+        <v>109.92</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.002577027199698113</v>
+        <v>0.002640362963432702</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>11.22</v>
+        <v>3.77</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.1160529582126603</v>
+        <v>0.03551577955723034</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>-1.03</v>
+        <v>-1.01</v>
       </c>
       <c r="N44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>11.40066159</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3138,17 +3138,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Gladstone Commercial</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>US3765361080</t>
+          <t>AN8068571086</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3157,34 +3157,34 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>11.40066159</v>
+        <v>2.76637723</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>12.56856884</v>
+        <v>54.82621761</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>12.87</v>
+        <v>53.86</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>106.15</v>
+        <v>112.48</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>107.41</v>
+        <v>109.33</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.002565324295825526</v>
+        <v>0.002626190709535093</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>1.26</v>
+        <v>-3.15</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.01186999528968441</v>
+        <v>-0.0280049786628734</v>
       </c>
       <c r="M45" s="2" t="n">
-        <v>-1.26</v>
+        <v>-1.19</v>
       </c>
       <c r="N45" s="4" t="n">
-        <v>11.40066159</v>
+        <v>2.76637723</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3220,25 +3220,25 @@
         <v>249.91595261</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>281.91</v>
+        <v>283.01</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>107.07</v>
+        <v>107.74</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002557203913546588</v>
+        <v>0.002587997686319499</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>11.13</v>
+        <v>11.8</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.1160100062539087</v>
+        <v>0.122993537627684</v>
       </c>
       <c r="M46" s="2" t="n">
-        <v>-1.02</v>
+        <v>-0.8</v>
       </c>
       <c r="N46" s="4" t="n">
         <v>0.51881442</v>
@@ -3277,25 +3277,25 @@
         <v>74.99726962</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>83.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>107.06</v>
+        <v>107.64</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.002556965078773679</v>
+        <v>0.002585595609387701</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>10.38</v>
+        <v>10.96</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.1073645014480761</v>
+        <v>0.1133636739760033</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>-1.04</v>
+        <v>-0.82</v>
       </c>
       <c r="N47" s="4" t="n">
         <v>1.74206342</v>
@@ -3309,17 +3309,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>General Dynamics</t>
+          <t>Chubb</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>US3695501086</t>
+          <t>CH0044328745</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3328,34 +3328,34 @@
         </is>
       </c>
       <c r="E48" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.42255419</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>341.38450299</v>
+        <v>324.07677699</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>384.24</v>
+        <v>345.51</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>106.36</v>
+        <v>107.13</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.002540246644669984</v>
+        <v>0.00257334501703553</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>10.85</v>
+        <v>5.74</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.1136006700869019</v>
+        <v>0.05661307821284151</v>
       </c>
       <c r="M48" s="2" t="n">
-        <v>-1.01</v>
+        <v>-0.91</v>
       </c>
       <c r="N48" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.42255419</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -3391,25 +3391,25 @@
         <v>10.85229847</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>10.92</v>
+        <v>10.97</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>106.34</v>
+        <v>107.08</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.002539768975124164</v>
+        <v>0.002572143978569631</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>-0.62</v>
+        <v>0.12</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>-0.005796559461480928</v>
+        <v>0.001121914734480179</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>-1.28</v>
+        <v>-1.03</v>
       </c>
       <c r="N49" s="4" t="n">
         <v>13.30225117</v>
@@ -3423,17 +3423,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Chubb</t>
+          <t>JPMorgan Chase &amp; Co</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CH0044328745</t>
+          <t>US46625H1005</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -3442,34 +3442,34 @@
         </is>
       </c>
       <c r="E50" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.40867246</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>324.07677699</v>
+        <v>306.99401668</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>341</v>
+        <v>356.22</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>101.39</v>
+        <v>92.83</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>105.48</v>
+        <v>106.82</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.00251922918465391</v>
+        <v>0.002565898578546955</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>4.09</v>
+        <v>13.99</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.04033928395305257</v>
+        <v>0.1507055908650221</v>
       </c>
       <c r="M50" s="2" t="n">
-        <v>-1.14</v>
+        <v>-0.77</v>
       </c>
       <c r="N50" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.40867246</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -3480,17 +3480,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPMorgan Chase &amp; Co</t>
+          <t>Ecolab</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>US46625H1005</t>
+          <t>US2788651006</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3499,34 +3499,34 @@
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.50675322</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>306.99401668</v>
+        <v>257.81779936</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>351.99</v>
+        <v>286.54</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>92.83</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>105.3</v>
+        <v>106.55</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.002514930158741531</v>
+        <v>0.002559412970831099</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>12.47</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.1343315738446623</v>
+        <v>0.1020893669838643</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>-0.99</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N51" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.50675322</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
@@ -3537,17 +3537,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Realty Income</t>
+          <t>General Dynamics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>US7561091049</t>
+          <t>US3695501086</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3556,34 +3556,34 @@
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.37810738</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>62.95787236</v>
+        <v>341.38450299</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>62.76</v>
+        <v>381.9</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>106.15</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>104.56</v>
+        <v>105.96</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.002497256385546197</v>
+        <v>0.002545240716933489</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>-1.59</v>
+        <v>10.45</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>-0.01497880357983985</v>
+        <v>0.1094126269500576</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>-1.26</v>
+        <v>-0.79</v>
       </c>
       <c r="N52" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.37810738</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -3594,17 +3594,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Ecolab</t>
+          <t>Realty Income</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>US2788651006</t>
+          <t>US7561091049</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3613,34 +3613,34 @@
         </is>
       </c>
       <c r="E53" s="4" t="n">
-        <v>0.50675322</v>
+        <v>2.27580753</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>257.81779936</v>
+        <v>62.95787236</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>281.63</v>
+        <v>62.94</v>
       </c>
       <c r="H53" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>104.48</v>
+        <v>105.11</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002495345707362918</v>
+        <v>0.002524823063013204</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>7.8</v>
+        <v>-1.04</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.08067852709971038</v>
+        <v>-0.009797456429580782</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>-1.03</v>
+        <v>-1.01</v>
       </c>
       <c r="N53" s="4" t="n">
-        <v>0.50675322</v>
+        <v>2.27580753</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -3676,25 +3676,25 @@
         <v>137.713206</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>157.61</v>
+        <v>157.33</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>92.27</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>104.47</v>
+        <v>104.53</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.002495106872590008</v>
+        <v>0.002510891016808773</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>12.2</v>
+        <v>12.26</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.1322206567681803</v>
+        <v>0.1328709222932697</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>-0.99</v>
+        <v>-0.77</v>
       </c>
       <c r="N54" s="4" t="n">
         <v>0.90543241</v>
@@ -3708,17 +3708,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bank of Montreal</t>
+          <t>Cardinal Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CA0636711016</t>
+          <t>US14149Y1082</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -3727,34 +3727,34 @@
         </is>
       </c>
       <c r="E55" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.61215748</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>148.63893521</v>
+        <v>194.45976548</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>175</v>
+        <v>230.58</v>
       </c>
       <c r="H55" s="2" t="n">
-        <v>88.44</v>
+        <v>88.09</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>103.01</v>
+        <v>103.57</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.002460236995745158</v>
+        <v>0.00248783107826351</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>14.57</v>
+        <v>15.48</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.1647444595205789</v>
+        <v>0.175729367692133</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>-0.95</v>
+        <v>-0.74</v>
       </c>
       <c r="N55" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.61215748</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
@@ -3765,17 +3765,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Royal Bank of Canada</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>CA7800871021</t>
+          <t>US7134481081</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -3784,34 +3784,34 @@
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.97307689</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>176.50746647</v>
+        <v>154.44822659</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>205.34</v>
+        <v>144.63</v>
       </c>
       <c r="H56" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>102.96</v>
+        <v>103.27</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.002459042821880609</v>
+        <v>0.002480624847468115</v>
       </c>
       <c r="K56" s="2" t="n">
-        <v>13.5</v>
+        <v>-8.17</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.1509054325955735</v>
+        <v>-0.0733129935391242</v>
       </c>
       <c r="M56" s="2" t="n">
-        <v>-0.96</v>
+        <v>-1.16</v>
       </c>
       <c r="N56" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.97307689</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
@@ -3822,17 +3822,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cardinal Health</t>
+          <t>Royal Bank of Canada</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>US14149Y1082</t>
+          <t>CA7800871021</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -3841,34 +3841,34 @@
         </is>
       </c>
       <c r="E57" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.68495686</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>194.45976548</v>
+        <v>176.50746647</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>229.26</v>
+        <v>204.09</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>88.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>102.74</v>
+        <v>102.58</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.00245378845687659</v>
+        <v>0.002464050516638706</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>14.65</v>
+        <v>13.12</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.1663071858326711</v>
+        <v>0.1466577241225129</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>-0.95</v>
+        <v>-0.74</v>
       </c>
       <c r="N57" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.68495686</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
@@ -3879,17 +3879,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Aflac</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>US7134481081</t>
+          <t>US0010551028</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3898,34 +3898,34 @@
         </is>
       </c>
       <c r="E58" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.17949395</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>154.44822659</v>
+        <v>113.12478542</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>143.45</v>
+        <v>118</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>111.44</v>
+        <v>98.72</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>102.19</v>
+        <v>102.13</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.002440652544366544</v>
+        <v>0.002453241170445614</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>-9.25</v>
+        <v>3.41</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>-0.08300430725053841</v>
+        <v>0.0345421393841167</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>-1.42</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="N58" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.17949395</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -3936,17 +3936,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Bank of Nova Scotia</t>
+          <t>Bank of Montreal</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CA0641491075</t>
+          <t>CA0636711016</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3955,34 +3955,34 @@
         </is>
       </c>
       <c r="E59" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.80409618</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>76.19636644000001</v>
+        <v>148.63893521</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>87.56999999999999</v>
+        <v>172.21</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>89.66</v>
+        <v>88.44</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>101.93</v>
+        <v>101.61</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.002434442840270886</v>
+        <v>0.002440750370400263</v>
       </c>
       <c r="K59" s="2" t="n">
-        <v>12.27</v>
+        <v>13.17</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.1368503234441222</v>
+        <v>0.1489145183175034</v>
       </c>
       <c r="M59" s="2" t="n">
-        <v>-0.97</v>
+        <v>-0.74</v>
       </c>
       <c r="N59" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.80409618</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -4018,25 +4018,25 @@
         <v>76.24181082</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>73.88</v>
+        <v>74.27</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>100.55</v>
+        <v>101.32</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.002401483641609316</v>
+        <v>0.002433784347298048</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>-4.43</v>
+        <v>-3.66</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>-0.04219851400266717</v>
+        <v>-0.03486378357782435</v>
       </c>
       <c r="M60" s="2" t="n">
-        <v>-1.22</v>
+        <v>-0.97</v>
       </c>
       <c r="N60" s="4" t="n">
         <v>1.85908491</v>
@@ -4050,17 +4050,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>WW Grainger</t>
+          <t>Bank of Nova Scotia</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US3848021040</t>
+          <t>CA0641491075</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4069,34 +4069,34 @@
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.59010207</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>1150.02597682</v>
+        <v>76.19636644000001</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>1312.24</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="H61" s="2" t="n">
-        <v>88.89</v>
+        <v>89.66</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>100.35</v>
+        <v>101.3</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.002396706946151118</v>
+        <v>0.002433303931911688</v>
       </c>
       <c r="K61" s="2" t="n">
-        <v>11.46</v>
+        <v>11.64</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.1289233884576443</v>
+        <v>0.1298237787196074</v>
       </c>
       <c r="M61" s="2" t="n">
-        <v>-0.9399999999999999</v>
+        <v>-0.76</v>
       </c>
       <c r="N61" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.59010207</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
@@ -4107,17 +4107,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Aflac</t>
+          <t>WW Grainger</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US0010551028</t>
+          <t>US3848021040</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4126,34 +4126,34 @@
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.10445851</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>113.12478542</v>
+        <v>1150.02597682</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>116.07</v>
+        <v>1318.39</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>98.72</v>
+        <v>88.89</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>100.22</v>
+        <v>101.05</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.002393602094103288</v>
+        <v>0.002427298739582192</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>1.5</v>
+        <v>12.16</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.01519448946515397</v>
+        <v>0.1367982900213747</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>-1.04</v>
+        <v>-0.74</v>
       </c>
       <c r="N62" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.10445851</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
@@ -4164,17 +4164,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Toronto-Dominion Bank</t>
+          <t>Duke Energy</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CA8911605092</t>
+          <t>US26441C2044</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -4183,34 +4183,34 @@
         </is>
       </c>
       <c r="E63" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.11796351</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>104.90344487</v>
+        <v>127.23134407</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>117.15</v>
+        <v>121.87</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>89.53</v>
+        <v>105.36</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>98.91</v>
+        <v>99.97</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002362314738852088</v>
+        <v>0.00240135630871877</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>-5.39</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.1047693510555121</v>
+        <v>-0.05115793470007593</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>-0.96</v>
+        <v>-0.99</v>
       </c>
       <c r="N63" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.11796351</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
@@ -4246,25 +4246,25 @@
         <v>221.99877812</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>243</v>
+        <v>243.77</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>98.73999999999999</v>
+        <v>99.28</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.002358254547712619</v>
+        <v>0.002384781977889362</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>7.56</v>
+        <v>8.1</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.08291291949989031</v>
+        <v>0.08883527089273963</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>-0.97</v>
+        <v>-0.77</v>
       </c>
       <c r="N64" s="4" t="n">
         <v>0.5550481</v>
@@ -4278,17 +4278,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Duke Energy</t>
+          <t>Lowe's</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>US26441C2044</t>
+          <t>US5486611073</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4297,34 +4297,34 @@
         </is>
       </c>
       <c r="E65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.6214908</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>127.23134407</v>
+        <v>234.11448729</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>120.27</v>
+        <v>217.16</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>105.36</v>
+        <v>107.82</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>98.43000000000001</v>
+        <v>99.03</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.002350850669752412</v>
+        <v>0.002378776785559867</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>-6.93</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>-0.0657744874715262</v>
+        <v>-0.08152476349471341</v>
       </c>
       <c r="M65" s="2" t="n">
-        <v>-1.23</v>
+        <v>-1.06</v>
       </c>
       <c r="N65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.6214908</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
@@ -4335,17 +4335,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Lowe's</t>
+          <t>Toronto-Dominion Bank</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US5486611073</t>
+          <t>CA8911605092</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -4354,34 +4354,34 @@
         </is>
       </c>
       <c r="E66" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.1533463</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>234.11448729</v>
+        <v>104.90344487</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>216.05</v>
+        <v>116.61</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>107.82</v>
+        <v>89.53</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>98.3</v>
+        <v>98.69</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.002347745817704582</v>
+        <v>0.002370609723991752</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>-9.52</v>
+        <v>9.16</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>-0.08829530699313672</v>
+        <v>0.1023120741650843</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>-1.3</v>
+        <v>-0.75</v>
       </c>
       <c r="N66" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.1533463</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
@@ -4417,25 +4417,25 @@
         <v>147.21071381</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>144.88</v>
+        <v>145.93</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>97.19</v>
+        <v>98.12</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.002321235157911581</v>
+        <v>0.002356917885480502</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>-2.66</v>
+        <v>-1.73</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>-0.02663995993990987</v>
+        <v>-0.01732598898347521</v>
       </c>
       <c r="M67" s="2" t="n">
-        <v>-1.1</v>
+        <v>-0.87</v>
       </c>
       <c r="N67" s="4" t="n">
         <v>0.9163735200000001</v>
@@ -4474,25 +4474,25 @@
         <v>107.56862839</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>113.55</v>
+        <v>113.32</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>96.89</v>
+        <v>96.92</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.002314070114724283</v>
+        <v>0.002328092962298922</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>4.12</v>
+        <v>4.15</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.04441090869893285</v>
+        <v>0.04473428910208042</v>
       </c>
       <c r="M68" s="2" t="n">
-        <v>-0.98</v>
+        <v>-0.77</v>
       </c>
       <c r="N68" s="4" t="n">
         <v>1.16558147</v>
@@ -4506,17 +4506,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Citigroup</t>
+          <t>Walmart</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US1729674242</t>
+          <t>US9311421039</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4525,34 +4525,34 @@
         </is>
       </c>
       <c r="E69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>127.79185697</v>
+        <v>126.99866255</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>131.73</v>
+        <v>105.97</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>88.38</v>
+        <v>110.45</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>90.12</v>
+        <v>91.22</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.002152378973464262</v>
+        <v>0.002191174577186419</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>1.74</v>
+        <v>-19.23</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.01968771215207061</v>
+        <v>-0.1741059302851969</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>-0.95</v>
+        <v>-1.13</v>
       </c>
       <c r="N69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="O69" t="inlineStr">
         <is>
@@ -4563,17 +4563,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Walmart</t>
+          <t>Citigroup</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US9311421039</t>
+          <t>US1729674242</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -4582,34 +4582,34 @@
         </is>
       </c>
       <c r="E70" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>126.99866255</v>
+        <v>127.79185697</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>103.66</v>
+        <v>131.9</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>110.45</v>
+        <v>88.38</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>89.02</v>
+        <v>90.45</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.00212610714844417</v>
+        <v>0.002172678584811572</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>-21.43</v>
+        <v>2.07</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>-0.19402444545043</v>
+        <v>0.02342158859470468</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>-1.39</v>
+        <v>-0.75</v>
       </c>
       <c r="N70" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
@@ -4645,25 +4645,25 @@
         <v>80.72233697999999</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>64.59999999999999</v>
+        <v>63.67</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>87.34</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.002085982906595303</v>
+        <v>0.002072752184448762</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>-23.19</v>
+        <v>-24.24</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>-0.2098072921378811</v>
+        <v>-0.2193069754817696</v>
       </c>
       <c r="M71" s="2" t="n">
-        <v>-1.39</v>
+        <v>-1.13</v>
       </c>
       <c r="N71" s="4" t="n">
         <v>1.84694851</v>
@@ -4702,25 +4702,25 @@
         <v>102.32267085</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>110.5</v>
+        <v>111.48</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>51.14</v>
+        <v>51.72</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.001221401028661367</v>
+        <v>0.001242354189126086</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3.27</v>
+        <v>3.85</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.06831000626697306</v>
+        <v>0.08042615416753708</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>-0.51</v>
+        <v>-0.4</v>
       </c>
       <c r="N72" s="4" t="n">
         <v>0.63221571</v>
@@ -4759,25 +4759,25 @@
         <v>290.55592566</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>270.85</v>
+        <v>272.45</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>48.05</v>
+        <v>48.45</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.001147601083832199</v>
+        <v>0.001163806273456281</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>-4.06</v>
+        <v>-3.66</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>-0.0779121090001919</v>
+        <v>-0.07023603914795624</v>
       </c>
       <c r="M73" s="2" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.44</v>
       </c>
       <c r="N73" s="4" t="n">
         <v>0.24236298</v>
@@ -4869,34 +4869,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-23 18:55:10</t>
+          <t>2026-08-24 19:09:11</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
-        <v>43186.96</v>
+        <v>42898.68</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>41894.09</v>
+        <v>41655.67</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>36639.92</v>
+        <v>36640.46</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>5254.17</v>
+        <v>5015.21</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>0.1434001493453043</v>
+        <v>0.1368762837584463</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>1243.5</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1317.01</v>
+        <v>1267.69</v>
       </c>
       <c r="J2" t="n">
         <v>72</v>
@@ -4965,7 +4965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4977,22 +4977,22 @@
         <v>64</v>
       </c>
       <c r="D2" t="n">
-        <v>108.88</v>
+        <v>108.5</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>6968.32</v>
+        <v>6944</v>
       </c>
       <c r="F2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>922.55</v>
+        <v>898.23</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -5004,22 +5004,22 @@
         <v>290</v>
       </c>
       <c r="D3" t="n">
-        <v>14.364</v>
+        <v>13.928</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4165.56</v>
+        <v>4039.12</v>
       </c>
       <c r="F3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>734.85</v>
+        <v>608.41</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -5031,22 +5031,22 @@
         <v>176.393183</v>
       </c>
       <c r="D4" t="n">
-        <v>1518.4</v>
+        <v>1529</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>2678.35</v>
+        <v>2697.05</v>
       </c>
       <c r="F4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1482.39</v>
+        <v>1501.09</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -5058,22 +5058,22 @@
         <v>24.80610988</v>
       </c>
       <c r="D5" t="n">
-        <v>111.2</v>
+        <v>110.63</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>2019.33</v>
+        <v>2013.69</v>
       </c>
       <c r="F5" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>372.76</v>
+        <v>367.12</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -5085,76 +5085,76 @@
         <v>115</v>
       </c>
       <c r="D6" t="n">
-        <v>23.81</v>
+        <v>23.25</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>2004.47</v>
+        <v>1961.92</v>
       </c>
       <c r="F6" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>78.66</v>
+        <v>36.11</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="D7" t="n">
-        <v>472.31</v>
+        <v>209.3</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>1728.78</v>
+        <v>1678.01</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>-169.77</v>
+        <v>425.33</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>10.9260596</v>
+        <v>5</v>
       </c>
       <c r="D8" t="n">
-        <v>215.38</v>
+        <v>457.32</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1722.71</v>
+        <v>1677.84</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>1252.68</v>
+        <v>1898.55</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>470.03</v>
+        <v>-220.71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -5166,22 +5166,22 @@
         <v>9.6</v>
       </c>
       <c r="D9" t="n">
-        <v>236.1</v>
+        <v>230.86</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1659.24</v>
+        <v>1626.23</v>
       </c>
       <c r="F9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-336.82</v>
+        <v>-369.83</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -5193,22 +5193,22 @@
         <v>12.5822526</v>
       </c>
       <c r="D10" t="n">
-        <v>153.75</v>
+        <v>151.57</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1416.17</v>
+        <v>1399.37</v>
       </c>
       <c r="F10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-455.67</v>
+        <v>-472.47</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -5220,22 +5220,22 @@
         <v>15.9020618</v>
       </c>
       <c r="D11" t="n">
-        <v>119.16</v>
+        <v>119.14</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1387.16</v>
+        <v>1390.18</v>
       </c>
       <c r="F11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>43.37</v>
+        <v>46.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5247,22 +5247,22 @@
         <v>35</v>
       </c>
       <c r="D12" t="n">
-        <v>42.5</v>
+        <v>43.2</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1358.86</v>
+        <v>1382.07</v>
       </c>
       <c r="F12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>130.52</v>
+        <v>153.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5274,22 +5274,22 @@
         <v>3.2220691</v>
       </c>
       <c r="D13" t="n">
-        <v>440.8</v>
+        <v>445.4</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1214.81</v>
+        <v>1227.98</v>
       </c>
       <c r="F13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>300.32</v>
+        <v>313.49</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -5301,22 +5301,22 @@
         <v>1014.362806</v>
       </c>
       <c r="D14" t="n">
-        <v>111.25</v>
+        <v>111.6</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1128.48</v>
+        <v>1132.03</v>
       </c>
       <c r="F14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>521.29</v>
+        <v>524.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -5328,22 +5328,22 @@
         <v>160</v>
       </c>
       <c r="D15" t="n">
-        <v>683.8</v>
+        <v>688.8</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1094.08</v>
+        <v>1102.08</v>
       </c>
       <c r="F15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>340.62</v>
+        <v>348.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -5355,22 +5355,22 @@
         <v>4.3814255</v>
       </c>
       <c r="D16" t="n">
-        <v>333.48</v>
+        <v>325.4</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1069.62</v>
+        <v>1046.15</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>427.63</v>
+        <v>404.16</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -5382,22 +5382,22 @@
         <v>3.05990683</v>
       </c>
       <c r="D17" t="n">
-        <v>309.69</v>
+        <v>311.45</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>693.71</v>
+        <v>699.29</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>491.05</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>202.66</v>
+        <v>208.24</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -5409,22 +5409,22 @@
         <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>46.81</v>
+        <v>46.97</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>685.35</v>
+        <v>689.3099999999999</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>867.58</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>-182.23</v>
+        <v>-178.27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -5436,22 +5436,22 @@
         <v>65</v>
       </c>
       <c r="D19" t="n">
-        <v>1036</v>
+        <v>1030</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>673.4</v>
+        <v>669.5</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>662.6799999999999</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>10.72</v>
+        <v>6.82</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -5463,22 +5463,22 @@
         <v>1.8650317</v>
       </c>
       <c r="D20" t="n">
-        <v>483.61</v>
+        <v>487.75</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>660.27</v>
+        <v>667.49</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>534.38</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>125.89</v>
+        <v>133.11</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -5490,22 +5490,22 @@
         <v>9.195978999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>97.37</v>
+        <v>98.47</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>655.49</v>
+        <v>664.45</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>549.1799999999999</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>106.31</v>
+        <v>115.27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -5517,22 +5517,22 @@
         <v>2.330043</v>
       </c>
       <c r="D22" t="n">
-        <v>336.05</v>
+        <v>337.68</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>573.21</v>
+        <v>577.34</v>
       </c>
       <c r="F22" s="2" t="n">
         <v>489.27</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>83.94</v>
+        <v>88.06999999999999</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -5544,22 +5544,22 @@
         <v>140</v>
       </c>
       <c r="D23" t="n">
-        <v>3.798</v>
+        <v>3.8</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>531.72</v>
+        <v>532</v>
       </c>
       <c r="F23" s="2" t="n">
         <v>538.37</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>-6.65</v>
+        <v>-6.37</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5571,22 +5571,22 @@
         <v>2</v>
       </c>
       <c r="D24" t="n">
-        <v>345.1</v>
+        <v>348.93</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>505.26</v>
+        <v>512.0700000000001</v>
       </c>
       <c r="F24" s="2" t="n">
         <v>407.92</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>97.34</v>
+        <v>104.15</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5598,22 +5598,22 @@
         <v>1.11022215</v>
       </c>
       <c r="D25" t="n">
-        <v>235.8</v>
+        <v>232.71</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>191.64</v>
+        <v>189.58</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>196.52</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>-4.88</v>
+        <v>-6.94</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5625,22 +5625,22 @@
         <v>1.55804584</v>
       </c>
       <c r="D26" t="n">
-        <v>116.55</v>
+        <v>116.79</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>132.93</v>
+        <v>133.52</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>105.28</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>27.65</v>
+        <v>28.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5652,103 +5652,103 @@
         <v>0.63422137</v>
       </c>
       <c r="D27" t="n">
-        <v>280.81</v>
+        <v>282.48</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>130.38</v>
+        <v>131.46</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>30.53</v>
+        <v>31.61</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CF_US_EQ</t>
+          <t>ROP_US_EQ</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>1.32559468</v>
+        <v>0.42010405</v>
       </c>
       <c r="D28" t="n">
-        <v>132</v>
+        <v>414.15</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>128.09</v>
+        <v>127.67</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>119.73</v>
+        <v>109.16</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>8.359999999999999</v>
+        <v>18.51</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ROP_US_EQ</t>
+          <t>CF_US_EQ</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>0.42010405</v>
+        <v>1.32559468</v>
       </c>
       <c r="D29" t="n">
-        <v>414.88</v>
+        <v>128.87</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>127.59</v>
+        <v>125.35</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>109.16</v>
+        <v>119.73</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>18.43</v>
+        <v>5.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>TTWO_US_EQ</t>
+          <t>BMY_US_EQ</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>0.7</v>
+        <v>2.50421091</v>
       </c>
       <c r="D30" t="n">
-        <v>242.69</v>
+        <v>67.22</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>124.36</v>
+        <v>123.52</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>118.76</v>
+        <v>106.81</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>5.6</v>
+        <v>16.71</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -5760,157 +5760,157 @@
         <v>3.30858696</v>
       </c>
       <c r="D31" t="n">
-        <v>51.31</v>
+        <v>50.64</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>124.28</v>
+        <v>122.94</v>
       </c>
       <c r="F31" s="2" t="n">
         <v>112.71</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>11.57</v>
+        <v>10.23</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BMY_US_EQ</t>
+          <t>MA_US_EQ</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>2.50421091</v>
+        <v>0.28038062</v>
       </c>
       <c r="D32" t="n">
-        <v>67</v>
+        <v>597.52</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>122.83</v>
+        <v>122.93</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>106.81</v>
+        <v>105.75</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>16.02</v>
+        <v>17.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>MA_US_EQ</t>
+          <t>TTWO_US_EQ</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
-        <v>0.28038062</v>
+        <v>0.7</v>
       </c>
       <c r="D33" t="n">
-        <v>580.05</v>
+        <v>234.95</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>119.06</v>
+        <v>120.68</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>105.75</v>
+        <v>118.76</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>13.31</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVX_US_EQ</t>
+          <t>RGLD_US_EQ</t>
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>0.7905852</v>
+        <v>0.62445608</v>
       </c>
       <c r="D34" t="n">
-        <v>205.28</v>
+        <v>261.69</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>118.81</v>
+        <v>119.91</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>110.41</v>
+        <v>108.77</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>8.4</v>
+        <v>11.14</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RGLD_US_EQ</t>
+          <t>JNJ_US_EQ</t>
         </is>
       </c>
       <c r="C35" s="4" t="n">
-        <v>0.62445608</v>
+        <v>0.59183053</v>
       </c>
       <c r="D35" t="n">
-        <v>258.59</v>
+        <v>272.91</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>118.21</v>
+        <v>118.52</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>108.77</v>
+        <v>99.84999999999999</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>9.44</v>
+        <v>18.67</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>JNJ_US_EQ</t>
+          <t>CVX_US_EQ</t>
         </is>
       </c>
       <c r="C36" s="4" t="n">
-        <v>0.59183053</v>
+        <v>0.7905852</v>
       </c>
       <c r="D36" t="n">
-        <v>271</v>
+        <v>203.46</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>117.41</v>
+        <v>118.03</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>99.84999999999999</v>
+        <v>110.41</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>17.56</v>
+        <v>7.62</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -5922,22 +5922,22 @@
         <v>2.70722512</v>
       </c>
       <c r="D37" t="n">
-        <v>58.44</v>
+        <v>58.91</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>115.82</v>
+        <v>117.02</v>
       </c>
       <c r="F37" s="2" t="n">
         <v>107.64</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>8.18</v>
+        <v>9.380000000000001</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -5949,22 +5949,22 @@
         <v>1.73400968</v>
       </c>
       <c r="D38" t="n">
-        <v>91.06</v>
+        <v>91.56</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>115.59</v>
+        <v>116.5</v>
       </c>
       <c r="F38" s="2" t="n">
         <v>101.53</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>14.06</v>
+        <v>14.97</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -5976,22 +5976,22 @@
         <v>5.691347</v>
       </c>
       <c r="D39" t="n">
-        <v>27.11</v>
+        <v>27.5</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>112.95</v>
+        <v>114.84</v>
       </c>
       <c r="F39" s="2" t="n">
         <v>452.96</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>-340.01</v>
+        <v>-338.12</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -6003,22 +6003,22 @@
         <v>3.81488812</v>
       </c>
       <c r="D40" t="n">
-        <v>40.27</v>
+        <v>40.35</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>112.46</v>
+        <v>112.95</v>
       </c>
       <c r="F40" s="2" t="n">
         <v>108.23</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>4.23</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -6030,7 +6030,7 @@
         <v>0.43583007</v>
       </c>
       <c r="D41" t="n">
-        <v>347.6</v>
+        <v>346.79</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>110.9</v>
@@ -6045,115 +6045,115 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SLB_US_EQ</t>
+          <t>BLK_US_EQ</t>
         </is>
       </c>
       <c r="C42" s="4" t="n">
-        <v>2.76637723</v>
+        <v>0.1285649</v>
       </c>
       <c r="D42" t="n">
-        <v>53.79</v>
+        <v>1168.5</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>108.93</v>
+        <v>110.23</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>112.48</v>
+        <v>98.89</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>-3.55</v>
+        <v>11.34</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BLK_US_EQ</t>
+          <t>KMB_US_EQ</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>0.1285649</v>
+        <v>1.35094641</v>
       </c>
       <c r="D43" t="n">
-        <v>1156.55</v>
+        <v>111.11</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>108.85</v>
+        <v>110.14</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>98.89</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>9.960000000000001</v>
+        <v>13.46</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>KMB_US_EQ</t>
+          <t>GOOD_US_EQ</t>
         </is>
       </c>
       <c r="C44" s="4" t="n">
-        <v>1.35094641</v>
+        <v>11.40066159</v>
       </c>
       <c r="D44" t="n">
-        <v>109.1</v>
+        <v>13.14</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>107.9</v>
+        <v>109.92</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>11.22</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GOOD_US_EQ</t>
+          <t>SLB_US_EQ</t>
         </is>
       </c>
       <c r="C45" s="4" t="n">
-        <v>11.40066159</v>
+        <v>2.76637723</v>
       </c>
       <c r="D45" t="n">
-        <v>12.87</v>
+        <v>53.86</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>107.41</v>
+        <v>109.33</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>106.15</v>
+        <v>112.48</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>1.26</v>
+        <v>-3.15</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -6165,22 +6165,22 @@
         <v>0.51881442</v>
       </c>
       <c r="D46" t="n">
-        <v>281.91</v>
+        <v>283.01</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>107.07</v>
+        <v>107.74</v>
       </c>
       <c r="F46" s="2" t="n">
         <v>95.94</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>11.13</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -6192,49 +6192,49 @@
         <v>1.74206342</v>
       </c>
       <c r="D47" t="n">
-        <v>83.95</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>107.06</v>
+        <v>107.64</v>
       </c>
       <c r="F47" s="2" t="n">
         <v>96.68000000000001</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>10.38</v>
+        <v>10.96</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GD_US_EQ</t>
+          <t>CB_US_EQ</t>
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>0.37810738</v>
+        <v>0.42255419</v>
       </c>
       <c r="D48" t="n">
-        <v>384.24</v>
+        <v>345.51</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>106.36</v>
+        <v>107.13</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>95.51000000000001</v>
+        <v>101.39</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>10.85</v>
+        <v>5.74</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -6246,130 +6246,130 @@
         <v>13.30225117</v>
       </c>
       <c r="D49" t="n">
-        <v>10.92</v>
+        <v>10.97</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>106.34</v>
+        <v>107.08</v>
       </c>
       <c r="F49" s="2" t="n">
         <v>106.96</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>-0.62</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CB_US_EQ</t>
+          <t>JPM_US_EQ</t>
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>0.42255419</v>
+        <v>0.40867246</v>
       </c>
       <c r="D50" t="n">
-        <v>341</v>
+        <v>356.22</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>105.48</v>
+        <v>106.82</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>101.39</v>
+        <v>92.83</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>4.09</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>JPM_US_EQ</t>
+          <t>ECL_US_EQ</t>
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>0.40867246</v>
+        <v>0.50675322</v>
       </c>
       <c r="D51" t="n">
-        <v>351.99</v>
+        <v>286.54</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>105.3</v>
+        <v>106.55</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>92.83</v>
+        <v>96.68000000000001</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>12.47</v>
+        <v>9.869999999999999</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>O_US_EQ</t>
+          <t>GD_US_EQ</t>
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>2.27580753</v>
+        <v>0.37810738</v>
       </c>
       <c r="D52" t="n">
-        <v>62.76</v>
+        <v>381.9</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>104.56</v>
+        <v>105.96</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>106.15</v>
+        <v>95.51000000000001</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>-1.59</v>
+        <v>10.45</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ECL_US_EQ</t>
+          <t>O_US_EQ</t>
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>0.50675322</v>
+        <v>2.27580753</v>
       </c>
       <c r="D53" t="n">
-        <v>281.63</v>
+        <v>62.94</v>
       </c>
       <c r="E53" s="2" t="n">
-        <v>104.48</v>
+        <v>105.11</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>96.68000000000001</v>
+        <v>106.15</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>7.8</v>
+        <v>-1.04</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6381,157 +6381,157 @@
         <v>0.90543241</v>
       </c>
       <c r="D54" t="n">
-        <v>157.61</v>
+        <v>157.33</v>
       </c>
       <c r="E54" s="2" t="n">
-        <v>104.47</v>
+        <v>104.53</v>
       </c>
       <c r="F54" s="2" t="n">
         <v>92.27</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>12.2</v>
+        <v>12.26</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BMO_US_EQ</t>
+          <t>CAH_US_EQ</t>
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>0.80409618</v>
+        <v>0.61215748</v>
       </c>
       <c r="D55" t="n">
-        <v>175</v>
+        <v>230.58</v>
       </c>
       <c r="E55" s="2" t="n">
-        <v>103.01</v>
+        <v>103.57</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>88.44</v>
+        <v>88.09</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>14.57</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RY_US_EQ</t>
+          <t>PEP_US_EQ</t>
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>0.68495686</v>
+        <v>0.97307689</v>
       </c>
       <c r="D56" t="n">
-        <v>205.34</v>
+        <v>144.63</v>
       </c>
       <c r="E56" s="2" t="n">
-        <v>102.96</v>
+        <v>103.27</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>89.45999999999999</v>
+        <v>111.44</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>13.5</v>
+        <v>-8.17</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CAH_US_EQ</t>
+          <t>RY_US_EQ</t>
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>0.61215748</v>
+        <v>0.68495686</v>
       </c>
       <c r="D57" t="n">
-        <v>229.26</v>
+        <v>204.09</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>102.74</v>
+        <v>102.58</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>88.09</v>
+        <v>89.45999999999999</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>14.65</v>
+        <v>13.12</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PEP_US_EQ</t>
+          <t>AFL_US_EQ</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>0.97307689</v>
+        <v>1.17949395</v>
       </c>
       <c r="D58" t="n">
-        <v>143.45</v>
+        <v>118</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>102.19</v>
+        <v>102.13</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>111.44</v>
+        <v>98.72</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>-9.25</v>
+        <v>3.41</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BNS_US_EQ</t>
+          <t>BMO_US_EQ</t>
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1.59010207</v>
+        <v>0.80409618</v>
       </c>
       <c r="D59" t="n">
-        <v>87.56999999999999</v>
+        <v>172.21</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>101.93</v>
+        <v>101.61</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>89.66</v>
+        <v>88.44</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>12.27</v>
+        <v>13.17</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -6543,103 +6543,103 @@
         <v>1.85908491</v>
       </c>
       <c r="D60" t="n">
-        <v>73.88</v>
+        <v>74.27</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>100.55</v>
+        <v>101.32</v>
       </c>
       <c r="F60" s="2" t="n">
         <v>104.98</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>-4.43</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GWW_US_EQ</t>
+          <t>BNS_US_EQ</t>
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>0.10445851</v>
+        <v>1.59010207</v>
       </c>
       <c r="D61" t="n">
-        <v>1312.24</v>
+        <v>86.81999999999999</v>
       </c>
       <c r="E61" s="2" t="n">
-        <v>100.35</v>
+        <v>101.3</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>88.89</v>
+        <v>89.66</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>11.46</v>
+        <v>11.64</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AFL_US_EQ</t>
+          <t>GWW_US_EQ</t>
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>1.17949395</v>
+        <v>0.10445851</v>
       </c>
       <c r="D62" t="n">
-        <v>116.07</v>
+        <v>1318.39</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>100.22</v>
+        <v>101.05</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>98.72</v>
+        <v>88.89</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>1.5</v>
+        <v>12.16</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>TD_US_EQ</t>
+          <t>DUK_US_EQ</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>1.1533463</v>
+        <v>1.11796351</v>
       </c>
       <c r="D63" t="n">
-        <v>117.15</v>
+        <v>121.87</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>98.91</v>
+        <v>99.97</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>89.53</v>
+        <v>105.36</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>9.380000000000001</v>
+        <v>-5.39</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -6651,76 +6651,76 @@
         <v>0.5550481</v>
       </c>
       <c r="D64" t="n">
-        <v>243</v>
+        <v>243.77</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>98.73999999999999</v>
+        <v>99.28</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>91.18000000000001</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>7.56</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DUK_US_EQ</t>
+          <t>LOW_US_EQ</t>
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>1.11796351</v>
+        <v>0.6214908</v>
       </c>
       <c r="D65" t="n">
-        <v>120.27</v>
+        <v>217.16</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>98.43000000000001</v>
+        <v>99.03</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>105.36</v>
+        <v>107.82</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>-6.93</v>
+        <v>-8.789999999999999</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>LOW_US_EQ</t>
+          <t>TD_US_EQ</t>
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>0.6214908</v>
+        <v>1.1533463</v>
       </c>
       <c r="D66" t="n">
-        <v>216.05</v>
+        <v>116.61</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>98.3</v>
+        <v>98.69</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>107.82</v>
+        <v>89.53</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>-9.52</v>
+        <v>9.16</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -6732,22 +6732,22 @@
         <v>0.9163735200000001</v>
       </c>
       <c r="D67" t="n">
-        <v>144.88</v>
+        <v>145.93</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>97.19</v>
+        <v>98.12</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>99.84999999999999</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>-2.66</v>
+        <v>-1.73</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -6759,76 +6759,76 @@
         <v>1.16558147</v>
       </c>
       <c r="D68" t="n">
-        <v>113.55</v>
+        <v>113.32</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>96.89</v>
+        <v>96.92</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>92.77</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>4.12</v>
+        <v>4.15</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>C_US_EQ</t>
+          <t>WMT_US_EQ</t>
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>0.93456659</v>
+        <v>1.17308322</v>
       </c>
       <c r="D69" t="n">
-        <v>131.73</v>
+        <v>105.97</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>90.12</v>
+        <v>91.22</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>88.38</v>
+        <v>110.45</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>1.74</v>
+        <v>-19.23</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>WMT_US_EQ</t>
+          <t>C_US_EQ</t>
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>1.17308322</v>
+        <v>0.93456659</v>
       </c>
       <c r="D70" t="n">
-        <v>103.66</v>
+        <v>131.9</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>89.02</v>
+        <v>90.45</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>110.45</v>
+        <v>88.38</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>-21.43</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -6840,22 +6840,22 @@
         <v>1.84694851</v>
       </c>
       <c r="D71" t="n">
-        <v>64.59999999999999</v>
+        <v>63.67</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>87.34</v>
+        <v>86.29000000000001</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>110.53</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>-23.19</v>
+        <v>-24.24</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -6867,22 +6867,22 @@
         <v>0.63221571</v>
       </c>
       <c r="D72" t="n">
-        <v>110.5</v>
+        <v>111.48</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>51.14</v>
+        <v>51.72</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>47.87</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>3.27</v>
+        <v>3.85</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -6894,16 +6894,16 @@
         <v>0.24236298</v>
       </c>
       <c r="D73" t="n">
-        <v>270.85</v>
+        <v>272.45</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>48.05</v>
+        <v>48.45</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>52.11</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>-4.06</v>
+        <v>-3.66</v>
       </c>
     </row>
   </sheetData>

--- a/portfolio.xlsx
+++ b/portfolio.xlsx
@@ -481,7 +481,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>42898.68</v>
+        <v>43262.79</v>
       </c>
     </row>
     <row r="5">
@@ -491,7 +491,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>41655.67</v>
+        <v>42013.44</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>5015.21</v>
+        <v>5372.98</v>
       </c>
     </row>
     <row r="8">
@@ -521,7 +521,7 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>0.1368762837584463</v>
+        <v>0.1466406262366793</v>
       </c>
     </row>
     <row r="9">
@@ -541,7 +541,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>1243.01</v>
+        <v>1249.35</v>
       </c>
     </row>
     <row r="11">
@@ -572,7 +572,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-08-24 19:09:11</t>
+          <t>2026-08-25 19:07:46</t>
         </is>
       </c>
     </row>
@@ -712,22 +712,22 @@
         <v>94.46515625000001</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>108.5</v>
+        <v>108.72</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>6045.77</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>6944</v>
+        <v>6958.08</v>
       </c>
       <c r="J2" s="3" t="n">
-        <v>0.1668002221440747</v>
+        <v>0.1657098410699426</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>898.23</v>
+        <v>912.3099999999999</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.1485716459607296</v>
+        <v>0.150900546994014</v>
       </c>
       <c r="M2" s="2" t="n">
         <v>0</v>
@@ -769,22 +769,22 @@
         <v>11.83003448</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>13.928</v>
+        <v>14.256</v>
       </c>
       <c r="H3" s="2" t="n">
         <v>3430.71</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4039.12</v>
+        <v>4134.24</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.0970227697676519</v>
+        <v>0.09845880664565507</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>608.41</v>
+        <v>703.53</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.1773422994074113</v>
+        <v>0.2050683386237834</v>
       </c>
       <c r="M3" s="2" t="n">
         <v>0</v>
@@ -826,22 +826,22 @@
         <v>678.00976186</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1529</v>
+        <v>1517</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>1195.96</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>2697.05</v>
+        <v>2675.88</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06478521588906633</v>
+        <v>0.0637272997036881</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1501.09</v>
+        <v>1479.92</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>1.25513395096826</v>
+        <v>1.237432690056524</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>0</v>
@@ -883,25 +883,25 @@
         <v>89.05910724</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>110.63</v>
+        <v>111.06</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>1646.57</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2013.69</v>
+        <v>2018.87</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.04837038296792939</v>
+        <v>0.04808030761946903</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>367.12</v>
+        <v>372.3</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.2229604571928312</v>
+        <v>0.226106390861002</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>-25.51</v>
+        <v>-27.64</v>
       </c>
       <c r="N5" s="4" t="n">
         <v>1.15856288</v>
@@ -940,25 +940,25 @@
         <v>22.51</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>23.25</v>
+        <v>23.5</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>1925.81</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1961.92</v>
+        <v>1980.42</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.04712682774033741</v>
+        <v>0.04716460337503101</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>36.11</v>
+        <v>54.61</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.01875055171590136</v>
+        <v>0.02835689917489264</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>-26.33</v>
+        <v>-28.82</v>
       </c>
       <c r="N6" s="4" t="n">
         <v>0</v>
@@ -972,17 +972,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NVDA_US_EQ</t>
+          <t>AMD_US_EQ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Nvidia</t>
+          <t>Advanced Micro Devices</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US67066G1040</t>
+          <t>US0079031078</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -991,55 +991,55 @@
         </is>
       </c>
       <c r="E7" s="4" t="n">
-        <v>10.9260596</v>
+        <v>5</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>150.09436705</v>
+        <v>509.97</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>209.3</v>
+        <v>479.79</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1252.68</v>
+        <v>1898.55</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>1678.01</v>
+        <v>1757.97</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.04030709112326882</v>
+        <v>0.04186685541208596</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>425.33</v>
+        <v>-140.58</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.3395360347415142</v>
+        <v>-0.07404598246029866</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>-49.34</v>
+        <v>-30</v>
       </c>
       <c r="N7" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2024-08-12</t>
+          <t>2026-05-28</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AMD_US_EQ</t>
+          <t>NVDA_US_EQ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Advanced Micro Devices</t>
+          <t>Nvidia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US0079031078</t>
+          <t>US67066G1040</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1048,38 +1048,38 @@
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>5</v>
+        <v>10.9260596</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>509.97</v>
+        <v>150.09436705</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>457.32</v>
+        <v>212.73</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>1898.55</v>
+        <v>1252.68</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>1677.84</v>
+        <v>1703.27</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.04030300759248476</v>
+        <v>0.04056415002402979</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>-220.71</v>
+        <v>450.59</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>-0.1162518764320139</v>
+        <v>0.3597008014816234</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>-27.54</v>
+        <v>-50.92</v>
       </c>
       <c r="N8" s="4" t="n">
         <v>0</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-28</t>
+          <t>2024-08-12</t>
         </is>
       </c>
     </row>
@@ -1111,25 +1111,25 @@
         <v>278.55208333</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>230.86</v>
+        <v>240.6</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>1996.06</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>1626.23</v>
+        <v>1692.62</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03906329568798366</v>
+        <v>0.04031051542836619</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>-369.83</v>
+        <v>-303.44</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>-0.1852800016031582</v>
+        <v>-0.1520194783723936</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>-33.88</v>
+        <v>-36.45</v>
       </c>
       <c r="N9" s="4" t="n">
         <v>0</v>
@@ -1168,25 +1168,25 @@
         <v>191.52532353</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>151.57</v>
+        <v>161.01</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>1871.84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>1399.37</v>
+        <v>1484.58</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.03361394396050601</v>
+        <v>0.03535594817185422</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>-472.47</v>
+        <v>-387.26</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>-0.2524093939652962</v>
+        <v>-0.2068873407983588</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>-103.58</v>
+        <v>-105.9</v>
       </c>
       <c r="N10" s="4" t="n">
         <v>0</v>
@@ -1225,25 +1225,25 @@
         <v>113.04005874</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>119.14</v>
+        <v>119.22</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>1343.79</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>1390.18</v>
+        <v>1389.29</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.03339319309047375</v>
+        <v>0.0330865734656774</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>46.39</v>
+        <v>45.5</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.03452176307309922</v>
+        <v>0.03385945720685524</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>-24.79</v>
+        <v>-26.52</v>
       </c>
       <c r="N11" s="4" t="n">
         <v>0</v>
@@ -1282,25 +1282,25 @@
         <v>37.05</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>43.2</v>
+        <v>43.22</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>1228.34</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1382.07</v>
+        <v>1382.24</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.0331983846513049</v>
+        <v>0.0329186745079846</v>
       </c>
       <c r="K12" s="2" t="n">
-        <v>153.73</v>
+        <v>153.9</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.1251526450331341</v>
+        <v>0.1252910431965091</v>
       </c>
       <c r="M12" s="2" t="n">
-        <v>-43.02</v>
+        <v>-43.43</v>
       </c>
       <c r="N12" s="4" t="n">
         <v>0</v>
@@ -1339,25 +1339,25 @@
         <v>330.7067499</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>445.4</v>
+        <v>450</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>914.49</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>1227.98</v>
+        <v>1240.52</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.02949702430709689</v>
+        <v>0.02954354822653451</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>313.49</v>
+        <v>326.03</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.3428030924340343</v>
+        <v>0.3565156535336635</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>-2.72</v>
+        <v>-2.83</v>
       </c>
       <c r="N13" s="4" t="n">
         <v>0</v>
@@ -1396,22 +1396,22 @@
         <v>59.85909543</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>111.6</v>
+        <v>111.45</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>607.1900000000001</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1132.03</v>
+        <v>1130.51</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.02719223149103641</v>
+        <v>0.02692361002287712</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>524.84</v>
+        <v>523.3200000000001</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.8643752367463232</v>
+        <v>0.8618719017111612</v>
       </c>
       <c r="M14" s="2" t="n">
         <v>0</v>
@@ -1453,22 +1453,22 @@
         <v>470.9125</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>688.8</v>
+        <v>690.2</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>753.46</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>1102.08</v>
+        <v>1104.32</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02647280944996281</v>
+        <v>0.02629988325663962</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>348.62</v>
+        <v>350.86</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.462692113715393</v>
+        <v>0.465665065166034</v>
       </c>
       <c r="M15" s="2" t="n">
         <v>0</v>
@@ -1510,25 +1510,25 @@
         <v>187.8703632</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>325.4</v>
+        <v>314.12</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>641.99</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1046.15</v>
+        <v>1008.56</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.02512932782200802</v>
+        <v>0.02401931528661661</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>404.16</v>
+        <v>366.57</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>0.6295425162385707</v>
+        <v>0.5709902023396003</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>-37.99</v>
+        <v>-38.79</v>
       </c>
       <c r="N16" s="4" t="n">
         <v>0</v>
@@ -1542,17 +1542,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AAPL_US_EQ</t>
+          <t>NVO_US_EQ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Novo Nordisk</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US0378331005</t>
+          <t>US6701002056</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1561,55 +1561,55 @@
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>3.05990683</v>
+        <v>20</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>207.87234231</v>
+        <v>57.84</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>311.45</v>
+        <v>48.31</v>
       </c>
       <c r="H17" s="2" t="n">
-        <v>491.05</v>
+        <v>867.58</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>699.29</v>
+        <v>708.04</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.0167974837763724</v>
+        <v>0.01686229475245501</v>
       </c>
       <c r="K17" s="2" t="n">
-        <v>208.24</v>
+        <v>-159.54</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.4240708685469912</v>
+        <v>-0.1838908227483344</v>
       </c>
       <c r="M17" s="2" t="n">
-        <v>-24.32</v>
+        <v>-19.87</v>
       </c>
       <c r="N17" s="4" t="n">
-        <v>0.46065664</v>
+        <v>0</v>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2024-01-24</t>
+          <t>2025-10-13</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>NVO_US_EQ</t>
+          <t>AAPL_US_EQ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Novo Nordisk</t>
+          <t>Apple</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US6701002056</t>
+          <t>US0378331005</t>
         </